--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C72A2F-E25D-4913-A95C-A36B2BAEE181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C3209F-083E-4BEC-8D8C-4D9CB1DE1CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="11340" yWindow="825" windowWidth="16575" windowHeight="14745" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2360</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2537</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="191">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -3293,6 +3293,525 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLP (28)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Read </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (29)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>ROL (2A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &lt;&lt; 1) | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
     </r>
   </si>
 </sst>
@@ -3888,11 +4407,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C2320"/>
+  <dimension ref="A1:C2487"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="88.28515625" customWidth="1"/>
+    <col min="3" max="3" width="93.28515625" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="6" max="8" width="9.140625" customWidth="1"/>
   </cols>
@@ -5359,7 +5878,9 @@
         <v>3.1</v>
       </c>
       <c r="B481" s="9"/>
-      <c r="C481" s="10"/>
+      <c r="C481" s="10" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8">
@@ -7200,21 +7721,21 @@
       <c r="C1249" s="26"/>
     </row>
     <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1250" s="8">
+      <c r="A1250" s="15">
         <v>3.2</v>
       </c>
-      <c r="B1250" s="9"/>
-      <c r="C1250" s="10"/>
+      <c r="B1250" s="16"/>
+      <c r="C1250" s="23"/>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1251" s="8">
+      <c r="A1251" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B1251" s="9"/>
-      <c r="C1251" s="14"/>
+      <c r="B1251" s="16"/>
+      <c r="C1251" s="17"/>
     </row>
     <row r="1252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1252" s="8">
+      <c r="A1252" s="18">
         <v>4.2</v>
       </c>
       <c r="B1252" s="9" t="s">
@@ -9801,7 +10322,7 @@
       <c r="C2256" s="26"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2257" s="8">
+      <c r="A2257" s="18">
         <v>5.2</v>
       </c>
       <c r="B2257" s="9" t="s">
@@ -10012,6 +10533,297 @@
       </c>
       <c r="B2320" s="20"/>
       <c r="C2320" s="22"/>
+    </row>
+    <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2361" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2361" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2361" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2362" s="4"/>
+      <c r="B2362" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2362" s="25"/>
+    </row>
+    <row r="2363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2363" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2363" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2363" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2364" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2364" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2364" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2365" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2365" s="9"/>
+      <c r="C2365" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2366" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B2366" s="9"/>
+      <c r="C2366" s="10"/>
+    </row>
+    <row r="2367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2367" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B2367" s="9"/>
+      <c r="C2367" s="10"/>
+    </row>
+    <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2368" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2368" s="9"/>
+      <c r="C2368" s="10"/>
+    </row>
+    <row r="2369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2369" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B2369" s="9"/>
+      <c r="C2369" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2370" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B2370" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2370" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2371" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2371" s="9"/>
+      <c r="C2371" s="14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2372" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B2372" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2372" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2373" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2373" s="20"/>
+      <c r="C2373" s="22"/>
+    </row>
+    <row r="2420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2420" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2420" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2420" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2421" s="4"/>
+      <c r="B2421" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2421" s="6"/>
+    </row>
+    <row r="2422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2422" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2422" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2422" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2423" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2423" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2423" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2424" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2424" s="9"/>
+      <c r="C2424" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2425" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B2425" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2425" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2426" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B2426" s="9"/>
+      <c r="C2426" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2427" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2427" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2427" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2428" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2428" s="20"/>
+      <c r="C2428" s="22"/>
+    </row>
+    <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2479" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2479" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2479" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2480" s="4"/>
+      <c r="B2480" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2480" s="6"/>
+    </row>
+    <row r="2481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2481" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2481" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2481" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2482" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2482" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2482" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2483" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2483" s="9"/>
+      <c r="C2483" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2484" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B2484" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2484" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2485" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B2485" s="9"/>
+      <c r="C2485" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2486" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2486" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2486" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2487" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2487" s="20"/>
+      <c r="C2487" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="33">

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF49918-62C2-4006-BC9B-6C1B5D5359E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942B98AB-4E6F-42C6-8FA1-D9B61FA370EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$3835</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$4071</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="234">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -1110,6 +1110,32 @@
     <t>Write to Pointer:Bank</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
     <t>ORA (1F)</t>
   </si>
   <si>
@@ -1258,6 +1284,2824 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Pointer to Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Address.L = Pointer.L.  Address.H = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Set Vector to $FFF4.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.  Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Address to Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L | $100. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; Operand.L). Perform Operand |= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80). Perform Operand.L &lt;&lt;= 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets Operand.L to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags set.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &lt;&lt;= 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If not branching, end (next half-cycle is 4.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L to Address.L. If not BoundaryCrossed, end (next half-cycle is 4.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to Address.H</t>
+    </r>
+  </si>
+  <si>
+    <t>If Orig.H == Pointer.H, skip 2 half-cycles.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and Z based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &amp; Operand.L). Perform Operand &amp;= ~</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L is 0, Address.L = Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, Address.H = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H, otherwise Address = Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L is 0, skip 2 half-cycles.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.l is not 0, read (Address + 1), otherwise read (Address &amp; $FF00) | ui8(Address.L + 1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.l is not 0, read (Address + 2), otherwise read (Address &amp; $FF00) | ui8(Address.L + 2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform Tmp = ui32(Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3.  Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80). Perform Operand.L = (Operand.L &lt;&lt; 1) | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLP (28)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (29)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>ROL (2A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &lt;&lt; 1) | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Store as Operand.L.</t>
+  </si>
+  <si>
+    <t>PLD (2B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Address to Pointer + (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100).</t>
+    </r>
+  </si>
+  <si>
+    <t>BIT (2C)</t>
+  </si>
+  <si>
+    <t>AND (2D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $40).</t>
+    </r>
+  </si>
+  <si>
+    <t>ROL (2E)</t>
+  </si>
+  <si>
+    <t>AND (2F)</t>
+  </si>
+  <si>
+    <t>BMI (30)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as Operand. Address = i16(i8(Operand.L)) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, BoundaryCrossed = Address.H != </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H. If not branching or not BoundaryCrossed, poll interrupts.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (31)</t>
+  </si>
+  <si>
+    <t>AND (32)</t>
+  </si>
+  <si>
+    <t>AND (33)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&amp;= Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Z </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L.</t>
+    </r>
+  </si>
+  <si>
+    <t>BIT (34)</t>
+  </si>
+  <si>
+    <t>AND (35)</t>
+  </si>
+  <si>
+    <t>ROL (36)</t>
+  </si>
+  <si>
+    <t>AND (37)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>SEC (38)</t>
+  </si>
+  <si>
+    <t>AND (39)</t>
+  </si>
+  <si>
+    <t>DEC (3A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &amp; $80), set</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TSC (3B)</t>
+  </si>
+  <si>
+    <t>BIT (3C)</t>
+  </si>
+  <si>
+    <t>AND (3D)</t>
+  </si>
+  <si>
+    <t>ROL (3E)</t>
+  </si>
+  <si>
+    <t>AND (3F)</t>
+  </si>
+  <si>
+    <t>Direct, X (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <r>
       <t>*** Write to (</t>
     </r>
     <r>
@@ -1279,7 +4123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>+0) | $0100</t>
+      <t>.L+0) | $0100</t>
     </r>
   </si>
   <si>
@@ -1305,7 +4149,85 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-1) | $0100</t>
+      <t>.L-1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-2) | $0100</t>
     </r>
   </si>
   <si>
@@ -1331,7 +4253,349 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-2) | $0100</t>
+      <t>.L-2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)-1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)-2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Read </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L | $0100). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTI (40)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand.</t>
     </r>
   </si>
   <si>
@@ -1347,6 +4611,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PC</t>
     </r>
     <r>
@@ -1357,70 +4642,36 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">. Set Pointer to Pointer + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Address.L = Pointer.L.  Address.H = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H. </t>
+      <t xml:space="preserve"> to Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (41)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
@@ -1446,7 +4697,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> |= Operand. Set </t>
+      <t xml:space="preserve"> ^= Operand. Set </t>
     </r>
     <r>
       <rPr>
@@ -1534,2985 +4785,10 @@
     </r>
   </si>
   <si>
-    <t>Set Vector to $FFF4.</t>
-  </si>
-  <si>
-    <r>
-      <t>Write to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+0) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Copy Address to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.  Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set Address to Pointer + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L | $100. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; Operand.L). Perform Operand |= </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80). Perform Operand.L &lt;&lt;= 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sets Operand.L to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flags set.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80). Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &lt;&lt;= 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100)-1)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. If not branching, end (next half-cycle is 4.2).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L to Address.L. If not BoundaryCrossed, end (next half-cycle is 4.2).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to Address.H</t>
-    </r>
-  </si>
-  <si>
-    <t>If Orig.H == Pointer.H, skip 2 half-cycles.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and Z based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &amp; Operand.L). Perform Operand &amp;= ~</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L is 0, Address.L = Operand + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L, Address.H = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H, otherwise Address = Operand + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L is 0, skip 2 half-cycles.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.l is not 0, read (Address + 1), otherwise read (Address &amp; $FF00) | ui8(Address.L + 1)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.l is not 0, read (Address + 2), otherwise read (Address &amp; $FF00) | ui8(Address.L + 2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L += 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Perform Tmp = ui32(Pointer + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp;= Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100)-2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+0) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3.  Copy Address to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Copy Bank to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80). Perform Operand.L = (Operand.L &lt;&lt; 1) | </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>PLP (28)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Read </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 1. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = Operand.L, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flags, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>AND (29)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp;= Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 1.</t>
-    </r>
-  </si>
-  <si>
-    <t>ROL (2A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80). Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &lt;&lt; 1) | </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>Store as Operand.L.</t>
-  </si>
-  <si>
-    <t>PLD (2B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 2. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100)+2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100)+1)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Set Address to Pointer + (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L | $0100).</t>
-    </r>
-  </si>
-  <si>
-    <t>BIT (2C)</t>
-  </si>
-  <si>
-    <t>AND (2D)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; Operand.L), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $40).</t>
-    </r>
-  </si>
-  <si>
-    <t>ROL (2E)</t>
-  </si>
-  <si>
-    <t>AND (2F)</t>
-  </si>
-  <si>
-    <t>BMI (30)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Decide to branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Store as Operand. Address = i16(i8(Operand.L)) + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, BoundaryCrossed = Address.H != </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H. If not branching or not BoundaryCrossed, poll interrupts.</t>
-    </r>
-  </si>
-  <si>
-    <t>AND (31)</t>
-  </si>
-  <si>
-    <t>AND (32)</t>
-  </si>
-  <si>
-    <t>AND (33)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">&amp;= Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">N </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Z </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>L.</t>
-    </r>
-  </si>
-  <si>
-    <t>BIT (34)</t>
-  </si>
-  <si>
-    <t>AND (35)</t>
-  </si>
-  <si>
-    <t>ROL (36)</t>
-  </si>
-  <si>
-    <t>AND (37)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sets the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 1.</t>
-    </r>
-  </si>
-  <si>
-    <t>SEC (38)</t>
-  </si>
-  <si>
-    <t>AND (39)</t>
-  </si>
-  <si>
-    <t>DEC (3A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L -= 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &amp; $80), set</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>TSC (3B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | $0100). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>BIT (3C)</t>
-  </si>
-  <si>
-    <t>AND (3D)</t>
-  </si>
-  <si>
-    <t>ROL (3E)</t>
-  </si>
-  <si>
-    <t>AND (3F)</t>
+    <t>WDM (42)</t>
+  </si>
+  <si>
+    <t>EOR (43)</t>
   </si>
 </sst>
 </file>
@@ -5113,7 +5389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C3793"/>
+  <dimension ref="A1:C4025"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -5196,7 +5472,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>148</v>
+        <v>212</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>35</v>
@@ -5214,7 +5490,7 @@
         <v>3.2</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>36</v>
@@ -5240,14 +5516,14 @@
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5255,7 +5531,7 @@
         <v>4.2</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>59</v>
@@ -5267,7 +5543,7 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5307,7 +5583,7 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5430,7 +5706,7 @@
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5506,7 +5782,7 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>9</v>
@@ -5518,7 +5794,7 @@
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5613,7 +5889,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>35</v>
@@ -5631,7 +5907,7 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>36</v>
@@ -5643,7 +5919,7 @@
       </c>
       <c r="B129" s="9"/>
       <c r="C129" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5651,7 +5927,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>62</v>
@@ -5663,7 +5939,7 @@
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5703,7 +5979,7 @@
       </c>
       <c r="B135" s="9"/>
       <c r="C135" s="14" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5825,7 +6101,7 @@
       </c>
       <c r="B184" s="9"/>
       <c r="C184" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5859,7 +6135,7 @@
       </c>
       <c r="B188" s="9"/>
       <c r="C188" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6000,7 +6276,7 @@
       </c>
       <c r="B249" s="9"/>
       <c r="C249" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6141,7 +6417,7 @@
       </c>
       <c r="B306" s="9"/>
       <c r="C306" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6282,7 +6558,7 @@
       </c>
       <c r="B367" s="9"/>
       <c r="C367" s="26" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6482,7 +6758,7 @@
       </c>
       <c r="B430" s="9"/>
       <c r="C430" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6565,7 +6841,7 @@
       </c>
       <c r="B479" s="9"/>
       <c r="C479" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6573,7 +6849,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="9" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C480" s="10" t="s">
         <v>49</v>
@@ -6585,7 +6861,7 @@
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="10" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6672,7 +6948,7 @@
       </c>
       <c r="B538" s="9"/>
       <c r="C538" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6759,7 +7035,7 @@
       </c>
       <c r="B597" s="9"/>
       <c r="C597" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6848,7 +7124,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B657" s="9" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C657" s="10" t="s">
         <v>75</v>
@@ -6866,7 +7142,7 @@
         <v>3.2</v>
       </c>
       <c r="B659" s="9" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C659" s="10" t="s">
         <v>76</v>
@@ -7021,7 +7297,7 @@
       </c>
       <c r="B721" s="9"/>
       <c r="C721" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7166,7 +7442,7 @@
       </c>
       <c r="B778" s="9"/>
       <c r="C778" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7311,7 +7587,7 @@
       </c>
       <c r="B839" s="9"/>
       <c r="C839" s="26" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7481,7 +7757,7 @@
       </c>
       <c r="B898" s="9"/>
       <c r="C898" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7559,7 +7835,7 @@
         <v>72</v>
       </c>
       <c r="C950" s="26" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7573,7 +7849,7 @@
       </c>
       <c r="B952" s="9"/>
       <c r="C952" s="10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7589,7 +7865,7 @@
       </c>
       <c r="B954" s="9"/>
       <c r="C954" s="10" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7607,7 +7883,7 @@
       </c>
       <c r="B956" s="9"/>
       <c r="C956" s="10" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7641,10 +7917,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="4"/>
-      <c r="B1005" s="24" t="s">
+      <c r="B1005" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C1005" s="25"/>
+      <c r="C1005" s="28"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="12" t="s">
@@ -7769,7 +8045,7 @@
       <c r="A1019" s="8"/>
       <c r="B1019" s="9"/>
       <c r="C1019" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7810,7 +8086,7 @@
       </c>
       <c r="B1024" s="9"/>
       <c r="C1024" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7969,7 +8245,7 @@
       </c>
       <c r="B1077" s="9"/>
       <c r="C1077" s="10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8056,7 +8332,7 @@
       </c>
       <c r="B1128" s="9"/>
       <c r="C1128" s="10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8156,7 +8432,7 @@
       </c>
       <c r="B1140" s="9"/>
       <c r="C1140" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8297,7 +8573,7 @@
       </c>
       <c r="B1193" s="9"/>
       <c r="C1193" s="10" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8418,7 +8694,7 @@
       </c>
       <c r="B1248" s="9"/>
       <c r="C1248" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8457,7 +8733,7 @@
       </c>
       <c r="B1253" s="9"/>
       <c r="C1253" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8492,7 +8768,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
       <c r="B1300" s="27" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="C1300" s="28"/>
     </row>
@@ -8560,7 +8836,7 @@
       </c>
       <c r="B1307" s="9"/>
       <c r="C1307" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8617,7 +8893,7 @@
       </c>
       <c r="B1314" s="9"/>
       <c r="C1314" s="26" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8769,7 +9045,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="34" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C1369" s="14" t="s">
         <v>37</v>
@@ -8797,7 +9073,7 @@
         <v>5.2</v>
       </c>
       <c r="B1373" s="34" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C1373" s="10" t="s">
         <v>69</v>
@@ -8853,7 +9129,7 @@
       </c>
       <c r="B1380" s="9"/>
       <c r="C1380" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9068,7 +9344,7 @@
       <c r="A1487" s="8"/>
       <c r="B1487" s="9"/>
       <c r="C1487" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9109,7 +9385,7 @@
       </c>
       <c r="B1492" s="9"/>
       <c r="C1492" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9196,7 +9472,7 @@
       </c>
       <c r="B1541" s="9"/>
       <c r="C1541" s="10" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9428,7 +9704,7 @@
       </c>
       <c r="B1665" s="9"/>
       <c r="C1665" s="14" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9574,7 +9850,7 @@
       <c r="A1723" s="8"/>
       <c r="B1723" s="9"/>
       <c r="C1723" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9615,7 +9891,7 @@
       </c>
       <c r="B1728" s="9"/>
       <c r="C1728" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9722,7 +9998,7 @@
       </c>
       <c r="B1779" s="9"/>
       <c r="C1779" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9788,7 +10064,7 @@
       </c>
       <c r="B1787" s="9"/>
       <c r="C1787" s="26" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9834,7 +10110,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1830" s="2" t="s">
         <v>19</v>
@@ -9846,7 +10122,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="4"/>
       <c r="B1831" s="27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1831" s="28"/>
     </row>
@@ -9938,7 +10214,7 @@
       </c>
       <c r="B1840" s="9"/>
       <c r="C1840" s="10" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9972,7 +10248,7 @@
       </c>
       <c r="B1844" s="9"/>
       <c r="C1844" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9995,7 +10271,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1889" s="2" t="s">
         <v>6</v>
@@ -10007,7 +10283,7 @@
     <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1890" s="4"/>
       <c r="B1890" s="27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C1890" s="28"/>
     </row>
@@ -10099,7 +10375,7 @@
       </c>
       <c r="B1899" s="9"/>
       <c r="C1899" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10107,7 +10383,7 @@
         <v>4.2</v>
       </c>
       <c r="B1900" s="9" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C1900" s="10" t="s">
         <v>35</v>
@@ -10125,7 +10401,7 @@
         <v>5.2</v>
       </c>
       <c r="B1902" s="9" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
       <c r="C1902" s="10" t="s">
         <v>36</v>
@@ -10137,7 +10413,7 @@
       </c>
       <c r="B1903" s="9"/>
       <c r="C1903" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10160,7 +10436,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1948" s="2" t="s">
         <v>6</v>
@@ -10224,7 +10500,7 @@
       </c>
       <c r="B1954" s="9"/>
       <c r="C1954" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10312,7 +10588,7 @@
       </c>
       <c r="B1964" s="9"/>
       <c r="C1964" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10335,7 +10611,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2007" s="2" t="s">
         <v>14</v>
@@ -10347,7 +10623,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="4"/>
       <c r="B2008" s="24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2008" s="25"/>
     </row>
@@ -10427,7 +10703,7 @@
         <v>3.2</v>
       </c>
       <c r="B2016" s="9" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C2016" s="10" t="s">
         <v>57</v>
@@ -10445,7 +10721,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="9" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="C2018" s="14" t="s">
         <v>73</v>
@@ -10481,7 +10757,7 @@
         <v>6.2</v>
       </c>
       <c r="B2022" s="9" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="C2022" s="14" t="s">
         <v>35</v>
@@ -10499,7 +10775,7 @@
         <v>7.2</v>
       </c>
       <c r="B2024" s="9" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="C2024" s="14" t="s">
         <v>36</v>
@@ -10511,7 +10787,7 @@
       </c>
       <c r="B2025" s="9"/>
       <c r="C2025" s="10" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10534,7 +10810,7 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B2066" s="2" t="s">
         <v>24</v>
@@ -10598,7 +10874,7 @@
       </c>
       <c r="B2072" s="9"/>
       <c r="C2072" s="10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10632,7 +10908,7 @@
       </c>
       <c r="B2076" s="9"/>
       <c r="C2076" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10655,7 +10931,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2125" s="2" t="s">
         <v>15</v>
@@ -10755,7 +11031,7 @@
       </c>
       <c r="B2135" s="9"/>
       <c r="C2135" s="14" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10778,7 +11054,7 @@
     </row>
     <row r="2184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2184" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2184" s="2" t="s">
         <v>15</v>
@@ -10878,7 +11154,7 @@
       </c>
       <c r="B2194" s="9"/>
       <c r="C2194" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10901,7 +11177,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2243" s="2" t="s">
         <v>19</v>
@@ -11019,7 +11295,7 @@
       </c>
       <c r="B2255" s="9"/>
       <c r="C2255" s="26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11065,7 +11341,7 @@
     </row>
     <row r="2302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2302" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B2302" s="2" t="s">
         <v>6</v>
@@ -11219,7 +11495,7 @@
       </c>
       <c r="B2318" s="9"/>
       <c r="C2318" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11242,7 +11518,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B2361" s="2" t="s">
         <v>24</v>
@@ -11316,7 +11592,7 @@
       </c>
       <c r="B2369" s="9"/>
       <c r="C2369" s="10" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11324,10 +11600,10 @@
         <v>3.2</v>
       </c>
       <c r="B2370" s="9" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="C2370" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11336,7 +11612,7 @@
       </c>
       <c r="B2371" s="9"/>
       <c r="C2371" s="14" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11359,7 +11635,7 @@
     </row>
     <row r="2420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2420" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B2420" s="2" t="s">
         <v>22</v>
@@ -11423,7 +11699,7 @@
       </c>
       <c r="B2426" s="9"/>
       <c r="C2426" s="10" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11446,7 +11722,7 @@
     </row>
     <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2479" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B2479" s="2" t="s">
         <v>22</v>
@@ -11510,7 +11786,7 @@
       </c>
       <c r="B2485" s="9"/>
       <c r="C2485" s="10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11533,7 +11809,7 @@
     </row>
     <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2538" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B2538" s="2" t="s">
         <v>19</v>
@@ -11613,10 +11889,10 @@
         <v>3.2</v>
       </c>
       <c r="B2547" s="9" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C2547" s="10" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11631,7 +11907,7 @@
         <v>4.2</v>
       </c>
       <c r="B2549" s="9" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="C2549" s="14" t="s">
         <v>45</v>
@@ -11643,7 +11919,7 @@
       </c>
       <c r="B2550" s="9"/>
       <c r="C2550" s="10" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11666,7 +11942,7 @@
     </row>
     <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2597" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B2597" s="2" t="s">
         <v>24</v>
@@ -11770,7 +12046,7 @@
       </c>
       <c r="B2607" s="9"/>
       <c r="C2607" s="14" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11793,7 +12069,7 @@
     </row>
     <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2656" s="1" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B2656" s="2" t="s">
         <v>24</v>
@@ -11897,7 +12173,7 @@
       </c>
       <c r="B2666" s="9"/>
       <c r="C2666" s="14" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11920,7 +12196,7 @@
     </row>
     <row r="2715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2715" s="1" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B2715" s="2" t="s">
         <v>24</v>
@@ -12024,7 +12300,7 @@
       </c>
       <c r="B2725" s="9"/>
       <c r="C2725" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12047,7 +12323,7 @@
     </row>
     <row r="2774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2774" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B2774" s="2" t="s">
         <v>6</v>
@@ -12169,7 +12445,7 @@
       </c>
       <c r="B2786" s="9"/>
       <c r="C2786" s="26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12215,7 +12491,7 @@
     </row>
     <row r="2833" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2833" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B2833" s="2" t="s">
         <v>19</v>
@@ -12339,7 +12615,7 @@
       </c>
       <c r="B2845" s="9"/>
       <c r="C2845" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12362,7 +12638,7 @@
     </row>
     <row r="2892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2892" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B2892" s="2" t="s">
         <v>22</v>
@@ -12406,7 +12682,7 @@
       </c>
       <c r="B2896" s="9"/>
       <c r="C2896" s="10" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12417,7 +12693,7 @@
         <v>72</v>
       </c>
       <c r="C2897" s="26" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12431,7 +12707,7 @@
       </c>
       <c r="B2899" s="9"/>
       <c r="C2899" s="10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12447,7 +12723,7 @@
       </c>
       <c r="B2901" s="9"/>
       <c r="C2901" s="10" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12465,7 +12741,7 @@
       </c>
       <c r="B2903" s="9"/>
       <c r="C2903" s="10" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12488,7 +12764,7 @@
     </row>
     <row r="2951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2951" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B2951" s="2" t="s">
         <v>19</v>
@@ -12627,7 +12903,7 @@
       <c r="A2966" s="8"/>
       <c r="B2966" s="9"/>
       <c r="C2966" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12668,7 +12944,7 @@
       </c>
       <c r="B2971" s="9"/>
       <c r="C2971" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12691,7 +12967,7 @@
     </row>
     <row r="3010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3010" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B3010" s="2" t="s">
         <v>19</v>
@@ -12827,7 +13103,7 @@
       </c>
       <c r="B3024" s="9"/>
       <c r="C3024" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12850,7 +13126,7 @@
     </row>
     <row r="3069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3069" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B3069" s="2" t="s">
         <v>98</v>
@@ -12914,7 +13190,7 @@
       </c>
       <c r="B3075" s="9"/>
       <c r="C3075" s="10" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13014,7 +13290,7 @@
       </c>
       <c r="B3087" s="9"/>
       <c r="C3087" s="10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13037,7 +13313,7 @@
     </row>
     <row r="3128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3128" s="1" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B3128" s="2" t="s">
         <v>24</v>
@@ -13117,7 +13393,7 @@
       </c>
       <c r="B3136" s="9"/>
       <c r="C3136" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13156,7 +13432,7 @@
       </c>
       <c r="B3141" s="9"/>
       <c r="C3141" s="10" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13179,7 +13455,7 @@
     </row>
     <row r="3187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3187" s="1" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B3187" s="2" t="s">
         <v>24</v>
@@ -13259,7 +13535,7 @@
       </c>
       <c r="B3195" s="9"/>
       <c r="C3195" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13298,7 +13574,7 @@
       </c>
       <c r="B3200" s="9"/>
       <c r="C3200" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13321,7 +13597,7 @@
     </row>
     <row r="3246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3246" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B3246" s="2" t="s">
         <v>6</v>
@@ -13401,7 +13677,7 @@
       </c>
       <c r="B3254" s="9"/>
       <c r="C3254" s="26" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13458,7 +13734,7 @@
       </c>
       <c r="B3261" s="9"/>
       <c r="C3261" s="26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13504,7 +13780,7 @@
     </row>
     <row r="3305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3305" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B3305" s="2" t="s">
         <v>6</v>
@@ -13610,7 +13886,7 @@
         <v>4.2</v>
       </c>
       <c r="B3316" s="34" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C3316" s="10" t="s">
         <v>37</v>
@@ -13638,7 +13914,7 @@
         <v>5.2</v>
       </c>
       <c r="B3320" s="34" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C3320" s="10" t="s">
         <v>69</v>
@@ -13694,7 +13970,7 @@
       </c>
       <c r="B3327" s="9"/>
       <c r="C3327" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13717,7 +13993,7 @@
     </row>
     <row r="3364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3364" s="1" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B3364" s="2" t="s">
         <v>22</v>
@@ -13781,7 +14057,7 @@
       </c>
       <c r="B3370" s="9"/>
       <c r="C3370" s="10" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13804,7 +14080,7 @@
     </row>
     <row r="3423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3423" s="1" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B3423" s="2" t="s">
         <v>24</v>
@@ -13909,7 +14185,7 @@
       <c r="A3434" s="8"/>
       <c r="B3434" s="9"/>
       <c r="C3434" s="10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13950,7 +14226,7 @@
       </c>
       <c r="B3439" s="32"/>
       <c r="C3439" s="10" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13973,7 +14249,7 @@
     </row>
     <row r="3482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3482" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B3482" s="2" t="s">
         <v>22</v>
@@ -14037,7 +14313,7 @@
       </c>
       <c r="B3488" s="9"/>
       <c r="C3488" s="10" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14060,7 +14336,7 @@
     </row>
     <row r="3541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3541" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B3541" s="2" t="s">
         <v>22</v>
@@ -14124,7 +14400,7 @@
       </c>
       <c r="B3547" s="9"/>
       <c r="C3547" s="10" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14147,7 +14423,7 @@
     </row>
     <row r="3600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3600" s="1" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B3600" s="2" t="s">
         <v>24</v>
@@ -14252,7 +14528,7 @@
       <c r="A3611" s="8"/>
       <c r="B3611" s="9"/>
       <c r="C3611" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14293,7 +14569,7 @@
       </c>
       <c r="B3616" s="9"/>
       <c r="C3616" s="10" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14316,7 +14592,7 @@
     </row>
     <row r="3659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3659" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B3659" s="2" t="s">
         <v>24</v>
@@ -14421,7 +14697,7 @@
       <c r="A3670" s="8"/>
       <c r="B3670" s="9"/>
       <c r="C3670" s="14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14462,7 +14738,7 @@
       </c>
       <c r="B3675" s="9"/>
       <c r="C3675" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14485,7 +14761,7 @@
     </row>
     <row r="3718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3718" s="1" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B3718" s="2" t="s">
         <v>98</v>
@@ -14569,7 +14845,7 @@
       </c>
       <c r="B3726" s="9"/>
       <c r="C3726" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14635,7 +14911,7 @@
       </c>
       <c r="B3734" s="9"/>
       <c r="C3734" s="26" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14681,7 +14957,7 @@
     </row>
     <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3777" s="1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B3777" s="2" t="s">
         <v>19</v>
@@ -14693,7 +14969,7 @@
     <row r="3778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3778" s="4"/>
       <c r="B3778" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3778" s="25"/>
     </row>
@@ -14785,7 +15061,7 @@
       </c>
       <c r="B3787" s="9"/>
       <c r="C3787" s="14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14819,7 +15095,7 @@
       </c>
       <c r="B3791" s="9"/>
       <c r="C3791" s="14" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14840,9 +15116,549 @@
       <c r="B3793" s="20"/>
       <c r="C3793" s="22"/>
     </row>
+    <row r="3836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3836" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B3836" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3836" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3837" s="4"/>
+      <c r="B3837" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3837" s="25"/>
+    </row>
+    <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3838" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3838" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3838" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3839" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3839" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3839" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3840" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3840" s="9"/>
+      <c r="C3840" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3841" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B3841" s="9"/>
+      <c r="C3841" s="10"/>
+    </row>
+    <row r="3842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3842" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3842" s="9"/>
+      <c r="C3842" s="10"/>
+    </row>
+    <row r="3843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3843" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3843" s="9"/>
+      <c r="C3843" s="10"/>
+    </row>
+    <row r="3844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3844" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B3844" s="9"/>
+      <c r="C3844" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3845" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B3845" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3845" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3846" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3846" s="9"/>
+      <c r="C3846" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3847" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B3847" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3847" s="14" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3848" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3848" s="9"/>
+      <c r="C3848" s="14"/>
+    </row>
+    <row r="3849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3849" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B3849" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3849" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3850" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B3850" s="9"/>
+      <c r="C3850" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3851" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B3851" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3851" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3852" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3852" s="20"/>
+      <c r="C3852" s="22"/>
+    </row>
+    <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3895" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3895" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3895" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3896" s="4"/>
+      <c r="B3896" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3896" s="28"/>
+    </row>
+    <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3897" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3897" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3897" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3898" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3898" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3898" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3899" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3899" s="9"/>
+      <c r="C3899" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3900" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B3900" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3900" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3901" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3901" s="9"/>
+      <c r="C3901" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3902" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3902" s="9"/>
+      <c r="C3902" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3903" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="B3903" s="16"/>
+      <c r="C3903" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3904" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B3904" s="16"/>
+      <c r="C3904" s="17"/>
+    </row>
+    <row r="3905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3905" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3905" s="9"/>
+      <c r="C3905" s="14"/>
+    </row>
+    <row r="3906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3906" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B3906" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3906" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3907" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3907" s="9"/>
+      <c r="C3907" s="14"/>
+    </row>
+    <row r="3908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3908" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B3908" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3908" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3909" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B3909" s="9"/>
+      <c r="C3909" s="14"/>
+    </row>
+    <row r="3910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3910" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B3910" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3910" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3911" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B3911" s="9"/>
+      <c r="C3911" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3912" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B3912" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3912" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3913" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3913" s="20"/>
+      <c r="C3913" s="22"/>
+    </row>
+    <row r="3954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3954" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3954" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3954" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3955" s="4"/>
+      <c r="B3955" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3955" s="28"/>
+    </row>
+    <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3956" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3956" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3956" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3957" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3957" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3957" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3958" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3958" s="9"/>
+      <c r="C3958" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3959" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B3959" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3959" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3960" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B3960" s="9"/>
+      <c r="C3960" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3961" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3961" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3961" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3962" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3962" s="20"/>
+      <c r="C3962" s="22"/>
+    </row>
+    <row r="4013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4013" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4013" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4013" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4014" s="4"/>
+      <c r="B4014" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4014" s="25"/>
+    </row>
+    <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4015" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4015" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4015" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4016" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4016" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4016" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4017" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4017" s="9"/>
+      <c r="C4017" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4018" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B4018" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4018" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4019" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B4019" s="9"/>
+      <c r="C4019" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4020" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4020" s="9"/>
+      <c r="C4020" s="10"/>
+    </row>
+    <row r="4021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4021" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B4021" s="9"/>
+      <c r="C4021" s="14"/>
+    </row>
+    <row r="4022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4022" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B4022" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4022" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4023" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4023" s="9"/>
+      <c r="C4023" s="14" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4024" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B4024" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4024" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4025" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4025" s="20"/>
+      <c r="C4025" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="55">
     <mergeCell ref="B3719:C3719"/>
+    <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="B3955:C3955"/>
     <mergeCell ref="B3424:C3424"/>
     <mergeCell ref="C3734:C3735"/>
     <mergeCell ref="B3316:B3318"/>
@@ -14894,6 +15710,7 @@
     <mergeCell ref="B1123:C1123"/>
     <mergeCell ref="B61:C61"/>
     <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1005:C1005"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21507DF-AEA7-4007-8BFF-B95F7253643D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147C02FF-BB19-4DF8-BCAF-35B663EDEF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -17134,7 +17134,7 @@
       </c>
     </row>
     <row r="4081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4081" s="8">
+      <c r="A4081" s="18">
         <v>3.2</v>
       </c>
       <c r="B4081" s="9" t="s">
@@ -18931,10 +18931,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="4"/>
-      <c r="B4899" s="24" t="s">
+      <c r="B4899" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="C4899" s="25"/>
+      <c r="C4899" s="32"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="12" t="s">
@@ -20773,7 +20773,7 @@
       </c>
     </row>
     <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5560" s="8">
+      <c r="A5560" s="18">
         <v>4.2</v>
       </c>
       <c r="B5560" s="9" t="s">
@@ -20811,7 +20811,7 @@
       <c r="C5563" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="79">
     <mergeCell ref="B5548:C5548"/>
     <mergeCell ref="B5371:C5371"/>
     <mergeCell ref="B5430:C5430"/>
@@ -20826,6 +20826,7 @@
     <mergeCell ref="C5024:C5025"/>
     <mergeCell ref="B4781:C4781"/>
     <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="B4899:C4899"/>
     <mergeCell ref="C4615:C4616"/>
     <mergeCell ref="B4604:C4604"/>
     <mergeCell ref="B4663:C4663"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147C02FF-BB19-4DF8-BCAF-35B663EDEF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC56D92A-640B-4C83-8302-3DE023BDC2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5605</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5959</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="310">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -5915,6 +5915,35 @@
     <t>EOR (59)</t>
   </si>
   <si>
+    <t>PHY (5A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
     <t>TCD (5B)</t>
   </si>
   <si>
@@ -6112,6 +6141,616 @@
   </si>
   <si>
     <t>EOR (5F)</t>
+  </si>
+  <si>
+    <t>RTS (60)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1).</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (Lo &gt; 9) Lo += 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CarryToHi = Lo &gt; $0F ? 1 : 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (HiSum &gt; 9) HiSum += 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Result = ui8(((HiSum &amp; 0x0F) &lt;&lt; 4) | (Lo &amp; $0F)).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag == 0:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result &gt; $FF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag == 1:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L) + ui16(Operand) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui8(Result). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result == $00. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Lo = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; 0x0F) + ui16(Operand &amp; 0x0F) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  HiSum = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) + ui16(Operand &gt;&gt; 4) + CarryToHi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = HiSum &gt; $0F.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result == $00. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>PER (62)</t>
+  </si>
+  <si>
+    <t>Push Operand.H onto stack.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Operand to Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (63)</t>
+  </si>
+  <si>
+    <t>STZ (64)</t>
+  </si>
+  <si>
+    <t>Direct (Write)</t>
+  </si>
+  <si>
+    <t>Write 0.</t>
   </si>
 </sst>
 </file>
@@ -6712,7 +7351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C5563"/>
+  <dimension ref="A1:C5913"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -8172,7 +8811,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C480" s="10" t="s">
         <v>49</v>
@@ -20082,7 +20721,7 @@
         <v>273</v>
       </c>
       <c r="B5311" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5311" s="3" t="s">
         <v>13</v>
@@ -20127,60 +20766,74 @@
       </c>
     </row>
     <row r="5316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5316" s="18">
+      <c r="A5316" s="8">
         <v>1.2</v>
       </c>
-      <c r="B5316" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5316" s="10" t="s">
-        <v>73</v>
-      </c>
+      <c r="B5316" s="9"/>
+      <c r="C5316" s="10"/>
     </row>
     <row r="5317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5317" s="8">
         <v>2.1</v>
       </c>
       <c r="B5317" s="9"/>
-      <c r="C5317" s="10" t="s">
+      <c r="C5317" s="10"/>
+    </row>
+    <row r="5318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5318" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5318" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5318" s="10" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="5318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5318" s="8">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B5318" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5318" s="10" t="s">
+    <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5319" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5319" s="9"/>
+      <c r="C5319" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5320" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5320" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5320" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5319" s="19" t="s">
+    <row r="5321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5321" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5319" s="20"/>
-      <c r="C5319" s="22"/>
+      <c r="B5321" s="20"/>
+      <c r="C5321" s="22"/>
     </row>
     <row r="5370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5370" s="1" t="s">
         <v>275</v>
       </c>
       <c r="B5370" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5370" s="3" t="s">
-        <v>82</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5371" s="4"/>
-      <c r="B5371" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="C5371" s="32"/>
+      <c r="B5371" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5371" s="25"/>
     </row>
     <row r="5372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5372" s="12" t="s">
@@ -20214,14 +20867,14 @@
       </c>
     </row>
     <row r="5375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5375" s="8">
+      <c r="A5375" s="18">
         <v>1.2</v>
       </c>
       <c r="B5375" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C5375" s="10" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20230,7 +20883,7 @@
       </c>
       <c r="B5376" s="9"/>
       <c r="C5376" s="10" t="s">
-        <v>56</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20241,71 +20894,31 @@
         <v>72</v>
       </c>
       <c r="C5377" s="10" t="s">
-        <v>276</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5378" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="B5378" s="9"/>
-      <c r="C5378" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5379" s="18">
-        <v>3.2</v>
-      </c>
-      <c r="B5379" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5379" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5380" s="8">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B5380" s="9"/>
-      <c r="C5380" s="10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5381" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="B5381" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5381" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5382" s="19" t="s">
+      <c r="A5378" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5382" s="20"/>
-      <c r="C5382" s="22"/>
+      <c r="B5378" s="20"/>
+      <c r="C5378" s="22"/>
     </row>
     <row r="5429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5429" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5429" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C5429" s="3" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5430" s="4"/>
       <c r="B5430" s="31" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C5430" s="32"/>
     </row>
@@ -20345,10 +20958,10 @@
         <v>1.2</v>
       </c>
       <c r="B5434" s="9" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C5434" s="10" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20365,10 +20978,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B5436" s="9" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C5436" s="10" t="s">
-        <v>37</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20377,88 +20990,53 @@
       </c>
       <c r="B5437" s="9"/>
       <c r="C5437" s="10" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5438" s="8"/>
-      <c r="B5438" s="9"/>
+      <c r="A5438" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B5438" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="C5438" s="10" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5439" s="8"/>
+      <c r="A5439" s="8">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="B5439" s="9"/>
       <c r="C5439" s="10" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="5440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5440" s="8"/>
-      <c r="B5440" s="9"/>
+      <c r="A5440" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5440" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="C5440" s="10" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5441" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="B5441" s="16"/>
-      <c r="C5441" s="23"/>
-    </row>
-    <row r="5442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5442" s="15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B5442" s="16"/>
-      <c r="C5442" s="23"/>
-    </row>
-    <row r="5443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5443" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="B5443" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5443" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5444" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B5444" s="9"/>
-      <c r="C5444" s="10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5445" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="B5445" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5445" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5446" s="19" t="s">
+      <c r="A5441" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5446" s="20"/>
-      <c r="C5446" s="22"/>
+      <c r="B5441" s="20"/>
+      <c r="C5441" s="22"/>
     </row>
     <row r="5488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5488" s="1" t="s">
         <v>280</v>
       </c>
       <c r="B5488" s="2" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="C5488" s="3" t="s">
         <v>32</v>
@@ -20467,7 +21045,7 @@
     <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5489" s="4"/>
       <c r="B5489" s="31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C5489" s="32"/>
     </row>
@@ -20507,7 +21085,7 @@
         <v>1.2</v>
       </c>
       <c r="B5493" s="9" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C5493" s="10" t="s">
         <v>31</v>
@@ -20527,7 +21105,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B5495" s="9" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C5495" s="10" t="s">
         <v>37</v>
@@ -20539,131 +21117,97 @@
       </c>
       <c r="B5496" s="9"/>
       <c r="C5496" s="10" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5497" s="8"/>
       <c r="B5497" s="9"/>
       <c r="C5497" s="10" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5498" s="8"/>
       <c r="B5498" s="9"/>
       <c r="C5498" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5499" s="8"/>
+      <c r="B5499" s="9"/>
+      <c r="C5499" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="5499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5499" s="8">
+    <row r="5500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5500" s="15">
         <v>3.2</v>
       </c>
-      <c r="B5499" s="9"/>
-      <c r="C5499" s="10"/>
-    </row>
-    <row r="5500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5500" s="8">
+      <c r="B5500" s="16"/>
+      <c r="C5500" s="23"/>
+    </row>
+    <row r="5501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5501" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B5500" s="9"/>
-      <c r="C5500" s="10"/>
-    </row>
-    <row r="5501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5501" s="8">
+      <c r="B5501" s="16"/>
+      <c r="C5501" s="23"/>
+    </row>
+    <row r="5502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5502" s="18">
         <v>4.2</v>
       </c>
-      <c r="B5501" s="9" t="s">
+      <c r="B5502" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C5501" s="10" t="s">
+      <c r="C5502" s="10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5502" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B5502" s="9"/>
-      <c r="C5502" s="10"/>
     </row>
     <row r="5503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5503" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="B5503" s="9" t="s">
-        <v>128</v>
-      </c>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5503" s="9"/>
       <c r="C5503" s="10" t="s">
-        <v>47</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5504" s="8">
-        <v>6.1</v>
-      </c>
-      <c r="B5504" s="9"/>
-      <c r="C5504" s="30" t="s">
-        <v>232</v>
+        <v>5.2</v>
+      </c>
+      <c r="B5504" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5504" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5505" s="8"/>
-      <c r="B5505" s="9"/>
-      <c r="C5505" s="30"/>
-    </row>
-    <row r="5506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5506" s="18">
-        <v>6.2</v>
-      </c>
-      <c r="B5506" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5506" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5507" s="8">
-        <v>7.1</v>
-      </c>
-      <c r="B5507" s="9"/>
-      <c r="C5507" s="10"/>
-    </row>
-    <row r="5508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5508" s="8">
-        <v>7.2</v>
-      </c>
-      <c r="B5508" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5508" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5509" s="19" t="s">
+      <c r="A5505" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5509" s="20"/>
-      <c r="C5509" s="22"/>
+      <c r="B5505" s="20"/>
+      <c r="C5505" s="22"/>
     </row>
     <row r="5547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5547" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B5547" s="2" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C5547" s="3" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5548" s="4"/>
       <c r="B5548" s="31" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C5548" s="32"/>
     </row>
@@ -20735,45 +21279,39 @@
       </c>
       <c r="B5555" s="9"/>
       <c r="C5555" s="10" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5556" s="8">
-        <v>3.2</v>
-      </c>
-      <c r="B5556" s="9" t="s">
-        <v>72</v>
-      </c>
+      <c r="A5556" s="8"/>
+      <c r="B5556" s="9"/>
       <c r="C5556" s="10" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5557" s="8">
-        <v>4.0999999999999996</v>
-      </c>
+      <c r="A5557" s="8"/>
       <c r="B5557" s="9"/>
       <c r="C5557" s="10" t="s">
-        <v>168</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5558" s="8"/>
+      <c r="A5558" s="8">
+        <v>3.2</v>
+      </c>
       <c r="B5558" s="9"/>
-      <c r="C5558" s="10" t="s">
-        <v>102</v>
-      </c>
+      <c r="C5558" s="10"/>
     </row>
     <row r="5559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5559" s="8"/>
+      <c r="A5559" s="8">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="B5559" s="9"/>
-      <c r="C5559" s="10" t="s">
-        <v>118</v>
-      </c>
+      <c r="C5559" s="10"/>
     </row>
     <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5560" s="18">
+      <c r="A5560" s="8">
         <v>4.2</v>
       </c>
       <c r="B5560" s="9" t="s">
@@ -20788,35 +21326,1164 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B5561" s="9"/>
-      <c r="C5561" s="10" t="s">
-        <v>222</v>
-      </c>
+      <c r="C5561" s="10"/>
     </row>
     <row r="5562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5562" s="8">
         <v>5.2</v>
       </c>
       <c r="B5562" s="9" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C5562" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5563" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5563" s="9"/>
+      <c r="C5563" s="30" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5564" s="8"/>
+      <c r="B5564" s="9"/>
+      <c r="C5564" s="30"/>
+    </row>
+    <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5565" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B5565" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5565" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5566" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B5566" s="9"/>
+      <c r="C5566" s="10"/>
+    </row>
+    <row r="5567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5567" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B5567" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5567" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5563" s="19" t="s">
+    <row r="5568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5568" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5563" s="20"/>
-      <c r="C5563" s="22"/>
+      <c r="B5568" s="20"/>
+      <c r="C5568" s="22"/>
+    </row>
+    <row r="5606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5606" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5606" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5606" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5607" s="4"/>
+      <c r="B5607" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5607" s="32"/>
+    </row>
+    <row r="5608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5608" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5608" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5608" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5609" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5609" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5609" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5610" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5610" s="9"/>
+      <c r="C5610" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5611" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5611" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5611" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5612" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5612" s="9"/>
+      <c r="C5612" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5613" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5613" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5613" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5614" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5614" s="9"/>
+      <c r="C5614" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5615" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5615" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5615" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5616" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5616" s="9"/>
+      <c r="C5616" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5617" s="8"/>
+      <c r="B5617" s="9"/>
+      <c r="C5617" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5618" s="8"/>
+      <c r="B5618" s="9"/>
+      <c r="C5618" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5619" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B5619" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5619" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5620" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5620" s="9"/>
+      <c r="C5620" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5621" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B5621" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5621" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5622" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5622" s="20"/>
+      <c r="C5622" s="22"/>
+    </row>
+    <row r="5665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5665" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5665" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5665" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5666" s="4"/>
+      <c r="B5666" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5666" s="25"/>
+    </row>
+    <row r="5667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5667" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5667" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5667" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5668" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5668" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5668" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5669" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5669" s="9"/>
+      <c r="C5669" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5670" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5670" s="9"/>
+      <c r="C5670" s="10"/>
+    </row>
+    <row r="5671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5671" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5671" s="9"/>
+      <c r="C5671" s="10"/>
+    </row>
+    <row r="5672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5672" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5672" s="9"/>
+      <c r="C5672" s="10"/>
+    </row>
+    <row r="5673" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5673" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5673" s="9"/>
+      <c r="C5673" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5674" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5674" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5674" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5674" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5675" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5675" s="9"/>
+      <c r="C5675" s="10"/>
+    </row>
+    <row r="5676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5676" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5676" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5676" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5677" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5677" s="9"/>
+      <c r="C5677" s="10"/>
+    </row>
+    <row r="5678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5678" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B5678" s="9"/>
+      <c r="C5678" s="10"/>
+    </row>
+    <row r="5679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5679" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5679" s="9"/>
+      <c r="C5679" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5680" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5680" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5680" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5681" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5681" s="20"/>
+      <c r="C5681" s="22"/>
+    </row>
+    <row r="5724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5724" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5724" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5724" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5725" s="4"/>
+      <c r="B5725" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5725" s="32"/>
+    </row>
+    <row r="5726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5726" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5726" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5726" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5727" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5727" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5727" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5728" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5728" s="9"/>
+      <c r="C5728" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5729" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5729" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5729" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5730" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5730" s="9"/>
+      <c r="C5730" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5731" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5731" s="9"/>
+      <c r="C5731" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5732" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="B5732" s="16"/>
+      <c r="C5732" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5733" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B5733" s="16"/>
+      <c r="C5733" s="23"/>
+    </row>
+    <row r="5734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5734" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5734" s="9"/>
+      <c r="C5734" s="10"/>
+    </row>
+    <row r="5735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5735" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5735" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5735" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5736" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5736" s="9"/>
+      <c r="C5736" s="10"/>
+    </row>
+    <row r="5737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5737" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B5737" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5737" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5738" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5738" s="9"/>
+      <c r="C5738" s="10"/>
+    </row>
+    <row r="5739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5739" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B5739" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5739" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5740" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B5740" s="9"/>
+      <c r="C5740" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5741" s="8"/>
+      <c r="B5741" s="9"/>
+      <c r="C5741" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5742" s="8"/>
+      <c r="B5742" s="9"/>
+      <c r="C5742" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5743" s="8"/>
+      <c r="B5743" s="9"/>
+      <c r="C5743" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5744" s="8"/>
+      <c r="B5744" s="9"/>
+      <c r="C5744" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5745" s="8"/>
+      <c r="B5745" s="9"/>
+      <c r="C5745" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="5746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5746" s="8"/>
+      <c r="B5746" s="9"/>
+      <c r="C5746" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5747" s="8"/>
+      <c r="B5747" s="9"/>
+      <c r="C5747" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5748" s="8"/>
+      <c r="B5748" s="9"/>
+      <c r="C5748" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5749" s="8"/>
+      <c r="B5749" s="9"/>
+      <c r="C5749" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5750" s="8"/>
+      <c r="B5750" s="9"/>
+      <c r="C5750" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5751" s="8"/>
+      <c r="B5751" s="9"/>
+      <c r="C5751" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5752" s="8"/>
+      <c r="B5752" s="9"/>
+      <c r="C5752" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5753" s="8"/>
+      <c r="B5753" s="9"/>
+      <c r="C5753" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5754" s="8"/>
+      <c r="B5754" s="9"/>
+      <c r="C5754" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5755" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B5755" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5755" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5756" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5756" s="20"/>
+      <c r="C5756" s="22"/>
+    </row>
+    <row r="5783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5783" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5783" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5783" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5784" s="4"/>
+      <c r="B5784" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5784" s="25"/>
+    </row>
+    <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5785" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5785" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5785" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5786" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5786" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5786" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5787" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5787" s="9"/>
+      <c r="C5787" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5788" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5788" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5788" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5789" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5789" s="9"/>
+      <c r="C5789" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5790" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5790" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5790" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5791" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5791" s="9"/>
+      <c r="C5791" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5792" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B5792" s="9"/>
+      <c r="C5792" s="10"/>
+    </row>
+    <row r="5793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5793" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5793" s="9"/>
+      <c r="C5793" s="10"/>
+    </row>
+    <row r="5794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5794" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5794" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5794" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5795" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5795" s="9"/>
+      <c r="C5795" s="10"/>
+    </row>
+    <row r="5796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5796" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B5796" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5796" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5797" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B5797" s="9"/>
+      <c r="C5797" s="10" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5798" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B5798" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5798" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5799" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5799" s="20"/>
+      <c r="C5799" s="22"/>
+    </row>
+    <row r="5842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5842" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5842" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5842" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5843" s="4"/>
+      <c r="B5843" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5843" s="25"/>
+    </row>
+    <row r="5844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5844" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5844" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5844" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5845" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5845" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5845" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5846" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5846" s="9"/>
+      <c r="C5846" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5847" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5847" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5847" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5848" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B5848" s="9"/>
+      <c r="C5848" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="5849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5849" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5849" s="9"/>
+      <c r="C5849" s="10"/>
+    </row>
+    <row r="5850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5850" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5850" s="9"/>
+      <c r="C5850" s="10"/>
+    </row>
+    <row r="5851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5851" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B5851" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5851" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5852" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5852" s="9"/>
+      <c r="C5852" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5853" s="8"/>
+      <c r="B5853" s="9"/>
+      <c r="C5853" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5854" s="8"/>
+      <c r="B5854" s="9"/>
+      <c r="C5854" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5855" s="8"/>
+      <c r="B5855" s="9"/>
+      <c r="C5855" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5856" s="8"/>
+      <c r="B5856" s="9"/>
+      <c r="C5856" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5857" s="8"/>
+      <c r="B5857" s="9"/>
+      <c r="C5857" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="5858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5858" s="8"/>
+      <c r="B5858" s="9"/>
+      <c r="C5858" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5859" s="8"/>
+      <c r="B5859" s="9"/>
+      <c r="C5859" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5860" s="8"/>
+      <c r="B5860" s="9"/>
+      <c r="C5860" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5861" s="8"/>
+      <c r="B5861" s="9"/>
+      <c r="C5861" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5862" s="8"/>
+      <c r="B5862" s="9"/>
+      <c r="C5862" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5863" s="8"/>
+      <c r="B5863" s="9"/>
+      <c r="C5863" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5864" s="8"/>
+      <c r="B5864" s="9"/>
+      <c r="C5864" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5865" s="8"/>
+      <c r="B5865" s="9"/>
+      <c r="C5865" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5866" s="8"/>
+      <c r="B5866" s="9"/>
+      <c r="C5866" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5867" s="8"/>
+      <c r="B5867" s="9"/>
+      <c r="C5867" s="10"/>
+    </row>
+    <row r="5868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5868" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5868" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5868" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5869" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5869" s="20"/>
+      <c r="C5869" s="22"/>
+    </row>
+    <row r="5901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5901" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5901" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5901" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5902" s="4"/>
+      <c r="B5902" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5902" s="25"/>
+    </row>
+    <row r="5903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5903" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5903" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5903" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5904" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5904" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5904" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5905" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5905" s="9"/>
+      <c r="C5905" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5906" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5906" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5906" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5907" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B5907" s="16"/>
+      <c r="C5907" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5908" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5908" s="16"/>
+      <c r="C5908" s="23"/>
+    </row>
+    <row r="5909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5909" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5909" s="9"/>
+      <c r="C5909" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5910" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B5910" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5910" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="5911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5911" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5911" s="9"/>
+      <c r="C5911" s="10"/>
+    </row>
+    <row r="5912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5912" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5912" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5912" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5913" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5913" s="20"/>
+      <c r="C5913" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="B5548:C5548"/>
-    <mergeCell ref="B5371:C5371"/>
+  <mergeCells count="80">
+    <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="B5607:C5607"/>
     <mergeCell ref="B5430:C5430"/>
     <mergeCell ref="B5489:C5489"/>
-    <mergeCell ref="C5504:C5505"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
     <mergeCell ref="B5135:C5135"/>
     <mergeCell ref="B5145:B5147"/>
     <mergeCell ref="B5149:B5151"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC56D92A-640B-4C83-8302-3DE023BDC2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94886885-B220-4532-9DAD-FCA78D6CA6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5959</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$6608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2407" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="332">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -6751,6 +6751,718 @@
   </si>
   <si>
     <t>Write 0.</t>
+  </si>
+  <si>
+    <t>ADC (65)</t>
+  </si>
+  <si>
+    <t>ROR (66)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01). Perform Operand.L = (Operand.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (67)</t>
+  </si>
+  <si>
+    <t>PLA (68)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (69)</t>
+  </si>
+  <si>
+    <t>ROR (6A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL (6B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (6C)</t>
+  </si>
+  <si>
+    <t>Absolute Indirect</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
+    <t>ADC (6D)</t>
+  </si>
+  <si>
+    <t>ROR (6E)</t>
+  </si>
+  <si>
+    <t>ADC (6F)</t>
   </si>
 </sst>
 </file>
@@ -7351,7 +8063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C5913"/>
+  <dimension ref="A1:C6578"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -22333,27 +23045,22 @@
       </c>
     </row>
     <row r="5867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5867" s="8"/>
-      <c r="B5867" s="9"/>
-      <c r="C5867" s="10"/>
+      <c r="A5867" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5867" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5867" s="10" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5868" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="B5868" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5868" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5869" s="19" t="s">
+      <c r="A5868" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5869" s="20"/>
-      <c r="C5869" s="22"/>
+      <c r="B5868" s="20"/>
+      <c r="C5868" s="22"/>
     </row>
     <row r="5901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5901" s="1" t="s">
@@ -22476,9 +23183,2002 @@
       <c r="B5913" s="20"/>
       <c r="C5913" s="22"/>
     </row>
+    <row r="5960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5960" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5960" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5960" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5961" s="4"/>
+      <c r="B5961" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5961" s="25"/>
+    </row>
+    <row r="5962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5962" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5962" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5962" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5963" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5963" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5963" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5964" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5964" s="9"/>
+      <c r="C5964" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5965" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B5965" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5965" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5966" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B5966" s="16"/>
+      <c r="C5966" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5967" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5967" s="16"/>
+      <c r="C5967" s="23"/>
+    </row>
+    <row r="5968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5968" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B5968" s="9"/>
+      <c r="C5968" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5969" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B5969" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5969" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5970" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5970" s="9"/>
+      <c r="C5970" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5971" s="8"/>
+      <c r="B5971" s="9"/>
+      <c r="C5971" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5972" s="8"/>
+      <c r="B5972" s="9"/>
+      <c r="C5972" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5973" s="8"/>
+      <c r="B5973" s="9"/>
+      <c r="C5973" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5974" s="8"/>
+      <c r="B5974" s="9"/>
+      <c r="C5974" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5975" s="8"/>
+      <c r="B5975" s="9"/>
+      <c r="C5975" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="5976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5976" s="8"/>
+      <c r="B5976" s="9"/>
+      <c r="C5976" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="5977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5977" s="8"/>
+      <c r="B5977" s="9"/>
+      <c r="C5977" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5978" s="8"/>
+      <c r="B5978" s="9"/>
+      <c r="C5978" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5979" s="8"/>
+      <c r="B5979" s="9"/>
+      <c r="C5979" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5980" s="8"/>
+      <c r="B5980" s="9"/>
+      <c r="C5980" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="5981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5981" s="8"/>
+      <c r="B5981" s="9"/>
+      <c r="C5981" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5982" s="8"/>
+      <c r="B5982" s="9"/>
+      <c r="C5982" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5983" s="8"/>
+      <c r="B5983" s="9"/>
+      <c r="C5983" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5984" s="8"/>
+      <c r="B5984" s="9"/>
+      <c r="C5984" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5985" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B5985" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5985" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5986" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5986" s="20"/>
+      <c r="C5986" s="22"/>
+    </row>
+    <row r="6019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6019" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6019" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6019" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6020" s="4"/>
+      <c r="B6020" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6020" s="32"/>
+    </row>
+    <row r="6021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6021" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6021" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6021" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6022" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6022" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6022" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6023" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6023" s="9"/>
+      <c r="C6023" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6024" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6024" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6024" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6025" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B6025" s="16"/>
+      <c r="C6025" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6026" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6026" s="16"/>
+      <c r="C6026" s="23"/>
+    </row>
+    <row r="6027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6027" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6027" s="9"/>
+      <c r="C6027" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6028" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6028" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6028" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6029" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6029" s="9"/>
+      <c r="C6029" s="10"/>
+    </row>
+    <row r="6030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6030" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6030" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6030" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6031" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6031" s="9"/>
+      <c r="C6031" s="30" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6032" s="8"/>
+      <c r="B6032" s="9"/>
+      <c r="C6032" s="30"/>
+    </row>
+    <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6033" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B6033" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6033" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6034" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6034" s="9"/>
+      <c r="C6034" s="10"/>
+    </row>
+    <row r="6035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6035" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6035" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6035" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6036" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6036" s="20"/>
+      <c r="C6036" s="21"/>
+    </row>
+    <row r="6078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6078" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6078" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6078" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6079" s="4"/>
+      <c r="B6079" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6079" s="25"/>
+    </row>
+    <row r="6080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6080" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6080" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6080" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6081" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6081" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6081" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6082" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6082" s="9"/>
+      <c r="C6082" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6083" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6083" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6083" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6084" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B6084" s="16"/>
+      <c r="C6084" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6085" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6085" s="16"/>
+      <c r="C6085" s="23"/>
+    </row>
+    <row r="6086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6086" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6086" s="9"/>
+      <c r="C6086" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6087" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6087" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6087" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6088" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6088" s="9"/>
+      <c r="C6088" s="10"/>
+    </row>
+    <row r="6089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6089" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6089" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6089" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6090" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6090" s="9"/>
+      <c r="C6090" s="10"/>
+    </row>
+    <row r="6091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6091" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6091" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6091" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6092" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6092" s="9"/>
+      <c r="C6092" s="10"/>
+    </row>
+    <row r="6093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6093" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B6093" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6093" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6094" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6094" s="9"/>
+      <c r="C6094" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6095" s="8"/>
+      <c r="B6095" s="9"/>
+      <c r="C6095" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6096" s="8"/>
+      <c r="B6096" s="9"/>
+      <c r="C6096" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6097" s="8"/>
+      <c r="B6097" s="9"/>
+      <c r="C6097" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6098" s="8"/>
+      <c r="B6098" s="9"/>
+      <c r="C6098" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6099" s="8"/>
+      <c r="B6099" s="9"/>
+      <c r="C6099" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6100" s="8"/>
+      <c r="B6100" s="9"/>
+      <c r="C6100" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6101" s="8"/>
+      <c r="B6101" s="9"/>
+      <c r="C6101" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6102" s="8"/>
+      <c r="B6102" s="9"/>
+      <c r="C6102" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6103" s="8"/>
+      <c r="B6103" s="9"/>
+      <c r="C6103" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6104" s="8"/>
+      <c r="B6104" s="9"/>
+      <c r="C6104" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6105" s="8"/>
+      <c r="B6105" s="9"/>
+      <c r="C6105" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6106" s="8"/>
+      <c r="B6106" s="9"/>
+      <c r="C6106" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6107" s="8"/>
+      <c r="B6107" s="9"/>
+      <c r="C6107" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6108" s="8"/>
+      <c r="B6108" s="9"/>
+      <c r="C6108" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6109" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B6109" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6109" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6110" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6110" s="20"/>
+      <c r="C6110" s="22"/>
+    </row>
+    <row r="6137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6137" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6137" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6138" s="4"/>
+      <c r="B6138" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6138" s="25"/>
+    </row>
+    <row r="6139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6139" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6139" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6139" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6140" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6140" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6140" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6141" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6141" s="9"/>
+      <c r="C6141" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6142" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6142" s="9"/>
+      <c r="C6142" s="10"/>
+    </row>
+    <row r="6143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6143" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6143" s="9"/>
+      <c r="C6143" s="10"/>
+    </row>
+    <row r="6144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6144" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6144" s="9"/>
+      <c r="C6144" s="10"/>
+    </row>
+    <row r="6145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6145" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6145" s="9"/>
+      <c r="C6145" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6146" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B6146" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6146" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6147" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6147" s="9"/>
+      <c r="C6147" s="35" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6148" s="8"/>
+      <c r="B6148" s="9"/>
+      <c r="C6148" s="35"/>
+    </row>
+    <row r="6149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6149" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6149" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6149" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6150" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6150" s="20"/>
+      <c r="C6150" s="22"/>
+    </row>
+    <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6196" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6196" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6196" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6197" s="4"/>
+      <c r="B6197" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6197" s="25"/>
+    </row>
+    <row r="6198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6198" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6198" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6198" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6199" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6199" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6199" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6200" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6200" s="9"/>
+      <c r="C6200" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6201" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B6201" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6201" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6202" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6202" s="9"/>
+      <c r="C6202" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6203" s="8"/>
+      <c r="B6203" s="9"/>
+      <c r="C6203" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6204" s="8"/>
+      <c r="B6204" s="9"/>
+      <c r="C6204" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6205" s="8"/>
+      <c r="B6205" s="9"/>
+      <c r="C6205" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6206" s="8"/>
+      <c r="B6206" s="9"/>
+      <c r="C6206" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6207" s="8"/>
+      <c r="B6207" s="9"/>
+      <c r="C6207" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6208" s="8"/>
+      <c r="B6208" s="9"/>
+      <c r="C6208" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6209" s="8"/>
+      <c r="B6209" s="9"/>
+      <c r="C6209" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6210" s="8"/>
+      <c r="B6210" s="9"/>
+      <c r="C6210" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6211" s="8"/>
+      <c r="B6211" s="9"/>
+      <c r="C6211" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6212" s="8"/>
+      <c r="B6212" s="9"/>
+      <c r="C6212" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6213" s="8"/>
+      <c r="B6213" s="9"/>
+      <c r="C6213" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6214" s="8"/>
+      <c r="B6214" s="9"/>
+      <c r="C6214" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6215" s="8"/>
+      <c r="B6215" s="9"/>
+      <c r="C6215" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6216" s="8"/>
+      <c r="B6216" s="9"/>
+      <c r="C6216" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6217" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6217" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6217" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6218" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6218" s="20"/>
+      <c r="C6218" s="22"/>
+    </row>
+    <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6255" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6255" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6255" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6256" s="4"/>
+      <c r="B6256" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6256" s="25"/>
+    </row>
+    <row r="6257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6257" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6257" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6257" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6258" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6258" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6258" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6259" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6259" s="9"/>
+      <c r="C6259" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6260" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B6260" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6260" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6261" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6261" s="9"/>
+      <c r="C6261" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6262" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6262" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6262" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6263" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6263" s="20"/>
+      <c r="C6263" s="22"/>
+    </row>
+    <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6314" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6314" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6314" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6315" s="4"/>
+      <c r="B6315" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6315" s="25"/>
+    </row>
+    <row r="6316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6316" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6316" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6316" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6317" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6317" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6317" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6318" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6318" s="9"/>
+      <c r="C6318" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6319" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6319" s="9"/>
+      <c r="C6319" s="10"/>
+    </row>
+    <row r="6320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6320" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6320" s="9"/>
+      <c r="C6320" s="10"/>
+    </row>
+    <row r="6321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6321" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6321" s="9"/>
+      <c r="C6321" s="10"/>
+    </row>
+    <row r="6322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6322" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6322" s="9"/>
+      <c r="C6322" s="10"/>
+    </row>
+    <row r="6323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6323" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6323" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6323" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6324" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6324" s="9"/>
+      <c r="C6324" s="10"/>
+    </row>
+    <row r="6325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6325" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6325" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6325" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6326" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6326" s="9"/>
+      <c r="C6326" s="10"/>
+    </row>
+    <row r="6327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6327" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B6327" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6327" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6328" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6328" s="9"/>
+      <c r="C6328" s="10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6329" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6329" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6329" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6330" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6330" s="20"/>
+      <c r="C6330" s="22"/>
+    </row>
+    <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6373" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B6373" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6373" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6374" s="4"/>
+      <c r="B6374" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="C6374" s="25"/>
+    </row>
+    <row r="6375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6375" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6375" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6375" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6376" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6376" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6376" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6377" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6377" s="9"/>
+      <c r="C6377" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6378" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6378" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6378" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6379" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6379" s="9"/>
+      <c r="C6379" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6380" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6380" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6380" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6381" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6381" s="9"/>
+      <c r="C6381" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6382" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6382" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6382" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6383" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6383" s="9"/>
+      <c r="C6383" s="10"/>
+    </row>
+    <row r="6384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6384" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B6384" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6384" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6385" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6385" s="9"/>
+      <c r="C6385" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6386" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6386" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6386" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6387" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6387" s="20"/>
+      <c r="C6387" s="22"/>
+    </row>
+    <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6432" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6432" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6432" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6433" s="4"/>
+      <c r="B6433" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6433" s="25"/>
+    </row>
+    <row r="6434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6434" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6434" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6434" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6435" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6435" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6435" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6436" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6436" s="9"/>
+      <c r="C6436" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6437" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6437" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6437" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6438" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6438" s="9"/>
+      <c r="C6438" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6439" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6439" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6439" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6440" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6440" s="9"/>
+      <c r="C6440" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6441" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B6441" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6441" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6442" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6442" s="9"/>
+      <c r="C6442" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6443" s="8"/>
+      <c r="B6443" s="9"/>
+      <c r="C6443" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6444" s="8"/>
+      <c r="B6444" s="9"/>
+      <c r="C6444" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6445" s="8"/>
+      <c r="B6445" s="9"/>
+      <c r="C6445" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6446" s="8"/>
+      <c r="B6446" s="9"/>
+      <c r="C6446" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6447" s="8"/>
+      <c r="B6447" s="9"/>
+      <c r="C6447" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6448" s="8"/>
+      <c r="B6448" s="9"/>
+      <c r="C6448" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6449" s="8"/>
+      <c r="B6449" s="9"/>
+      <c r="C6449" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6450" s="8"/>
+      <c r="B6450" s="9"/>
+      <c r="C6450" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6451" s="8"/>
+      <c r="B6451" s="9"/>
+      <c r="C6451" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6452" s="8"/>
+      <c r="B6452" s="9"/>
+      <c r="C6452" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6453" s="8"/>
+      <c r="B6453" s="9"/>
+      <c r="C6453" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6454" s="8"/>
+      <c r="B6454" s="9"/>
+      <c r="C6454" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6455" s="8"/>
+      <c r="B6455" s="9"/>
+      <c r="C6455" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6456" s="8"/>
+      <c r="B6456" s="9"/>
+      <c r="C6456" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6457" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6457" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6457" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6458" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6458" s="20"/>
+      <c r="C6458" s="22"/>
+    </row>
+    <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6491" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6491" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6491" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6492" s="4"/>
+      <c r="B6492" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6492" s="32"/>
+    </row>
+    <row r="6493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6493" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6493" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6493" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6494" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6494" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6494" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6495" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6495" s="9"/>
+      <c r="C6495" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6496" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6496" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6496" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6497" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6497" s="9"/>
+      <c r="C6497" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6498" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6498" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6498" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6499" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6499" s="9"/>
+      <c r="C6499" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6500" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6500" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6500" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6501" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6501" s="9"/>
+      <c r="C6501" s="10"/>
+    </row>
+    <row r="6502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6502" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6502" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6502" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6503" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6503" s="9"/>
+      <c r="C6503" s="30" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6504" s="8"/>
+      <c r="B6504" s="9"/>
+      <c r="C6504" s="30"/>
+    </row>
+    <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6505" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B6505" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6505" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6506" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6506" s="9"/>
+      <c r="C6506" s="10"/>
+    </row>
+    <row r="6507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6507" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6507" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6507" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6508" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6508" s="20"/>
+      <c r="C6508" s="22"/>
+    </row>
+    <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6550" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6550" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6550" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6551" s="4"/>
+      <c r="B6551" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6551" s="25"/>
+    </row>
+    <row r="6552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6552" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6552" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6552" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6553" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6553" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6553" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6554" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6554" s="9"/>
+      <c r="C6554" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6555" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6555" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6555" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6556" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6556" s="9"/>
+      <c r="C6556" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6557" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6557" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6557" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6558" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6558" s="9"/>
+      <c r="C6558" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6559" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6559" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6559" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6560" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6560" s="9"/>
+      <c r="C6560" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6561" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B6561" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6561" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6562" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6562" s="9"/>
+      <c r="C6562" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6563" s="8"/>
+      <c r="B6563" s="9"/>
+      <c r="C6563" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6564" s="8"/>
+      <c r="B6564" s="9"/>
+      <c r="C6564" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6565" s="8"/>
+      <c r="B6565" s="9"/>
+      <c r="C6565" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6566" s="8"/>
+      <c r="B6566" s="9"/>
+      <c r="C6566" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6567" s="8"/>
+      <c r="B6567" s="9"/>
+      <c r="C6567" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6568" s="8"/>
+      <c r="B6568" s="9"/>
+      <c r="C6568" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6569" s="8"/>
+      <c r="B6569" s="9"/>
+      <c r="C6569" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6570" s="8"/>
+      <c r="B6570" s="9"/>
+      <c r="C6570" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6571" s="8"/>
+      <c r="B6571" s="9"/>
+      <c r="C6571" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6572" s="8"/>
+      <c r="B6572" s="9"/>
+      <c r="C6572" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6573" s="8"/>
+      <c r="B6573" s="9"/>
+      <c r="C6573" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6574" s="8"/>
+      <c r="B6574" s="9"/>
+      <c r="C6574" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6575" s="8"/>
+      <c r="B6575" s="9"/>
+      <c r="C6575" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6576" s="8"/>
+      <c r="B6576" s="9"/>
+      <c r="C6576" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6577" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6577" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6577" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6578" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6578" s="20"/>
+      <c r="C6578" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="80">
+  <mergeCells count="85">
+    <mergeCell ref="C6031:C6032"/>
+    <mergeCell ref="C6147:C6148"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6503:C6504"/>
     <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="B6020:C6020"/>
     <mergeCell ref="B5607:C5607"/>
     <mergeCell ref="B5430:C5430"/>
     <mergeCell ref="B5489:C5489"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94886885-B220-4532-9DAD-FCA78D6CA6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228D394-E0DD-4A0C-8CED-D52FD7D6F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -6854,6 +6854,12 @@
     <t>PLA (68)</t>
   </si>
   <si>
+    <t>ADC (69)</t>
+  </si>
+  <si>
+    <t>ROR (6A)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Set </t>
     </r>
@@ -6866,6 +6872,27 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -6876,6 +6903,375 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">.L &amp; $01). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL (6B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (6C)</t>
+  </si>
+  <si>
+    <t>Absolute Indirect</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
+    <t>ADC (6D)</t>
+  </si>
+  <si>
+    <t>ROR (6E)</t>
+  </si>
+  <si>
+    <t>ADC (6F)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">.L to Operand.L. Set </t>
     </r>
     <r>
@@ -6960,509 +7356,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.L. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>ADC (69)</t>
-  </si>
-  <si>
-    <t>ROR (6A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $01). Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 1) | (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>.L.</t>
     </r>
-  </si>
-  <si>
-    <t>RTL (6B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Store as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L | $0100)+3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <t>JMP (6C)</t>
-  </si>
-  <si>
-    <t>Absolute Indirect</t>
-  </si>
-  <si>
-    <t>Read Pointer</t>
-  </si>
-  <si>
-    <t>Read Pointer + 1</t>
-  </si>
-  <si>
-    <t>ADC (6D)</t>
-  </si>
-  <si>
-    <t>ROR (6E)</t>
-  </si>
-  <si>
-    <t>ADC (6F)</t>
   </si>
 </sst>
 </file>
@@ -23938,36 +23833,31 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B6147" s="9"/>
-      <c r="C6147" s="35" t="s">
-        <v>315</v>
+      <c r="C6147" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6148" s="8"/>
-      <c r="B6148" s="9"/>
-      <c r="C6148" s="35"/>
+      <c r="A6148" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6148" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6148" s="10" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6149" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="B6149" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6149" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6150" s="19" t="s">
+      <c r="A6149" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B6150" s="20"/>
-      <c r="C6150" s="22"/>
+      <c r="B6149" s="20"/>
+      <c r="C6149" s="22"/>
     </row>
     <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6196" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B6196" s="2" t="s">
         <v>22</v>
@@ -24152,7 +24042,7 @@
     </row>
     <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6255" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B6255" s="2" t="s">
         <v>22</v>
@@ -24216,7 +24106,7 @@
       </c>
       <c r="B6261" s="9"/>
       <c r="C6261" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24239,7 +24129,7 @@
     </row>
     <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6314" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B6314" s="2" t="s">
         <v>6</v>
@@ -24319,7 +24209,7 @@
         <v>3.2</v>
       </c>
       <c r="B6323" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C6323" s="10" t="s">
         <v>180</v>
@@ -24337,7 +24227,7 @@
         <v>4.2</v>
       </c>
       <c r="B6325" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C6325" s="10" t="s">
         <v>45</v>
@@ -24355,10 +24245,10 @@
         <v>5.2</v>
       </c>
       <c r="B6327" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6327" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24367,7 +24257,7 @@
       </c>
       <c r="B6328" s="9"/>
       <c r="C6328" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24390,7 +24280,7 @@
     </row>
     <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B6373" s="2" t="s">
         <v>19</v>
@@ -24402,7 +24292,7 @@
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="4"/>
       <c r="B6374" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6374" s="25"/>
     </row>
@@ -24482,7 +24372,7 @@
         <v>3.2</v>
       </c>
       <c r="B6382" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C6382" s="10" t="s">
         <v>16</v>
@@ -24500,7 +24390,7 @@
         <v>4.2</v>
       </c>
       <c r="B6384" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C6384" s="10" t="s">
         <v>278</v>
@@ -24535,7 +24425,7 @@
     </row>
     <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6432" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B6432" s="2" t="s">
         <v>24</v>
@@ -24760,7 +24650,7 @@
     </row>
     <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6491" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B6491" s="2" t="s">
         <v>6</v>
@@ -24928,7 +24818,7 @@
     </row>
     <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6550" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B6550" s="2" t="s">
         <v>19</v>
@@ -25172,9 +25062,8 @@
       <c r="C6578" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="84">
     <mergeCell ref="C6031:C6032"/>
-    <mergeCell ref="C6147:C6148"/>
     <mergeCell ref="B6492:C6492"/>
     <mergeCell ref="C6503:C6504"/>
     <mergeCell ref="B5725:C5725"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0228D394-E0DD-4A0C-8CED-D52FD7D6F380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC99B2E1-C349-4ECD-AFA6-2A029381FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -7232,9 +7232,6 @@
     <t>JMP (6C)</t>
   </si>
   <si>
-    <t>Absolute Indirect</t>
-  </si>
-  <si>
     <t>Read Pointer</t>
   </si>
   <si>
@@ -7358,6 +7355,9 @@
       </rPr>
       <t>.L.</t>
     </r>
+  </si>
+  <si>
+    <t>Absolute Indirect (Jump)</t>
   </si>
 </sst>
 </file>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="B6147" s="9"/>
       <c r="C6147" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24292,7 +24292,7 @@
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="4"/>
       <c r="B6374" s="24" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C6374" s="25"/>
     </row>
@@ -24372,7 +24372,7 @@
         <v>3.2</v>
       </c>
       <c r="B6382" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6382" s="10" t="s">
         <v>16</v>
@@ -24390,7 +24390,7 @@
         <v>4.2</v>
       </c>
       <c r="B6384" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C6384" s="10" t="s">
         <v>278</v>
@@ -24425,7 +24425,7 @@
     </row>
     <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6432" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B6432" s="2" t="s">
         <v>24</v>
@@ -24650,7 +24650,7 @@
     </row>
     <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6491" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B6491" s="2" t="s">
         <v>6</v>
@@ -24818,7 +24818,7 @@
     </row>
     <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6550" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B6550" s="2" t="s">
         <v>19</v>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC99B2E1-C349-4ECD-AFA6-2A029381FD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8EE092-7680-4139-8BF2-AC9B5B0A7A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$6608</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$6907</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="337">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -4957,8 +4957,345 @@
     <t>EOR (49)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"> Inc. </t>
+    <t>LSR (4A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;&gt;= 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*** Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*** Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*** Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L-2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
     </r>
     <r>
       <rPr>
@@ -4979,6 +5316,1941 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>. Set Address to Pointer + (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L | $100). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Address to Pointer + (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L | $100.) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (4C)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Address.</t>
+    </r>
+  </si>
+  <si>
+    <t>PHK (4B)</t>
+  </si>
+  <si>
+    <t>EOR (4D)</t>
+  </si>
+  <si>
+    <t>LSR (4E)</t>
+  </si>
+  <si>
+    <t>EOR (4F)</t>
+  </si>
+  <si>
+    <t>BVC (50)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>Block Move (Positive)</t>
+  </si>
+  <si>
+    <t>EOR (51)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If Orig.H == Pointer.H, skip 2 half-cycles. Bank = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + (Tmp &gt;&gt; 16).</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (52)</t>
+  </si>
+  <si>
+    <t>EOR (53)</t>
+  </si>
+  <si>
+    <t>MVN (54)</t>
+  </si>
+  <si>
+    <t>Block Move (Negative)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag is set, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, otherwise perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1 and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not $FFFF, perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 3.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (55)</t>
+  </si>
+  <si>
+    <t>LSR (56)</t>
+  </si>
+  <si>
+    <t>EOR (57)</t>
+  </si>
+  <si>
+    <t>CLI (58)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (59)</t>
+  </si>
+  <si>
+    <t>PHY (5A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCD (5B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>JML (5C)</t>
+  </si>
+  <si>
+    <t>Store as Address.H.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (5D)</t>
+  </si>
+  <si>
+    <t>Pointer = ui16(Tmp). If Orig.H == Pointer.H, skip 2 half-cycles.</t>
+  </si>
+  <si>
+    <t>LSR (5E)</t>
+  </si>
+  <si>
+    <t>EOR (5F)</t>
+  </si>
+  <si>
+    <t>RTS (60)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1).</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (Lo &gt; 9) Lo += 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CarryToHi = Lo &gt; $0F ? 1 : 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (HiSum &gt; 9) HiSum += 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Result = ui8(((HiSum &amp; 0x0F) &lt;&lt; 4) | (Lo &amp; $0F)).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag == 0:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result &gt; $FF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag == 1:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L) + ui16(Operand) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui8(Result). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result == $00. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Lo = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; 0x0F) + ui16(Operand &amp; 0x0F) + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  HiSum = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) + ui16(Operand &gt;&gt; 4) + CarryToHi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = HiSum &gt; $0F.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result == $00. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>PER (62)</t>
+  </si>
+  <si>
+    <t>Push Operand.H onto stack.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Operand to Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (63)</t>
+  </si>
+  <si>
+    <t>STZ (64)</t>
+  </si>
+  <si>
+    <t>Direct (Write)</t>
+  </si>
+  <si>
+    <t>Write 0.</t>
+  </si>
+  <si>
+    <t>ADC (65)</t>
+  </si>
+  <si>
+    <t>ROR (66)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $01). Perform Operand.L = (Operand.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (67)</t>
+  </si>
+  <si>
+    <t>PLA (68)</t>
+  </si>
+  <si>
+    <t>ADC (69)</t>
+  </si>
+  <si>
+    <t>ROR (6A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $01). Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 1) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>RTL (6B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L | $0100)+3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L+1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (6C)</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
+    <t>ADC (6D)</t>
+  </si>
+  <si>
+    <t>ROR (6E)</t>
+  </si>
+  <si>
+    <t>ADC (6F)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>Absolute Indirect (Jump)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">. Perform </t>
     </r>
     <r>
@@ -5088,341 +7360,7 @@
     </r>
   </si>
   <si>
-    <t>LSR (4A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $01). Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &gt;&gt;= 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*** Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+0) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*** Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L-1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>*** Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L-2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+0) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L-1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L-2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+0) | $0100</t>
-    </r>
+    <t>BVS (70)</t>
   </si>
   <si>
     <r>
@@ -5447,191 +7385,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Set Address to Pointer + (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L | $100). </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Set Address to Pointer + (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L | $100.) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>JMP (4C)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Address.</t>
-    </r>
-  </si>
-  <si>
-    <t>PHK (4B)</t>
-  </si>
-  <si>
-    <t>EOR (4D)</t>
-  </si>
-  <si>
-    <t>LSR (4E)</t>
-  </si>
-  <si>
-    <t>EOR (4F)</t>
-  </si>
-  <si>
-    <t>BVC (50)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">. Decide to branch if </t>
     </r>
     <r>
@@ -5653,1711 +7406,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> is 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>Block Move (Positive)</t>
-  </si>
-  <si>
-    <t>EOR (51)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If Orig.H == Pointer.H, skip 2 half-cycles. Bank = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + (Tmp &gt;&gt; 16).</t>
-    </r>
-  </si>
-  <si>
-    <t>EOR (52)</t>
-  </si>
-  <si>
-    <t>EOR (53)</t>
-  </si>
-  <si>
-    <t>MVN (54)</t>
-  </si>
-  <si>
-    <t>Block Move (Negative)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -= 1. If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag is set, perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L += 1 and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L += 1, otherwise perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> += 1 and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> += 1. If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is not $FFFF, perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -= 3.</t>
-    </r>
-  </si>
-  <si>
-    <t>EOR (55)</t>
-  </si>
-  <si>
-    <t>LSR (56)</t>
-  </si>
-  <si>
-    <t>EOR (57)</t>
-  </si>
-  <si>
-    <t>CLI (58)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sets the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>EOR (59)</t>
-  </si>
-  <si>
-    <t>PHY (5A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Push </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L onto stack.</t>
-    </r>
-  </si>
-  <si>
-    <t>TCD (5B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>JML (5C)</t>
-  </si>
-  <si>
-    <t>Store as Address.H.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Copy Address to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Copy Bank to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>EOR (5D)</t>
-  </si>
-  <si>
-    <t>Pointer = ui16(Tmp). If Orig.H == Pointer.H, skip 2 half-cycles.</t>
-  </si>
-  <si>
-    <t>LSR (5E)</t>
-  </si>
-  <si>
-    <t>EOR (5F)</t>
-  </si>
-  <si>
-    <t>RTS (60)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1).</t>
-    </r>
-  </si>
-  <si>
-    <t>ADC (61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (Lo &gt; 9) Lo += 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  CarryToHi = Lo &gt; $0F ? 1 : 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (HiSum &gt; 9) HiSum += 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Result = ui8(((HiSum &amp; 0x0F) &lt;&lt; 4) | (Lo &amp; $0F)).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag == 0:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = Result &gt; $FF.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag == 1:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Result = ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L) + ui16(Operand) + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (~(ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Result = ui8(Result). </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = Result == $00. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Lo = ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; 0x0F) + ui16(Operand &amp; 0x0F) + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  HiSum = ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) + ui16(Operand &gt;&gt; 4) + CarryToHi.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (~((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = HiSum &gt; $0F.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = Result == $00. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Result &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>PER (62)</t>
-  </si>
-  <si>
-    <t>Push Operand.H onto stack.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set Operand to Operand + </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 2.</t>
-    </r>
-  </si>
-  <si>
-    <t>ADC (63)</t>
-  </si>
-  <si>
-    <t>STZ (64)</t>
-  </si>
-  <si>
-    <t>Direct (Write)</t>
-  </si>
-  <si>
-    <t>Write 0.</t>
-  </si>
-  <si>
-    <t>ADC (65)</t>
-  </si>
-  <si>
-    <t>ROR (66)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $01). Perform Operand.L = (Operand.L &gt;&gt; 1) | (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>ADC (67)</t>
-  </si>
-  <si>
-    <t>PLA (68)</t>
-  </si>
-  <si>
-    <t>ADC (69)</t>
-  </si>
-  <si>
-    <t>ROR (6A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $01). Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 1) | (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;&lt; 7). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>RTL (6B)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Store as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L | $0100)+3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <t>JMP (6C)</t>
-  </si>
-  <si>
-    <t>Read Pointer</t>
-  </si>
-  <si>
-    <t>Read Pointer + 1</t>
-  </si>
-  <si>
-    <t>ADC (6D)</t>
-  </si>
-  <si>
-    <t>ROR (6E)</t>
-  </si>
-  <si>
-    <t>ADC (6F)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L to Operand.L. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>Absolute Indirect (Jump)</t>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (71)</t>
+  </si>
+  <si>
+    <t>ADC (72)</t>
+  </si>
+  <si>
+    <t>ADC (73)</t>
   </si>
 </sst>
 </file>
@@ -7958,7 +8017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C6578"/>
+  <dimension ref="A1:C6820"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -8041,7 +8100,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>35</v>
@@ -8059,7 +8118,7 @@
         <v>3.2</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>36</v>
@@ -8100,7 +8159,7 @@
         <v>4.2</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>59</v>
@@ -8458,7 +8517,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>35</v>
@@ -8476,7 +8535,7 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>36</v>
@@ -8496,7 +8555,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>62</v>
@@ -8670,7 +8729,7 @@
       </c>
       <c r="B184" s="9"/>
       <c r="C184" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9693,7 +9752,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B657" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C657" s="10" t="s">
         <v>75</v>
@@ -10901,7 +10960,7 @@
       </c>
       <c r="B1128" s="9"/>
       <c r="C1128" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12952,7 +13011,7 @@
         <v>4.2</v>
       </c>
       <c r="B1900" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C1900" s="10" t="s">
         <v>35</v>
@@ -12970,7 +13029,7 @@
         <v>5.2</v>
       </c>
       <c r="B1902" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C1902" s="10" t="s">
         <v>36</v>
@@ -13272,7 +13331,7 @@
         <v>3.2</v>
       </c>
       <c r="B2016" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C2016" s="10" t="s">
         <v>57</v>
@@ -13290,7 +13349,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2018" s="14" t="s">
         <v>73</v>
@@ -18130,7 +18189,7 @@
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
       <c r="B4014" s="31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C4014" s="32"/>
     </row>
@@ -18182,7 +18241,7 @@
       </c>
       <c r="B4019" s="9"/>
       <c r="C4019" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18925,7 +18984,7 @@
       </c>
       <c r="B4314" s="9"/>
       <c r="C4314" s="10" t="s">
-        <v>238</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18948,7 +19007,7 @@
     </row>
     <row r="4367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4367" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B4367" s="2" t="s">
         <v>22</v>
@@ -19012,7 +19071,7 @@
       </c>
       <c r="B4373" s="9"/>
       <c r="C4373" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19035,7 +19094,7 @@
     </row>
     <row r="4426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4426" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4426" s="2" t="s">
         <v>15</v>
@@ -19136,7 +19195,7 @@
     </row>
     <row r="4485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4485" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4485" s="2" t="s">
         <v>15</v>
@@ -19220,7 +19279,7 @@
       </c>
       <c r="B4493" s="9"/>
       <c r="C4493" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19243,7 +19302,7 @@
     </row>
     <row r="4544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4544" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4544" s="2" t="s">
         <v>24</v>
@@ -19370,7 +19429,7 @@
     </row>
     <row r="4603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4603" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B4603" s="2" t="s">
         <v>6</v>
@@ -19538,7 +19597,7 @@
     </row>
     <row r="4662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4662" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4662" s="2" t="s">
         <v>19</v>
@@ -19685,7 +19744,7 @@
     </row>
     <row r="4721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4721" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B4721" s="2" t="s">
         <v>22</v>
@@ -19729,7 +19788,7 @@
       </c>
       <c r="B4725" s="9"/>
       <c r="C4725" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19811,7 +19870,7 @@
     </row>
     <row r="4780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4780" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4780" s="2" t="s">
         <v>19</v>
@@ -19950,7 +20009,7 @@
       <c r="A4795" s="8"/>
       <c r="B4795" s="9"/>
       <c r="C4795" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20007,7 +20066,7 @@
     </row>
     <row r="4839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4839" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B4839" s="2" t="s">
         <v>19</v>
@@ -20166,7 +20225,7 @@
     </row>
     <row r="4898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4898" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B4898" s="2" t="s">
         <v>98</v>
@@ -20353,7 +20412,7 @@
     </row>
     <row r="4957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4957" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B4957" s="2" t="s">
         <v>98</v>
@@ -20365,7 +20424,7 @@
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="4"/>
       <c r="B4958" s="24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4958" s="25"/>
     </row>
@@ -20417,7 +20476,7 @@
       </c>
       <c r="B4963" s="9"/>
       <c r="C4963" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20475,7 +20534,7 @@
       </c>
       <c r="B4969" s="9"/>
       <c r="C4969" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20531,7 +20590,7 @@
     </row>
     <row r="5016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5016" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B5016" s="2" t="s">
         <v>24</v>
@@ -20673,7 +20732,7 @@
     </row>
     <row r="5075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5075" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5075" s="2" t="s">
         <v>6</v>
@@ -20856,7 +20915,7 @@
     </row>
     <row r="5134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5134" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B5134" s="2" t="s">
         <v>6</v>
@@ -21069,7 +21128,7 @@
     </row>
     <row r="5193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5193" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B5193" s="2" t="s">
         <v>22</v>
@@ -21133,7 +21192,7 @@
       </c>
       <c r="B5199" s="9"/>
       <c r="C5199" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21156,7 +21215,7 @@
     </row>
     <row r="5252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5252" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B5252" s="2" t="s">
         <v>24</v>
@@ -21325,7 +21384,7 @@
     </row>
     <row r="5311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5311" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B5311" s="2" t="s">
         <v>15</v>
@@ -21394,7 +21453,7 @@
         <v>235</v>
       </c>
       <c r="C5318" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21426,7 +21485,7 @@
     </row>
     <row r="5370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5370" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B5370" s="2" t="s">
         <v>22</v>
@@ -21490,7 +21549,7 @@
       </c>
       <c r="B5376" s="9"/>
       <c r="C5376" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21513,7 +21572,7 @@
     </row>
     <row r="5429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5429" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B5429" s="2" t="s">
         <v>24</v>
@@ -21588,7 +21647,7 @@
         <v>72</v>
       </c>
       <c r="C5436" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21617,7 +21676,7 @@
       </c>
       <c r="B5439" s="9"/>
       <c r="C5439" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21640,7 +21699,7 @@
     </row>
     <row r="5488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5488" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B5488" s="2" t="s">
         <v>24</v>
@@ -21738,7 +21797,7 @@
       <c r="A5498" s="8"/>
       <c r="B5498" s="9"/>
       <c r="C5498" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21802,7 +21861,7 @@
     </row>
     <row r="5547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5547" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B5547" s="2" t="s">
         <v>98</v>
@@ -21998,7 +22057,7 @@
     </row>
     <row r="5606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5606" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B5606" s="2" t="s">
         <v>19</v>
@@ -22159,7 +22218,7 @@
     </row>
     <row r="5665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5665" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5665" s="2" t="s">
         <v>6</v>
@@ -22285,7 +22344,7 @@
       </c>
       <c r="B5679" s="9"/>
       <c r="C5679" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22308,7 +22367,7 @@
     </row>
     <row r="5724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5724" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B5724" s="2" t="s">
         <v>6</v>
@@ -22460,105 +22519,105 @@
       </c>
       <c r="B5740" s="9"/>
       <c r="C5740" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5741" s="8"/>
       <c r="B5741" s="9"/>
       <c r="C5741" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5742" s="8"/>
       <c r="B5742" s="9"/>
       <c r="C5742" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5743" s="8"/>
       <c r="B5743" s="9"/>
       <c r="C5743" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5744" s="8"/>
       <c r="B5744" s="9"/>
       <c r="C5744" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5745" s="8"/>
       <c r="B5745" s="9"/>
       <c r="C5745" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5746" s="8"/>
       <c r="B5746" s="9"/>
       <c r="C5746" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5747" s="8"/>
       <c r="B5747" s="9"/>
       <c r="C5747" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5748" s="8"/>
       <c r="B5748" s="9"/>
       <c r="C5748" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5749" s="8"/>
       <c r="B5749" s="9"/>
       <c r="C5749" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5750" s="8"/>
       <c r="B5750" s="9"/>
       <c r="C5750" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5751" s="8"/>
       <c r="B5751" s="9"/>
       <c r="C5751" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5752" s="8"/>
       <c r="B5752" s="9"/>
       <c r="C5752" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5753" s="8"/>
       <c r="B5753" s="9"/>
       <c r="C5753" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5754" s="8"/>
       <c r="B5754" s="9"/>
       <c r="C5754" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22581,7 +22640,7 @@
     </row>
     <row r="5783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5783" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B5783" s="2" t="s">
         <v>6</v>
@@ -22665,7 +22724,7 @@
       </c>
       <c r="B5791" s="9"/>
       <c r="C5791" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22690,7 +22749,7 @@
         <v>235</v>
       </c>
       <c r="C5794" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22717,7 +22776,7 @@
       </c>
       <c r="B5797" s="9"/>
       <c r="C5797" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22740,7 +22799,7 @@
     </row>
     <row r="5842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5842" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B5842" s="2" t="s">
         <v>24</v>
@@ -22838,105 +22897,105 @@
       </c>
       <c r="B5852" s="9"/>
       <c r="C5852" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5853" s="8"/>
       <c r="B5853" s="9"/>
       <c r="C5853" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5854" s="8"/>
       <c r="B5854" s="9"/>
       <c r="C5854" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5855" s="8"/>
       <c r="B5855" s="9"/>
       <c r="C5855" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5856" s="8"/>
       <c r="B5856" s="9"/>
       <c r="C5856" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5857" s="8"/>
       <c r="B5857" s="9"/>
       <c r="C5857" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5858" s="8"/>
       <c r="B5858" s="9"/>
       <c r="C5858" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5859" s="8"/>
       <c r="B5859" s="9"/>
       <c r="C5859" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5860" s="8"/>
       <c r="B5860" s="9"/>
       <c r="C5860" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5861" s="8"/>
       <c r="B5861" s="9"/>
       <c r="C5861" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5862" s="8"/>
       <c r="B5862" s="9"/>
       <c r="C5862" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5863" s="8"/>
       <c r="B5863" s="9"/>
       <c r="C5863" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5864" s="8"/>
       <c r="B5864" s="9"/>
       <c r="C5864" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5865" s="8"/>
       <c r="B5865" s="9"/>
       <c r="C5865" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5866" s="8"/>
       <c r="B5866" s="9"/>
       <c r="C5866" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22959,7 +23018,7 @@
     </row>
     <row r="5901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5901" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B5901" s="2" t="s">
         <v>15</v>
@@ -22971,7 +23030,7 @@
     <row r="5902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5902" s="4"/>
       <c r="B5902" s="24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C5902" s="25"/>
     </row>
@@ -23050,7 +23109,7 @@
         <v>46</v>
       </c>
       <c r="C5910" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23080,7 +23139,7 @@
     </row>
     <row r="5960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5960" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B5960" s="2" t="s">
         <v>15</v>
@@ -23180,105 +23239,105 @@
       </c>
       <c r="B5970" s="9"/>
       <c r="C5970" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5971" s="8"/>
       <c r="B5971" s="9"/>
       <c r="C5971" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5972" s="8"/>
       <c r="B5972" s="9"/>
       <c r="C5972" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5973" s="8"/>
       <c r="B5973" s="9"/>
       <c r="C5973" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5974" s="8"/>
       <c r="B5974" s="9"/>
       <c r="C5974" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5975" s="8"/>
       <c r="B5975" s="9"/>
       <c r="C5975" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5976" s="8"/>
       <c r="B5976" s="9"/>
       <c r="C5976" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5977" s="8"/>
       <c r="B5977" s="9"/>
       <c r="C5977" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5978" s="8"/>
       <c r="B5978" s="9"/>
       <c r="C5978" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5979" s="8"/>
       <c r="B5979" s="9"/>
       <c r="C5979" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5980" s="8"/>
       <c r="B5980" s="9"/>
       <c r="C5980" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5981" s="8"/>
       <c r="B5981" s="9"/>
       <c r="C5981" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5982" s="8"/>
       <c r="B5982" s="9"/>
       <c r="C5982" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5983" s="8"/>
       <c r="B5983" s="9"/>
       <c r="C5983" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5984" s="8"/>
       <c r="B5984" s="9"/>
       <c r="C5984" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23301,7 +23360,7 @@
     </row>
     <row r="6019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6019" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B6019" s="2" t="s">
         <v>19</v>
@@ -23419,7 +23478,7 @@
       </c>
       <c r="B6031" s="9"/>
       <c r="C6031" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23465,7 +23524,7 @@
     </row>
     <row r="6078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6078" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B6078" s="2" t="s">
         <v>6</v>
@@ -23619,105 +23678,105 @@
       </c>
       <c r="B6094" s="9"/>
       <c r="C6094" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6095" s="8"/>
       <c r="B6095" s="9"/>
       <c r="C6095" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6096" s="8"/>
       <c r="B6096" s="9"/>
       <c r="C6096" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6097" s="8"/>
       <c r="B6097" s="9"/>
       <c r="C6097" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6098" s="8"/>
       <c r="B6098" s="9"/>
       <c r="C6098" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6099" s="8"/>
       <c r="B6099" s="9"/>
       <c r="C6099" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6100" s="8"/>
       <c r="B6100" s="9"/>
       <c r="C6100" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6101" s="8"/>
       <c r="B6101" s="9"/>
       <c r="C6101" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6102" s="8"/>
       <c r="B6102" s="9"/>
       <c r="C6102" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6103" s="8"/>
       <c r="B6103" s="9"/>
       <c r="C6103" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6104" s="8"/>
       <c r="B6104" s="9"/>
       <c r="C6104" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6105" s="8"/>
       <c r="B6105" s="9"/>
       <c r="C6105" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6106" s="8"/>
       <c r="B6106" s="9"/>
       <c r="C6106" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6107" s="8"/>
       <c r="B6107" s="9"/>
       <c r="C6107" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6108" s="8"/>
       <c r="B6108" s="9"/>
       <c r="C6108" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23740,7 +23799,7 @@
     </row>
     <row r="6137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6137" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B6137" s="2" t="s">
         <v>24</v>
@@ -23822,7 +23881,7 @@
         <v>3.2</v>
       </c>
       <c r="B6146" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C6146" s="10" t="s">
         <v>180</v>
@@ -23834,7 +23893,7 @@
       </c>
       <c r="B6147" s="9"/>
       <c r="C6147" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23857,7 +23916,7 @@
     </row>
     <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6196" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B6196" s="2" t="s">
         <v>22</v>
@@ -23921,105 +23980,105 @@
       </c>
       <c r="B6202" s="9"/>
       <c r="C6202" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6203" s="8"/>
       <c r="B6203" s="9"/>
       <c r="C6203" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6204" s="8"/>
       <c r="B6204" s="9"/>
       <c r="C6204" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6205" s="8"/>
       <c r="B6205" s="9"/>
       <c r="C6205" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6206" s="8"/>
       <c r="B6206" s="9"/>
       <c r="C6206" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6207" s="8"/>
       <c r="B6207" s="9"/>
       <c r="C6207" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6208" s="8"/>
       <c r="B6208" s="9"/>
       <c r="C6208" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6209" s="8"/>
       <c r="B6209" s="9"/>
       <c r="C6209" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6210" s="8"/>
       <c r="B6210" s="9"/>
       <c r="C6210" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6211" s="8"/>
       <c r="B6211" s="9"/>
       <c r="C6211" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6212" s="8"/>
       <c r="B6212" s="9"/>
       <c r="C6212" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6213" s="8"/>
       <c r="B6213" s="9"/>
       <c r="C6213" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6214" s="8"/>
       <c r="B6214" s="9"/>
       <c r="C6214" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6215" s="8"/>
       <c r="B6215" s="9"/>
       <c r="C6215" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6216" s="8"/>
       <c r="B6216" s="9"/>
       <c r="C6216" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24042,7 +24101,7 @@
     </row>
     <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6255" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B6255" s="2" t="s">
         <v>22</v>
@@ -24106,7 +24165,7 @@
       </c>
       <c r="B6261" s="9"/>
       <c r="C6261" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24129,7 +24188,7 @@
     </row>
     <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6314" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B6314" s="2" t="s">
         <v>6</v>
@@ -24209,7 +24268,7 @@
         <v>3.2</v>
       </c>
       <c r="B6323" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C6323" s="10" t="s">
         <v>180</v>
@@ -24227,7 +24286,7 @@
         <v>4.2</v>
       </c>
       <c r="B6325" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6325" s="10" t="s">
         <v>45</v>
@@ -24245,10 +24304,10 @@
         <v>5.2</v>
       </c>
       <c r="B6327" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C6327" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24257,7 +24316,7 @@
       </c>
       <c r="B6328" s="9"/>
       <c r="C6328" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24280,7 +24339,7 @@
     </row>
     <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B6373" s="2" t="s">
         <v>19</v>
@@ -24292,7 +24351,7 @@
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="4"/>
       <c r="B6374" s="24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C6374" s="25"/>
     </row>
@@ -24372,7 +24431,7 @@
         <v>3.2</v>
       </c>
       <c r="B6382" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6382" s="10" t="s">
         <v>16</v>
@@ -24390,10 +24449,10 @@
         <v>4.2</v>
       </c>
       <c r="B6384" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6384" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24402,7 +24461,7 @@
       </c>
       <c r="B6385" s="9"/>
       <c r="C6385" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24425,7 +24484,7 @@
     </row>
     <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6432" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6432" s="2" t="s">
         <v>24</v>
@@ -24500,7 +24559,7 @@
         <v>72</v>
       </c>
       <c r="C6439" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24529,105 +24588,105 @@
       </c>
       <c r="B6442" s="9"/>
       <c r="C6442" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6443" s="8"/>
       <c r="B6443" s="9"/>
       <c r="C6443" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6444" s="8"/>
       <c r="B6444" s="9"/>
       <c r="C6444" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6445" s="8"/>
       <c r="B6445" s="9"/>
       <c r="C6445" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6446" s="8"/>
       <c r="B6446" s="9"/>
       <c r="C6446" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6447" s="8"/>
       <c r="B6447" s="9"/>
       <c r="C6447" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6448" s="8"/>
       <c r="B6448" s="9"/>
       <c r="C6448" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6449" s="8"/>
       <c r="B6449" s="9"/>
       <c r="C6449" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6450" s="8"/>
       <c r="B6450" s="9"/>
       <c r="C6450" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6451" s="8"/>
       <c r="B6451" s="9"/>
       <c r="C6451" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6452" s="8"/>
       <c r="B6452" s="9"/>
       <c r="C6452" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6453" s="8"/>
       <c r="B6453" s="9"/>
       <c r="C6453" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6454" s="8"/>
       <c r="B6454" s="9"/>
       <c r="C6454" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6455" s="8"/>
       <c r="B6455" s="9"/>
       <c r="C6455" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6456" s="8"/>
       <c r="B6456" s="9"/>
       <c r="C6456" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24650,7 +24709,7 @@
     </row>
     <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6491" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B6491" s="2" t="s">
         <v>6</v>
@@ -24725,7 +24784,7 @@
         <v>72</v>
       </c>
       <c r="C6498" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24772,7 +24831,7 @@
       </c>
       <c r="B6503" s="9"/>
       <c r="C6503" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24818,7 +24877,7 @@
     </row>
     <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6550" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B6550" s="2" t="s">
         <v>19</v>
@@ -24893,7 +24952,7 @@
         <v>72</v>
       </c>
       <c r="C6557" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24942,105 +25001,105 @@
       </c>
       <c r="B6562" s="9"/>
       <c r="C6562" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6563" s="8"/>
       <c r="B6563" s="9"/>
       <c r="C6563" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6564" s="8"/>
       <c r="B6564" s="9"/>
       <c r="C6564" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6565" s="8"/>
       <c r="B6565" s="9"/>
       <c r="C6565" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6566" s="8"/>
       <c r="B6566" s="9"/>
       <c r="C6566" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6567" s="8"/>
       <c r="B6567" s="9"/>
       <c r="C6567" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6568" s="8"/>
       <c r="B6568" s="9"/>
       <c r="C6568" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6569" s="8"/>
       <c r="B6569" s="9"/>
       <c r="C6569" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6570" s="8"/>
       <c r="B6570" s="9"/>
       <c r="C6570" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6571" s="8"/>
       <c r="B6571" s="9"/>
       <c r="C6571" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6572" s="8"/>
       <c r="B6572" s="9"/>
       <c r="C6572" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6573" s="8"/>
       <c r="B6573" s="9"/>
       <c r="C6573" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6574" s="8"/>
       <c r="B6574" s="9"/>
       <c r="C6574" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6575" s="8"/>
       <c r="B6575" s="9"/>
       <c r="C6575" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6576" s="8"/>
       <c r="B6576" s="9"/>
       <c r="C6576" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25061,11 +25120,983 @@
       <c r="B6578" s="20"/>
       <c r="C6578" s="22"/>
     </row>
+    <row r="6609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6609" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6609" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6609" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6610" s="4"/>
+      <c r="B6610" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6610" s="6"/>
+    </row>
+    <row r="6611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6611" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6611" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6611" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6612" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6612" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6612" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6613" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6613" s="9"/>
+      <c r="C6613" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6614" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B6614" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6614" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6615" s="8"/>
+      <c r="B6615" s="9"/>
+      <c r="C6615" s="30"/>
+    </row>
+    <row r="6616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6616" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6616" s="9"/>
+      <c r="C6616" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6617" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6617" s="9"/>
+      <c r="C6617" s="10"/>
+    </row>
+    <row r="6618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6618" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6618" s="9"/>
+      <c r="C6618" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6619" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B6619" s="9"/>
+      <c r="C6619" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6620" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6620" s="9"/>
+      <c r="C6620" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6621" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6621" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6621" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6622" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6622" s="20"/>
+      <c r="C6622" s="21"/>
+    </row>
+    <row r="6668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6668" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6668" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6668" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6669" s="4"/>
+      <c r="B6669" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6669" s="32"/>
+    </row>
+    <row r="6670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6670" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6670" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6670" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6671" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6671" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6671" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6672" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6672" s="9"/>
+      <c r="C6672" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6673" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6673" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6673" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6674" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B6674" s="16"/>
+      <c r="C6674" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6675" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6675" s="16"/>
+      <c r="C6675" s="23"/>
+    </row>
+    <row r="6676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6676" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6676" s="9"/>
+      <c r="C6676" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6677" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6677" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6677" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6678" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6678" s="9"/>
+      <c r="C6678" s="10"/>
+    </row>
+    <row r="6679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6679" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6679" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6679" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6680" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6680" s="9"/>
+      <c r="C6680" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6681" s="8"/>
+      <c r="B6681" s="9"/>
+      <c r="C6681" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6682" s="8"/>
+      <c r="B6682" s="9"/>
+      <c r="C6682" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6683" s="8"/>
+      <c r="B6683" s="9"/>
+      <c r="C6683" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6684" s="8"/>
+      <c r="B6684" s="9"/>
+      <c r="C6684" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6685" s="15">
+        <v>5.2</v>
+      </c>
+      <c r="B6685" s="16"/>
+      <c r="C6685" s="23"/>
+    </row>
+    <row r="6686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6686" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="B6686" s="16"/>
+      <c r="C6686" s="23"/>
+    </row>
+    <row r="6687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6687" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B6687" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6687" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6688" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6688" s="9"/>
+      <c r="C6688" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6689" s="8"/>
+      <c r="B6689" s="9"/>
+      <c r="C6689" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6690" s="8"/>
+      <c r="B6690" s="9"/>
+      <c r="C6690" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6691" s="8"/>
+      <c r="B6691" s="9"/>
+      <c r="C6691" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6692" s="8"/>
+      <c r="B6692" s="9"/>
+      <c r="C6692" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6693" s="8"/>
+      <c r="B6693" s="9"/>
+      <c r="C6693" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6694" s="8"/>
+      <c r="B6694" s="9"/>
+      <c r="C6694" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6695" s="8"/>
+      <c r="B6695" s="9"/>
+      <c r="C6695" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6696" s="8"/>
+      <c r="B6696" s="9"/>
+      <c r="C6696" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6697" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6697" s="8"/>
+      <c r="B6697" s="9"/>
+      <c r="C6697" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6698" s="8"/>
+      <c r="B6698" s="9"/>
+      <c r="C6698" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6699" s="8"/>
+      <c r="B6699" s="9"/>
+      <c r="C6699" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6700" s="8"/>
+      <c r="B6700" s="9"/>
+      <c r="C6700" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6701" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6701" s="8"/>
+      <c r="B6701" s="9"/>
+      <c r="C6701" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6702" s="8"/>
+      <c r="B6702" s="9"/>
+      <c r="C6702" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6703" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B6703" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6703" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6704" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6704" s="20"/>
+      <c r="C6704" s="22"/>
+    </row>
+    <row r="6727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6727" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B6727" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6727" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6728" s="4"/>
+      <c r="B6728" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6728" s="25"/>
+    </row>
+    <row r="6729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6729" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6729" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6729" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6730" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6730" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6730" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6731" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6731" s="9"/>
+      <c r="C6731" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6732" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6732" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6732" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6733" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B6733" s="16"/>
+      <c r="C6733" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6734" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6734" s="16"/>
+      <c r="C6734" s="23"/>
+    </row>
+    <row r="6735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6735" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6735" s="9"/>
+      <c r="C6735" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6736" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6736" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6736" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6737" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6737" s="9"/>
+      <c r="C6737" s="10"/>
+    </row>
+    <row r="6738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6738" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6738" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6738" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6739" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6739" s="9"/>
+      <c r="C6739" s="10"/>
+    </row>
+    <row r="6740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6740" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B6740" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6740" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6741" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6741" s="9"/>
+      <c r="C6741" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6742" s="8"/>
+      <c r="B6742" s="9"/>
+      <c r="C6742" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6743" s="8"/>
+      <c r="B6743" s="9"/>
+      <c r="C6743" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6744" s="8"/>
+      <c r="B6744" s="9"/>
+      <c r="C6744" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6745" s="8"/>
+      <c r="B6745" s="9"/>
+      <c r="C6745" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6746" s="8"/>
+      <c r="B6746" s="9"/>
+      <c r="C6746" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6747" s="8"/>
+      <c r="B6747" s="9"/>
+      <c r="C6747" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6748" s="8"/>
+      <c r="B6748" s="9"/>
+      <c r="C6748" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6749" s="8"/>
+      <c r="B6749" s="9"/>
+      <c r="C6749" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6750" s="8"/>
+      <c r="B6750" s="9"/>
+      <c r="C6750" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6751" s="8"/>
+      <c r="B6751" s="9"/>
+      <c r="C6751" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6752" s="8"/>
+      <c r="B6752" s="9"/>
+      <c r="C6752" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6753" s="8"/>
+      <c r="B6753" s="9"/>
+      <c r="C6753" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6754" s="8"/>
+      <c r="B6754" s="9"/>
+      <c r="C6754" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6755" s="8"/>
+      <c r="B6755" s="9"/>
+      <c r="C6755" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6756" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B6756" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6756" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6757" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6757" s="20"/>
+      <c r="C6757" s="22"/>
+    </row>
+    <row r="6786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6786" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6786" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6786" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6787" s="4"/>
+      <c r="B6787" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6787" s="32"/>
+    </row>
+    <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6788" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6788" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6788" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6789" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6789" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6789" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6790" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6790" s="9"/>
+      <c r="C6790" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6791" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6791" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6791" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6792" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6792" s="9"/>
+      <c r="C6792" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6793" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6793" s="9"/>
+      <c r="C6793" s="10"/>
+    </row>
+    <row r="6794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6794" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6794" s="9"/>
+      <c r="C6794" s="10"/>
+    </row>
+    <row r="6795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6795" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6795" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6795" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6796" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6796" s="9"/>
+      <c r="C6796" s="10"/>
+    </row>
+    <row r="6797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6797" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6797" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6797" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6798" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6798" s="9"/>
+      <c r="C6798" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6799" s="8"/>
+      <c r="B6799" s="9"/>
+      <c r="C6799" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6800" s="8"/>
+      <c r="B6800" s="9"/>
+      <c r="C6800" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6801" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6801" s="9"/>
+      <c r="C6801" s="10"/>
+    </row>
+    <row r="6802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6802" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6802" s="9"/>
+      <c r="C6802" s="10"/>
+    </row>
+    <row r="6803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6803" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B6803" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6803" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6804" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6804" s="9"/>
+      <c r="C6804" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6805" s="8"/>
+      <c r="B6805" s="9"/>
+      <c r="C6805" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6806" s="8"/>
+      <c r="B6806" s="9"/>
+      <c r="C6806" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6807" s="8"/>
+      <c r="B6807" s="9"/>
+      <c r="C6807" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6808" s="8"/>
+      <c r="B6808" s="9"/>
+      <c r="C6808" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6809" s="8"/>
+      <c r="B6809" s="9"/>
+      <c r="C6809" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6810" s="8"/>
+      <c r="B6810" s="9"/>
+      <c r="C6810" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6811" s="8"/>
+      <c r="B6811" s="9"/>
+      <c r="C6811" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6812" s="8"/>
+      <c r="B6812" s="9"/>
+      <c r="C6812" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6813" s="8"/>
+      <c r="B6813" s="9"/>
+      <c r="C6813" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6814" s="8"/>
+      <c r="B6814" s="9"/>
+      <c r="C6814" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6815" s="8"/>
+      <c r="B6815" s="9"/>
+      <c r="C6815" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6816" s="8"/>
+      <c r="B6816" s="9"/>
+      <c r="C6816" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6817" s="8"/>
+      <c r="B6817" s="9"/>
+      <c r="C6817" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6818" s="8"/>
+      <c r="B6818" s="9"/>
+      <c r="C6818" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6819" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B6819" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6819" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6820" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6820" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6820" s="20"/>
+      <c r="C6820" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="87">
+    <mergeCell ref="B6669:C6669"/>
+    <mergeCell ref="B6787:C6787"/>
     <mergeCell ref="C6031:C6032"/>
     <mergeCell ref="B6492:C6492"/>
     <mergeCell ref="C6503:C6504"/>
+    <mergeCell ref="C6614:C6615"/>
     <mergeCell ref="B5725:C5725"/>
     <mergeCell ref="B6020:C6020"/>
     <mergeCell ref="B5607:C5607"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8EE092-7680-4139-8BF2-AC9B5B0A7A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB5C5A1-2E7E-4F7C-803D-90B3BAB72959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$6907</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7662</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2868" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="366">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -7417,6 +7417,521 @@
   </si>
   <si>
     <t>ADC (73)</t>
+  </si>
+  <si>
+    <t>STZ (74)</t>
+  </si>
+  <si>
+    <t>Direct, X (Write)</t>
+  </si>
+  <si>
+    <t>ADC (75)</t>
+  </si>
+  <si>
+    <t>ROR (76)</t>
+  </si>
+  <si>
+    <t>ADC (77)</t>
+  </si>
+  <si>
+    <t>CLI (78)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (79)</t>
+  </si>
+  <si>
+    <t>Inc. PC. Perform Orig = Pointer.</t>
+  </si>
+  <si>
+    <t>PLY (7A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TDC (7B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (7C)</t>
+  </si>
+  <si>
+    <t>Absolute Indexed Indirect (Jump)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Pointer += </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Bank = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Read Pointer + 1:Bank</t>
+  </si>
+  <si>
+    <t>ADC (7D)</t>
+  </si>
+  <si>
+    <t>ROR (7E)</t>
+  </si>
+  <si>
+    <t>ADC (7F)</t>
+  </si>
+  <si>
+    <t>BRA (80)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Decide to branch always.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (81)</t>
+  </si>
+  <si>
+    <t>Direct Indexed Indirect (d,x) (Write)</t>
+  </si>
+  <si>
+    <t>Address.L = Pointer.L.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address.H = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Pointer to Pointer + X + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to Pointer:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets Operand.L to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -7665,13 +8180,16 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7679,9 +8197,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8017,7 +8532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C6820"/>
+  <dimension ref="A1:C7632"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -8233,40 +8748,40 @@
       <c r="C22" s="21"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -8281,10 +8796,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="32"/>
+      <c r="C61" s="31"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -8629,39 +9144,39 @@
       <c r="C137" s="22"/>
     </row>
     <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="33"/>
-      <c r="B139" s="33"/>
-      <c r="C139" s="33"/>
+      <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
+      <c r="C139" s="34"/>
     </row>
     <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="33"/>
-      <c r="B140" s="33"/>
-      <c r="C140" s="33"/>
+      <c r="A140" s="34"/>
+      <c r="B140" s="34"/>
+      <c r="C140" s="34"/>
     </row>
     <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="33"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="33"/>
+      <c r="A141" s="34"/>
+      <c r="B141" s="34"/>
+      <c r="C141" s="34"/>
     </row>
     <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="33"/>
-      <c r="B142" s="33"/>
-      <c r="C142" s="33"/>
+      <c r="A142" s="34"/>
+      <c r="B142" s="34"/>
+      <c r="C142" s="34"/>
     </row>
     <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="33"/>
-      <c r="B143" s="33"/>
-      <c r="C143" s="33"/>
+      <c r="A143" s="34"/>
+      <c r="B143" s="34"/>
+      <c r="C143" s="34"/>
     </row>
     <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="33"/>
-      <c r="B144" s="33"/>
-      <c r="C144" s="33"/>
+      <c r="A144" s="34"/>
+      <c r="B144" s="34"/>
+      <c r="C144" s="34"/>
     </row>
     <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="33"/>
-      <c r="B145" s="33"/>
-      <c r="C145" s="33"/>
+      <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
+      <c r="C145" s="34"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
@@ -8676,10 +9191,10 @@
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
-      <c r="B179" s="31" t="s">
+      <c r="B179" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="C179" s="32"/>
+      <c r="C179" s="31"/>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
@@ -9185,14 +9700,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="30" t="s">
+      <c r="C367" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="30"/>
+      <c r="C368" s="32"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="18">
@@ -9243,10 +9758,10 @@
     </row>
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
-      <c r="B415" s="31" t="s">
+      <c r="B415" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C415" s="32"/>
+      <c r="C415" s="31"/>
     </row>
     <row r="416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="12" t="s">
@@ -9814,10 +10329,10 @@
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="4"/>
-      <c r="B710" s="31" t="s">
+      <c r="B710" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C710" s="32"/>
+      <c r="C710" s="31"/>
     </row>
     <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12" t="s">
@@ -10104,10 +10619,10 @@
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="4"/>
-      <c r="B828" s="31" t="s">
+      <c r="B828" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C828" s="32"/>
+      <c r="C828" s="31"/>
     </row>
     <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="12" t="s">
@@ -10214,14 +10729,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="30" t="s">
+      <c r="C839" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="30"/>
+      <c r="C840" s="32"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
@@ -10272,10 +10787,10 @@
     </row>
     <row r="887" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="4"/>
-      <c r="B887" s="31" t="s">
+      <c r="B887" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C887" s="32"/>
+      <c r="C887" s="31"/>
     </row>
     <row r="888" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="12" t="s">
@@ -10462,14 +10977,14 @@
       <c r="B950" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C950" s="30" t="s">
+      <c r="C950" s="32" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="8"/>
       <c r="B951" s="9"/>
-      <c r="C951" s="30"/>
+      <c r="C951" s="32"/>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="8">
@@ -10545,10 +11060,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="4"/>
-      <c r="B1005" s="31" t="s">
+      <c r="B1005" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C1005" s="32"/>
+      <c r="C1005" s="31"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="12" t="s">
@@ -10748,10 +11263,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="4"/>
-      <c r="B1064" s="31" t="s">
+      <c r="B1064" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C1064" s="32"/>
+      <c r="C1064" s="31"/>
     </row>
     <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="12" t="s">
@@ -10907,10 +11422,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="4"/>
-      <c r="B1123" s="31" t="s">
+      <c r="B1123" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C1123" s="32"/>
+      <c r="C1123" s="31"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="12" t="s">
@@ -11094,10 +11609,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="4"/>
-      <c r="B1182" s="31" t="s">
+      <c r="B1182" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C1182" s="32"/>
+      <c r="C1182" s="31"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="12" t="s">
@@ -11321,14 +11836,14 @@
         <v>3.1</v>
       </c>
       <c r="B1248" s="9"/>
-      <c r="C1248" s="30" t="s">
+      <c r="C1248" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="8"/>
       <c r="B1249" s="9"/>
-      <c r="C1249" s="30"/>
+      <c r="C1249" s="32"/>
     </row>
     <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="15">
@@ -11395,10 +11910,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
-      <c r="B1300" s="31" t="s">
+      <c r="B1300" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="C1300" s="32"/>
+      <c r="C1300" s="31"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="12" t="s">
@@ -11463,14 +11978,14 @@
         <v>3.1</v>
       </c>
       <c r="B1307" s="9"/>
-      <c r="C1307" s="30" t="s">
+      <c r="C1307" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1308" s="8"/>
       <c r="B1308" s="9"/>
-      <c r="C1308" s="30"/>
+      <c r="C1308" s="32"/>
     </row>
     <row r="1309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="15">
@@ -11520,14 +12035,14 @@
         <v>6.1</v>
       </c>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="30" t="s">
+      <c r="C1314" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="30"/>
+      <c r="C1315" s="32"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="18">
@@ -11578,10 +12093,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="4"/>
-      <c r="B1359" s="31" t="s">
+      <c r="B1359" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C1359" s="32"/>
+      <c r="C1359" s="31"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="12" t="s">
@@ -11672,7 +12187,7 @@
       <c r="A1369" s="8">
         <v>4.2</v>
       </c>
-      <c r="B1369" s="35" t="s">
+      <c r="B1369" s="33" t="s">
         <v>165</v>
       </c>
       <c r="C1369" s="14" t="s">
@@ -11681,12 +12196,12 @@
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="8"/>
-      <c r="B1370" s="35"/>
+      <c r="B1370" s="33"/>
       <c r="C1370" s="14"/>
     </row>
     <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="8"/>
-      <c r="B1371" s="35"/>
+      <c r="B1371" s="33"/>
       <c r="C1371" s="14"/>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11700,7 +12215,7 @@
       <c r="A1373" s="8">
         <v>5.2</v>
       </c>
-      <c r="B1373" s="35" t="s">
+      <c r="B1373" s="33" t="s">
         <v>166</v>
       </c>
       <c r="C1373" s="10" t="s">
@@ -11709,12 +12224,12 @@
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1374" s="8"/>
-      <c r="B1374" s="35"/>
+      <c r="B1374" s="33"/>
       <c r="C1374" s="10"/>
     </row>
     <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="8"/>
-      <c r="B1375" s="35"/>
+      <c r="B1375" s="33"/>
       <c r="C1375" s="10"/>
     </row>
     <row r="1376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11878,10 +12393,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="4"/>
-      <c r="B1477" s="31" t="s">
+      <c r="B1477" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C1477" s="32"/>
+      <c r="C1477" s="31"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="12" t="s">
@@ -12221,10 +12736,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="4"/>
-      <c r="B1654" s="31" t="s">
+      <c r="B1654" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="32"/>
+      <c r="C1654" s="31"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="12" t="s">
@@ -12384,10 +12899,10 @@
     </row>
     <row r="1713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1713" s="4"/>
-      <c r="B1713" s="31" t="s">
+      <c r="B1713" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C1713" s="32"/>
+      <c r="C1713" s="31"/>
     </row>
     <row r="1714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1714" s="12" t="s">
@@ -12553,10 +13068,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="4"/>
-      <c r="B1772" s="31" t="s">
+      <c r="B1772" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C1772" s="32"/>
+      <c r="C1772" s="31"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="12" t="s">
@@ -12691,14 +13206,14 @@
         <v>6.1</v>
       </c>
       <c r="B1787" s="9"/>
-      <c r="C1787" s="30" t="s">
+      <c r="C1787" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="8"/>
       <c r="B1788" s="9"/>
-      <c r="C1788" s="30"/>
+      <c r="C1788" s="32"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="18">
@@ -12749,10 +13264,10 @@
     </row>
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="4"/>
-      <c r="B1831" s="31" t="s">
+      <c r="B1831" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C1831" s="32"/>
+      <c r="C1831" s="31"/>
     </row>
     <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1832" s="12" t="s">
@@ -12910,10 +13425,10 @@
     </row>
     <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1890" s="4"/>
-      <c r="B1890" s="31" t="s">
+      <c r="B1890" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C1890" s="32"/>
+      <c r="C1890" s="31"/>
     </row>
     <row r="1891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1891" s="12" t="s">
@@ -13075,10 +13590,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="4"/>
-      <c r="B1949" s="31" t="s">
+      <c r="B1949" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C1949" s="32"/>
+      <c r="C1949" s="31"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="12" t="s">
@@ -13816,10 +14331,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="4"/>
-      <c r="B2244" s="31" t="s">
+      <c r="B2244" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C2244" s="32"/>
+      <c r="C2244" s="31"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="12" t="s">
@@ -13922,14 +14437,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="30" t="s">
+      <c r="C2255" s="32" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="30"/>
+      <c r="C2256" s="32"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="18">
@@ -14708,10 +15223,10 @@
     </row>
     <row r="2657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2657" s="4"/>
-      <c r="B2657" s="31" t="s">
+      <c r="B2657" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C2657" s="32"/>
+      <c r="C2657" s="31"/>
     </row>
     <row r="2658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2658" s="12" t="s">
@@ -14835,10 +15350,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="4"/>
-      <c r="B2716" s="31" t="s">
+      <c r="B2716" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="32"/>
+      <c r="C2716" s="31"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="12" t="s">
@@ -14945,14 +15460,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="30" t="s">
+      <c r="C2727" s="32" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="30"/>
+      <c r="C2728" s="32"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="18">
@@ -15003,10 +15518,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="4"/>
-      <c r="B2775" s="31" t="s">
+      <c r="B2775" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C2775" s="32"/>
+      <c r="C2775" s="31"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="12" t="s">
@@ -15193,14 +15708,14 @@
       <c r="B2838" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C2838" s="30" t="s">
+      <c r="C2838" s="32" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2839" s="8"/>
       <c r="B2839" s="9"/>
-      <c r="C2839" s="30"/>
+      <c r="C2839" s="32"/>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2840" s="8">
@@ -15276,10 +15791,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="4"/>
-      <c r="B2893" s="31" t="s">
+      <c r="B2893" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C2893" s="32"/>
+      <c r="C2893" s="31"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="12" t="s">
@@ -15638,10 +16153,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="4"/>
-      <c r="B3011" s="31" t="s">
+      <c r="B3011" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C3011" s="32"/>
+      <c r="C3011" s="31"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="12" t="s">
@@ -15893,14 +16408,14 @@
         <v>3.1</v>
       </c>
       <c r="B3077" s="9"/>
-      <c r="C3077" s="30" t="s">
+      <c r="C3077" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3078" s="8"/>
       <c r="B3078" s="9"/>
-      <c r="C3078" s="30"/>
+      <c r="C3078" s="32"/>
     </row>
     <row r="3079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3079" s="15">
@@ -16045,14 +16560,14 @@
         <v>3.1</v>
       </c>
       <c r="B3136" s="9"/>
-      <c r="C3136" s="30" t="s">
+      <c r="C3136" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3137" s="8"/>
       <c r="B3137" s="9"/>
-      <c r="C3137" s="30"/>
+      <c r="C3137" s="32"/>
     </row>
     <row r="3138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3138" s="15">
@@ -16119,10 +16634,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="4"/>
-      <c r="B3188" s="31" t="s">
+      <c r="B3188" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="C3188" s="32"/>
+      <c r="C3188" s="31"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="12" t="s">
@@ -16187,14 +16702,14 @@
         <v>3.1</v>
       </c>
       <c r="B3195" s="9"/>
-      <c r="C3195" s="30" t="s">
+      <c r="C3195" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3196" s="8"/>
       <c r="B3196" s="9"/>
-      <c r="C3196" s="30"/>
+      <c r="C3196" s="32"/>
     </row>
     <row r="3197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3197" s="15">
@@ -16244,14 +16759,14 @@
         <v>6.1</v>
       </c>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="30" t="s">
+      <c r="C3202" s="32" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="30"/>
+      <c r="C3203" s="32"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="18">
@@ -16312,10 +16827,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="4"/>
-      <c r="B3247" s="31" t="s">
+      <c r="B3247" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C3247" s="32"/>
+      <c r="C3247" s="31"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="12" t="s">
@@ -16406,7 +16921,7 @@
       <c r="A3257" s="8">
         <v>4.2</v>
       </c>
-      <c r="B3257" s="35" t="s">
+      <c r="B3257" s="33" t="s">
         <v>165</v>
       </c>
       <c r="C3257" s="10" t="s">
@@ -16415,12 +16930,12 @@
     </row>
     <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3258" s="8"/>
-      <c r="B3258" s="35"/>
+      <c r="B3258" s="33"/>
       <c r="C3258" s="10"/>
     </row>
     <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3259" s="8"/>
-      <c r="B3259" s="35"/>
+      <c r="B3259" s="33"/>
       <c r="C3259" s="10"/>
     </row>
     <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16434,7 +16949,7 @@
       <c r="A3261" s="8">
         <v>5.2</v>
       </c>
-      <c r="B3261" s="35" t="s">
+      <c r="B3261" s="33" t="s">
         <v>166</v>
       </c>
       <c r="C3261" s="10" t="s">
@@ -16443,12 +16958,12 @@
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3262" s="8"/>
-      <c r="B3262" s="35"/>
+      <c r="B3262" s="33"/>
       <c r="C3262" s="10"/>
     </row>
     <row r="3263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3263" s="8"/>
-      <c r="B3263" s="35"/>
+      <c r="B3263" s="33"/>
       <c r="C3263" s="10"/>
     </row>
     <row r="3264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16612,10 +17127,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="4"/>
-      <c r="B3365" s="31" t="s">
+      <c r="B3365" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C3365" s="32"/>
+      <c r="C3365" s="31"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="12" t="s">
@@ -17293,10 +17808,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="4"/>
-      <c r="B3660" s="31" t="s">
+      <c r="B3660" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C3660" s="32"/>
+      <c r="C3660" s="31"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="12" t="s">
@@ -17431,14 +17946,14 @@
         <v>6.1</v>
       </c>
       <c r="B3675" s="9"/>
-      <c r="C3675" s="30" t="s">
+      <c r="C3675" s="32" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3676" s="8"/>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="30"/>
+      <c r="C3676" s="32"/>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="18">
@@ -17805,10 +18320,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="4"/>
-      <c r="B3837" s="31" t="s">
+      <c r="B3837" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C3837" s="32"/>
+      <c r="C3837" s="31"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="12" t="s">
@@ -17980,10 +18495,10 @@
     </row>
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="4"/>
-      <c r="B3896" s="31" t="s">
+      <c r="B3896" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C3896" s="32"/>
+      <c r="C3896" s="31"/>
     </row>
     <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3897" s="12" t="s">
@@ -18188,10 +18703,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
-      <c r="B4014" s="31" t="s">
+      <c r="B4014" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="C4014" s="32"/>
+      <c r="C4014" s="31"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="12" t="s">
@@ -18298,14 +18813,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="9"/>
-      <c r="C4025" s="30" t="s">
+      <c r="C4025" s="32" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="8"/>
       <c r="B4026" s="9"/>
-      <c r="C4026" s="30"/>
+      <c r="C4026" s="32"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="8">
@@ -18489,10 +19004,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="4"/>
-      <c r="B4132" s="31" t="s">
+      <c r="B4132" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C4132" s="32"/>
+      <c r="C4132" s="31"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="12" t="s">
@@ -18595,14 +19110,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="9"/>
-      <c r="C4143" s="30" t="s">
+      <c r="C4143" s="32" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="8"/>
       <c r="B4144" s="9"/>
-      <c r="C4144" s="30"/>
+      <c r="C4144" s="32"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="18">
@@ -18653,10 +19168,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="4"/>
-      <c r="B4191" s="31" t="s">
+      <c r="B4191" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C4191" s="32"/>
+      <c r="C4191" s="31"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="12" t="s">
@@ -19440,10 +19955,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="4"/>
-      <c r="B4604" s="31" t="s">
+      <c r="B4604" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="32"/>
+      <c r="C4604" s="31"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="12" t="s">
@@ -19550,14 +20065,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4615" s="9"/>
-      <c r="C4615" s="30" t="s">
+      <c r="C4615" s="32" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4616" s="8"/>
       <c r="B4616" s="9"/>
-      <c r="C4616" s="30"/>
+      <c r="C4616" s="32"/>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="18">
@@ -19608,10 +20123,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="4"/>
-      <c r="B4663" s="31" t="s">
+      <c r="B4663" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C4663" s="32"/>
+      <c r="C4663" s="31"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="12" t="s">
@@ -19798,14 +20313,14 @@
       <c r="B4726" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C4726" s="30" t="s">
+      <c r="C4726" s="32" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4727" s="8"/>
       <c r="B4727" s="9"/>
-      <c r="C4727" s="30"/>
+      <c r="C4727" s="32"/>
     </row>
     <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4728" s="8">
@@ -19881,10 +20396,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="4"/>
-      <c r="B4781" s="31" t="s">
+      <c r="B4781" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C4781" s="32"/>
+      <c r="C4781" s="31"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="12" t="s">
@@ -20236,10 +20751,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="4"/>
-      <c r="B4899" s="31" t="s">
+      <c r="B4899" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C4899" s="32"/>
+      <c r="C4899" s="31"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="12" t="s">
@@ -20533,14 +21048,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="9"/>
-      <c r="C4969" s="30" t="s">
+      <c r="C4969" s="32" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="8"/>
       <c r="B4970" s="9"/>
-      <c r="C4970" s="30"/>
+      <c r="C4970" s="32"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="8">
@@ -20669,14 +21184,14 @@
         <v>3.1</v>
       </c>
       <c r="B5024" s="9"/>
-      <c r="C5024" s="30" t="s">
+      <c r="C5024" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5025" s="8"/>
       <c r="B5025" s="9"/>
-      <c r="C5025" s="30"/>
+      <c r="C5025" s="32"/>
     </row>
     <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5026" s="15">
@@ -20743,10 +21258,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="4"/>
-      <c r="B5076" s="31" t="s">
+      <c r="B5076" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="C5076" s="32"/>
+      <c r="C5076" s="31"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="12" t="s">
@@ -20811,14 +21326,14 @@
         <v>3.1</v>
       </c>
       <c r="B5083" s="9"/>
-      <c r="C5083" s="30" t="s">
+      <c r="C5083" s="32" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5084" s="8"/>
       <c r="B5084" s="9"/>
-      <c r="C5084" s="30"/>
+      <c r="C5084" s="32"/>
     </row>
     <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5085" s="15">
@@ -20868,14 +21383,14 @@
         <v>6.1</v>
       </c>
       <c r="B5090" s="9"/>
-      <c r="C5090" s="30" t="s">
+      <c r="C5090" s="32" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="8"/>
       <c r="B5091" s="9"/>
-      <c r="C5091" s="30"/>
+      <c r="C5091" s="32"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="18">
@@ -20926,10 +21441,10 @@
     </row>
     <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5135" s="4"/>
-      <c r="B5135" s="31" t="s">
+      <c r="B5135" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C5135" s="32"/>
+      <c r="C5135" s="31"/>
     </row>
     <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5136" s="12" t="s">
@@ -21020,7 +21535,7 @@
       <c r="A5145" s="8">
         <v>4.2</v>
       </c>
-      <c r="B5145" s="35" t="s">
+      <c r="B5145" s="33" t="s">
         <v>165</v>
       </c>
       <c r="C5145" s="10" t="s">
@@ -21029,12 +21544,12 @@
     </row>
     <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5146" s="8"/>
-      <c r="B5146" s="35"/>
+      <c r="B5146" s="33"/>
       <c r="C5146" s="10"/>
     </row>
     <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5147" s="8"/>
-      <c r="B5147" s="35"/>
+      <c r="B5147" s="33"/>
       <c r="C5147" s="10"/>
     </row>
     <row r="5148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21048,7 +21563,7 @@
       <c r="A5149" s="8">
         <v>5.2</v>
       </c>
-      <c r="B5149" s="35" t="s">
+      <c r="B5149" s="33" t="s">
         <v>166</v>
       </c>
       <c r="C5149" s="10" t="s">
@@ -21057,12 +21572,12 @@
     </row>
     <row r="5150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5150" s="8"/>
-      <c r="B5150" s="35"/>
+      <c r="B5150" s="33"/>
       <c r="C5150" s="10"/>
     </row>
     <row r="5151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5151" s="8"/>
-      <c r="B5151" s="35"/>
+      <c r="B5151" s="33"/>
       <c r="C5151" s="10"/>
     </row>
     <row r="5152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21583,10 +22098,10 @@
     </row>
     <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5430" s="4"/>
-      <c r="B5430" s="31" t="s">
+      <c r="B5430" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="C5430" s="32"/>
+      <c r="C5430" s="31"/>
     </row>
     <row r="5431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5431" s="12" t="s">
@@ -21710,10 +22225,10 @@
     </row>
     <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5489" s="4"/>
-      <c r="B5489" s="31" t="s">
+      <c r="B5489" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="C5489" s="32"/>
+      <c r="C5489" s="31"/>
     </row>
     <row r="5490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5490" s="12" t="s">
@@ -21872,10 +22387,10 @@
     </row>
     <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5548" s="4"/>
-      <c r="B5548" s="31" t="s">
+      <c r="B5548" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C5548" s="32"/>
+      <c r="C5548" s="31"/>
     </row>
     <row r="5549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5549" s="12" t="s">
@@ -22010,14 +22525,14 @@
         <v>6.1</v>
       </c>
       <c r="B5563" s="9"/>
-      <c r="C5563" s="30" t="s">
+      <c r="C5563" s="32" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="8"/>
       <c r="B5564" s="9"/>
-      <c r="C5564" s="30"/>
+      <c r="C5564" s="32"/>
     </row>
     <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5565" s="18">
@@ -22068,10 +22583,10 @@
     </row>
     <row r="5607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5607" s="4"/>
-      <c r="B5607" s="31" t="s">
+      <c r="B5607" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C5607" s="32"/>
+      <c r="C5607" s="31"/>
     </row>
     <row r="5608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5608" s="12" t="s">
@@ -22378,10 +22893,10 @@
     </row>
     <row r="5725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5725" s="4"/>
-      <c r="B5725" s="31" t="s">
+      <c r="B5725" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C5725" s="32"/>
+      <c r="C5725" s="31"/>
     </row>
     <row r="5726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5726" s="12" t="s">
@@ -23371,10 +23886,10 @@
     </row>
     <row r="6020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6020" s="4"/>
-      <c r="B6020" s="31" t="s">
+      <c r="B6020" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="C6020" s="32"/>
+      <c r="C6020" s="31"/>
     </row>
     <row r="6021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6021" s="12" t="s">
@@ -23477,14 +23992,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6031" s="9"/>
-      <c r="C6031" s="30" t="s">
+      <c r="C6031" s="32" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6032" s="8"/>
       <c r="B6032" s="9"/>
-      <c r="C6032" s="30"/>
+      <c r="C6032" s="32"/>
     </row>
     <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6033" s="18">
@@ -24720,10 +25235,10 @@
     </row>
     <row r="6492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6492" s="4"/>
-      <c r="B6492" s="31" t="s">
+      <c r="B6492" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C6492" s="32"/>
+      <c r="C6492" s="31"/>
     </row>
     <row r="6493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6493" s="12" t="s">
@@ -24830,14 +25345,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6503" s="9"/>
-      <c r="C6503" s="30" t="s">
+      <c r="C6503" s="32" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="8"/>
       <c r="B6504" s="9"/>
-      <c r="C6504" s="30"/>
+      <c r="C6504" s="32"/>
     </row>
     <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6505" s="18">
@@ -25176,14 +25691,14 @@
       <c r="B6614" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6614" s="30" t="s">
+      <c r="C6614" s="32" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6615" s="8"/>
       <c r="B6615" s="9"/>
-      <c r="C6615" s="30"/>
+      <c r="C6615" s="32"/>
     </row>
     <row r="6616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6616" s="8">
@@ -25259,10 +25774,10 @@
     </row>
     <row r="6669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6669" s="4"/>
-      <c r="B6669" s="31" t="s">
+      <c r="B6669" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C6669" s="32"/>
+      <c r="C6669" s="31"/>
     </row>
     <row r="6670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6670" s="12" t="s">
@@ -25817,10 +26332,10 @@
     </row>
     <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6787" s="4"/>
-      <c r="B6787" s="31" t="s">
+      <c r="B6787" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C6787" s="32"/>
+      <c r="C6787" s="31"/>
     </row>
     <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6788" s="12" t="s">
@@ -26089,68 +26604,2666 @@
       <c r="B6820" s="20"/>
       <c r="C6820" s="22"/>
     </row>
+    <row r="6845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6845" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6845" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6845" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6846" s="4"/>
+      <c r="B6846" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="C6846" s="25"/>
+    </row>
+    <row r="6847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6847" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6847" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6847" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6848" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6848" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6848" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6849" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6849" s="9"/>
+      <c r="C6849" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6850" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6850" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6850" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6851" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6851" s="9"/>
+      <c r="C6851" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6852" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6852" s="9"/>
+      <c r="C6852" s="10"/>
+    </row>
+    <row r="6853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6853" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6853" s="9"/>
+      <c r="C6853" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6854" s="8"/>
+      <c r="B6854" s="9"/>
+      <c r="C6854" s="32"/>
+    </row>
+    <row r="6855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6855" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6855" s="9"/>
+      <c r="C6855" s="10"/>
+    </row>
+    <row r="6856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6856" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6856" s="9"/>
+      <c r="C6856" s="10"/>
+    </row>
+    <row r="6857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6857" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B6857" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6857" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6858" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6858" s="9"/>
+      <c r="C6858" s="10"/>
+    </row>
+    <row r="6859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6859" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6859" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6859" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6860" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6860" s="20"/>
+      <c r="C6860" s="22"/>
+    </row>
+    <row r="6904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6904" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6904" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6904" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6905" s="4"/>
+      <c r="B6905" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6905" s="25"/>
+    </row>
+    <row r="6906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6906" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6906" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6906" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6907" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6907" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6907" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6908" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6908" s="9"/>
+      <c r="C6908" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6909" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6909" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6909" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6910" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6910" s="9"/>
+      <c r="C6910" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6911" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6911" s="9"/>
+      <c r="C6911" s="10"/>
+    </row>
+    <row r="6912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6912" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6912" s="9"/>
+      <c r="C6912" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6913" s="8"/>
+      <c r="B6913" s="9"/>
+      <c r="C6913" s="32"/>
+    </row>
+    <row r="6914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6914" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6914" s="9"/>
+      <c r="C6914" s="10"/>
+    </row>
+    <row r="6915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6915" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6915" s="9"/>
+      <c r="C6915" s="10"/>
+    </row>
+    <row r="6916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6916" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B6916" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6916" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6917" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6917" s="9"/>
+      <c r="C6917" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6918" s="8"/>
+      <c r="B6918" s="9"/>
+      <c r="C6918" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6919" s="8"/>
+      <c r="B6919" s="9"/>
+      <c r="C6919" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6920" s="8"/>
+      <c r="B6920" s="9"/>
+      <c r="C6920" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6921" s="8"/>
+      <c r="B6921" s="9"/>
+      <c r="C6921" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6922" s="8"/>
+      <c r="B6922" s="9"/>
+      <c r="C6922" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6923" s="8"/>
+      <c r="B6923" s="9"/>
+      <c r="C6923" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6924" s="8"/>
+      <c r="B6924" s="9"/>
+      <c r="C6924" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6925" s="8"/>
+      <c r="B6925" s="9"/>
+      <c r="C6925" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6926" s="8"/>
+      <c r="B6926" s="9"/>
+      <c r="C6926" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6927" s="8"/>
+      <c r="B6927" s="9"/>
+      <c r="C6927" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="6928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6928" s="8"/>
+      <c r="B6928" s="9"/>
+      <c r="C6928" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6929" s="8"/>
+      <c r="B6929" s="9"/>
+      <c r="C6929" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6930" s="8"/>
+      <c r="B6930" s="9"/>
+      <c r="C6930" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6931" s="8"/>
+      <c r="B6931" s="9"/>
+      <c r="C6931" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6932" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6932" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6932" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6933" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6933" s="20"/>
+      <c r="C6933" s="22"/>
+    </row>
+    <row r="6963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6963" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B6963" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6963" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6964" s="4"/>
+      <c r="B6964" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6964" s="31"/>
+    </row>
+    <row r="6965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6965" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6965" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6965" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6966" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6966" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6966" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6967" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B6967" s="9"/>
+      <c r="C6967" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6968" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B6968" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6968" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6969" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B6969" s="9"/>
+      <c r="C6969" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6970" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B6970" s="9"/>
+      <c r="C6970" s="10"/>
+    </row>
+    <row r="6971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6971" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B6971" s="9"/>
+      <c r="C6971" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6972" s="8"/>
+      <c r="B6972" s="9"/>
+      <c r="C6972" s="32"/>
+    </row>
+    <row r="6973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6973" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B6973" s="9"/>
+      <c r="C6973" s="10"/>
+    </row>
+    <row r="6974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6974" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B6974" s="9"/>
+      <c r="C6974" s="10"/>
+    </row>
+    <row r="6975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6975" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B6975" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6975" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6976" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B6976" s="9"/>
+      <c r="C6976" s="10"/>
+    </row>
+    <row r="6977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6977" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B6977" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6977" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6978" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B6978" s="9"/>
+      <c r="C6978" s="32" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6979" s="8"/>
+      <c r="B6979" s="9"/>
+      <c r="C6979" s="32"/>
+    </row>
+    <row r="6980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6980" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B6980" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6980" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6981" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B6981" s="9"/>
+      <c r="C6981" s="10"/>
+    </row>
+    <row r="6982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6982" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B6982" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6982" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6983" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6983" s="20"/>
+      <c r="C6983" s="22"/>
+    </row>
+    <row r="7022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7022" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B7022" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7022" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7023" s="4"/>
+      <c r="B7023" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7023" s="31"/>
+    </row>
+    <row r="7024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7024" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7024" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7024" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7025" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7025" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7025" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7026" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7026" s="9"/>
+      <c r="C7026" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7027" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7027" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7027" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7028" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B7028" s="16"/>
+      <c r="C7028" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7029" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7029" s="16"/>
+      <c r="C7029" s="23"/>
+    </row>
+    <row r="7030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7030" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7030" s="9"/>
+      <c r="C7030" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7031" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7031" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7031" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7032" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7032" s="9"/>
+      <c r="C7032" s="10"/>
+    </row>
+    <row r="7033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7033" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7033" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7033" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7034" s="8"/>
+      <c r="B7034" s="33"/>
+      <c r="C7034" s="10"/>
+    </row>
+    <row r="7035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7035" s="8"/>
+      <c r="B7035" s="33"/>
+      <c r="C7035" s="10"/>
+    </row>
+    <row r="7036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7036" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7036" s="9"/>
+      <c r="C7036" s="10"/>
+    </row>
+    <row r="7037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7037" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7037" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7037" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7038" s="8"/>
+      <c r="B7038" s="33"/>
+      <c r="C7038" s="10"/>
+    </row>
+    <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7039" s="8"/>
+      <c r="B7039" s="33"/>
+      <c r="C7039" s="10"/>
+    </row>
+    <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7040" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7040" s="9"/>
+      <c r="C7040" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7041" s="8"/>
+      <c r="B7041" s="9"/>
+      <c r="C7041" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7042" s="8"/>
+      <c r="B7042" s="9"/>
+      <c r="C7042" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7043" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B7043" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7043" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7044" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B7044" s="9"/>
+      <c r="C7044" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7045" s="8"/>
+      <c r="B7045" s="9"/>
+      <c r="C7045" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7046" s="8"/>
+      <c r="B7046" s="9"/>
+      <c r="C7046" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7047" s="8"/>
+      <c r="B7047" s="9"/>
+      <c r="C7047" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7048" s="8"/>
+      <c r="B7048" s="9"/>
+      <c r="C7048" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7049" s="8"/>
+      <c r="B7049" s="9"/>
+      <c r="C7049" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7050" s="8"/>
+      <c r="B7050" s="9"/>
+      <c r="C7050" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7051" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7051" s="8"/>
+      <c r="B7051" s="9"/>
+      <c r="C7051" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7052" s="8"/>
+      <c r="B7052" s="9"/>
+      <c r="C7052" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7053" s="8"/>
+      <c r="B7053" s="9"/>
+      <c r="C7053" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7054" s="8"/>
+      <c r="B7054" s="9"/>
+      <c r="C7054" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7055" s="8"/>
+      <c r="B7055" s="9"/>
+      <c r="C7055" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7056" s="8"/>
+      <c r="B7056" s="9"/>
+      <c r="C7056" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7057" s="8"/>
+      <c r="B7057" s="9"/>
+      <c r="C7057" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7058" s="8"/>
+      <c r="B7058" s="9"/>
+      <c r="C7058" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7059" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B7059" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7059" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7060" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7060" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7060" s="20"/>
+      <c r="C7060" s="22"/>
+    </row>
+    <row r="7081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7081" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B7081" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7081" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7082" s="4"/>
+      <c r="B7082" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7082" s="25"/>
+    </row>
+    <row r="7083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7083" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7083" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7083" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7084" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7084" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7084" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7085" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7085" s="9"/>
+      <c r="C7085" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7086" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B7086" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7086" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7087" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7087" s="9"/>
+      <c r="C7087" s="10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7088" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7088" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7088" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7089" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7089" s="20"/>
+      <c r="C7089" s="22"/>
+    </row>
+    <row r="7140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7140" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7140" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7140" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7141" s="4"/>
+      <c r="B7141" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7141" s="25"/>
+    </row>
+    <row r="7142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7142" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7142" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7142" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7143" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7143" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7143" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7144" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7144" s="9"/>
+      <c r="C7144" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7145" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7145" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7145" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7146" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7146" s="9"/>
+      <c r="C7146" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7147" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7147" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7147" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7148" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7148" s="9"/>
+      <c r="C7148" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7149" s="8"/>
+      <c r="B7149" s="9"/>
+      <c r="C7149" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7150" s="8"/>
+      <c r="B7150" s="9"/>
+      <c r="C7150" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7151" s="8"/>
+      <c r="B7151" s="9"/>
+      <c r="C7151" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7152" s="8"/>
+      <c r="B7152" s="9"/>
+      <c r="C7152" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7153" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7153" s="9"/>
+      <c r="C7153" s="10"/>
+    </row>
+    <row r="7154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7154" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7154" s="9"/>
+      <c r="C7154" s="10"/>
+    </row>
+    <row r="7155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7155" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B7155" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7155" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7156" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7156" s="27"/>
+      <c r="C7156" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7157" s="8"/>
+      <c r="B7157" s="27"/>
+      <c r="C7157" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7158" s="8"/>
+      <c r="B7158" s="9"/>
+      <c r="C7158" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7159" s="8"/>
+      <c r="B7159" s="27"/>
+      <c r="C7159" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7160" s="8"/>
+      <c r="B7160" s="27"/>
+      <c r="C7160" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7161" s="8"/>
+      <c r="B7161" s="27"/>
+      <c r="C7161" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7162" s="8"/>
+      <c r="B7162" s="9"/>
+      <c r="C7162" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7163" s="8"/>
+      <c r="B7163" s="9"/>
+      <c r="C7163" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7164" s="8"/>
+      <c r="B7164" s="9"/>
+      <c r="C7164" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7165" s="8"/>
+      <c r="B7165" s="9"/>
+      <c r="C7165" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7166" s="8"/>
+      <c r="B7166" s="9"/>
+      <c r="C7166" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7167" s="8"/>
+      <c r="B7167" s="9"/>
+      <c r="C7167" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7168" s="8"/>
+      <c r="B7168" s="9"/>
+      <c r="C7168" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7169" s="8"/>
+      <c r="B7169" s="9"/>
+      <c r="C7169" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7170" s="8"/>
+      <c r="B7170" s="9"/>
+      <c r="C7170" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7171" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7171" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7171" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7172" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7172" s="20"/>
+      <c r="C7172" s="22"/>
+    </row>
+    <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7199" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7199" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7199" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7200" s="4"/>
+      <c r="B7200" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7200" s="25"/>
+    </row>
+    <row r="7201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7201" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7201" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7201" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7202" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7202" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7202" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7203" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7203" s="9"/>
+      <c r="C7203" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7204" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7204" s="9"/>
+      <c r="C7204" s="10"/>
+    </row>
+    <row r="7205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7205" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7205" s="9"/>
+      <c r="C7205" s="10"/>
+    </row>
+    <row r="7206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7206" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7206" s="9"/>
+      <c r="C7206" s="10"/>
+    </row>
+    <row r="7207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7207" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7207" s="9"/>
+      <c r="C7207" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7208" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7208" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7208" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7209" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7209" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7209" s="10"/>
+    </row>
+    <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7210" s="8"/>
+      <c r="B7210" s="33"/>
+      <c r="C7210" s="10"/>
+    </row>
+    <row r="7211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7211" s="8"/>
+      <c r="B7211" s="33"/>
+      <c r="C7211" s="10"/>
+    </row>
+    <row r="7212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7212" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7212" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7212" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7213" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7213" s="20"/>
+      <c r="C7213" s="22"/>
+    </row>
+    <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7258" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B7258" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7258" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7259" s="4"/>
+      <c r="B7259" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7259" s="25"/>
+    </row>
+    <row r="7260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7260" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7260" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7260" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7261" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7261" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7261" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7262" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7262" s="9"/>
+      <c r="C7262" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7263" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B7263" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7263" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7264" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7264" s="9"/>
+      <c r="C7264" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7265" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7265" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7265" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7266" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7266" s="20"/>
+      <c r="C7266" s="22"/>
+    </row>
+    <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7317" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7317" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7317" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7318" s="4"/>
+      <c r="B7318" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7318" s="31"/>
+    </row>
+    <row r="7319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7319" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7319" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7319" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7320" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7320" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7320" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7321" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7321" s="9"/>
+      <c r="C7321" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7322" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7322" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7322" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7323" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7323" s="9"/>
+      <c r="C7323" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7324" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7324" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7324" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7325" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7325" s="9"/>
+      <c r="C7325" s="10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7326" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7326" s="9"/>
+      <c r="C7326" s="10"/>
+    </row>
+    <row r="7327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7327" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7327" s="9"/>
+      <c r="C7327" s="10"/>
+    </row>
+    <row r="7328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7328" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7328" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7328" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7329" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7329" s="9"/>
+      <c r="C7329" s="10"/>
+    </row>
+    <row r="7330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7330" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B7330" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C7330" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7331" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7331" s="9"/>
+      <c r="C7331" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7332" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B7332" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7332" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7333" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7333" s="20"/>
+      <c r="C7333" s="22"/>
+    </row>
+    <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7376" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7376" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7376" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7377" s="4"/>
+      <c r="B7377" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7377" s="25"/>
+    </row>
+    <row r="7378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7378" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7378" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7378" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7379" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7379" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7379" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7380" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7380" s="9"/>
+      <c r="C7380" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7381" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7381" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7381" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7382" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7382" s="9"/>
+      <c r="C7382" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7383" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7383" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7383" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7384" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7384" s="9"/>
+      <c r="C7384" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7385" s="8"/>
+      <c r="B7385" s="9"/>
+      <c r="C7385" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7386" s="8"/>
+      <c r="B7386" s="9"/>
+      <c r="C7386" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7387" s="8"/>
+      <c r="B7387" s="9"/>
+      <c r="C7387" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7388" s="8"/>
+      <c r="B7388" s="9"/>
+      <c r="C7388" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7389" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7389" s="9"/>
+      <c r="C7389" s="10"/>
+    </row>
+    <row r="7390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7390" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7390" s="9"/>
+      <c r="C7390" s="10"/>
+    </row>
+    <row r="7391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7391" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B7391" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7391" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7392" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7392" s="27"/>
+      <c r="C7392" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7393" s="8"/>
+      <c r="B7393" s="27"/>
+      <c r="C7393" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7394" s="8"/>
+      <c r="B7394" s="9"/>
+      <c r="C7394" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7395" s="8"/>
+      <c r="B7395" s="27"/>
+      <c r="C7395" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7396" s="8"/>
+      <c r="B7396" s="27"/>
+      <c r="C7396" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7397" s="8"/>
+      <c r="B7397" s="27"/>
+      <c r="C7397" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7398" s="8"/>
+      <c r="B7398" s="9"/>
+      <c r="C7398" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7399" s="8"/>
+      <c r="B7399" s="9"/>
+      <c r="C7399" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7400" s="8"/>
+      <c r="B7400" s="9"/>
+      <c r="C7400" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7401" s="8"/>
+      <c r="B7401" s="9"/>
+      <c r="C7401" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7402" s="8"/>
+      <c r="B7402" s="9"/>
+      <c r="C7402" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7403" s="8"/>
+      <c r="B7403" s="9"/>
+      <c r="C7403" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7404" s="8"/>
+      <c r="B7404" s="9"/>
+      <c r="C7404" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7405" s="8"/>
+      <c r="B7405" s="9"/>
+      <c r="C7405" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7406" s="8"/>
+      <c r="B7406" s="9"/>
+      <c r="C7406" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7407" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7407" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7407" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7408" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7408" s="20"/>
+      <c r="C7408" s="22"/>
+    </row>
+    <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7435" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B7435" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7435" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7436" s="4"/>
+      <c r="B7436" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7436" s="31"/>
+    </row>
+    <row r="7437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7437" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7437" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7437" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7438" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7438" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7438" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7439" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7439" s="9"/>
+      <c r="C7439" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7440" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7440" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7440" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7441" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7441" s="9"/>
+      <c r="C7441" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7442" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7442" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7442" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7443" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7443" s="9"/>
+      <c r="C7443" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7444" s="8"/>
+      <c r="B7444" s="9"/>
+      <c r="C7444" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7445" s="8"/>
+      <c r="B7445" s="9"/>
+      <c r="C7445" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7446" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7446" s="9"/>
+      <c r="C7446" s="10"/>
+    </row>
+    <row r="7447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7447" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7447" s="9"/>
+      <c r="C7447" s="10"/>
+    </row>
+    <row r="7448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7448" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7448" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7448" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7449" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7449" s="9"/>
+      <c r="C7449" s="10"/>
+    </row>
+    <row r="7450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7450" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7450" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7450" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7451" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7451" s="27"/>
+      <c r="C7451" s="32" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7452" s="8"/>
+      <c r="B7452" s="27"/>
+      <c r="C7452" s="32"/>
+    </row>
+    <row r="7453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7453" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B7453" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7453" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7454" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B7454" s="9"/>
+      <c r="C7454" s="10"/>
+    </row>
+    <row r="7455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7455" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B7455" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7455" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7456" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7456" s="20"/>
+      <c r="C7456" s="22"/>
+    </row>
+    <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7494" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7494" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7494" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7495" s="4"/>
+      <c r="B7495" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7495" s="25"/>
+    </row>
+    <row r="7496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7496" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7496" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7496" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7497" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7497" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7497" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7498" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7498" s="9"/>
+      <c r="C7498" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7499" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7499" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7499" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7500" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7500" s="9"/>
+      <c r="C7500" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7501" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7501" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7501" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7502" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7502" s="9"/>
+      <c r="C7502" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7503" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7503" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7503" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7504" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7504" s="9"/>
+      <c r="C7504" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7505" s="8"/>
+      <c r="B7505" s="9"/>
+      <c r="C7505" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7506" s="8"/>
+      <c r="B7506" s="9"/>
+      <c r="C7506" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7507" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B7507" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7507" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7508" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7508" s="9"/>
+      <c r="C7508" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7509" s="8"/>
+      <c r="B7509" s="9"/>
+      <c r="C7509" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7510" s="8"/>
+      <c r="B7510" s="9"/>
+      <c r="C7510" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7511" s="8"/>
+      <c r="B7511" s="9"/>
+      <c r="C7511" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7512" s="8"/>
+      <c r="B7512" s="9"/>
+      <c r="C7512" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7513" s="8"/>
+      <c r="B7513" s="9"/>
+      <c r="C7513" s="10" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="7514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7514" s="8"/>
+      <c r="B7514" s="9"/>
+      <c r="C7514" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7515" s="8"/>
+      <c r="B7515" s="9"/>
+      <c r="C7515" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7516" s="8"/>
+      <c r="B7516" s="9"/>
+      <c r="C7516" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7517" s="8"/>
+      <c r="B7517" s="9"/>
+      <c r="C7517" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7518" s="8"/>
+      <c r="B7518" s="9"/>
+      <c r="C7518" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7519" s="8"/>
+      <c r="B7519" s="9"/>
+      <c r="C7519" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7520" s="8"/>
+      <c r="B7520" s="9"/>
+      <c r="C7520" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7521" s="8"/>
+      <c r="B7521" s="9"/>
+      <c r="C7521" s="10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7522" s="8"/>
+      <c r="B7522" s="27"/>
+      <c r="C7522" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7523" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7523" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7523" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7524" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7524" s="20"/>
+      <c r="C7524" s="22"/>
+    </row>
+    <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7553" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7553" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7553" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7554" s="4"/>
+      <c r="B7554" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7554" s="25"/>
+    </row>
+    <row r="7555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7555" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7555" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7555" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7556" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7556" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7556" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7557" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7557" s="9"/>
+      <c r="C7557" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7558" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B7558" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7558" s="32" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7559" s="18"/>
+      <c r="B7559" s="9"/>
+      <c r="C7559" s="32"/>
+    </row>
+    <row r="7560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7560" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7560" s="9"/>
+      <c r="C7560" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7561" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7561" s="9"/>
+      <c r="C7561" s="10"/>
+    </row>
+    <row r="7562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7562" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7562" s="9"/>
+      <c r="C7562" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7563" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7563" s="9"/>
+      <c r="C7563" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7564" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7564" s="9"/>
+      <c r="C7564" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7565" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7565" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7565" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7566" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7566" s="20"/>
+      <c r="C7566" s="22"/>
+    </row>
+    <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7612" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B7612" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7612" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7613" s="4"/>
+      <c r="B7613" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7613" s="31"/>
+    </row>
+    <row r="7614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7614" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7614" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7614" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7615" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7615" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7615" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7616" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7616" s="9"/>
+      <c r="C7616" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7617" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7617" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7617" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7618" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7618" s="9"/>
+      <c r="C7618" s="10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7619" s="8"/>
+      <c r="B7619" s="9"/>
+      <c r="C7619" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7620" s="8"/>
+      <c r="B7620" s="9"/>
+      <c r="C7620" s="10" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7621" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7621" s="9"/>
+      <c r="C7621" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7622" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="B7622" s="16"/>
+      <c r="C7622" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7623" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B7623" s="16"/>
+      <c r="C7623" s="23"/>
+    </row>
+    <row r="7624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7624" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7624" s="9"/>
+      <c r="C7624" s="10"/>
+    </row>
+    <row r="7625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7625" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7625" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7625" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7626" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7626" s="9"/>
+      <c r="C7626" s="10"/>
+    </row>
+    <row r="7627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7627" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7627" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7627" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7628" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7628" s="9"/>
+      <c r="C7628" s="10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7629" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B7629" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7629" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7630" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B7630" s="9"/>
+      <c r="C7630" s="10"/>
+    </row>
+    <row r="7631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7631" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B7631" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7631" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7632" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7632" s="20"/>
+      <c r="C7632" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="87">
-    <mergeCell ref="B6669:C6669"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="C6031:C6032"/>
-    <mergeCell ref="B6492:C6492"/>
-    <mergeCell ref="C6503:C6504"/>
-    <mergeCell ref="C6614:C6615"/>
-    <mergeCell ref="B5725:C5725"/>
-    <mergeCell ref="B6020:C6020"/>
-    <mergeCell ref="B5607:C5607"/>
-    <mergeCell ref="B5430:C5430"/>
-    <mergeCell ref="B5489:C5489"/>
-    <mergeCell ref="B5548:C5548"/>
-    <mergeCell ref="C5563:C5564"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5147"/>
-    <mergeCell ref="B5149:B5151"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5083:C5084"/>
-    <mergeCell ref="C5090:C5091"/>
-    <mergeCell ref="C5024:C5025"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4615:C4616"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4726:C4727"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3896:C3896"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3675:C3676"/>
-    <mergeCell ref="B3257:B3259"/>
-    <mergeCell ref="B3261:B3263"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="C3202:C3203"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3077:C3078"/>
-    <mergeCell ref="C3136:C3137"/>
-    <mergeCell ref="C3195:C3196"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2838:C2839"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="B2657:C2657"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2727:C2728"/>
-    <mergeCell ref="C1307:C1308"/>
-    <mergeCell ref="C1314:C1315"/>
-    <mergeCell ref="B1369:B1371"/>
-    <mergeCell ref="B1373:B1375"/>
-    <mergeCell ref="C2255:C2256"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="B1890:C1890"/>
-    <mergeCell ref="B1831:C1831"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="B1713:C1713"/>
-    <mergeCell ref="C1787:C1788"/>
-    <mergeCell ref="B1654:C1654"/>
+  <mergeCells count="101">
+    <mergeCell ref="B7613:C7613"/>
+    <mergeCell ref="C7451:C7452"/>
+    <mergeCell ref="B7436:C7436"/>
+    <mergeCell ref="C7558:C7559"/>
+    <mergeCell ref="B7209:B7211"/>
+    <mergeCell ref="B7318:C7318"/>
+    <mergeCell ref="C6978:C6979"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7035"/>
+    <mergeCell ref="B7037:B7039"/>
+    <mergeCell ref="C6853:C6854"/>
+    <mergeCell ref="C6912:C6913"/>
+    <mergeCell ref="C6971:C6972"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="A139:C144"/>
+    <mergeCell ref="A145:C145"/>
     <mergeCell ref="A24:C27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
@@ -26167,17 +29280,71 @@
     <mergeCell ref="B828:C828"/>
     <mergeCell ref="C839:C840"/>
     <mergeCell ref="B179:C179"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="A139:C144"/>
-    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="C1307:C1308"/>
+    <mergeCell ref="C1314:C1315"/>
+    <mergeCell ref="B1369:B1371"/>
+    <mergeCell ref="B1373:B1375"/>
+    <mergeCell ref="C2255:C2256"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="B1890:C1890"/>
+    <mergeCell ref="B1831:C1831"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="B1713:C1713"/>
+    <mergeCell ref="C1787:C1788"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2838:C2839"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B2657:C2657"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2727:C2728"/>
+    <mergeCell ref="C3202:C3203"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3077:C3078"/>
+    <mergeCell ref="C3136:C3137"/>
+    <mergeCell ref="C3195:C3196"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3675:C3676"/>
+    <mergeCell ref="B3257:B3259"/>
+    <mergeCell ref="B3261:B3263"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4726:C4727"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3896:C3896"/>
     <mergeCell ref="C4143:C4144"/>
     <mergeCell ref="B4191:C4191"/>
     <mergeCell ref="B4014:C4014"/>
     <mergeCell ref="C4025:C4026"/>
     <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C5024:C5025"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4615:C4616"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5147"/>
+    <mergeCell ref="B5149:B5151"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5083:C5084"/>
+    <mergeCell ref="C5090:C5091"/>
+    <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="B6020:C6020"/>
+    <mergeCell ref="B5607:C5607"/>
+    <mergeCell ref="B5430:C5430"/>
+    <mergeCell ref="B5489:C5489"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
+    <mergeCell ref="B6669:C6669"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="C6031:C6032"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6503:C6504"/>
+    <mergeCell ref="C6614:C6615"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB5C5A1-2E7E-4F7C-803D-90B3BAB72959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE479A29-F3A7-4A31-9B1C-6F6FE0F62F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7662</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$8496</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3270" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3557" uniqueCount="398">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -7434,9 +7434,6 @@
     <t>ADC (77)</t>
   </si>
   <si>
-    <t>CLI (78)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Sets the </t>
     </r>
@@ -7932,6 +7929,675 @@
       </rPr>
       <t>.L.</t>
     </r>
+  </si>
+  <si>
+    <t>Program Counter Relative Long</t>
+  </si>
+  <si>
+    <t>SEI (78)</t>
+  </si>
+  <si>
+    <t>BRL (82)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (83)</t>
+  </si>
+  <si>
+    <t>Stack Relative (Write)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STY (84)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (85)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>STX (86)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (87)</t>
+  </si>
+  <si>
+    <t>Direct Indirect Long (Write)</t>
+  </si>
+  <si>
+    <t>DEY (88)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>BIT (89)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &amp; Operand.L).</t>
+    </r>
+  </si>
+  <si>
+    <t>TXA (8A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>PHB (8B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>STY (8C)</t>
+  </si>
+  <si>
+    <t>Absolute (Write)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (8D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STX (8E)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sets Operand to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (8F)</t>
+  </si>
+  <si>
+    <t>Absolute Long (Write)</t>
+  </si>
+  <si>
+    <t>Write to Address:Bank</t>
   </si>
 </sst>
 </file>
@@ -8532,7 +9198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C7632"/>
+  <dimension ref="A1:C8452"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -23166,10 +23832,10 @@
     </row>
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="4"/>
-      <c r="B5784" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5784" s="25"/>
+      <c r="B5784" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5784" s="31"/>
     </row>
     <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5785" s="12" t="s">
@@ -27480,7 +28146,7 @@
     </row>
     <row r="7081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7081" s="1" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="B7081" s="2" t="s">
         <v>22</v>
@@ -27544,7 +28210,7 @@
       </c>
       <c r="B7087" s="9"/>
       <c r="C7087" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27567,7 +28233,7 @@
     </row>
     <row r="7140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7140" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7140" s="2" t="s">
         <v>24</v>
@@ -27834,7 +28500,7 @@
     </row>
     <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7199" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B7199" s="2" t="s">
         <v>24</v>
@@ -27927,7 +28593,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B7209" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
@@ -27961,7 +28627,7 @@
     </row>
     <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7258" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B7258" s="2" t="s">
         <v>22</v>
@@ -28025,7 +28691,7 @@
       </c>
       <c r="B7264" s="9"/>
       <c r="C7264" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28048,7 +28714,7 @@
     </row>
     <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7317" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B7317" s="2" t="s">
         <v>6</v>
@@ -28060,7 +28726,7 @@
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
       <c r="B7318" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C7318" s="31"/>
     </row>
@@ -28132,7 +28798,7 @@
       </c>
       <c r="B7325" s="9"/>
       <c r="C7325" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28172,7 +28838,7 @@
         <v>5.2</v>
       </c>
       <c r="B7330" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C7330" s="10" t="s">
         <v>277</v>
@@ -28207,7 +28873,7 @@
     </row>
     <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7376" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B7376" s="2" t="s">
         <v>24</v>
@@ -28291,7 +28957,7 @@
       </c>
       <c r="B7384" s="9"/>
       <c r="C7384" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28474,7 +29140,7 @@
     </row>
     <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7435" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B7435" s="2" t="s">
         <v>98</v>
@@ -28670,7 +29336,7 @@
     </row>
     <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7494" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B7494" s="2" t="s">
         <v>19</v>
@@ -28929,7 +29595,7 @@
     </row>
     <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7553" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B7553" s="2" t="s">
         <v>15</v>
@@ -28973,7 +29639,7 @@
       </c>
       <c r="B7557" s="9"/>
       <c r="C7557" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29055,7 +29721,7 @@
     </row>
     <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7612" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B7612" s="2" t="s">
         <v>6</v>
@@ -29067,7 +29733,7 @@
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
       <c r="B7613" s="30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C7613" s="31"/>
     </row>
@@ -29119,21 +29785,21 @@
       </c>
       <c r="B7618" s="9"/>
       <c r="C7618" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7619" s="8"/>
       <c r="B7619" s="9"/>
       <c r="C7619" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7620" s="8"/>
       <c r="B7620" s="9"/>
       <c r="C7620" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29203,7 +29869,7 @@
       </c>
       <c r="B7628" s="9"/>
       <c r="C7628" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29211,7 +29877,7 @@
         <v>6.2</v>
       </c>
       <c r="B7629" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7629" s="10" t="s">
         <v>47</v>
@@ -29242,9 +29908,1677 @@
       <c r="B7632" s="20"/>
       <c r="C7632" s="22"/>
     </row>
+    <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7671" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7671" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7671" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7672" s="4"/>
+      <c r="B7672" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="C7672" s="31"/>
+    </row>
+    <row r="7673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7673" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7673" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7673" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7674" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7674" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7674" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7675" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7675" s="9"/>
+      <c r="C7675" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7676" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7676" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7676" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7677" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7677" s="9"/>
+      <c r="C7677" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7678" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7678" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7678" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7679" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7679" s="9"/>
+      <c r="C7679" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7680" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7680" s="9"/>
+      <c r="C7680" s="10"/>
+    </row>
+    <row r="7681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7681" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7681" s="9"/>
+      <c r="C7681" s="10" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7682" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7682" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7682" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7683" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7683" s="20"/>
+      <c r="C7683" s="22"/>
+    </row>
+    <row r="7730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7730" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7730" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7730" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7731" s="4"/>
+      <c r="B7731" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7731" s="25"/>
+    </row>
+    <row r="7732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7732" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7732" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7732" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7733" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7733" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7733" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7734" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7734" s="9"/>
+      <c r="C7734" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7735" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7735" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7735" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7736" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B7736" s="9"/>
+      <c r="C7736" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7737" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7737" s="9"/>
+      <c r="C7737" s="10"/>
+    </row>
+    <row r="7738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7738" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7738" s="9"/>
+      <c r="C7738" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7739" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7739" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7739" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7740" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7740" s="9"/>
+      <c r="C7740" s="10"/>
+    </row>
+    <row r="7741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7741" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7741" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7741" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7742" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7742" s="20"/>
+      <c r="C7742" s="22"/>
+    </row>
+    <row r="7789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7789" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7789" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7789" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7790" s="4"/>
+      <c r="B7790" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7790" s="25"/>
+    </row>
+    <row r="7791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7791" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7791" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7791" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7792" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7792" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7792" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7793" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7793" s="9"/>
+      <c r="C7793" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7794" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7794" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7794" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7795" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B7795" s="16"/>
+      <c r="C7795" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7796" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7796" s="16"/>
+      <c r="C7796" s="23"/>
+    </row>
+    <row r="7797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7797" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7797" s="9"/>
+      <c r="C7797" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7798" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7798" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7798" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7799" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7799" s="9"/>
+      <c r="C7799" s="10"/>
+    </row>
+    <row r="7800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7800" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7800" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7800" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7801" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7801" s="20"/>
+      <c r="C7801" s="22"/>
+    </row>
+    <row r="7848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7848" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7848" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7848" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7849" s="4"/>
+      <c r="B7849" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7849" s="25"/>
+    </row>
+    <row r="7850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7850" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7850" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7850" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7851" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7851" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7851" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7852" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7852" s="9"/>
+      <c r="C7852" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7853" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7853" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7853" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7854" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B7854" s="16"/>
+      <c r="C7854" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7855" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7855" s="16"/>
+      <c r="C7855" s="23"/>
+    </row>
+    <row r="7856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7856" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7856" s="9"/>
+      <c r="C7856" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7857" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7857" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7857" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7858" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7858" s="9"/>
+      <c r="C7858" s="10"/>
+    </row>
+    <row r="7859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7859" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7859" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7859" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7860" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7860" s="20"/>
+      <c r="C7860" s="22"/>
+    </row>
+    <row r="7907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7907" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7907" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7907" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7908" s="4"/>
+      <c r="B7908" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7908" s="25"/>
+    </row>
+    <row r="7909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7909" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7909" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7909" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7910" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7910" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7910" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7911" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7911" s="9"/>
+      <c r="C7911" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7912" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7912" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7912" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7913" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B7913" s="16"/>
+      <c r="C7913" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7914" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7914" s="16"/>
+      <c r="C7914" s="23"/>
+    </row>
+    <row r="7915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7915" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7915" s="9"/>
+      <c r="C7915" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7916" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B7916" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7916" s="10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7917" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7917" s="9"/>
+      <c r="C7917" s="10"/>
+    </row>
+    <row r="7918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7918" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7918" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7918" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7919" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7919" s="20"/>
+      <c r="C7919" s="22"/>
+    </row>
+    <row r="7966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7966" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7966" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7966" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7967" s="4"/>
+      <c r="B7967" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7967" s="25"/>
+    </row>
+    <row r="7968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7968" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7968" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7968" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7969" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7969" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7969" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7970" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7970" s="9"/>
+      <c r="C7970" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7971" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B7971" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7971" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7972" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B7972" s="16"/>
+      <c r="C7972" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7973" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7973" s="16"/>
+      <c r="C7973" s="23"/>
+    </row>
+    <row r="7974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7974" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B7974" s="9"/>
+      <c r="C7974" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7975" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B7975" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7975" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7976" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7976" s="9"/>
+      <c r="C7976" s="10"/>
+    </row>
+    <row r="7977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7977" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B7977" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7977" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7978" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7978" s="9"/>
+      <c r="C7978" s="10"/>
+    </row>
+    <row r="7979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7979" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B7979" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7979" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7980" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7980" s="9"/>
+      <c r="C7980" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7981" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B7981" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7981" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7982" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B7982" s="9"/>
+      <c r="C7982" s="10"/>
+    </row>
+    <row r="7983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7983" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B7983" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7983" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7984" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7984" s="20"/>
+      <c r="C7984" s="22"/>
+    </row>
+    <row r="8025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8025" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8025" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8025" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8026" s="4"/>
+      <c r="B8026" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8026" s="25"/>
+    </row>
+    <row r="8027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8027" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8027" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8027" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8028" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8028" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8028" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8029" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8029" s="9"/>
+      <c r="C8029" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8030" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B8030" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8030" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8031" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8031" s="9"/>
+      <c r="C8031" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8032" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8032" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8032" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8033" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8033" s="20"/>
+      <c r="C8033" s="22"/>
+    </row>
+    <row r="8084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8084" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B8084" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8084" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8085" s="4"/>
+      <c r="B8085" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8085" s="25"/>
+    </row>
+    <row r="8086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8086" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8086" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8086" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8087" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8087" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8087" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8088" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8088" s="9"/>
+      <c r="C8088" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8089" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B8089" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8089" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8090" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8090" s="9"/>
+      <c r="C8090" s="10" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8091" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8091" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8091" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8092" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8092" s="20"/>
+      <c r="C8092" s="22"/>
+    </row>
+    <row r="8143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8143" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8143" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8143" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8144" s="4"/>
+      <c r="B8144" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8144" s="25"/>
+    </row>
+    <row r="8145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8145" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8145" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8145" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8146" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8146" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8146" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8147" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8147" s="9"/>
+      <c r="C8147" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8148" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B8148" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8148" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8149" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8149" s="9"/>
+      <c r="C8149" s="10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="8150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8150" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8150" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8150" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8151" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8151" s="20"/>
+      <c r="C8151" s="22"/>
+    </row>
+    <row r="8202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8202" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B8202" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8202" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8203" s="4"/>
+      <c r="B8203" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8203" s="25"/>
+    </row>
+    <row r="8204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8204" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8204" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8204" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8205" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8205" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8205" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8206" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8206" s="9"/>
+      <c r="C8206" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8207" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8207" s="9"/>
+      <c r="C8207" s="10"/>
+    </row>
+    <row r="8208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8208" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8208" s="9"/>
+      <c r="C8208" s="10"/>
+    </row>
+    <row r="8209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8209" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8209" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8209" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8210" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8210" s="9"/>
+      <c r="C8210" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8211" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8211" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8211" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8212" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8212" s="20"/>
+      <c r="C8212" s="22"/>
+    </row>
+    <row r="8261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8261" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8261" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8261" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8262" s="4"/>
+      <c r="B8262" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="C8262" s="25"/>
+    </row>
+    <row r="8263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8263" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8263" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8263" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8264" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8264" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8264" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8265" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8265" s="9"/>
+      <c r="C8265" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8266" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8266" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8266" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8267" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8267" s="9"/>
+      <c r="C8267" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8268" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8268" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8268" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8269" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8269" s="9"/>
+      <c r="C8269" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8270" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B8270" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8270" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8271" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8271" s="9"/>
+      <c r="C8271" s="10"/>
+    </row>
+    <row r="8272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8272" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8272" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8272" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8273" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8273" s="20"/>
+      <c r="C8273" s="22"/>
+    </row>
+    <row r="8320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8320" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B8320" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8320" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8321" s="4"/>
+      <c r="B8321" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="C8321" s="25"/>
+    </row>
+    <row r="8322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8322" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8322" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8322" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8323" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8323" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8323" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8324" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8324" s="9"/>
+      <c r="C8324" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8325" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8325" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8325" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8326" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8326" s="9"/>
+      <c r="C8326" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8327" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8327" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8327" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8328" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8328" s="9"/>
+      <c r="C8328" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8329" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B8329" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8329" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8330" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8330" s="9"/>
+      <c r="C8330" s="10"/>
+    </row>
+    <row r="8331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8331" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8331" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8331" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8332" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8332" s="20"/>
+      <c r="C8332" s="22"/>
+    </row>
+    <row r="8379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8379" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B8379" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8379" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8380" s="4"/>
+      <c r="B8380" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="C8380" s="25"/>
+    </row>
+    <row r="8381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8381" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8381" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8381" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8382" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8382" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8382" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8383" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8383" s="9"/>
+      <c r="C8383" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8384" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8384" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8384" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8385" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8385" s="9"/>
+      <c r="C8385" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8386" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8386" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8386" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8387" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8387" s="9"/>
+      <c r="C8387" s="10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8388" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B8388" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8388" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8389" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8389" s="9"/>
+      <c r="C8389" s="10"/>
+    </row>
+    <row r="8390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8390" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8390" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8390" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8391" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8391" s="20"/>
+      <c r="C8391" s="22"/>
+    </row>
+    <row r="8438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8438" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B8438" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8438" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8439" s="4"/>
+      <c r="B8439" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="C8439" s="25"/>
+    </row>
+    <row r="8440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8440" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8440" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8440" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8441" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8441" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8441" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8442" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8442" s="9"/>
+      <c r="C8442" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8443" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8443" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8443" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8444" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8444" s="9"/>
+      <c r="C8444" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8445" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8445" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8445" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8446" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8446" s="9"/>
+      <c r="C8446" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8447" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8447" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8447" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8448" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8448" s="9"/>
+      <c r="C8448" s="10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8449" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B8449" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="C8449" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8450" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8450" s="9"/>
+      <c r="C8450" s="10"/>
+    </row>
+    <row r="8451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8451" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8451" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8451" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8452" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8452" s="20"/>
+      <c r="C8452" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="101">
+  <mergeCells count="103">
     <mergeCell ref="B7613:C7613"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B7672:C7672"/>
     <mergeCell ref="C7451:C7452"/>
     <mergeCell ref="B7436:C7436"/>
     <mergeCell ref="C7558:C7559"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE479A29-F3A7-4A31-9B1C-6F6FE0F62F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC17F24-02BC-4AFA-AD54-B53BBFD981A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$8496</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$9323</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3557" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3697" uniqueCount="408">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -1016,9 +1016,6 @@
     <t>INC (1A)</t>
   </si>
   <si>
-    <t>TSC (1B)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Sets </t>
     </r>
@@ -8598,6 +8595,83 @@
   </si>
   <si>
     <t>Write to Address:Bank</t>
+  </si>
+  <si>
+    <t>TCS (1B)</t>
+  </si>
+  <si>
+    <t>BCC (90)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (91)</t>
+  </si>
+  <si>
+    <t>Direct Indirect Indexed (d),y (Write)</t>
+  </si>
+  <si>
+    <t>STA (92)</t>
+  </si>
+  <si>
+    <t>Direct Indirect (Write)</t>
+  </si>
+  <si>
+    <t>STA (93)</t>
+  </si>
+  <si>
+    <t>Stack Relative Indirect Indexed (Write)</t>
+  </si>
+  <si>
+    <t>STY (94)</t>
+  </si>
+  <si>
+    <t>STA (95)</t>
   </si>
 </sst>
 </file>
@@ -9198,7 +9272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C8452"/>
+  <dimension ref="A1:C8807"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9281,7 +9355,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>35</v>
@@ -9299,7 +9373,7 @@
         <v>3.2</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>36</v>
@@ -9325,14 +9399,14 @@
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9340,7 +9414,7 @@
         <v>4.2</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>59</v>
@@ -9352,7 +9426,7 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9392,7 +9466,7 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9515,7 +9589,7 @@
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9591,7 +9665,7 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>9</v>
@@ -9603,7 +9677,7 @@
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9698,7 +9772,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>35</v>
@@ -9716,7 +9790,7 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>36</v>
@@ -9728,7 +9802,7 @@
       </c>
       <c r="B129" s="9"/>
       <c r="C129" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9736,7 +9810,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C130" s="14" t="s">
         <v>62</v>
@@ -9748,7 +9822,7 @@
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9788,7 +9862,7 @@
       </c>
       <c r="B135" s="9"/>
       <c r="C135" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9910,7 +9984,7 @@
       </c>
       <c r="B184" s="9"/>
       <c r="C184" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9944,7 +10018,7 @@
       </c>
       <c r="B188" s="9"/>
       <c r="C188" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10085,7 +10159,7 @@
       </c>
       <c r="B249" s="9"/>
       <c r="C249" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10226,7 +10300,7 @@
       </c>
       <c r="B306" s="9"/>
       <c r="C306" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10367,7 +10441,7 @@
       </c>
       <c r="B367" s="9"/>
       <c r="C367" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10567,7 +10641,7 @@
       </c>
       <c r="B430" s="9"/>
       <c r="C430" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10650,7 +10724,7 @@
       </c>
       <c r="B479" s="9"/>
       <c r="C479" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10658,7 +10732,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C480" s="10" t="s">
         <v>49</v>
@@ -10670,7 +10744,7 @@
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10757,7 +10831,7 @@
       </c>
       <c r="B538" s="9"/>
       <c r="C538" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10844,7 +10918,7 @@
       </c>
       <c r="B597" s="9"/>
       <c r="C597" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10933,7 +11007,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B657" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C657" s="10" t="s">
         <v>75</v>
@@ -10951,7 +11025,7 @@
         <v>3.2</v>
       </c>
       <c r="B659" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C659" s="10" t="s">
         <v>76</v>
@@ -11106,7 +11180,7 @@
       </c>
       <c r="B721" s="9"/>
       <c r="C721" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11251,7 +11325,7 @@
       </c>
       <c r="B778" s="9"/>
       <c r="C778" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11396,7 +11470,7 @@
       </c>
       <c r="B839" s="9"/>
       <c r="C839" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11566,7 +11640,7 @@
       </c>
       <c r="B898" s="9"/>
       <c r="C898" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11644,7 +11718,7 @@
         <v>72</v>
       </c>
       <c r="C950" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11658,7 +11732,7 @@
       </c>
       <c r="B952" s="9"/>
       <c r="C952" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11674,7 +11748,7 @@
       </c>
       <c r="B954" s="9"/>
       <c r="C954" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11692,7 +11766,7 @@
       </c>
       <c r="B956" s="9"/>
       <c r="C956" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11854,7 +11928,7 @@
       <c r="A1019" s="8"/>
       <c r="B1019" s="9"/>
       <c r="C1019" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11895,7 +11969,7 @@
       </c>
       <c r="B1024" s="9"/>
       <c r="C1024" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12054,7 +12128,7 @@
       </c>
       <c r="B1077" s="9"/>
       <c r="C1077" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="1078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12141,7 +12215,7 @@
       </c>
       <c r="B1128" s="9"/>
       <c r="C1128" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12241,7 +12315,7 @@
       </c>
       <c r="B1140" s="9"/>
       <c r="C1140" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12382,7 +12456,7 @@
       </c>
       <c r="B1193" s="9"/>
       <c r="C1193" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12503,7 +12577,7 @@
       </c>
       <c r="B1248" s="9"/>
       <c r="C1248" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12542,7 +12616,7 @@
       </c>
       <c r="B1253" s="9"/>
       <c r="C1253" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12577,7 +12651,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
       <c r="B1300" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C1300" s="31"/>
     </row>
@@ -12645,7 +12719,7 @@
       </c>
       <c r="B1307" s="9"/>
       <c r="C1307" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12702,7 +12776,7 @@
       </c>
       <c r="B1314" s="9"/>
       <c r="C1314" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12854,7 +12928,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C1369" s="14" t="s">
         <v>37</v>
@@ -12882,7 +12956,7 @@
         <v>5.2</v>
       </c>
       <c r="B1373" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C1373" s="10" t="s">
         <v>69</v>
@@ -12938,7 +13012,7 @@
       </c>
       <c r="B1380" s="9"/>
       <c r="C1380" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13153,7 +13227,7 @@
       <c r="A1487" s="8"/>
       <c r="B1487" s="9"/>
       <c r="C1487" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13194,7 +13268,7 @@
       </c>
       <c r="B1492" s="9"/>
       <c r="C1492" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13281,7 +13355,7 @@
       </c>
       <c r="B1541" s="9"/>
       <c r="C1541" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13304,7 +13378,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="1" t="s">
-        <v>120</v>
+        <v>397</v>
       </c>
       <c r="B1594" s="2" t="s">
         <v>22</v>
@@ -13368,7 +13442,7 @@
       </c>
       <c r="B1600" s="9"/>
       <c r="C1600" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13391,7 +13465,7 @@
     </row>
     <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1653" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B1653" s="2" t="s">
         <v>6</v>
@@ -13513,7 +13587,7 @@
       </c>
       <c r="B1665" s="9"/>
       <c r="C1665" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13554,7 +13628,7 @@
     </row>
     <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1712" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1712" s="2" t="s">
         <v>24</v>
@@ -13566,7 +13640,7 @@
     <row r="1713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1713" s="4"/>
       <c r="B1713" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1713" s="31"/>
     </row>
@@ -13645,7 +13719,7 @@
       <c r="A1721" s="8"/>
       <c r="B1721" s="9"/>
       <c r="C1721" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13659,7 +13733,7 @@
       <c r="A1723" s="8"/>
       <c r="B1723" s="9"/>
       <c r="C1723" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13700,7 +13774,7 @@
       </c>
       <c r="B1728" s="9"/>
       <c r="C1728" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13723,7 +13797,7 @@
     </row>
     <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1771" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B1771" s="2" t="s">
         <v>98</v>
@@ -13735,7 +13809,7 @@
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="4"/>
       <c r="B1772" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C1772" s="31"/>
     </row>
@@ -13807,7 +13881,7 @@
       </c>
       <c r="B1779" s="9"/>
       <c r="C1779" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13861,7 +13935,7 @@
         <v>5.2</v>
       </c>
       <c r="B1786" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C1786" s="10" t="s">
         <v>47</v>
@@ -13873,7 +13947,7 @@
       </c>
       <c r="B1787" s="9"/>
       <c r="C1787" s="32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13886,7 +13960,7 @@
         <v>6.2</v>
       </c>
       <c r="B1789" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C1789" s="10" t="s">
         <v>47</v>
@@ -13919,7 +13993,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1830" s="2" t="s">
         <v>19</v>
@@ -13931,7 +14005,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="4"/>
       <c r="B1831" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1831" s="31"/>
     </row>
@@ -14023,7 +14097,7 @@
       </c>
       <c r="B1840" s="9"/>
       <c r="C1840" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14057,7 +14131,7 @@
       </c>
       <c r="B1844" s="9"/>
       <c r="C1844" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14080,7 +14154,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1889" s="2" t="s">
         <v>6</v>
@@ -14092,7 +14166,7 @@
     <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1890" s="4"/>
       <c r="B1890" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C1890" s="31"/>
     </row>
@@ -14184,7 +14258,7 @@
       </c>
       <c r="B1899" s="9"/>
       <c r="C1899" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14192,7 +14266,7 @@
         <v>4.2</v>
       </c>
       <c r="B1900" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C1900" s="10" t="s">
         <v>35</v>
@@ -14210,7 +14284,7 @@
         <v>5.2</v>
       </c>
       <c r="B1902" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C1902" s="10" t="s">
         <v>36</v>
@@ -14222,7 +14296,7 @@
       </c>
       <c r="B1903" s="9"/>
       <c r="C1903" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14245,7 +14319,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B1948" s="2" t="s">
         <v>6</v>
@@ -14309,7 +14383,7 @@
       </c>
       <c r="B1954" s="9"/>
       <c r="C1954" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14397,7 +14471,7 @@
       </c>
       <c r="B1964" s="9"/>
       <c r="C1964" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14420,7 +14494,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2007" s="2" t="s">
         <v>14</v>
@@ -14432,7 +14506,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="4"/>
       <c r="B2008" s="24" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C2008" s="25"/>
     </row>
@@ -14512,7 +14586,7 @@
         <v>3.2</v>
       </c>
       <c r="B2016" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2016" s="10" t="s">
         <v>57</v>
@@ -14530,7 +14604,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C2018" s="14" t="s">
         <v>73</v>
@@ -14566,7 +14640,7 @@
         <v>6.2</v>
       </c>
       <c r="B2022" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C2022" s="14" t="s">
         <v>35</v>
@@ -14584,7 +14658,7 @@
         <v>7.2</v>
       </c>
       <c r="B2024" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C2024" s="14" t="s">
         <v>36</v>
@@ -14596,7 +14670,7 @@
       </c>
       <c r="B2025" s="9"/>
       <c r="C2025" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14619,7 +14693,7 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2066" s="2" t="s">
         <v>24</v>
@@ -14683,7 +14757,7 @@
       </c>
       <c r="B2072" s="9"/>
       <c r="C2072" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14717,7 +14791,7 @@
       </c>
       <c r="B2076" s="9"/>
       <c r="C2076" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14740,7 +14814,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2125" s="2" t="s">
         <v>15</v>
@@ -14840,7 +14914,7 @@
       </c>
       <c r="B2135" s="9"/>
       <c r="C2135" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14863,7 +14937,7 @@
     </row>
     <row r="2184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2184" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B2184" s="2" t="s">
         <v>15</v>
@@ -14963,7 +15037,7 @@
       </c>
       <c r="B2194" s="9"/>
       <c r="C2194" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14986,7 +15060,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2243" s="2" t="s">
         <v>19</v>
@@ -15104,7 +15178,7 @@
       </c>
       <c r="B2255" s="9"/>
       <c r="C2255" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15150,7 +15224,7 @@
     </row>
     <row r="2302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2302" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2302" s="2" t="s">
         <v>6</v>
@@ -15304,7 +15378,7 @@
       </c>
       <c r="B2318" s="9"/>
       <c r="C2318" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15327,7 +15401,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B2361" s="2" t="s">
         <v>24</v>
@@ -15401,7 +15475,7 @@
       </c>
       <c r="B2369" s="9"/>
       <c r="C2369" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15409,10 +15483,10 @@
         <v>3.2</v>
       </c>
       <c r="B2370" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C2370" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15421,7 +15495,7 @@
       </c>
       <c r="B2371" s="9"/>
       <c r="C2371" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15444,7 +15518,7 @@
     </row>
     <row r="2420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2420" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B2420" s="2" t="s">
         <v>22</v>
@@ -15508,7 +15582,7 @@
       </c>
       <c r="B2426" s="9"/>
       <c r="C2426" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15531,7 +15605,7 @@
     </row>
     <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2479" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B2479" s="2" t="s">
         <v>22</v>
@@ -15595,7 +15669,7 @@
       </c>
       <c r="B2485" s="9"/>
       <c r="C2485" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15618,7 +15692,7 @@
     </row>
     <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2538" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2538" s="2" t="s">
         <v>19</v>
@@ -15698,10 +15772,10 @@
         <v>3.2</v>
       </c>
       <c r="B2547" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C2547" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15716,7 +15790,7 @@
         <v>4.2</v>
       </c>
       <c r="B2549" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C2549" s="14" t="s">
         <v>45</v>
@@ -15728,7 +15802,7 @@
       </c>
       <c r="B2550" s="9"/>
       <c r="C2550" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15751,7 +15825,7 @@
     </row>
     <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2597" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2597" s="2" t="s">
         <v>24</v>
@@ -15855,7 +15929,7 @@
       </c>
       <c r="B2607" s="9"/>
       <c r="C2607" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15878,7 +15952,7 @@
     </row>
     <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2656" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B2656" s="2" t="s">
         <v>24</v>
@@ -15982,7 +16056,7 @@
       </c>
       <c r="B2666" s="9"/>
       <c r="C2666" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16005,7 +16079,7 @@
     </row>
     <row r="2715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2715" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2715" s="2" t="s">
         <v>6</v>
@@ -16127,7 +16201,7 @@
       </c>
       <c r="B2727" s="9"/>
       <c r="C2727" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16173,7 +16247,7 @@
     </row>
     <row r="2774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2774" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2774" s="2" t="s">
         <v>19</v>
@@ -16297,7 +16371,7 @@
       </c>
       <c r="B2786" s="9"/>
       <c r="C2786" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16320,7 +16394,7 @@
     </row>
     <row r="2833" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2833" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B2833" s="2" t="s">
         <v>22</v>
@@ -16364,7 +16438,7 @@
       </c>
       <c r="B2837" s="9"/>
       <c r="C2837" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16375,7 +16449,7 @@
         <v>72</v>
       </c>
       <c r="C2838" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16389,7 +16463,7 @@
       </c>
       <c r="B2840" s="9"/>
       <c r="C2840" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16405,7 +16479,7 @@
       </c>
       <c r="B2842" s="9"/>
       <c r="C2842" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16423,7 +16497,7 @@
       </c>
       <c r="B2844" s="9"/>
       <c r="C2844" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16446,7 +16520,7 @@
     </row>
     <row r="2892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2892" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2892" s="2" t="s">
         <v>19</v>
@@ -16585,7 +16659,7 @@
       <c r="A2907" s="8"/>
       <c r="B2907" s="9"/>
       <c r="C2907" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16626,7 +16700,7 @@
       </c>
       <c r="B2912" s="9"/>
       <c r="C2912" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16649,7 +16723,7 @@
     </row>
     <row r="2951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2951" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2951" s="2" t="s">
         <v>19</v>
@@ -16785,7 +16859,7 @@
       </c>
       <c r="B2965" s="9"/>
       <c r="C2965" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16808,7 +16882,7 @@
     </row>
     <row r="3010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3010" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3010" s="2" t="s">
         <v>98</v>
@@ -16872,7 +16946,7 @@
       </c>
       <c r="B3016" s="9"/>
       <c r="C3016" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16972,7 +17046,7 @@
       </c>
       <c r="B3028" s="9"/>
       <c r="C3028" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16995,7 +17069,7 @@
     </row>
     <row r="3069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3069" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B3069" s="2" t="s">
         <v>24</v>
@@ -17075,7 +17149,7 @@
       </c>
       <c r="B3077" s="9"/>
       <c r="C3077" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17114,7 +17188,7 @@
       </c>
       <c r="B3082" s="9"/>
       <c r="C3082" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17147,7 +17221,7 @@
     </row>
     <row r="3128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3128" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B3128" s="2" t="s">
         <v>24</v>
@@ -17227,7 +17301,7 @@
       </c>
       <c r="B3136" s="9"/>
       <c r="C3136" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17266,7 +17340,7 @@
       </c>
       <c r="B3141" s="9"/>
       <c r="C3141" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17289,7 +17363,7 @@
     </row>
     <row r="3187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3187" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B3187" s="2" t="s">
         <v>6</v>
@@ -17369,7 +17443,7 @@
       </c>
       <c r="B3195" s="9"/>
       <c r="C3195" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17426,7 +17500,7 @@
       </c>
       <c r="B3202" s="9"/>
       <c r="C3202" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17482,7 +17556,7 @@
     </row>
     <row r="3246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3246" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3246" s="2" t="s">
         <v>6</v>
@@ -17588,7 +17662,7 @@
         <v>4.2</v>
       </c>
       <c r="B3257" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3257" s="10" t="s">
         <v>37</v>
@@ -17616,7 +17690,7 @@
         <v>5.2</v>
       </c>
       <c r="B3261" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3261" s="10" t="s">
         <v>69</v>
@@ -17672,7 +17746,7 @@
       </c>
       <c r="B3268" s="9"/>
       <c r="C3268" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17695,7 +17769,7 @@
     </row>
     <row r="3305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3305" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3305" s="2" t="s">
         <v>22</v>
@@ -17759,7 +17833,7 @@
       </c>
       <c r="B3311" s="9"/>
       <c r="C3311" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17782,7 +17856,7 @@
     </row>
     <row r="3364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3364" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B3364" s="2" t="s">
         <v>24</v>
@@ -17887,7 +17961,7 @@
       <c r="A3375" s="8"/>
       <c r="B3375" s="9"/>
       <c r="C3375" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17928,7 +18002,7 @@
       </c>
       <c r="B3380" s="27"/>
       <c r="C3380" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17951,7 +18025,7 @@
     </row>
     <row r="3423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3423" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B3423" s="2" t="s">
         <v>22</v>
@@ -18015,7 +18089,7 @@
       </c>
       <c r="B3429" s="9"/>
       <c r="C3429" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18038,7 +18112,7 @@
     </row>
     <row r="3482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3482" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B3482" s="2" t="s">
         <v>22</v>
@@ -18102,7 +18176,7 @@
       </c>
       <c r="B3488" s="9"/>
       <c r="C3488" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18125,7 +18199,7 @@
     </row>
     <row r="3541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3541" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B3541" s="2" t="s">
         <v>24</v>
@@ -18137,7 +18211,7 @@
     <row r="3542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3542" s="4"/>
       <c r="B3542" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3542" s="25"/>
     </row>
@@ -18216,7 +18290,7 @@
       <c r="A3550" s="8"/>
       <c r="B3550" s="9"/>
       <c r="C3550" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18230,7 +18304,7 @@
       <c r="A3552" s="8"/>
       <c r="B3552" s="9"/>
       <c r="C3552" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18271,7 +18345,7 @@
       </c>
       <c r="B3557" s="9"/>
       <c r="C3557" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18294,7 +18368,7 @@
     </row>
     <row r="3600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3600" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B3600" s="2" t="s">
         <v>24</v>
@@ -18306,7 +18380,7 @@
     <row r="3601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3601" s="4"/>
       <c r="B3601" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3601" s="25"/>
     </row>
@@ -18385,7 +18459,7 @@
       <c r="A3609" s="8"/>
       <c r="B3609" s="9"/>
       <c r="C3609" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18399,7 +18473,7 @@
       <c r="A3611" s="8"/>
       <c r="B3611" s="9"/>
       <c r="C3611" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18440,7 +18514,7 @@
       </c>
       <c r="B3616" s="9"/>
       <c r="C3616" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18463,7 +18537,7 @@
     </row>
     <row r="3659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3659" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B3659" s="2" t="s">
         <v>98</v>
@@ -18475,7 +18549,7 @@
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="4"/>
       <c r="B3660" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3660" s="31"/>
     </row>
@@ -18547,7 +18621,7 @@
       </c>
       <c r="B3667" s="9"/>
       <c r="C3667" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18601,7 +18675,7 @@
         <v>5.2</v>
       </c>
       <c r="B3674" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3674" s="14" t="s">
         <v>47</v>
@@ -18613,7 +18687,7 @@
       </c>
       <c r="B3675" s="9"/>
       <c r="C3675" s="32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18626,7 +18700,7 @@
         <v>6.2</v>
       </c>
       <c r="B3677" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3677" s="14" t="s">
         <v>47</v>
@@ -18659,7 +18733,7 @@
     </row>
     <row r="3718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3718" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B3718" s="2" t="s">
         <v>19</v>
@@ -18671,7 +18745,7 @@
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="4"/>
       <c r="B3719" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3719" s="25"/>
     </row>
@@ -18763,7 +18837,7 @@
       </c>
       <c r="B3728" s="9"/>
       <c r="C3728" s="14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18797,7 +18871,7 @@
       </c>
       <c r="B3732" s="9"/>
       <c r="C3732" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18820,7 +18894,7 @@
     </row>
     <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3777" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B3777" s="2" t="s">
         <v>6</v>
@@ -18894,7 +18968,7 @@
       </c>
       <c r="B3785" s="9"/>
       <c r="C3785" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18902,10 +18976,10 @@
         <v>3.2</v>
       </c>
       <c r="B3786" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C3786" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18914,7 +18988,7 @@
       </c>
       <c r="B3787" s="9"/>
       <c r="C3787" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18922,10 +18996,10 @@
         <v>4.2</v>
       </c>
       <c r="B3788" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C3788" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18940,7 +19014,7 @@
         <v>5.2</v>
       </c>
       <c r="B3790" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C3790" s="14" t="s">
         <v>45</v>
@@ -18952,7 +19026,7 @@
       </c>
       <c r="B3791" s="9"/>
       <c r="C3791" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18975,7 +19049,7 @@
     </row>
     <row r="3836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3836" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B3836" s="2" t="s">
         <v>6</v>
@@ -19019,7 +19093,7 @@
       </c>
       <c r="B3840" s="9"/>
       <c r="C3840" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19039,7 +19113,7 @@
       </c>
       <c r="B3842" s="9"/>
       <c r="C3842" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19127,7 +19201,7 @@
       </c>
       <c r="B3852" s="9"/>
       <c r="C3852" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19150,7 +19224,7 @@
     </row>
     <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3895" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B3895" s="2" t="s">
         <v>22</v>
@@ -19214,7 +19288,7 @@
       </c>
       <c r="B3901" s="9"/>
       <c r="C3901" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19237,7 +19311,7 @@
     </row>
     <row r="3954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3954" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B3954" s="2" t="s">
         <v>24</v>
@@ -19301,7 +19375,7 @@
       </c>
       <c r="B3960" s="9"/>
       <c r="C3960" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19335,7 +19409,7 @@
       </c>
       <c r="B3964" s="9"/>
       <c r="C3964" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19358,7 +19432,7 @@
     </row>
     <row r="4013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4013" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B4013" s="2" t="s">
         <v>98</v>
@@ -19370,7 +19444,7 @@
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
       <c r="B4014" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C4014" s="31"/>
     </row>
@@ -19422,7 +19496,7 @@
       </c>
       <c r="B4019" s="9"/>
       <c r="C4019" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19450,10 +19524,10 @@
         <v>3.2</v>
       </c>
       <c r="B4022" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4022" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19468,7 +19542,7 @@
         <v>4.2</v>
       </c>
       <c r="B4024" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4024" s="10" t="s">
         <v>47</v>
@@ -19480,7 +19554,7 @@
       </c>
       <c r="B4025" s="9"/>
       <c r="C4025" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19536,7 +19610,7 @@
     </row>
     <row r="4072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4072" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B4072" s="2" t="s">
         <v>15</v>
@@ -19636,7 +19710,7 @@
       </c>
       <c r="B4082" s="9"/>
       <c r="C4082" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19659,7 +19733,7 @@
     </row>
     <row r="4131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4131" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B4131" s="2" t="s">
         <v>19</v>
@@ -19777,7 +19851,7 @@
       </c>
       <c r="B4143" s="9"/>
       <c r="C4143" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19823,7 +19897,7 @@
     </row>
     <row r="4190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4190" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B4190" s="2" t="s">
         <v>6</v>
@@ -19977,7 +20051,7 @@
       </c>
       <c r="B4206" s="9"/>
       <c r="C4206" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20000,7 +20074,7 @@
     </row>
     <row r="4249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4249" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B4249" s="2" t="s">
         <v>15</v>
@@ -20066,10 +20140,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4256" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4256" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="C4256" s="10" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="4257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20078,7 +20152,7 @@
       </c>
       <c r="B4257" s="9"/>
       <c r="C4257" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20101,7 +20175,7 @@
     </row>
     <row r="4308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4308" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B4308" s="2" t="s">
         <v>22</v>
@@ -20165,7 +20239,7 @@
       </c>
       <c r="B4314" s="9"/>
       <c r="C4314" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20188,7 +20262,7 @@
     </row>
     <row r="4367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4367" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B4367" s="2" t="s">
         <v>22</v>
@@ -20252,7 +20326,7 @@
       </c>
       <c r="B4373" s="9"/>
       <c r="C4373" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20275,7 +20349,7 @@
     </row>
     <row r="4426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4426" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B4426" s="2" t="s">
         <v>15</v>
@@ -20341,7 +20415,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4433" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C4433" s="10" t="s">
         <v>57</v>
@@ -20353,7 +20427,7 @@
       </c>
       <c r="B4434" s="9"/>
       <c r="C4434" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20376,7 +20450,7 @@
     </row>
     <row r="4485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4485" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B4485" s="2" t="s">
         <v>15</v>
@@ -20388,7 +20462,7 @@
     <row r="4486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4486" s="4"/>
       <c r="B4486" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4486" s="25"/>
     </row>
@@ -20460,7 +20534,7 @@
       </c>
       <c r="B4493" s="9"/>
       <c r="C4493" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20483,7 +20557,7 @@
     </row>
     <row r="4544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4544" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4544" s="2" t="s">
         <v>24</v>
@@ -20587,7 +20661,7 @@
       </c>
       <c r="B4554" s="9"/>
       <c r="C4554" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20610,7 +20684,7 @@
     </row>
     <row r="4603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4603" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4603" s="2" t="s">
         <v>6</v>
@@ -20732,7 +20806,7 @@
       </c>
       <c r="B4615" s="9"/>
       <c r="C4615" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20778,7 +20852,7 @@
     </row>
     <row r="4662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4662" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B4662" s="2" t="s">
         <v>19</v>
@@ -20902,7 +20976,7 @@
       </c>
       <c r="B4674" s="9"/>
       <c r="C4674" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20925,7 +20999,7 @@
     </row>
     <row r="4721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4721" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4721" s="2" t="s">
         <v>22</v>
@@ -20969,7 +21043,7 @@
       </c>
       <c r="B4725" s="9"/>
       <c r="C4725" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20980,7 +21054,7 @@
         <v>72</v>
       </c>
       <c r="C4726" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20994,7 +21068,7 @@
       </c>
       <c r="B4728" s="9"/>
       <c r="C4728" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21010,7 +21084,7 @@
       </c>
       <c r="B4730" s="9"/>
       <c r="C4730" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21028,7 +21102,7 @@
       </c>
       <c r="B4732" s="9"/>
       <c r="C4732" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21051,7 +21125,7 @@
     </row>
     <row r="4780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4780" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B4780" s="2" t="s">
         <v>19</v>
@@ -21190,7 +21264,7 @@
       <c r="A4795" s="8"/>
       <c r="B4795" s="9"/>
       <c r="C4795" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21224,7 +21298,7 @@
       </c>
       <c r="B4799" s="9"/>
       <c r="C4799" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21247,7 +21321,7 @@
     </row>
     <row r="4839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4839" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B4839" s="2" t="s">
         <v>19</v>
@@ -21383,7 +21457,7 @@
       </c>
       <c r="B4853" s="9"/>
       <c r="C4853" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21406,7 +21480,7 @@
     </row>
     <row r="4898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4898" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B4898" s="2" t="s">
         <v>98</v>
@@ -21470,7 +21544,7 @@
       </c>
       <c r="B4904" s="9"/>
       <c r="C4904" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21570,7 +21644,7 @@
       </c>
       <c r="B4916" s="9"/>
       <c r="C4916" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21593,7 +21667,7 @@
     </row>
     <row r="4957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4957" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B4957" s="2" t="s">
         <v>98</v>
@@ -21605,7 +21679,7 @@
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="4"/>
       <c r="B4958" s="24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C4958" s="25"/>
     </row>
@@ -21657,7 +21731,7 @@
       </c>
       <c r="B4963" s="9"/>
       <c r="C4963" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21685,10 +21759,10 @@
         <v>3.2</v>
       </c>
       <c r="B4966" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4966" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21703,7 +21777,7 @@
         <v>4.2</v>
       </c>
       <c r="B4968" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4968" s="10" t="s">
         <v>47</v>
@@ -21715,7 +21789,7 @@
       </c>
       <c r="B4969" s="9"/>
       <c r="C4969" s="32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21771,7 +21845,7 @@
     </row>
     <row r="5016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5016" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5016" s="2" t="s">
         <v>24</v>
@@ -21851,7 +21925,7 @@
       </c>
       <c r="B5024" s="9"/>
       <c r="C5024" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21890,7 +21964,7 @@
       </c>
       <c r="B5029" s="9"/>
       <c r="C5029" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21913,7 +21987,7 @@
     </row>
     <row r="5075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5075" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B5075" s="2" t="s">
         <v>6</v>
@@ -21925,7 +21999,7 @@
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="4"/>
       <c r="B5076" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C5076" s="31"/>
     </row>
@@ -21993,7 +22067,7 @@
       </c>
       <c r="B5083" s="9"/>
       <c r="C5083" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22050,7 +22124,7 @@
       </c>
       <c r="B5090" s="9"/>
       <c r="C5090" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22096,7 +22170,7 @@
     </row>
     <row r="5134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5134" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5134" s="2" t="s">
         <v>6</v>
@@ -22202,7 +22276,7 @@
         <v>4.2</v>
       </c>
       <c r="B5145" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C5145" s="10" t="s">
         <v>37</v>
@@ -22230,7 +22304,7 @@
         <v>5.2</v>
       </c>
       <c r="B5149" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C5149" s="10" t="s">
         <v>69</v>
@@ -22286,7 +22360,7 @@
       </c>
       <c r="B5156" s="9"/>
       <c r="C5156" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22309,7 +22383,7 @@
     </row>
     <row r="5193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5193" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B5193" s="2" t="s">
         <v>22</v>
@@ -22373,7 +22447,7 @@
       </c>
       <c r="B5199" s="9"/>
       <c r="C5199" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22396,7 +22470,7 @@
     </row>
     <row r="5252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5252" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B5252" s="2" t="s">
         <v>24</v>
@@ -22501,7 +22575,7 @@
       <c r="A5263" s="8"/>
       <c r="B5263" s="9"/>
       <c r="C5263" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22542,7 +22616,7 @@
       </c>
       <c r="B5268" s="9"/>
       <c r="C5268" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22565,7 +22639,7 @@
     </row>
     <row r="5311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5311" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B5311" s="2" t="s">
         <v>15</v>
@@ -22631,10 +22705,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B5318" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5318" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22643,7 +22717,7 @@
       </c>
       <c r="B5319" s="9"/>
       <c r="C5319" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22666,7 +22740,7 @@
     </row>
     <row r="5370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5370" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B5370" s="2" t="s">
         <v>22</v>
@@ -22730,7 +22804,7 @@
       </c>
       <c r="B5376" s="9"/>
       <c r="C5376" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22753,7 +22827,7 @@
     </row>
     <row r="5429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5429" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B5429" s="2" t="s">
         <v>24</v>
@@ -22765,7 +22839,7 @@
     <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5430" s="4"/>
       <c r="B5430" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5430" s="31"/>
     </row>
@@ -22828,7 +22902,7 @@
         <v>72</v>
       </c>
       <c r="C5436" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22857,7 +22931,7 @@
       </c>
       <c r="B5439" s="9"/>
       <c r="C5439" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22880,7 +22954,7 @@
     </row>
     <row r="5488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5488" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B5488" s="2" t="s">
         <v>24</v>
@@ -22892,7 +22966,7 @@
     <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5489" s="4"/>
       <c r="B5489" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5489" s="31"/>
     </row>
@@ -22971,14 +23045,14 @@
       <c r="A5497" s="8"/>
       <c r="B5497" s="9"/>
       <c r="C5497" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5498" s="8"/>
       <c r="B5498" s="9"/>
       <c r="C5498" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23019,7 +23093,7 @@
       </c>
       <c r="B5503" s="9"/>
       <c r="C5503" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23042,7 +23116,7 @@
     </row>
     <row r="5547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5547" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B5547" s="2" t="s">
         <v>98</v>
@@ -23054,7 +23128,7 @@
     <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5548" s="4"/>
       <c r="B5548" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5548" s="31"/>
     </row>
@@ -23126,7 +23200,7 @@
       </c>
       <c r="B5555" s="9"/>
       <c r="C5555" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23180,7 +23254,7 @@
         <v>5.2</v>
       </c>
       <c r="B5562" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5562" s="10" t="s">
         <v>47</v>
@@ -23192,7 +23266,7 @@
       </c>
       <c r="B5563" s="9"/>
       <c r="C5563" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23205,7 +23279,7 @@
         <v>6.2</v>
       </c>
       <c r="B5565" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5565" s="10" t="s">
         <v>47</v>
@@ -23238,7 +23312,7 @@
     </row>
     <row r="5606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5606" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B5606" s="2" t="s">
         <v>19</v>
@@ -23250,7 +23324,7 @@
     <row r="5607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5607" s="4"/>
       <c r="B5607" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5607" s="31"/>
     </row>
@@ -23342,7 +23416,7 @@
       </c>
       <c r="B5616" s="9"/>
       <c r="C5616" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23376,7 +23450,7 @@
       </c>
       <c r="B5620" s="9"/>
       <c r="C5620" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23399,7 +23473,7 @@
     </row>
     <row r="5665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5665" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B5665" s="2" t="s">
         <v>6</v>
@@ -23473,7 +23547,7 @@
       </c>
       <c r="B5673" s="9"/>
       <c r="C5673" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5674" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23481,10 +23555,10 @@
         <v>3.2</v>
       </c>
       <c r="B5674" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C5674" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23499,7 +23573,7 @@
         <v>4.2</v>
       </c>
       <c r="B5676" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C5676" s="10" t="s">
         <v>45</v>
@@ -23525,7 +23599,7 @@
       </c>
       <c r="B5679" s="9"/>
       <c r="C5679" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23548,7 +23622,7 @@
     </row>
     <row r="5724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5724" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B5724" s="2" t="s">
         <v>6</v>
@@ -23612,7 +23686,7 @@
       </c>
       <c r="B5730" s="9"/>
       <c r="C5730" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23700,105 +23774,105 @@
       </c>
       <c r="B5740" s="9"/>
       <c r="C5740" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5741" s="8"/>
       <c r="B5741" s="9"/>
       <c r="C5741" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5742" s="8"/>
       <c r="B5742" s="9"/>
       <c r="C5742" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5743" s="8"/>
       <c r="B5743" s="9"/>
       <c r="C5743" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5744" s="8"/>
       <c r="B5744" s="9"/>
       <c r="C5744" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5745" s="8"/>
       <c r="B5745" s="9"/>
       <c r="C5745" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5746" s="8"/>
       <c r="B5746" s="9"/>
       <c r="C5746" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5747" s="8"/>
       <c r="B5747" s="9"/>
       <c r="C5747" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5748" s="8"/>
       <c r="B5748" s="9"/>
       <c r="C5748" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5749" s="8"/>
       <c r="B5749" s="9"/>
       <c r="C5749" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5750" s="8"/>
       <c r="B5750" s="9"/>
       <c r="C5750" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5751" s="8"/>
       <c r="B5751" s="9"/>
       <c r="C5751" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5752" s="8"/>
       <c r="B5752" s="9"/>
       <c r="C5752" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5753" s="8"/>
       <c r="B5753" s="9"/>
       <c r="C5753" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5754" s="8"/>
       <c r="B5754" s="9"/>
       <c r="C5754" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23821,7 +23895,7 @@
     </row>
     <row r="5783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5783" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B5783" s="2" t="s">
         <v>6</v>
@@ -23833,7 +23907,7 @@
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="4"/>
       <c r="B5784" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C5784" s="31"/>
     </row>
@@ -23905,7 +23979,7 @@
       </c>
       <c r="B5791" s="9"/>
       <c r="C5791" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23927,10 +24001,10 @@
         <v>4.2</v>
       </c>
       <c r="B5794" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5794" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23945,7 +24019,7 @@
         <v>5.2</v>
       </c>
       <c r="B5796" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C5796" s="10" t="s">
         <v>49</v>
@@ -23957,7 +24031,7 @@
       </c>
       <c r="B5797" s="9"/>
       <c r="C5797" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23980,7 +24054,7 @@
     </row>
     <row r="5842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5842" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B5842" s="2" t="s">
         <v>24</v>
@@ -24044,7 +24118,7 @@
       </c>
       <c r="B5848" s="9"/>
       <c r="C5848" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24078,105 +24152,105 @@
       </c>
       <c r="B5852" s="9"/>
       <c r="C5852" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5853" s="8"/>
       <c r="B5853" s="9"/>
       <c r="C5853" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5854" s="8"/>
       <c r="B5854" s="9"/>
       <c r="C5854" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5855" s="8"/>
       <c r="B5855" s="9"/>
       <c r="C5855" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5856" s="8"/>
       <c r="B5856" s="9"/>
       <c r="C5856" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5857" s="8"/>
       <c r="B5857" s="9"/>
       <c r="C5857" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5858" s="8"/>
       <c r="B5858" s="9"/>
       <c r="C5858" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5859" s="8"/>
       <c r="B5859" s="9"/>
       <c r="C5859" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5860" s="8"/>
       <c r="B5860" s="9"/>
       <c r="C5860" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5861" s="8"/>
       <c r="B5861" s="9"/>
       <c r="C5861" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5862" s="8"/>
       <c r="B5862" s="9"/>
       <c r="C5862" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5863" s="8"/>
       <c r="B5863" s="9"/>
       <c r="C5863" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5864" s="8"/>
       <c r="B5864" s="9"/>
       <c r="C5864" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5865" s="8"/>
       <c r="B5865" s="9"/>
       <c r="C5865" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5866" s="8"/>
       <c r="B5866" s="9"/>
       <c r="C5866" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24199,7 +24273,7 @@
     </row>
     <row r="5901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5901" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B5901" s="2" t="s">
         <v>15</v>
@@ -24211,7 +24285,7 @@
     <row r="5902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5902" s="4"/>
       <c r="B5902" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C5902" s="25"/>
     </row>
@@ -24290,7 +24364,7 @@
         <v>46</v>
       </c>
       <c r="C5910" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24320,7 +24394,7 @@
     </row>
     <row r="5960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5960" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B5960" s="2" t="s">
         <v>15</v>
@@ -24420,105 +24494,105 @@
       </c>
       <c r="B5970" s="9"/>
       <c r="C5970" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5971" s="8"/>
       <c r="B5971" s="9"/>
       <c r="C5971" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5972" s="8"/>
       <c r="B5972" s="9"/>
       <c r="C5972" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5973" s="8"/>
       <c r="B5973" s="9"/>
       <c r="C5973" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5974" s="8"/>
       <c r="B5974" s="9"/>
       <c r="C5974" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5975" s="8"/>
       <c r="B5975" s="9"/>
       <c r="C5975" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5976" s="8"/>
       <c r="B5976" s="9"/>
       <c r="C5976" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5977" s="8"/>
       <c r="B5977" s="9"/>
       <c r="C5977" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5978" s="8"/>
       <c r="B5978" s="9"/>
       <c r="C5978" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5979" s="8"/>
       <c r="B5979" s="9"/>
       <c r="C5979" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5980" s="8"/>
       <c r="B5980" s="9"/>
       <c r="C5980" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5981" s="8"/>
       <c r="B5981" s="9"/>
       <c r="C5981" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5982" s="8"/>
       <c r="B5982" s="9"/>
       <c r="C5982" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5983" s="8"/>
       <c r="B5983" s="9"/>
       <c r="C5983" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5984" s="8"/>
       <c r="B5984" s="9"/>
       <c r="C5984" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24541,7 +24615,7 @@
     </row>
     <row r="6019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6019" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B6019" s="2" t="s">
         <v>19</v>
@@ -24659,7 +24733,7 @@
       </c>
       <c r="B6031" s="9"/>
       <c r="C6031" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24705,7 +24779,7 @@
     </row>
     <row r="6078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6078" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B6078" s="2" t="s">
         <v>6</v>
@@ -24859,105 +24933,105 @@
       </c>
       <c r="B6094" s="9"/>
       <c r="C6094" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6095" s="8"/>
       <c r="B6095" s="9"/>
       <c r="C6095" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6096" s="8"/>
       <c r="B6096" s="9"/>
       <c r="C6096" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6097" s="8"/>
       <c r="B6097" s="9"/>
       <c r="C6097" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6098" s="8"/>
       <c r="B6098" s="9"/>
       <c r="C6098" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6099" s="8"/>
       <c r="B6099" s="9"/>
       <c r="C6099" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6100" s="8"/>
       <c r="B6100" s="9"/>
       <c r="C6100" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6101" s="8"/>
       <c r="B6101" s="9"/>
       <c r="C6101" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6102" s="8"/>
       <c r="B6102" s="9"/>
       <c r="C6102" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6103" s="8"/>
       <c r="B6103" s="9"/>
       <c r="C6103" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6104" s="8"/>
       <c r="B6104" s="9"/>
       <c r="C6104" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6105" s="8"/>
       <c r="B6105" s="9"/>
       <c r="C6105" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6106" s="8"/>
       <c r="B6106" s="9"/>
       <c r="C6106" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6107" s="8"/>
       <c r="B6107" s="9"/>
       <c r="C6107" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6108" s="8"/>
       <c r="B6108" s="9"/>
       <c r="C6108" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24980,7 +25054,7 @@
     </row>
     <row r="6137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6137" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B6137" s="2" t="s">
         <v>24</v>
@@ -25054,7 +25128,7 @@
       </c>
       <c r="B6145" s="9"/>
       <c r="C6145" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25062,10 +25136,10 @@
         <v>3.2</v>
       </c>
       <c r="B6146" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C6146" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25074,7 +25148,7 @@
       </c>
       <c r="B6147" s="9"/>
       <c r="C6147" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25097,7 +25171,7 @@
     </row>
     <row r="6196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6196" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B6196" s="2" t="s">
         <v>22</v>
@@ -25161,105 +25235,105 @@
       </c>
       <c r="B6202" s="9"/>
       <c r="C6202" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6203" s="8"/>
       <c r="B6203" s="9"/>
       <c r="C6203" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6204" s="8"/>
       <c r="B6204" s="9"/>
       <c r="C6204" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6205" s="8"/>
       <c r="B6205" s="9"/>
       <c r="C6205" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6206" s="8"/>
       <c r="B6206" s="9"/>
       <c r="C6206" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6207" s="8"/>
       <c r="B6207" s="9"/>
       <c r="C6207" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6208" s="8"/>
       <c r="B6208" s="9"/>
       <c r="C6208" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6209" s="8"/>
       <c r="B6209" s="9"/>
       <c r="C6209" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6210" s="8"/>
       <c r="B6210" s="9"/>
       <c r="C6210" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6211" s="8"/>
       <c r="B6211" s="9"/>
       <c r="C6211" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6212" s="8"/>
       <c r="B6212" s="9"/>
       <c r="C6212" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6213" s="8"/>
       <c r="B6213" s="9"/>
       <c r="C6213" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6214" s="8"/>
       <c r="B6214" s="9"/>
       <c r="C6214" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6215" s="8"/>
       <c r="B6215" s="9"/>
       <c r="C6215" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6216" s="8"/>
       <c r="B6216" s="9"/>
       <c r="C6216" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25282,7 +25356,7 @@
     </row>
     <row r="6255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6255" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B6255" s="2" t="s">
         <v>22</v>
@@ -25346,7 +25420,7 @@
       </c>
       <c r="B6261" s="9"/>
       <c r="C6261" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25369,7 +25443,7 @@
     </row>
     <row r="6314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6314" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B6314" s="2" t="s">
         <v>6</v>
@@ -25449,10 +25523,10 @@
         <v>3.2</v>
       </c>
       <c r="B6323" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C6323" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25467,7 +25541,7 @@
         <v>4.2</v>
       </c>
       <c r="B6325" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C6325" s="10" t="s">
         <v>45</v>
@@ -25485,10 +25559,10 @@
         <v>5.2</v>
       </c>
       <c r="B6327" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C6327" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25497,7 +25571,7 @@
       </c>
       <c r="B6328" s="9"/>
       <c r="C6328" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25520,7 +25594,7 @@
     </row>
     <row r="6373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6373" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B6373" s="2" t="s">
         <v>19</v>
@@ -25532,7 +25606,7 @@
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="4"/>
       <c r="B6374" s="24" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C6374" s="25"/>
     </row>
@@ -25612,7 +25686,7 @@
         <v>3.2</v>
       </c>
       <c r="B6382" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C6382" s="10" t="s">
         <v>16</v>
@@ -25630,10 +25704,10 @@
         <v>4.2</v>
       </c>
       <c r="B6384" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C6384" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25642,7 +25716,7 @@
       </c>
       <c r="B6385" s="9"/>
       <c r="C6385" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25665,7 +25739,7 @@
     </row>
     <row r="6432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6432" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B6432" s="2" t="s">
         <v>24</v>
@@ -25740,7 +25814,7 @@
         <v>72</v>
       </c>
       <c r="C6439" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25769,105 +25843,105 @@
       </c>
       <c r="B6442" s="9"/>
       <c r="C6442" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6443" s="8"/>
       <c r="B6443" s="9"/>
       <c r="C6443" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6444" s="8"/>
       <c r="B6444" s="9"/>
       <c r="C6444" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6445" s="8"/>
       <c r="B6445" s="9"/>
       <c r="C6445" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6446" s="8"/>
       <c r="B6446" s="9"/>
       <c r="C6446" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6447" s="8"/>
       <c r="B6447" s="9"/>
       <c r="C6447" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6448" s="8"/>
       <c r="B6448" s="9"/>
       <c r="C6448" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6449" s="8"/>
       <c r="B6449" s="9"/>
       <c r="C6449" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6450" s="8"/>
       <c r="B6450" s="9"/>
       <c r="C6450" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6451" s="8"/>
       <c r="B6451" s="9"/>
       <c r="C6451" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6452" s="8"/>
       <c r="B6452" s="9"/>
       <c r="C6452" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6453" s="8"/>
       <c r="B6453" s="9"/>
       <c r="C6453" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6454" s="8"/>
       <c r="B6454" s="9"/>
       <c r="C6454" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6455" s="8"/>
       <c r="B6455" s="9"/>
       <c r="C6455" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6456" s="8"/>
       <c r="B6456" s="9"/>
       <c r="C6456" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25890,7 +25964,7 @@
     </row>
     <row r="6491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6491" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6491" s="2" t="s">
         <v>6</v>
@@ -25965,7 +26039,7 @@
         <v>72</v>
       </c>
       <c r="C6498" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26012,7 +26086,7 @@
       </c>
       <c r="B6503" s="9"/>
       <c r="C6503" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26058,7 +26132,7 @@
     </row>
     <row r="6550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6550" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B6550" s="2" t="s">
         <v>19</v>
@@ -26133,7 +26207,7 @@
         <v>72</v>
       </c>
       <c r="C6557" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26182,105 +26256,105 @@
       </c>
       <c r="B6562" s="9"/>
       <c r="C6562" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6563" s="8"/>
       <c r="B6563" s="9"/>
       <c r="C6563" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6564" s="8"/>
       <c r="B6564" s="9"/>
       <c r="C6564" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6565" s="8"/>
       <c r="B6565" s="9"/>
       <c r="C6565" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6566" s="8"/>
       <c r="B6566" s="9"/>
       <c r="C6566" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6567" s="8"/>
       <c r="B6567" s="9"/>
       <c r="C6567" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6568" s="8"/>
       <c r="B6568" s="9"/>
       <c r="C6568" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6569" s="8"/>
       <c r="B6569" s="9"/>
       <c r="C6569" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6570" s="8"/>
       <c r="B6570" s="9"/>
       <c r="C6570" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6571" s="8"/>
       <c r="B6571" s="9"/>
       <c r="C6571" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6572" s="8"/>
       <c r="B6572" s="9"/>
       <c r="C6572" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6573" s="8"/>
       <c r="B6573" s="9"/>
       <c r="C6573" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6574" s="8"/>
       <c r="B6574" s="9"/>
       <c r="C6574" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6575" s="8"/>
       <c r="B6575" s="9"/>
       <c r="C6575" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6576" s="8"/>
       <c r="B6576" s="9"/>
       <c r="C6576" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26303,7 +26377,7 @@
     </row>
     <row r="6609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6609" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B6609" s="2" t="s">
         <v>22</v>
@@ -26347,7 +26421,7 @@
       </c>
       <c r="B6613" s="9"/>
       <c r="C6613" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26358,7 +26432,7 @@
         <v>72</v>
       </c>
       <c r="C6614" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26372,7 +26446,7 @@
       </c>
       <c r="B6616" s="9"/>
       <c r="C6616" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26388,7 +26462,7 @@
       </c>
       <c r="B6618" s="9"/>
       <c r="C6618" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26406,7 +26480,7 @@
       </c>
       <c r="B6620" s="9"/>
       <c r="C6620" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26429,7 +26503,7 @@
     </row>
     <row r="6668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6668" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B6668" s="2" t="s">
         <v>19</v>
@@ -26568,7 +26642,7 @@
       <c r="A6683" s="8"/>
       <c r="B6683" s="9"/>
       <c r="C6683" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26609,105 +26683,105 @@
       </c>
       <c r="B6688" s="9"/>
       <c r="C6688" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6689" s="8"/>
       <c r="B6689" s="9"/>
       <c r="C6689" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6690" s="8"/>
       <c r="B6690" s="9"/>
       <c r="C6690" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6691" s="8"/>
       <c r="B6691" s="9"/>
       <c r="C6691" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6692" s="8"/>
       <c r="B6692" s="9"/>
       <c r="C6692" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6693" s="8"/>
       <c r="B6693" s="9"/>
       <c r="C6693" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6694" s="8"/>
       <c r="B6694" s="9"/>
       <c r="C6694" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6695" s="8"/>
       <c r="B6695" s="9"/>
       <c r="C6695" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6696" s="8"/>
       <c r="B6696" s="9"/>
       <c r="C6696" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6697" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6697" s="8"/>
       <c r="B6697" s="9"/>
       <c r="C6697" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6698" s="8"/>
       <c r="B6698" s="9"/>
       <c r="C6698" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6699" s="8"/>
       <c r="B6699" s="9"/>
       <c r="C6699" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6700" s="8"/>
       <c r="B6700" s="9"/>
       <c r="C6700" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6701" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6701" s="8"/>
       <c r="B6701" s="9"/>
       <c r="C6701" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6702" s="8"/>
       <c r="B6702" s="9"/>
       <c r="C6702" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26730,7 +26804,7 @@
     </row>
     <row r="6727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6727" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B6727" s="2" t="s">
         <v>19</v>
@@ -26866,105 +26940,105 @@
       </c>
       <c r="B6741" s="9"/>
       <c r="C6741" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6742" s="8"/>
       <c r="B6742" s="9"/>
       <c r="C6742" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6743" s="8"/>
       <c r="B6743" s="9"/>
       <c r="C6743" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6744" s="8"/>
       <c r="B6744" s="9"/>
       <c r="C6744" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6745" s="8"/>
       <c r="B6745" s="9"/>
       <c r="C6745" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6746" s="8"/>
       <c r="B6746" s="9"/>
       <c r="C6746" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6747" s="8"/>
       <c r="B6747" s="9"/>
       <c r="C6747" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6748" s="8"/>
       <c r="B6748" s="9"/>
       <c r="C6748" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6749" s="8"/>
       <c r="B6749" s="9"/>
       <c r="C6749" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6750" s="8"/>
       <c r="B6750" s="9"/>
       <c r="C6750" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6751" s="8"/>
       <c r="B6751" s="9"/>
       <c r="C6751" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6752" s="8"/>
       <c r="B6752" s="9"/>
       <c r="C6752" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6753" s="8"/>
       <c r="B6753" s="9"/>
       <c r="C6753" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6754" s="8"/>
       <c r="B6754" s="9"/>
       <c r="C6754" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6755" s="8"/>
       <c r="B6755" s="9"/>
       <c r="C6755" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26987,7 +27061,7 @@
     </row>
     <row r="6786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6786" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B6786" s="2" t="s">
         <v>98</v>
@@ -27051,7 +27125,7 @@
       </c>
       <c r="B6792" s="9"/>
       <c r="C6792" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27151,105 +27225,105 @@
       </c>
       <c r="B6804" s="9"/>
       <c r="C6804" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6805" s="8"/>
       <c r="B6805" s="9"/>
       <c r="C6805" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6806" s="8"/>
       <c r="B6806" s="9"/>
       <c r="C6806" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6807" s="8"/>
       <c r="B6807" s="9"/>
       <c r="C6807" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6808" s="8"/>
       <c r="B6808" s="9"/>
       <c r="C6808" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6809" s="8"/>
       <c r="B6809" s="9"/>
       <c r="C6809" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6810" s="8"/>
       <c r="B6810" s="9"/>
       <c r="C6810" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6811" s="8"/>
       <c r="B6811" s="9"/>
       <c r="C6811" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6812" s="8"/>
       <c r="B6812" s="9"/>
       <c r="C6812" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6813" s="8"/>
       <c r="B6813" s="9"/>
       <c r="C6813" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6814" s="8"/>
       <c r="B6814" s="9"/>
       <c r="C6814" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6815" s="8"/>
       <c r="B6815" s="9"/>
       <c r="C6815" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6816" s="8"/>
       <c r="B6816" s="9"/>
       <c r="C6816" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6817" s="8"/>
       <c r="B6817" s="9"/>
       <c r="C6817" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6818" s="8"/>
       <c r="B6818" s="9"/>
       <c r="C6818" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27272,7 +27346,7 @@
     </row>
     <row r="6845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6845" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B6845" s="2" t="s">
         <v>24</v>
@@ -27284,7 +27358,7 @@
     <row r="6846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6846" s="4"/>
       <c r="B6846" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C6846" s="25"/>
     </row>
@@ -27352,7 +27426,7 @@
       </c>
       <c r="B6853" s="9"/>
       <c r="C6853" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27382,7 +27456,7 @@
         <v>46</v>
       </c>
       <c r="C6857" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27412,7 +27486,7 @@
     </row>
     <row r="6904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6904" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6904" s="2" t="s">
         <v>24</v>
@@ -27492,7 +27566,7 @@
       </c>
       <c r="B6912" s="9"/>
       <c r="C6912" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27531,105 +27605,105 @@
       </c>
       <c r="B6917" s="9"/>
       <c r="C6917" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6918" s="8"/>
       <c r="B6918" s="9"/>
       <c r="C6918" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6919" s="8"/>
       <c r="B6919" s="9"/>
       <c r="C6919" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6920" s="8"/>
       <c r="B6920" s="9"/>
       <c r="C6920" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6921" s="8"/>
       <c r="B6921" s="9"/>
       <c r="C6921" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6922" s="8"/>
       <c r="B6922" s="9"/>
       <c r="C6922" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6923" s="8"/>
       <c r="B6923" s="9"/>
       <c r="C6923" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6924" s="8"/>
       <c r="B6924" s="9"/>
       <c r="C6924" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6925" s="8"/>
       <c r="B6925" s="9"/>
       <c r="C6925" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6926" s="8"/>
       <c r="B6926" s="9"/>
       <c r="C6926" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6927" s="8"/>
       <c r="B6927" s="9"/>
       <c r="C6927" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6928" s="8"/>
       <c r="B6928" s="9"/>
       <c r="C6928" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6929" s="8"/>
       <c r="B6929" s="9"/>
       <c r="C6929" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6930" s="8"/>
       <c r="B6930" s="9"/>
       <c r="C6930" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6931" s="8"/>
       <c r="B6931" s="9"/>
       <c r="C6931" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27652,7 +27726,7 @@
     </row>
     <row r="6963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6963" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B6963" s="2" t="s">
         <v>6</v>
@@ -27664,7 +27738,7 @@
     <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6964" s="4"/>
       <c r="B6964" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6964" s="31"/>
     </row>
@@ -27732,7 +27806,7 @@
       </c>
       <c r="B6971" s="9"/>
       <c r="C6971" s="32" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27789,7 +27863,7 @@
       </c>
       <c r="B6978" s="9"/>
       <c r="C6978" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27835,7 +27909,7 @@
     </row>
     <row r="7022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7022" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B7022" s="2" t="s">
         <v>6</v>
@@ -27941,7 +28015,7 @@
         <v>4.2</v>
       </c>
       <c r="B7033" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C7033" s="10" t="s">
         <v>37</v>
@@ -27969,7 +28043,7 @@
         <v>5.2</v>
       </c>
       <c r="B7037" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C7037" s="10" t="s">
         <v>69</v>
@@ -28025,105 +28099,105 @@
       </c>
       <c r="B7044" s="9"/>
       <c r="C7044" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7045" s="8"/>
       <c r="B7045" s="9"/>
       <c r="C7045" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7046" s="8"/>
       <c r="B7046" s="9"/>
       <c r="C7046" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7047" s="8"/>
       <c r="B7047" s="9"/>
       <c r="C7047" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7048" s="8"/>
       <c r="B7048" s="9"/>
       <c r="C7048" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7049" s="8"/>
       <c r="B7049" s="9"/>
       <c r="C7049" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7050" s="8"/>
       <c r="B7050" s="9"/>
       <c r="C7050" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7051" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7051" s="8"/>
       <c r="B7051" s="9"/>
       <c r="C7051" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7052" s="8"/>
       <c r="B7052" s="9"/>
       <c r="C7052" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7053" s="8"/>
       <c r="B7053" s="9"/>
       <c r="C7053" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7054" s="8"/>
       <c r="B7054" s="9"/>
       <c r="C7054" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7055" s="8"/>
       <c r="B7055" s="9"/>
       <c r="C7055" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7056" s="8"/>
       <c r="B7056" s="9"/>
       <c r="C7056" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7057" s="8"/>
       <c r="B7057" s="9"/>
       <c r="C7057" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7058" s="8"/>
       <c r="B7058" s="9"/>
       <c r="C7058" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28146,7 +28220,7 @@
     </row>
     <row r="7081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7081" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B7081" s="2" t="s">
         <v>22</v>
@@ -28210,7 +28284,7 @@
       </c>
       <c r="B7087" s="9"/>
       <c r="C7087" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28233,7 +28307,7 @@
     </row>
     <row r="7140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7140" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B7140" s="2" t="s">
         <v>24</v>
@@ -28338,7 +28412,7 @@
       <c r="A7151" s="8"/>
       <c r="B7151" s="9"/>
       <c r="C7151" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28379,105 +28453,105 @@
       </c>
       <c r="B7156" s="27"/>
       <c r="C7156" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7157" s="8"/>
       <c r="B7157" s="27"/>
       <c r="C7157" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7158" s="8"/>
       <c r="B7158" s="9"/>
       <c r="C7158" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7159" s="8"/>
       <c r="B7159" s="27"/>
       <c r="C7159" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7160" s="8"/>
       <c r="B7160" s="27"/>
       <c r="C7160" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7161" s="8"/>
       <c r="B7161" s="27"/>
       <c r="C7161" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7162" s="8"/>
       <c r="B7162" s="9"/>
       <c r="C7162" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7163" s="8"/>
       <c r="B7163" s="9"/>
       <c r="C7163" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7164" s="8"/>
       <c r="B7164" s="9"/>
       <c r="C7164" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7165" s="8"/>
       <c r="B7165" s="9"/>
       <c r="C7165" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7166" s="8"/>
       <c r="B7166" s="9"/>
       <c r="C7166" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7167" s="8"/>
       <c r="B7167" s="9"/>
       <c r="C7167" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7168" s="8"/>
       <c r="B7168" s="9"/>
       <c r="C7168" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7169" s="8"/>
       <c r="B7169" s="9"/>
       <c r="C7169" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7170" s="8"/>
       <c r="B7170" s="9"/>
       <c r="C7170" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28500,7 +28574,7 @@
     </row>
     <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7199" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B7199" s="2" t="s">
         <v>24</v>
@@ -28574,7 +28648,7 @@
       </c>
       <c r="B7207" s="9"/>
       <c r="C7207" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28582,10 +28656,10 @@
         <v>3.2</v>
       </c>
       <c r="B7208" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C7208" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28593,7 +28667,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B7209" s="33" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
@@ -28627,7 +28701,7 @@
     </row>
     <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7258" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B7258" s="2" t="s">
         <v>22</v>
@@ -28691,7 +28765,7 @@
       </c>
       <c r="B7264" s="9"/>
       <c r="C7264" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28714,7 +28788,7 @@
     </row>
     <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7317" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B7317" s="2" t="s">
         <v>6</v>
@@ -28726,7 +28800,7 @@
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
       <c r="B7318" s="30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C7318" s="31"/>
     </row>
@@ -28798,7 +28872,7 @@
       </c>
       <c r="B7325" s="9"/>
       <c r="C7325" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28838,10 +28912,10 @@
         <v>5.2</v>
       </c>
       <c r="B7330" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C7330" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28850,7 +28924,7 @@
       </c>
       <c r="B7331" s="9"/>
       <c r="C7331" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28873,7 +28947,7 @@
     </row>
     <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7376" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B7376" s="2" t="s">
         <v>24</v>
@@ -28885,7 +28959,7 @@
     <row r="7377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7377" s="4"/>
       <c r="B7377" s="24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7377" s="25"/>
     </row>
@@ -28957,14 +29031,14 @@
       </c>
       <c r="B7384" s="9"/>
       <c r="C7384" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7385" s="8"/>
       <c r="B7385" s="9"/>
       <c r="C7385" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28978,7 +29052,7 @@
       <c r="A7387" s="8"/>
       <c r="B7387" s="9"/>
       <c r="C7387" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29019,105 +29093,105 @@
       </c>
       <c r="B7392" s="27"/>
       <c r="C7392" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7393" s="8"/>
       <c r="B7393" s="27"/>
       <c r="C7393" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7394" s="8"/>
       <c r="B7394" s="9"/>
       <c r="C7394" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7395" s="8"/>
       <c r="B7395" s="27"/>
       <c r="C7395" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7396" s="8"/>
       <c r="B7396" s="27"/>
       <c r="C7396" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7397" s="8"/>
       <c r="B7397" s="27"/>
       <c r="C7397" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7398" s="8"/>
       <c r="B7398" s="9"/>
       <c r="C7398" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7399" s="8"/>
       <c r="B7399" s="9"/>
       <c r="C7399" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7400" s="8"/>
       <c r="B7400" s="9"/>
       <c r="C7400" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7401" s="8"/>
       <c r="B7401" s="9"/>
       <c r="C7401" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7402" s="8"/>
       <c r="B7402" s="9"/>
       <c r="C7402" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7403" s="8"/>
       <c r="B7403" s="9"/>
       <c r="C7403" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7404" s="8"/>
       <c r="B7404" s="9"/>
       <c r="C7404" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7405" s="8"/>
       <c r="B7405" s="9"/>
       <c r="C7405" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7406" s="8"/>
       <c r="B7406" s="9"/>
       <c r="C7406" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29140,7 +29214,7 @@
     </row>
     <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7435" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B7435" s="2" t="s">
         <v>98</v>
@@ -29152,7 +29226,7 @@
     <row r="7436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7436" s="4"/>
       <c r="B7436" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7436" s="31"/>
     </row>
@@ -29224,7 +29298,7 @@
       </c>
       <c r="B7443" s="9"/>
       <c r="C7443" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29278,7 +29352,7 @@
         <v>5.2</v>
       </c>
       <c r="B7450" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7450" s="10" t="s">
         <v>47</v>
@@ -29290,7 +29364,7 @@
       </c>
       <c r="B7451" s="27"/>
       <c r="C7451" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29303,7 +29377,7 @@
         <v>6.2</v>
       </c>
       <c r="B7453" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7453" s="10" t="s">
         <v>47</v>
@@ -29336,7 +29410,7 @@
     </row>
     <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7494" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B7494" s="2" t="s">
         <v>19</v>
@@ -29348,7 +29422,7 @@
     <row r="7495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7495" s="4"/>
       <c r="B7495" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7495" s="25"/>
     </row>
@@ -29440,7 +29514,7 @@
       </c>
       <c r="B7504" s="9"/>
       <c r="C7504" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29474,105 +29548,105 @@
       </c>
       <c r="B7508" s="9"/>
       <c r="C7508" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7509" s="8"/>
       <c r="B7509" s="9"/>
       <c r="C7509" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7510" s="8"/>
       <c r="B7510" s="9"/>
       <c r="C7510" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7511" s="8"/>
       <c r="B7511" s="9"/>
       <c r="C7511" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7512" s="8"/>
       <c r="B7512" s="9"/>
       <c r="C7512" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7513" s="8"/>
       <c r="B7513" s="9"/>
       <c r="C7513" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7514" s="8"/>
       <c r="B7514" s="9"/>
       <c r="C7514" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7515" s="8"/>
       <c r="B7515" s="9"/>
       <c r="C7515" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7516" s="8"/>
       <c r="B7516" s="9"/>
       <c r="C7516" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7517" s="8"/>
       <c r="B7517" s="9"/>
       <c r="C7517" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7518" s="8"/>
       <c r="B7518" s="9"/>
       <c r="C7518" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7519" s="8"/>
       <c r="B7519" s="9"/>
       <c r="C7519" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7520" s="8"/>
       <c r="B7520" s="9"/>
       <c r="C7520" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7521" s="8"/>
       <c r="B7521" s="9"/>
       <c r="C7521" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7522" s="8"/>
       <c r="B7522" s="27"/>
       <c r="C7522" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29595,7 +29669,7 @@
     </row>
     <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7553" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B7553" s="2" t="s">
         <v>15</v>
@@ -29639,7 +29713,7 @@
       </c>
       <c r="B7557" s="9"/>
       <c r="C7557" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29650,7 +29724,7 @@
         <v>72</v>
       </c>
       <c r="C7558" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29664,7 +29738,7 @@
       </c>
       <c r="B7560" s="9"/>
       <c r="C7560" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29680,7 +29754,7 @@
       </c>
       <c r="B7562" s="9"/>
       <c r="C7562" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29698,7 +29772,7 @@
       </c>
       <c r="B7564" s="9"/>
       <c r="C7564" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29721,7 +29795,7 @@
     </row>
     <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7612" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B7612" s="2" t="s">
         <v>6</v>
@@ -29733,7 +29807,7 @@
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
       <c r="B7613" s="30" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C7613" s="31"/>
     </row>
@@ -29785,21 +29859,21 @@
       </c>
       <c r="B7618" s="9"/>
       <c r="C7618" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7619" s="8"/>
       <c r="B7619" s="9"/>
       <c r="C7619" s="10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7620" s="8"/>
       <c r="B7620" s="9"/>
       <c r="C7620" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29869,7 +29943,7 @@
       </c>
       <c r="B7628" s="9"/>
       <c r="C7628" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29877,7 +29951,7 @@
         <v>6.2</v>
       </c>
       <c r="B7629" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C7629" s="10" t="s">
         <v>47</v>
@@ -29910,7 +29984,7 @@
     </row>
     <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7671" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B7671" s="2" t="s">
         <v>24</v>
@@ -29922,7 +29996,7 @@
     <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7672" s="4"/>
       <c r="B7672" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C7672" s="31"/>
     </row>
@@ -30010,7 +30084,7 @@
       </c>
       <c r="B7681" s="9"/>
       <c r="C7681" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30033,7 +30107,7 @@
     </row>
     <row r="7730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7730" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B7730" s="2" t="s">
         <v>24</v>
@@ -30045,7 +30119,7 @@
     <row r="7731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7731" s="4"/>
       <c r="B7731" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C7731" s="25"/>
     </row>
@@ -30097,7 +30171,7 @@
       </c>
       <c r="B7736" s="9"/>
       <c r="C7736" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30113,7 +30187,7 @@
       </c>
       <c r="B7738" s="9"/>
       <c r="C7738" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30154,7 +30228,7 @@
     </row>
     <row r="7789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7789" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B7789" s="2" t="s">
         <v>15</v>
@@ -30166,7 +30240,7 @@
     <row r="7790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7790" s="4"/>
       <c r="B7790" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7790" s="25"/>
     </row>
@@ -30245,7 +30319,7 @@
         <v>46</v>
       </c>
       <c r="C7798" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30275,7 +30349,7 @@
     </row>
     <row r="7848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7848" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B7848" s="2" t="s">
         <v>15</v>
@@ -30287,7 +30361,7 @@
     <row r="7849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7849" s="4"/>
       <c r="B7849" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7849" s="25"/>
     </row>
@@ -30366,7 +30440,7 @@
         <v>46</v>
       </c>
       <c r="C7857" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30396,7 +30470,7 @@
     </row>
     <row r="7907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7907" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7907" s="2" t="s">
         <v>15</v>
@@ -30408,7 +30482,7 @@
     <row r="7908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7908" s="4"/>
       <c r="B7908" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7908" s="25"/>
     </row>
@@ -30487,7 +30561,7 @@
         <v>46</v>
       </c>
       <c r="C7916" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30517,7 +30591,7 @@
     </row>
     <row r="7966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7966" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B7966" s="2" t="s">
         <v>6</v>
@@ -30529,7 +30603,7 @@
     <row r="7967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7967" s="4"/>
       <c r="B7967" s="24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C7967" s="25"/>
     </row>
@@ -30653,7 +30727,7 @@
       </c>
       <c r="B7980" s="9"/>
       <c r="C7980" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30661,7 +30735,7 @@
         <v>6.2</v>
       </c>
       <c r="B7981" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7981" s="10" t="s">
         <v>47</v>
@@ -30694,7 +30768,7 @@
     </row>
     <row r="8025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8025" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B8025" s="2" t="s">
         <v>22</v>
@@ -30758,7 +30832,7 @@
       </c>
       <c r="B8031" s="9"/>
       <c r="C8031" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30781,7 +30855,7 @@
     </row>
     <row r="8084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8084" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B8084" s="2" t="s">
         <v>22</v>
@@ -30845,7 +30919,7 @@
       </c>
       <c r="B8090" s="9"/>
       <c r="C8090" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30868,7 +30942,7 @@
     </row>
     <row r="8143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8143" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B8143" s="2" t="s">
         <v>22</v>
@@ -30932,7 +31006,7 @@
       </c>
       <c r="B8149" s="9"/>
       <c r="C8149" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30955,7 +31029,7 @@
     </row>
     <row r="8202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8202" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B8202" s="2" t="s">
         <v>15</v>
@@ -31021,10 +31095,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8209" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C8209" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31033,7 +31107,7 @@
       </c>
       <c r="B8210" s="9"/>
       <c r="C8210" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31056,7 +31130,7 @@
     </row>
     <row r="8261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8261" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B8261" s="2" t="s">
         <v>24</v>
@@ -31068,7 +31142,7 @@
     <row r="8262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8262" s="4"/>
       <c r="B8262" s="24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C8262" s="25"/>
     </row>
@@ -31131,7 +31205,7 @@
         <v>72</v>
       </c>
       <c r="C8268" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31140,7 +31214,7 @@
       </c>
       <c r="B8269" s="9"/>
       <c r="C8269" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31181,7 +31255,7 @@
     </row>
     <row r="8320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8320" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B8320" s="2" t="s">
         <v>24</v>
@@ -31193,7 +31267,7 @@
     <row r="8321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8321" s="4"/>
       <c r="B8321" s="24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C8321" s="25"/>
     </row>
@@ -31256,7 +31330,7 @@
         <v>72</v>
       </c>
       <c r="C8327" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31265,7 +31339,7 @@
       </c>
       <c r="B8328" s="9"/>
       <c r="C8328" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31306,7 +31380,7 @@
     </row>
     <row r="8379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8379" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B8379" s="2" t="s">
         <v>24</v>
@@ -31318,7 +31392,7 @@
     <row r="8380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8380" s="4"/>
       <c r="B8380" s="24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C8380" s="25"/>
     </row>
@@ -31381,7 +31455,7 @@
         <v>72</v>
       </c>
       <c r="C8386" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31390,7 +31464,7 @@
       </c>
       <c r="B8387" s="9"/>
       <c r="C8387" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31431,7 +31505,7 @@
     </row>
     <row r="8438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8438" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B8438" s="2" t="s">
         <v>19</v>
@@ -31443,7 +31517,7 @@
     <row r="8439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8439" s="4"/>
       <c r="B8439" s="24" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C8439" s="25"/>
     </row>
@@ -31506,7 +31580,7 @@
         <v>72</v>
       </c>
       <c r="C8445" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31535,7 +31609,7 @@
       </c>
       <c r="B8448" s="9"/>
       <c r="C8448" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31543,7 +31617,7 @@
         <v>4.2</v>
       </c>
       <c r="B8449" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C8449" s="10" t="s">
         <v>47</v>
@@ -31574,8 +31648,954 @@
       <c r="B8452" s="20"/>
       <c r="C8452" s="22"/>
     </row>
+    <row r="8497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8497" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B8497" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8497" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8498" s="4"/>
+      <c r="B8498" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8498" s="6"/>
+    </row>
+    <row r="8499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8499" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8499" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8499" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8500" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8500" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8500" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8501" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8501" s="9"/>
+      <c r="C8501" s="10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="8502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8502" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B8502" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8502" s="32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8503" s="8"/>
+      <c r="B8503" s="9"/>
+      <c r="C8503" s="32"/>
+    </row>
+    <row r="8504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8504" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8504" s="9"/>
+      <c r="C8504" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8505" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8505" s="9"/>
+      <c r="C8505" s="10"/>
+    </row>
+    <row r="8506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8506" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8506" s="9"/>
+      <c r="C8506" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8507" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B8507" s="9"/>
+      <c r="C8507" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8508" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8508" s="9"/>
+      <c r="C8508" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8509" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8509" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8509" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8510" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8510" s="20"/>
+      <c r="C8510" s="21"/>
+    </row>
+    <row r="8556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8556" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8556" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8556" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8557" s="4"/>
+      <c r="B8557" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="C8557" s="31"/>
+    </row>
+    <row r="8558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8558" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8558" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8558" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8559" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8559" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8559" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8560" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8560" s="9"/>
+      <c r="C8560" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8561" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8561" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8561" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8562" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B8562" s="16"/>
+      <c r="C8562" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8563" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8563" s="16"/>
+      <c r="C8563" s="23"/>
+    </row>
+    <row r="8564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8564" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8564" s="9"/>
+      <c r="C8564" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8565" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8565" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8565" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8566" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8566" s="9"/>
+      <c r="C8566" s="10"/>
+    </row>
+    <row r="8567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8567" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8567" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8567" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8568" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8568" s="9"/>
+      <c r="C8568" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8569" s="8"/>
+      <c r="B8569" s="9"/>
+      <c r="C8569" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8570" s="8"/>
+      <c r="B8570" s="9"/>
+      <c r="C8570" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8571" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8571" s="9"/>
+      <c r="C8571" s="10"/>
+    </row>
+    <row r="8572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8572" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B8572" s="9"/>
+      <c r="C8572" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8573" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B8573" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8573" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8574" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B8574" s="9"/>
+      <c r="C8574" s="10"/>
+    </row>
+    <row r="8575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8575" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B8575" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8575" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8576" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8576" s="20"/>
+      <c r="C8576" s="21"/>
+    </row>
+    <row r="8615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8615" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8615" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8615" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8616" s="4"/>
+      <c r="B8616" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8616" s="25"/>
+    </row>
+    <row r="8617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8617" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8617" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8617" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8618" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8618" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8618" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8619" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8619" s="9"/>
+      <c r="C8619" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8620" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8620" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8620" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8621" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B8621" s="16"/>
+      <c r="C8621" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8622" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8622" s="16"/>
+      <c r="C8622" s="23"/>
+    </row>
+    <row r="8623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8623" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8623" s="9"/>
+      <c r="C8623" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8624" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8624" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8624" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8625" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8625" s="9"/>
+      <c r="C8625" s="10"/>
+    </row>
+    <row r="8626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8626" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8626" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8626" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8627" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8627" s="9"/>
+      <c r="C8627" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8628" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B8628" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8628" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8629" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B8629" s="9"/>
+      <c r="C8629" s="10"/>
+    </row>
+    <row r="8630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8630" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B8630" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8630" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8631" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8631" s="20"/>
+      <c r="C8631" s="21"/>
+    </row>
+    <row r="8674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8674" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B8674" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8674" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8675" s="4"/>
+      <c r="B8675" s="30" t="s">
+        <v>405</v>
+      </c>
+      <c r="C8675" s="31"/>
+    </row>
+    <row r="8676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8676" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8676" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8676" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8677" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8677" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8677" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8678" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8678" s="9"/>
+      <c r="C8678" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8679" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8679" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8679" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8680" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8680" s="9"/>
+      <c r="C8680" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8681" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8681" s="9"/>
+      <c r="C8681" s="10"/>
+    </row>
+    <row r="8682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8682" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8682" s="9"/>
+      <c r="C8682" s="10"/>
+    </row>
+    <row r="8683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8683" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8683" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8683" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8684" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8684" s="9"/>
+      <c r="C8684" s="10"/>
+    </row>
+    <row r="8685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8685" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8685" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8685" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8686" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8686" s="9"/>
+      <c r="C8686" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8687" s="8"/>
+      <c r="B8687" s="9"/>
+      <c r="C8687" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8688" s="8"/>
+      <c r="B8688" s="9"/>
+      <c r="C8688" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8689" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8689" s="9"/>
+      <c r="C8689" s="10"/>
+    </row>
+    <row r="8690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8690" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B8690" s="9"/>
+      <c r="C8690" s="10" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8691" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B8691" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8691" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8692" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B8692" s="9"/>
+      <c r="C8692" s="10"/>
+    </row>
+    <row r="8693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8693" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B8693" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8693" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8694" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8694" s="20"/>
+      <c r="C8694" s="21"/>
+    </row>
+    <row r="8733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8733" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B8733" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8733" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8734" s="4"/>
+      <c r="B8734" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8734" s="25"/>
+    </row>
+    <row r="8735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8735" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8735" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8735" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8736" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8736" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8736" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8737" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8737" s="9"/>
+      <c r="C8737" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8738" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8738" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8738" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8739" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8739" s="9"/>
+      <c r="C8739" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8740" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8740" s="9"/>
+      <c r="C8740" s="10"/>
+    </row>
+    <row r="8741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8741" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8741" s="9"/>
+      <c r="C8741" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8742" s="8"/>
+      <c r="B8742" s="9"/>
+      <c r="C8742" s="32"/>
+    </row>
+    <row r="8743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8743" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B8743" s="16"/>
+      <c r="C8743" s="23"/>
+    </row>
+    <row r="8744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8744" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8744" s="16"/>
+      <c r="C8744" s="23"/>
+    </row>
+    <row r="8745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8745" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B8745" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8745" s="10" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8746" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8746" s="9"/>
+      <c r="C8746" s="10"/>
+    </row>
+    <row r="8747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8747" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8747" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8747" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8748" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8748" s="20"/>
+      <c r="C8748" s="21"/>
+    </row>
+    <row r="8792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8792" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B8792" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8792" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8793" s="4"/>
+      <c r="B8793" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8793" s="25"/>
+    </row>
+    <row r="8794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8794" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8794" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8794" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8795" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8795" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8795" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8796" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8796" s="9"/>
+      <c r="C8796" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8797" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8797" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8797" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8798" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8798" s="9"/>
+      <c r="C8798" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8799" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8799" s="9"/>
+      <c r="C8799" s="10"/>
+    </row>
+    <row r="8800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8800" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8800" s="9"/>
+      <c r="C8800" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8801" s="8"/>
+      <c r="B8801" s="9"/>
+      <c r="C8801" s="32"/>
+    </row>
+    <row r="8802" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8802" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B8802" s="16"/>
+      <c r="C8802" s="23"/>
+    </row>
+    <row r="8803" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8803" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8803" s="16"/>
+      <c r="C8803" s="23"/>
+    </row>
+    <row r="8804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8804" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B8804" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8804" s="10" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8805" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8805" s="9"/>
+      <c r="C8805" s="10"/>
+    </row>
+    <row r="8806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8806" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8806" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8806" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8807" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8807" s="20"/>
+      <c r="C8807" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="108">
+    <mergeCell ref="C8741:C8742"/>
+    <mergeCell ref="C8800:C8801"/>
+    <mergeCell ref="C8502:C8503"/>
+    <mergeCell ref="B8557:C8557"/>
+    <mergeCell ref="B8675:C8675"/>
     <mergeCell ref="B7613:C7613"/>
     <mergeCell ref="B5784:C5784"/>
     <mergeCell ref="B7672:C7672"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC17F24-02BC-4AFA-AD54-B53BBFD981A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE0807F-6EEE-4B9C-8F6B-19FBEC57EF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$9323</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$10384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3697" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="457">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -7431,6 +7431,9 @@
     <t>ADC (77)</t>
   </si>
   <si>
+    <t>Store as Operand. If D.L is 0, skip the next cycle.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Sets the </t>
     </r>
@@ -7813,6 +7816,9 @@
     <t>Address.L = Pointer.L.</t>
   </si>
   <si>
+    <t>Address.H = D.H.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Address.H = </t>
     </r>
@@ -8672,6 +8678,1754 @@
   </si>
   <si>
     <t>STA (95)</t>
+  </si>
+  <si>
+    <t>STX (96)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L is 0, Address.L = Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, Address.H = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H, otherwise Address = Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L is 0, skip 2 half-cycles.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (97)</t>
+  </si>
+  <si>
+    <t>Direct Indirect Indexed Long [d],y (Write)</t>
+  </si>
+  <si>
+    <t>TYA (98)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (99)</t>
+  </si>
+  <si>
+    <t>Absolute, Y (Write)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Perform Tmp = ui32(Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>TXS (9A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TXY (9B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>STZ (9C)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Sets Operand to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>STA (9D)</t>
+  </si>
+  <si>
+    <t>Absolute, X (Write)</t>
+  </si>
+  <si>
+    <t>STZ (9E)</t>
+  </si>
+  <si>
+    <t>Sets Operand to 0.</t>
+  </si>
+  <si>
+    <t>STA (9F)</t>
+  </si>
+  <si>
+    <t>Absolute Long, X (Write)</t>
+  </si>
+  <si>
+    <t>LDY (A0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A1)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Pointer to Pointer + X + D.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDX (A2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A3)</t>
+  </si>
+  <si>
+    <t>LDY (A4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A5)</t>
+  </si>
+  <si>
+    <t>LDX (A6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A7)</t>
+  </si>
+  <si>
+    <t>TAY (A8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A9)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TAX (AA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLB (AB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDY (AC)</t>
+  </si>
+  <si>
+    <t>LDA (AD)</t>
+  </si>
+  <si>
+    <t>LDX (AE)</t>
+  </si>
+  <si>
+    <t>LDA (AF)</t>
   </si>
 </sst>
 </file>
@@ -9272,7 +11026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C8807"/>
+  <dimension ref="A1:C10340"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -13378,7 +15132,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B1594" s="2" t="s">
         <v>22</v>
@@ -23907,7 +25661,7 @@
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="4"/>
       <c r="B5784" s="30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C5784" s="31"/>
     </row>
@@ -28220,7 +29974,7 @@
     </row>
     <row r="7081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7081" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B7081" s="2" t="s">
         <v>22</v>
@@ -28284,7 +30038,7 @@
       </c>
       <c r="B7087" s="9"/>
       <c r="C7087" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28307,7 +30061,7 @@
     </row>
     <row r="7140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7140" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B7140" s="2" t="s">
         <v>24</v>
@@ -28574,7 +30328,7 @@
     </row>
     <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7199" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7199" s="2" t="s">
         <v>24</v>
@@ -28667,7 +30421,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B7209" s="33" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
@@ -28701,7 +30455,7 @@
     </row>
     <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7258" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7258" s="2" t="s">
         <v>22</v>
@@ -28765,7 +30519,7 @@
       </c>
       <c r="B7264" s="9"/>
       <c r="C7264" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28788,7 +30542,7 @@
     </row>
     <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7317" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B7317" s="2" t="s">
         <v>6</v>
@@ -28800,7 +30554,7 @@
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
       <c r="B7318" s="30" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C7318" s="31"/>
     </row>
@@ -28872,7 +30626,7 @@
       </c>
       <c r="B7325" s="9"/>
       <c r="C7325" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28912,7 +30666,7 @@
         <v>5.2</v>
       </c>
       <c r="B7330" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C7330" s="10" t="s">
         <v>276</v>
@@ -28947,7 +30701,7 @@
     </row>
     <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7376" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B7376" s="2" t="s">
         <v>24</v>
@@ -29031,7 +30785,7 @@
       </c>
       <c r="B7384" s="9"/>
       <c r="C7384" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29214,7 +30968,7 @@
     </row>
     <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7435" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B7435" s="2" t="s">
         <v>98</v>
@@ -29410,7 +31164,7 @@
     </row>
     <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7494" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B7494" s="2" t="s">
         <v>19</v>
@@ -29669,7 +31423,7 @@
     </row>
     <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7553" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B7553" s="2" t="s">
         <v>15</v>
@@ -29713,7 +31467,7 @@
       </c>
       <c r="B7557" s="9"/>
       <c r="C7557" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29795,7 +31549,7 @@
     </row>
     <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7612" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7612" s="2" t="s">
         <v>6</v>
@@ -29807,7 +31561,7 @@
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
       <c r="B7613" s="30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C7613" s="31"/>
     </row>
@@ -29859,21 +31613,21 @@
       </c>
       <c r="B7618" s="9"/>
       <c r="C7618" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7619" s="8"/>
       <c r="B7619" s="9"/>
       <c r="C7619" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7620" s="8"/>
       <c r="B7620" s="9"/>
       <c r="C7620" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29943,7 +31697,7 @@
       </c>
       <c r="B7628" s="9"/>
       <c r="C7628" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29951,7 +31705,7 @@
         <v>6.2</v>
       </c>
       <c r="B7629" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C7629" s="10" t="s">
         <v>47</v>
@@ -29984,7 +31738,7 @@
     </row>
     <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7671" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B7671" s="2" t="s">
         <v>24</v>
@@ -29996,7 +31750,7 @@
     <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7672" s="4"/>
       <c r="B7672" s="30" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C7672" s="31"/>
     </row>
@@ -30084,7 +31838,7 @@
       </c>
       <c r="B7681" s="9"/>
       <c r="C7681" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30107,7 +31861,7 @@
     </row>
     <row r="7730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7730" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B7730" s="2" t="s">
         <v>24</v>
@@ -30119,7 +31873,7 @@
     <row r="7731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7731" s="4"/>
       <c r="B7731" s="24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C7731" s="25"/>
     </row>
@@ -30187,7 +31941,7 @@
       </c>
       <c r="B7738" s="9"/>
       <c r="C7738" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30228,7 +31982,7 @@
     </row>
     <row r="7789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7789" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B7789" s="2" t="s">
         <v>15</v>
@@ -30319,7 +32073,7 @@
         <v>46</v>
       </c>
       <c r="C7798" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30349,7 +32103,7 @@
     </row>
     <row r="7848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7848" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B7848" s="2" t="s">
         <v>15</v>
@@ -30440,7 +32194,7 @@
         <v>46</v>
       </c>
       <c r="C7857" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30470,7 +32224,7 @@
     </row>
     <row r="7907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7907" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B7907" s="2" t="s">
         <v>15</v>
@@ -30561,7 +32315,7 @@
         <v>46</v>
       </c>
       <c r="C7916" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30591,7 +32345,7 @@
     </row>
     <row r="7966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7966" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B7966" s="2" t="s">
         <v>6</v>
@@ -30603,7 +32357,7 @@
     <row r="7967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7967" s="4"/>
       <c r="B7967" s="24" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C7967" s="25"/>
     </row>
@@ -30727,7 +32481,7 @@
       </c>
       <c r="B7980" s="9"/>
       <c r="C7980" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30768,7 +32522,7 @@
     </row>
     <row r="8025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8025" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B8025" s="2" t="s">
         <v>22</v>
@@ -30832,7 +32586,7 @@
       </c>
       <c r="B8031" s="9"/>
       <c r="C8031" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30855,7 +32609,7 @@
     </row>
     <row r="8084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8084" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B8084" s="2" t="s">
         <v>22</v>
@@ -30919,7 +32673,7 @@
       </c>
       <c r="B8090" s="9"/>
       <c r="C8090" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30942,7 +32696,7 @@
     </row>
     <row r="8143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8143" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B8143" s="2" t="s">
         <v>22</v>
@@ -31006,7 +32760,7 @@
       </c>
       <c r="B8149" s="9"/>
       <c r="C8149" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31029,7 +32783,7 @@
     </row>
     <row r="8202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8202" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B8202" s="2" t="s">
         <v>15</v>
@@ -31098,7 +32852,7 @@
         <v>234</v>
       </c>
       <c r="C8209" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31130,7 +32884,7 @@
     </row>
     <row r="8261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8261" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B8261" s="2" t="s">
         <v>24</v>
@@ -31142,7 +32896,7 @@
     <row r="8262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8262" s="4"/>
       <c r="B8262" s="24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C8262" s="25"/>
     </row>
@@ -31214,7 +32968,7 @@
       </c>
       <c r="B8269" s="9"/>
       <c r="C8269" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31255,7 +33009,7 @@
     </row>
     <row r="8320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8320" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B8320" s="2" t="s">
         <v>24</v>
@@ -31267,7 +33021,7 @@
     <row r="8321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8321" s="4"/>
       <c r="B8321" s="24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C8321" s="25"/>
     </row>
@@ -31339,7 +33093,7 @@
       </c>
       <c r="B8328" s="9"/>
       <c r="C8328" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31380,7 +33134,7 @@
     </row>
     <row r="8379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8379" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B8379" s="2" t="s">
         <v>24</v>
@@ -31392,7 +33146,7 @@
     <row r="8380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8380" s="4"/>
       <c r="B8380" s="24" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C8380" s="25"/>
     </row>
@@ -31464,7 +33218,7 @@
       </c>
       <c r="B8387" s="9"/>
       <c r="C8387" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31505,7 +33259,7 @@
     </row>
     <row r="8438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8438" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B8438" s="2" t="s">
         <v>19</v>
@@ -31517,7 +33271,7 @@
     <row r="8439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8439" s="4"/>
       <c r="B8439" s="24" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C8439" s="25"/>
     </row>
@@ -31609,7 +33363,7 @@
       </c>
       <c r="B8448" s="9"/>
       <c r="C8448" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31617,7 +33371,7 @@
         <v>4.2</v>
       </c>
       <c r="B8449" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C8449" s="10" t="s">
         <v>47</v>
@@ -31650,7 +33404,7 @@
     </row>
     <row r="8497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8497" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B8497" s="2" t="s">
         <v>22</v>
@@ -31694,7 +33448,7 @@
       </c>
       <c r="B8501" s="9"/>
       <c r="C8501" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31776,7 +33530,7 @@
     </row>
     <row r="8556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8556" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B8556" s="2" t="s">
         <v>6</v>
@@ -31788,7 +33542,7 @@
     <row r="8557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8557" s="4"/>
       <c r="B8557" s="30" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C8557" s="31"/>
     </row>
@@ -31924,7 +33678,7 @@
       </c>
       <c r="B8572" s="9"/>
       <c r="C8572" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31965,7 +33719,7 @@
     </row>
     <row r="8615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8615" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B8615" s="2" t="s">
         <v>19</v>
@@ -31977,7 +33731,7 @@
     <row r="8616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8616" s="4"/>
       <c r="B8616" s="24" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C8616" s="25"/>
     </row>
@@ -32083,7 +33837,7 @@
       </c>
       <c r="B8627" s="9"/>
       <c r="C8627" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32091,7 +33845,7 @@
         <v>5.2</v>
       </c>
       <c r="B8628" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8628" s="10" t="s">
         <v>47</v>
@@ -32124,7 +33878,7 @@
     </row>
     <row r="8674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8674" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B8674" s="2" t="s">
         <v>98</v>
@@ -32136,7 +33890,7 @@
     <row r="8675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8675" s="4"/>
       <c r="B8675" s="30" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C8675" s="31"/>
     </row>
@@ -32270,7 +34024,7 @@
       </c>
       <c r="B8690" s="9"/>
       <c r="C8690" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32311,7 +34065,7 @@
     </row>
     <row r="8733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8733" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B8733" s="2" t="s">
         <v>24</v>
@@ -32421,7 +34175,7 @@
         <v>46</v>
       </c>
       <c r="C8745" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32451,7 +34205,7 @@
     </row>
     <row r="8792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8792" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B8792" s="2" t="s">
         <v>24</v>
@@ -32561,7 +34315,7 @@
         <v>46</v>
       </c>
       <c r="C8804" s="10" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32589,10 +34343,3312 @@
       <c r="B8807" s="20"/>
       <c r="C8807" s="21"/>
     </row>
+    <row r="8851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8851" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B8851" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8851" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8852" s="4"/>
+      <c r="B8852" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8852" s="25"/>
+    </row>
+    <row r="8853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8853" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8853" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8853" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8854" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8854" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8854" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8855" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8855" s="9"/>
+      <c r="C8855" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8856" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8856" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8856" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8857" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8857" s="9"/>
+      <c r="C8857" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8858" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8858" s="9"/>
+      <c r="C8858" s="10"/>
+    </row>
+    <row r="8859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8859" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8859" s="9"/>
+      <c r="C8859" s="32" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8860" s="8"/>
+      <c r="B8860" s="9"/>
+      <c r="C8860" s="32"/>
+    </row>
+    <row r="8861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8861" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B8861" s="16"/>
+      <c r="C8861" s="23"/>
+    </row>
+    <row r="8862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8862" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8862" s="16"/>
+      <c r="C8862" s="23"/>
+    </row>
+    <row r="8863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8863" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B8863" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8863" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8864" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8864" s="9"/>
+      <c r="C8864" s="10"/>
+    </row>
+    <row r="8865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8865" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8865" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8865" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8866" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8866" s="20"/>
+      <c r="C8866" s="21"/>
+    </row>
+    <row r="8910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8910" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8910" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8910" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8911" s="4"/>
+      <c r="B8911" s="30" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8911" s="31"/>
+    </row>
+    <row r="8912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8912" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8912" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8912" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8913" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8913" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8913" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8914" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8914" s="9"/>
+      <c r="C8914" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8915" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B8915" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8915" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8916" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B8916" s="16"/>
+      <c r="C8916" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8917" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8917" s="16"/>
+      <c r="C8917" s="23"/>
+    </row>
+    <row r="8918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8918" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B8918" s="9"/>
+      <c r="C8918" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8919" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B8919" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8919" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8920" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8920" s="9"/>
+      <c r="C8920" s="14"/>
+    </row>
+    <row r="8921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8921" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B8921" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8921" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8922" s="8"/>
+      <c r="B8922" s="33"/>
+      <c r="C8922" s="14"/>
+    </row>
+    <row r="8923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8923" s="8"/>
+      <c r="B8923" s="33"/>
+      <c r="C8923" s="14"/>
+    </row>
+    <row r="8924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8924" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8924" s="9"/>
+      <c r="C8924" s="14"/>
+    </row>
+    <row r="8925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8925" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B8925" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8925" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8926" s="8"/>
+      <c r="B8926" s="33"/>
+      <c r="C8926" s="14"/>
+    </row>
+    <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8927" s="8"/>
+      <c r="B8927" s="33"/>
+      <c r="C8927" s="14"/>
+    </row>
+    <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8928" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B8928" s="9"/>
+      <c r="C8928" s="14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8929" s="8"/>
+      <c r="B8929" s="9"/>
+      <c r="C8929" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8930" s="8"/>
+      <c r="B8930" s="9"/>
+      <c r="C8930" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8931" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B8931" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8931" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8932" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B8932" s="9"/>
+      <c r="C8932" s="10"/>
+    </row>
+    <row r="8933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8933" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B8933" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8933" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8934" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8934" s="20"/>
+      <c r="C8934" s="21"/>
+    </row>
+    <row r="8969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8969" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8969" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8969" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8970" s="4"/>
+      <c r="B8970" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8970" s="25"/>
+    </row>
+    <row r="8971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8971" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8971" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8971" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8972" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8972" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8972" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8973" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8973" s="9"/>
+      <c r="C8973" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8974" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B8974" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8974" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8975" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B8975" s="9"/>
+      <c r="C8975" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8976" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8976" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8976" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8977" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8977" s="20"/>
+      <c r="C8977" s="21"/>
+    </row>
+    <row r="9028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9028" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B9028" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9028" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9029" s="4"/>
+      <c r="B9029" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9029" s="25"/>
+    </row>
+    <row r="9030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9030" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9030" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9030" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9031" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9031" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9031" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9032" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9032" s="9"/>
+      <c r="C9032" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9033" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9033" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9033" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9034" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9034" s="9"/>
+      <c r="C9034" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9035" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9035" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9035" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9036" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9036" s="9"/>
+      <c r="C9036" s="10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="9037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9037" s="8"/>
+      <c r="B9037" s="9"/>
+      <c r="C9037" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9038" s="8"/>
+      <c r="B9038" s="9"/>
+      <c r="C9038" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9039" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9039" s="9"/>
+      <c r="C9039" s="10"/>
+    </row>
+    <row r="9040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9040" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9040" s="9"/>
+      <c r="C9040" s="10" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9041" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B9041" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9041" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9042" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9042" s="9"/>
+      <c r="C9042" s="10"/>
+    </row>
+    <row r="9043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9043" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9043" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9043" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9044" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9044" s="20"/>
+      <c r="C9044" s="21"/>
+    </row>
+    <row r="9087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9087" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B9087" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9087" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9088" s="4"/>
+      <c r="B9088" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9088" s="25"/>
+    </row>
+    <row r="9089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9089" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9089" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9089" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9090" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9090" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9090" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9091" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9091" s="9"/>
+      <c r="C9091" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9092" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9092" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9092" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9093" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9093" s="9"/>
+      <c r="C9093" s="10" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9094" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9094" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9094" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9095" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9095" s="20"/>
+      <c r="C9095" s="21"/>
+    </row>
+    <row r="9146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9146" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B9146" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9146" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9147" s="4"/>
+      <c r="B9147" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9147" s="25"/>
+    </row>
+    <row r="9148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9148" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9148" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9148" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9149" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9149" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9149" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9150" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9150" s="9"/>
+      <c r="C9150" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9151" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9151" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9151" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9152" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9152" s="9"/>
+      <c r="C9152" s="10" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9153" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9153" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9153" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9154" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9154" s="20"/>
+      <c r="C9154" s="21"/>
+    </row>
+    <row r="9205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9205" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9205" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9205" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9206" s="4"/>
+      <c r="B9206" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9206" s="25"/>
+    </row>
+    <row r="9207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9207" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9207" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9207" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9208" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9208" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9208" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9209" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9209" s="9"/>
+      <c r="C9209" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9210" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9210" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9210" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9211" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9211" s="9"/>
+      <c r="C9211" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9212" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9212" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9212" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9213" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9213" s="9"/>
+      <c r="C9213" s="10" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="9214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9214" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B9214" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9214" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9215" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9215" s="9"/>
+      <c r="C9215" s="10"/>
+    </row>
+    <row r="9216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9216" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9216" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9216" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9217" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9217" s="20"/>
+      <c r="C9217" s="21"/>
+    </row>
+    <row r="9264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9264" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B9264" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9264" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9265" s="4"/>
+      <c r="B9265" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9265" s="25"/>
+    </row>
+    <row r="9266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9266" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9266" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9266" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9267" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9267" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9267" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9268" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9268" s="9"/>
+      <c r="C9268" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9269" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9269" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9269" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9270" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9270" s="9"/>
+      <c r="C9270" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9271" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9271" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9271" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9272" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9272" s="9"/>
+      <c r="C9272" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9273" s="8"/>
+      <c r="B9273" s="9"/>
+      <c r="C9273" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9274" s="8"/>
+      <c r="B9274" s="9"/>
+      <c r="C9274" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9275" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9275" s="9"/>
+      <c r="C9275" s="10"/>
+    </row>
+    <row r="9276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9276" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9276" s="9"/>
+      <c r="C9276" s="10" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9277" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B9277" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9277" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9278" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9278" s="9"/>
+      <c r="C9278" s="10"/>
+    </row>
+    <row r="9279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9279" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9279" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9279" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9280" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9280" s="20"/>
+      <c r="C9280" s="21"/>
+    </row>
+    <row r="9323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9323" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B9323" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9323" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9324" s="4"/>
+      <c r="B9324" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9324" s="25"/>
+    </row>
+    <row r="9325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9325" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9325" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9325" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9326" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9326" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9326" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9327" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9327" s="9"/>
+      <c r="C9327" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9328" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9328" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9328" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9329" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9329" s="9"/>
+      <c r="C9329" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9330" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9330" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9330" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9331" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9331" s="9"/>
+      <c r="C9331" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9332" s="8"/>
+      <c r="B9332" s="9"/>
+      <c r="C9332" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9333" s="8"/>
+      <c r="B9333" s="9"/>
+      <c r="C9333" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9334" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9334" s="9"/>
+      <c r="C9334" s="10"/>
+    </row>
+    <row r="9335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9335" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9335" s="9"/>
+      <c r="C9335" s="10" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9336" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B9336" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9336" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9337" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9337" s="9"/>
+      <c r="C9337" s="10"/>
+    </row>
+    <row r="9338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9338" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9338" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9338" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9339" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9339" s="20"/>
+      <c r="C9339" s="21"/>
+    </row>
+    <row r="9382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9382" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B9382" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9382" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9383" s="4"/>
+      <c r="B9383" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="C9383" s="25"/>
+    </row>
+    <row r="9384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9384" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9384" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9384" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9385" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9385" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9385" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9386" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9386" s="9"/>
+      <c r="C9386" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9387" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9387" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9387" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9388" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9388" s="9"/>
+      <c r="C9388" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9389" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9389" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9389" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9390" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9390" s="9"/>
+      <c r="C9390" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9391" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9391" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9391" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9392" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9392" s="9"/>
+      <c r="C9392" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9393" s="8"/>
+      <c r="B9393" s="9"/>
+      <c r="C9393" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9394" s="8"/>
+      <c r="B9394" s="9"/>
+      <c r="C9394" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9395" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B9395" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9395" s="10" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9396" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9396" s="9"/>
+      <c r="C9396" s="10"/>
+    </row>
+    <row r="9397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9397" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9397" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9397" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9398" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9398" s="20"/>
+      <c r="C9398" s="21"/>
+    </row>
+    <row r="9441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9441" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B9441" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9441" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9442" s="4"/>
+      <c r="B9442" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9442" s="25"/>
+    </row>
+    <row r="9443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9443" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9443" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9443" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9444" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9444" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9444" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9445" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9445" s="9"/>
+      <c r="C9445" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9446" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9446" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9446" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9447" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9447" s="9"/>
+      <c r="C9447" s="10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9448" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9448" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9448" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9449" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9449" s="20"/>
+      <c r="C9449" s="21"/>
+    </row>
+    <row r="9500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9500" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9500" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9500" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9501" s="4"/>
+      <c r="B9501" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9501" s="31"/>
+    </row>
+    <row r="9502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9502" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9502" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9502" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9503" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9503" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9503" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9504" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9504" s="9"/>
+      <c r="C9504" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9505" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9505" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9505" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9506" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9506" s="9"/>
+      <c r="C9506" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9507" s="8"/>
+      <c r="B9507" s="9"/>
+      <c r="C9507" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9508" s="8"/>
+      <c r="B9508" s="9"/>
+      <c r="C9508" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="9509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9509" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9509" s="9"/>
+      <c r="C9509" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9510" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="B9510" s="16"/>
+      <c r="C9510" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9511" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B9511" s="16"/>
+      <c r="C9511" s="23"/>
+    </row>
+    <row r="9512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9512" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9512" s="9"/>
+      <c r="C9512" s="10"/>
+    </row>
+    <row r="9513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9513" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9513" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9513" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9514" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9514" s="9"/>
+      <c r="C9514" s="10"/>
+    </row>
+    <row r="9515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9515" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9515" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9515" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9516" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B9516" s="9"/>
+      <c r="C9516" s="10"/>
+    </row>
+    <row r="9517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9517" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B9517" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9517" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9518" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B9518" s="9"/>
+      <c r="C9518" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9519" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B9519" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9519" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9520" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9520" s="20"/>
+      <c r="C9520" s="21"/>
+    </row>
+    <row r="9559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9559" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B9559" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9559" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9560" s="4"/>
+      <c r="B9560" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9560" s="25"/>
+    </row>
+    <row r="9561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9561" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9561" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9561" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9562" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9562" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9562" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9563" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9563" s="9"/>
+      <c r="C9563" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9564" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9564" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9564" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9565" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9565" s="9"/>
+      <c r="C9565" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9566" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9566" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9566" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9567" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9567" s="20"/>
+      <c r="C9567" s="21"/>
+    </row>
+    <row r="9618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9618" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B9618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9618" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9619" s="4"/>
+      <c r="B9619" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9619" s="25"/>
+    </row>
+    <row r="9620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9620" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9620" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9620" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9621" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9621" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9621" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9622" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9622" s="9"/>
+      <c r="C9622" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9623" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9623" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9623" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9624" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9624" s="9"/>
+      <c r="C9624" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9625" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9625" s="9"/>
+      <c r="C9625" s="10"/>
+    </row>
+    <row r="9626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9626" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9626" s="9"/>
+      <c r="C9626" s="10"/>
+    </row>
+    <row r="9627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9627" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B9627" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9627" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9628" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9628" s="9"/>
+      <c r="C9628" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9629" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9629" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9629" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9630" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9630" s="20"/>
+      <c r="C9630" s="21"/>
+    </row>
+    <row r="9677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9677" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9677" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9677" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9678" s="4"/>
+      <c r="B9678" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9678" s="25"/>
+    </row>
+    <row r="9679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9679" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9679" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9679" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9680" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9680" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9680" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9681" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9681" s="9"/>
+      <c r="C9681" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9682" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9682" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9682" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9683" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B9683" s="16"/>
+      <c r="C9683" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9684" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9684" s="16"/>
+      <c r="C9684" s="23"/>
+    </row>
+    <row r="9685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9685" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9685" s="9"/>
+      <c r="C9685" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9686" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B9686" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9686" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9687" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9687" s="9"/>
+      <c r="C9687" s="10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="9688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9688" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9688" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9688" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9689" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9689" s="20"/>
+      <c r="C9689" s="21"/>
+    </row>
+    <row r="9736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9736" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B9736" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9736" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9737" s="4"/>
+      <c r="B9737" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9737" s="25"/>
+    </row>
+    <row r="9738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9738" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9738" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9738" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9739" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9739" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9739" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9740" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9740" s="9"/>
+      <c r="C9740" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9741" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9741" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9741" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9742" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B9742" s="16"/>
+      <c r="C9742" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9743" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9743" s="16"/>
+      <c r="C9743" s="23"/>
+    </row>
+    <row r="9744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9744" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9744" s="9"/>
+      <c r="C9744" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9745" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B9745" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9745" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9746" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9746" s="9"/>
+      <c r="C9746" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9747" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9747" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9747" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9748" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9748" s="20"/>
+      <c r="C9748" s="21"/>
+    </row>
+    <row r="9795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9795" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B9795" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9795" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9796" s="4"/>
+      <c r="B9796" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9796" s="25"/>
+    </row>
+    <row r="9797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9797" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9797" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9797" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9798" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9798" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9798" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9799" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9799" s="9"/>
+      <c r="C9799" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9800" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9800" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9800" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9801" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B9801" s="16"/>
+      <c r="C9801" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9802" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9802" s="16"/>
+      <c r="C9802" s="23"/>
+    </row>
+    <row r="9803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9803" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9803" s="9"/>
+      <c r="C9803" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9804" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B9804" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9804" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9805" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9805" s="9"/>
+      <c r="C9805" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9806" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9806" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9806" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9807" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9807" s="20"/>
+      <c r="C9807" s="21"/>
+    </row>
+    <row r="9854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9854" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B9854" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9854" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9855" s="4"/>
+      <c r="B9855" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9855" s="25"/>
+    </row>
+    <row r="9856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9856" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9856" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9856" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9857" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9857" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9857" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9858" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9858" s="9"/>
+      <c r="C9858" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9859" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B9859" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9859" s="10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9860" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B9860" s="16"/>
+      <c r="C9860" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9861" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9861" s="16"/>
+      <c r="C9861" s="23"/>
+    </row>
+    <row r="9862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9862" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B9862" s="9"/>
+      <c r="C9862" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9863" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B9863" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9863" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9864" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9864" s="9"/>
+      <c r="C9864" s="10"/>
+    </row>
+    <row r="9865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9865" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B9865" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9865" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9866" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9866" s="9"/>
+      <c r="C9866" s="10"/>
+    </row>
+    <row r="9867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9867" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B9867" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9867" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9868" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B9868" s="9"/>
+      <c r="C9868" s="10"/>
+    </row>
+    <row r="9869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9869" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B9869" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9869" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9870" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B9870" s="9"/>
+      <c r="C9870" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9871" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B9871" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9871" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9872" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9872" s="20"/>
+      <c r="C9872" s="21"/>
+    </row>
+    <row r="9913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9913" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9913" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9913" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9914" s="4"/>
+      <c r="B9914" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9914" s="25"/>
+    </row>
+    <row r="9915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9915" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9915" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9915" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9916" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9916" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9916" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9917" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9917" s="9"/>
+      <c r="C9917" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9918" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9918" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9918" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9919" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9919" s="9"/>
+      <c r="C9919" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="9920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9920" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9920" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9920" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9921" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9921" s="20"/>
+      <c r="C9921" s="21"/>
+    </row>
+    <row r="9972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9972" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B9972" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9972" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9973" s="4"/>
+      <c r="B9973" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9973" s="25"/>
+    </row>
+    <row r="9974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9974" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9974" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9974" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9975" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9975" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9975" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9976" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9976" s="9"/>
+      <c r="C9976" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9977" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B9977" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9977" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9978" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B9978" s="9"/>
+      <c r="C9978" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9979" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9979" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9979" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9980" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9980" s="20"/>
+      <c r="C9980" s="21"/>
+    </row>
+    <row r="10031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10031" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B10031" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10031" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10032" s="4"/>
+      <c r="B10032" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10032" s="25"/>
+    </row>
+    <row r="10033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10033" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10033" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10033" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10034" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10034" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10034" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10035" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10035" s="9"/>
+      <c r="C10035" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10036" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B10036" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10036" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10037" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10037" s="9"/>
+      <c r="C10037" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10038" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10038" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10038" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10039" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10039" s="20"/>
+      <c r="C10039" s="21"/>
+    </row>
+    <row r="10090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10090" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10090" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10090" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10091" s="4"/>
+      <c r="B10091" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10091" s="25"/>
+    </row>
+    <row r="10092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10092" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10092" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10092" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10093" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10093" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10093" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10094" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10094" s="9"/>
+      <c r="C10094" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10095" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10095" s="9"/>
+      <c r="C10095" s="10"/>
+    </row>
+    <row r="10096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10096" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10096" s="9"/>
+      <c r="C10096" s="10"/>
+    </row>
+    <row r="10097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10097" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10097" s="9"/>
+      <c r="C10097" s="10"/>
+    </row>
+    <row r="10098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10098" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10098" s="9"/>
+      <c r="C10098" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10099" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B10099" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10099" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10100" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10100" s="9"/>
+      <c r="C10100" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="10101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10101" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10101" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10101" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10102" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10102" s="20"/>
+      <c r="C10102" s="21"/>
+    </row>
+    <row r="10149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10149" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B10149" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10149" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10150" s="4"/>
+      <c r="B10150" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10150" s="25"/>
+    </row>
+    <row r="10151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10151" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10151" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10151" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10152" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10152" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10152" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10153" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10153" s="9"/>
+      <c r="C10153" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10154" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10154" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10154" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10155" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10155" s="9"/>
+      <c r="C10155" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10156" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10156" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10156" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10157" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10157" s="9"/>
+      <c r="C10157" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10158" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B10158" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10158" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10159" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10159" s="9"/>
+      <c r="C10159" s="10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10160" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10160" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10160" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10161" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10161" s="20"/>
+      <c r="C10161" s="21"/>
+    </row>
+    <row r="10208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10208" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B10208" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10208" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10209" s="4"/>
+      <c r="B10209" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10209" s="25"/>
+    </row>
+    <row r="10210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10210" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10210" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10210" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10211" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10211" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10211" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10212" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10212" s="9"/>
+      <c r="C10212" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10213" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10213" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10213" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10214" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10214" s="9"/>
+      <c r="C10214" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10215" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10215" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10215" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10216" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10216" s="9"/>
+      <c r="C10216" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10217" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B10217" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10217" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10218" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10218" s="9"/>
+      <c r="C10218" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10219" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10219" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10219" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10220" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10220" s="20"/>
+      <c r="C10220" s="21"/>
+    </row>
+    <row r="10267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10267" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B10267" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10267" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10268" s="4"/>
+      <c r="B10268" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10268" s="25"/>
+    </row>
+    <row r="10269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10269" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10269" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10269" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10270" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10270" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10270" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10271" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10271" s="9"/>
+      <c r="C10271" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10272" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10272" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10272" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10273" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10273" s="9"/>
+      <c r="C10273" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10274" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10274" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10274" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10275" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10275" s="9"/>
+      <c r="C10275" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10276" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B10276" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10276" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10277" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10277" s="9"/>
+      <c r="C10277" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10278" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10278" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10278" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10279" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10279" s="20"/>
+      <c r="C10279" s="21"/>
+    </row>
+    <row r="10326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10326" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B10326" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10326" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10327" s="4"/>
+      <c r="B10327" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10327" s="25"/>
+    </row>
+    <row r="10328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10328" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10328" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10328" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10329" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10329" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10329" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10330" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10330" s="9"/>
+      <c r="C10330" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10331" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10331" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10331" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10332" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10332" s="9"/>
+      <c r="C10332" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10333" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10333" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10333" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10334" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10334" s="9"/>
+      <c r="C10334" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10335" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10335" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10335" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10336" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10336" s="9"/>
+      <c r="C10336" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10337" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B10337" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10337" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10338" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10338" s="9"/>
+      <c r="C10338" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10339" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10339" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10339" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10340" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10340" s="20"/>
+      <c r="C10340" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="113">
+    <mergeCell ref="B9501:C9501"/>
+    <mergeCell ref="B8925:B8927"/>
+    <mergeCell ref="B8921:B8923"/>
     <mergeCell ref="C8741:C8742"/>
     <mergeCell ref="C8800:C8801"/>
+    <mergeCell ref="C8859:C8860"/>
+    <mergeCell ref="B8911:C8911"/>
     <mergeCell ref="C8502:C8503"/>
     <mergeCell ref="B8557:C8557"/>
     <mergeCell ref="B8675:C8675"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE0807F-6EEE-4B9C-8F6B-19FBEC57EF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2062A52A-F9CA-443F-B41B-BAC3FAECB5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$10384</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$11328</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4257" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4639" uniqueCount="480">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -7435,6 +7435,32 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Inc. PC if previous cycle was skipped. Set Address to Operand + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Sets the </t>
     </r>
     <r>
@@ -7816,9 +7842,6 @@
     <t>Address.L = Pointer.L.</t>
   </si>
   <si>
-    <t>Address.H = D.H.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Address.H = </t>
     </r>
@@ -9506,6 +9529,9 @@
     </r>
   </si>
   <si>
+    <t>LDX (A2)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Inc. </t>
     </r>
@@ -9528,11 +9554,485 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Set Pointer to Pointer + X + D.</t>
-    </r>
-  </si>
-  <si>
-    <t>LDX (A2)</t>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A3)</t>
+  </si>
+  <si>
+    <t>LDY (A4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A5)</t>
+  </si>
+  <si>
+    <t>LDX (A6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A7)</t>
+  </si>
+  <si>
+    <t>TAY (A8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (A9)</t>
   </si>
   <si>
     <r>
@@ -9568,6 +10068,119 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TAX (AA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>X</t>
     </r>
     <r>
@@ -9578,7 +10191,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.L to Operand.L. Set </t>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
     </r>
     <r>
       <rPr>
@@ -9620,6 +10254,698 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLB (AB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDY (AC)</t>
+  </si>
+  <si>
+    <t>LDA (AD)</t>
+  </si>
+  <si>
+    <t>LDX (AE)</t>
+  </si>
+  <si>
+    <t>LDA (AF)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set Pointer to Pointer + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Direct, Y (Write)</t>
+  </si>
+  <si>
+    <t>BCS (B0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (B1)</t>
+  </si>
+  <si>
+    <t>LDA (B2)</t>
+  </si>
+  <si>
+    <t>LDA (B3)</t>
+  </si>
+  <si>
+    <t>LDY (B4)</t>
+  </si>
+  <si>
+    <t>LDA (B5)</t>
+  </si>
+  <si>
+    <t>LDX (B6)</t>
+  </si>
+  <si>
+    <t>Direct, Y (Read)</t>
+  </si>
+  <si>
+    <t>LDA (B7)</t>
+  </si>
+  <si>
+    <t>CLV (B8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sets the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDA (B9)</t>
+  </si>
+  <si>
+    <t>TSX (BA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>TYX (BB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>LDY (BC)</t>
+  </si>
+  <si>
+    <t>LDA (BD)</t>
+  </si>
+  <si>
+    <t>LDX (BE)</t>
+  </si>
+  <si>
+    <t>LDA (BF)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">L to Operand.L. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">.L &amp; $80). Set </t>
     </r>
     <r>
@@ -9652,7 +10978,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>X</t>
+      <t>A</t>
     </r>
     <r>
       <rPr>
@@ -9664,768 +10990,6 @@
       </rPr>
       <t>.L.</t>
     </r>
-  </si>
-  <si>
-    <t>LDA (A3)</t>
-  </si>
-  <si>
-    <t>LDY (A4)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L to Operand.L. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>LDA (A5)</t>
-  </si>
-  <si>
-    <t>LDX (A6)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L to Operand.L. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>LDA (A7)</t>
-  </si>
-  <si>
-    <t>TAY (A8)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">L = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>LDA (A9)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L to Operand.L. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>TAX (AA)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>PLB (AB)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; $80), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>LDY (AC)</t>
-  </si>
-  <si>
-    <t>LDA (AD)</t>
-  </si>
-  <si>
-    <t>LDX (AE)</t>
-  </si>
-  <si>
-    <t>LDA (AF)</t>
   </si>
 </sst>
 </file>
@@ -11026,7 +11590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C10340"/>
+  <dimension ref="A1:C11286"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -30038,7 +30602,7 @@
       </c>
       <c r="B7087" s="9"/>
       <c r="C7087" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30061,7 +30625,7 @@
     </row>
     <row r="7140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7140" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B7140" s="2" t="s">
         <v>24</v>
@@ -30328,7 +30892,7 @@
     </row>
     <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7199" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B7199" s="2" t="s">
         <v>24</v>
@@ -30421,7 +30985,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B7209" s="33" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
@@ -30455,7 +31019,7 @@
     </row>
     <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7258" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B7258" s="2" t="s">
         <v>22</v>
@@ -30519,7 +31083,7 @@
       </c>
       <c r="B7264" s="9"/>
       <c r="C7264" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30542,7 +31106,7 @@
     </row>
     <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7317" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B7317" s="2" t="s">
         <v>6</v>
@@ -30554,7 +31118,7 @@
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
       <c r="B7318" s="30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C7318" s="31"/>
     </row>
@@ -30626,7 +31190,7 @@
       </c>
       <c r="B7325" s="9"/>
       <c r="C7325" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30666,7 +31230,7 @@
         <v>5.2</v>
       </c>
       <c r="B7330" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C7330" s="10" t="s">
         <v>276</v>
@@ -30701,7 +31265,7 @@
     </row>
     <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7376" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B7376" s="2" t="s">
         <v>24</v>
@@ -30785,7 +31349,7 @@
       </c>
       <c r="B7384" s="9"/>
       <c r="C7384" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30968,7 +31532,7 @@
     </row>
     <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7435" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B7435" s="2" t="s">
         <v>98</v>
@@ -31164,7 +31728,7 @@
     </row>
     <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7494" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B7494" s="2" t="s">
         <v>19</v>
@@ -31423,7 +31987,7 @@
     </row>
     <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7553" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B7553" s="2" t="s">
         <v>15</v>
@@ -31467,7 +32031,7 @@
       </c>
       <c r="B7557" s="9"/>
       <c r="C7557" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31549,7 +32113,7 @@
     </row>
     <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7612" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B7612" s="2" t="s">
         <v>6</v>
@@ -31561,7 +32125,7 @@
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
       <c r="B7613" s="30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C7613" s="31"/>
     </row>
@@ -31620,7 +32184,7 @@
       <c r="A7619" s="8"/>
       <c r="B7619" s="9"/>
       <c r="C7619" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34357,7 +34921,7 @@
     <row r="8852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8852" s="4"/>
       <c r="B8852" s="24" t="s">
-        <v>337</v>
+        <v>457</v>
       </c>
       <c r="C8852" s="25"/>
     </row>
@@ -35857,21 +36421,21 @@
       </c>
       <c r="B9506" s="9"/>
       <c r="C9506" s="10" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9507" s="8"/>
       <c r="B9507" s="9"/>
       <c r="C9507" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9508" s="8"/>
       <c r="B9508" s="9"/>
       <c r="C9508" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35982,7 +36546,7 @@
     </row>
     <row r="9559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9559" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B9559" s="2" t="s">
         <v>22</v>
@@ -36046,7 +36610,7 @@
       </c>
       <c r="B9565" s="9"/>
       <c r="C9565" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36069,7 +36633,7 @@
     </row>
     <row r="9618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9618" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B9618" s="2" t="s">
         <v>24</v>
@@ -36190,7 +36754,7 @@
     </row>
     <row r="9677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9677" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B9677" s="2" t="s">
         <v>15</v>
@@ -36290,7 +36854,7 @@
       </c>
       <c r="B9687" s="9"/>
       <c r="C9687" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36313,7 +36877,7 @@
     </row>
     <row r="9736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9736" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B9736" s="2" t="s">
         <v>15</v>
@@ -36436,7 +37000,7 @@
     </row>
     <row r="9795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9795" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B9795" s="2" t="s">
         <v>15</v>
@@ -36536,7 +37100,7 @@
       </c>
       <c r="B9805" s="9"/>
       <c r="C9805" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36559,7 +37123,7 @@
     </row>
     <row r="9854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9854" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B9854" s="2" t="s">
         <v>6</v>
@@ -36736,7 +37300,7 @@
     </row>
     <row r="9913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9913" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B9913" s="2" t="s">
         <v>22</v>
@@ -36800,7 +37364,7 @@
       </c>
       <c r="B9919" s="9"/>
       <c r="C9919" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36823,7 +37387,7 @@
     </row>
     <row r="9972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9972" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B9972" s="2" t="s">
         <v>22</v>
@@ -36887,7 +37451,7 @@
       </c>
       <c r="B9978" s="9"/>
       <c r="C9978" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36910,7 +37474,7 @@
     </row>
     <row r="10031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10031" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B10031" s="2" t="s">
         <v>22</v>
@@ -36974,7 +37538,7 @@
       </c>
       <c r="B10037" s="9"/>
       <c r="C10037" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36997,7 +37561,7 @@
     </row>
     <row r="10090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10090" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B10090" s="2" t="s">
         <v>24</v>
@@ -37091,7 +37655,7 @@
       </c>
       <c r="B10100" s="9"/>
       <c r="C10100" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37114,7 +37678,7 @@
     </row>
     <row r="10149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10149" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10149" s="2" t="s">
         <v>24</v>
@@ -37218,7 +37782,7 @@
       </c>
       <c r="B10159" s="9"/>
       <c r="C10159" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37241,7 +37805,7 @@
     </row>
     <row r="10208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10208" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B10208" s="2" t="s">
         <v>24</v>
@@ -37368,7 +37932,7 @@
     </row>
     <row r="10267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10267" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B10267" s="2" t="s">
         <v>24</v>
@@ -37472,7 +38036,7 @@
       </c>
       <c r="B10277" s="9"/>
       <c r="C10277" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37495,7 +38059,7 @@
     </row>
     <row r="10326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10326" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B10326" s="2" t="s">
         <v>19</v>
@@ -37640,9 +38204,2430 @@
       <c r="B10340" s="20"/>
       <c r="C10340" s="21"/>
     </row>
+    <row r="10385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10385" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B10385" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10385" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10386" s="4"/>
+      <c r="B10386" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10386" s="6"/>
+    </row>
+    <row r="10387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10387" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10387" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10387" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10388" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10388" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10388" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10389" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10389" s="9"/>
+      <c r="C10389" s="10" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10390" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B10390" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10390" s="32" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10391" s="8"/>
+      <c r="B10391" s="9"/>
+      <c r="C10391" s="32"/>
+    </row>
+    <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10392" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10392" s="9"/>
+      <c r="C10392" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10393" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10393" s="9"/>
+      <c r="C10393" s="10"/>
+    </row>
+    <row r="10394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10394" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10394" s="9"/>
+      <c r="C10394" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10395" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B10395" s="9"/>
+      <c r="C10395" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10396" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10396" s="9"/>
+      <c r="C10396" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10397" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10397" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10397" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10398" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10398" s="20"/>
+      <c r="C10398" s="21"/>
+    </row>
+    <row r="10444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10444" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B10444" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10444" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10445" s="4"/>
+      <c r="B10445" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10445" s="31"/>
+    </row>
+    <row r="10446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10446" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10446" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10446" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10447" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10447" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10447" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10448" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10448" s="9"/>
+      <c r="C10448" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10449" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10449" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10449" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10450" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B10450" s="16"/>
+      <c r="C10450" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10451" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10451" s="16"/>
+      <c r="C10451" s="23"/>
+    </row>
+    <row r="10452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10452" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10452" s="9"/>
+      <c r="C10452" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10453" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10453" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10453" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10454" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10454" s="9"/>
+      <c r="C10454" s="10"/>
+    </row>
+    <row r="10455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10455" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10455" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10455" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10456" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10456" s="9"/>
+      <c r="C10456" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10457" s="8"/>
+      <c r="B10457" s="9"/>
+      <c r="C10457" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10458" s="8"/>
+      <c r="B10458" s="9"/>
+      <c r="C10458" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10459" s="8"/>
+      <c r="B10459" s="9"/>
+      <c r="C10459" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10460" s="8"/>
+      <c r="B10460" s="9"/>
+      <c r="C10460" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10461" s="15">
+        <v>5.2</v>
+      </c>
+      <c r="B10461" s="16"/>
+      <c r="C10461" s="23"/>
+    </row>
+    <row r="10462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10462" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="B10462" s="16"/>
+      <c r="C10462" s="23"/>
+    </row>
+    <row r="10463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10463" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B10463" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10463" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10464" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B10464" s="9"/>
+      <c r="C10464" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10465" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B10465" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10465" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10466" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10466" s="20"/>
+      <c r="C10466" s="21"/>
+    </row>
+    <row r="10503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10503" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B10503" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10503" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10504" s="4"/>
+      <c r="B10504" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10504" s="25"/>
+    </row>
+    <row r="10505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10505" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10505" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10505" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10506" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10506" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10506" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10507" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10507" s="9"/>
+      <c r="C10507" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10508" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10508" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10508" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10509" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B10509" s="16"/>
+      <c r="C10509" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10510" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10510" s="16"/>
+      <c r="C10510" s="23"/>
+    </row>
+    <row r="10511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10511" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10511" s="9"/>
+      <c r="C10511" s="10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10512" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10512" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10512" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10513" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10513" s="9"/>
+      <c r="C10513" s="10"/>
+    </row>
+    <row r="10514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10514" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10514" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10514" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10515" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10515" s="9"/>
+      <c r="C10515" s="10"/>
+    </row>
+    <row r="10516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10516" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B10516" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10516" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10517" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10517" s="9"/>
+      <c r="C10517" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10518" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B10518" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10518" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10519" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10519" s="20"/>
+      <c r="C10519" s="21"/>
+    </row>
+    <row r="10562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10562" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B10562" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10562" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10563" s="4"/>
+      <c r="B10563" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10563" s="31"/>
+    </row>
+    <row r="10564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10564" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10564" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10564" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10565" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10565" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10565" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10566" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10566" s="9"/>
+      <c r="C10566" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10567" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10567" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10567" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10568" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10568" s="9"/>
+      <c r="C10568" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10569" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10569" s="9"/>
+      <c r="C10569" s="10"/>
+    </row>
+    <row r="10570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10570" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10570" s="9"/>
+      <c r="C10570" s="10"/>
+    </row>
+    <row r="10571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10571" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10571" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10571" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10572" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10572" s="9"/>
+      <c r="C10572" s="10"/>
+    </row>
+    <row r="10573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10573" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10573" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10573" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10574" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10574" s="9"/>
+      <c r="C10574" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10575" s="8"/>
+      <c r="B10575" s="9"/>
+      <c r="C10575" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10576" s="8"/>
+      <c r="B10576" s="9"/>
+      <c r="C10576" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10577" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10577" s="9"/>
+      <c r="C10577" s="10"/>
+    </row>
+    <row r="10578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10578" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10578" s="9"/>
+      <c r="C10578" s="10"/>
+    </row>
+    <row r="10579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10579" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B10579" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10579" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10580" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B10580" s="9"/>
+      <c r="C10580" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10581" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B10581" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10581" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10582" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10582" s="20"/>
+      <c r="C10582" s="21"/>
+    </row>
+    <row r="10621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10621" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B10621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10621" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10622" s="4"/>
+      <c r="B10622" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10622" s="25"/>
+    </row>
+    <row r="10623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10623" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10623" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10623" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10624" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10624" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10624" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10625" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10625" s="9"/>
+      <c r="C10625" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10626" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10626" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10626" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10627" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10627" s="9"/>
+      <c r="C10627" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10628" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10628" s="9"/>
+      <c r="C10628" s="10"/>
+    </row>
+    <row r="10629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10629" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10629" s="9"/>
+      <c r="C10629" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10630" s="8"/>
+      <c r="B10630" s="9"/>
+      <c r="C10630" s="32"/>
+    </row>
+    <row r="10631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10631" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B10631" s="16"/>
+      <c r="C10631" s="23"/>
+    </row>
+    <row r="10632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10632" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10632" s="16"/>
+      <c r="C10632" s="23"/>
+    </row>
+    <row r="10633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10633" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B10633" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10633" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10634" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10634" s="9"/>
+      <c r="C10634" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10635" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10635" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10635" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10636" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10636" s="20"/>
+      <c r="C10636" s="21"/>
+    </row>
+    <row r="10680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10680" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10680" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10680" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10681" s="4"/>
+      <c r="B10681" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10681" s="25"/>
+    </row>
+    <row r="10682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10682" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10682" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10682" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10683" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10683" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10683" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10684" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10684" s="9"/>
+      <c r="C10684" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10685" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10685" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10685" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10686" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10686" s="9"/>
+      <c r="C10686" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10687" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10687" s="9"/>
+      <c r="C10687" s="10"/>
+    </row>
+    <row r="10688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10688" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10688" s="9"/>
+      <c r="C10688" s="32" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10689" s="8"/>
+      <c r="B10689" s="9"/>
+      <c r="C10689" s="32"/>
+    </row>
+    <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10690" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B10690" s="16"/>
+      <c r="C10690" s="23"/>
+    </row>
+    <row r="10691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10691" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10691" s="16"/>
+      <c r="C10691" s="23"/>
+    </row>
+    <row r="10692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10692" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B10692" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10692" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10693" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10693" s="9"/>
+      <c r="C10693" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10694" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10694" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10694" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10695" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10695" s="20"/>
+      <c r="C10695" s="21"/>
+    </row>
+    <row r="10739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10739" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B10739" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10739" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10740" s="4"/>
+      <c r="B10740" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="C10740" s="25"/>
+    </row>
+    <row r="10741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10741" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10741" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10741" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10742" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10742" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10742" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10743" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10743" s="9"/>
+      <c r="C10743" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10744" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10744" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10744" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10745" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10745" s="9"/>
+      <c r="C10745" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10746" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10746" s="9"/>
+      <c r="C10746" s="10"/>
+    </row>
+    <row r="10747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10747" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10747" s="9"/>
+      <c r="C10747" s="32" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10748" s="8"/>
+      <c r="B10748" s="9"/>
+      <c r="C10748" s="32"/>
+    </row>
+    <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10749" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B10749" s="16"/>
+      <c r="C10749" s="23"/>
+    </row>
+    <row r="10750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10750" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10750" s="16"/>
+      <c r="C10750" s="23"/>
+    </row>
+    <row r="10751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10751" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B10751" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10751" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10752" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10752" s="9"/>
+      <c r="C10752" s="10" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10753" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10753" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10753" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10754" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10754" s="20"/>
+      <c r="C10754" s="21"/>
+    </row>
+    <row r="10798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10798" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B10798" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10798" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10799" s="4"/>
+      <c r="B10799" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10799" s="31"/>
+    </row>
+    <row r="10800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10800" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10800" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10800" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10801" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10801" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10801" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10802" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10802" s="9"/>
+      <c r="C10802" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10803" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10803" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10803" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10804" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B10804" s="16"/>
+      <c r="C10804" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10805" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10805" s="16"/>
+      <c r="C10805" s="23"/>
+    </row>
+    <row r="10806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10806" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10806" s="9"/>
+      <c r="C10806" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10807" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B10807" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10807" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10808" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10808" s="9"/>
+      <c r="C10808" s="10"/>
+    </row>
+    <row r="10809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10809" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B10809" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10809" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10810" s="8"/>
+      <c r="B10810" s="33"/>
+      <c r="C10810" s="10"/>
+    </row>
+    <row r="10811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10811" s="8"/>
+      <c r="B10811" s="33"/>
+      <c r="C10811" s="10"/>
+    </row>
+    <row r="10812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10812" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10812" s="9"/>
+      <c r="C10812" s="10"/>
+    </row>
+    <row r="10813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10813" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10813" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10813" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10814" s="8"/>
+      <c r="B10814" s="33"/>
+      <c r="C10814" s="10"/>
+    </row>
+    <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10815" s="8"/>
+      <c r="B10815" s="33"/>
+      <c r="C10815" s="10"/>
+    </row>
+    <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10816" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B10816" s="9"/>
+      <c r="C10816" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10817" s="8"/>
+      <c r="B10817" s="9"/>
+      <c r="C10817" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10818" s="8"/>
+      <c r="B10818" s="9"/>
+      <c r="C10818" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10819" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B10819" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10819" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10820" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10820" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B10820" s="9"/>
+      <c r="C10820" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10821" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B10821" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10821" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10822" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10822" s="20"/>
+      <c r="C10822" s="21"/>
+    </row>
+    <row r="10857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10857" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B10857" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10857" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10858" s="4"/>
+      <c r="B10858" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10858" s="25"/>
+    </row>
+    <row r="10859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10859" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10859" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10859" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10860" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10860" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10860" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10861" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10861" s="9"/>
+      <c r="C10861" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10862" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B10862" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10862" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10863" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10863" s="9"/>
+      <c r="C10863" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="10864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10864" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10864" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10864" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10865" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10865" s="20"/>
+      <c r="C10865" s="21"/>
+    </row>
+    <row r="10916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10916" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B10916" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10916" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10917" s="4"/>
+      <c r="B10917" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10917" s="25"/>
+    </row>
+    <row r="10918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10918" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10918" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10918" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10919" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10919" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10919" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10920" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10920" s="9"/>
+      <c r="C10920" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10921" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B10921" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10921" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10922" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10922" s="9"/>
+      <c r="C10922" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10923" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10923" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10923" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10924" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B10924" s="9"/>
+      <c r="C10924" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10925" s="8"/>
+      <c r="B10925" s="9"/>
+      <c r="C10925" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10926" s="8"/>
+      <c r="B10926" s="9"/>
+      <c r="C10926" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10927" s="8"/>
+      <c r="B10927" s="9"/>
+      <c r="C10927" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10928" s="8"/>
+      <c r="B10928" s="9"/>
+      <c r="C10928" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10929" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B10929" s="16"/>
+      <c r="C10929" s="23"/>
+    </row>
+    <row r="10930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10930" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10930" s="16"/>
+      <c r="C10930" s="23"/>
+    </row>
+    <row r="10931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10931" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B10931" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10931" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10932" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10932" s="9"/>
+      <c r="C10932" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10933" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B10933" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10933" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10934" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10934" s="20"/>
+      <c r="C10934" s="21"/>
+    </row>
+    <row r="10975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10975" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B10975" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10975" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10976" s="4"/>
+      <c r="B10976" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10976" s="25"/>
+    </row>
+    <row r="10977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10977" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10977" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10977" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10978" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10978" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10978" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10979" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10979" s="9"/>
+      <c r="C10979" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10980" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B10980" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10980" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10981" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B10981" s="9"/>
+      <c r="C10981" s="10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10982" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10982" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10982" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10983" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10983" s="20"/>
+      <c r="C10983" s="21"/>
+    </row>
+    <row r="11034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11034" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B11034" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11034" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11035" s="4"/>
+      <c r="B11035" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11035" s="25"/>
+    </row>
+    <row r="11036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11036" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11036" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11036" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11037" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11037" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11037" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11038" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11038" s="9"/>
+      <c r="C11038" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11039" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B11039" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11039" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11040" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11040" s="9"/>
+      <c r="C11040" s="10" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11041" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11041" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11041" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11042" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11042" s="20"/>
+      <c r="C11042" s="21"/>
+    </row>
+    <row r="11093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11093" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B11093" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11093" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11094" s="4"/>
+      <c r="B11094" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11094" s="25"/>
+    </row>
+    <row r="11095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11095" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11095" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11095" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11096" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11096" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11096" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11097" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11097" s="9"/>
+      <c r="C11097" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11098" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11098" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11098" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11099" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11099" s="9"/>
+      <c r="C11099" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11100" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11100" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11100" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11101" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11101" s="9"/>
+      <c r="C11101" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11102" s="8"/>
+      <c r="B11102" s="9"/>
+      <c r="C11102" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11103" s="8"/>
+      <c r="B11103" s="9"/>
+      <c r="C11103" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11104" s="8"/>
+      <c r="B11104" s="9"/>
+      <c r="C11104" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11105" s="8"/>
+      <c r="B11105" s="9"/>
+      <c r="C11105" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11106" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B11106" s="16"/>
+      <c r="C11106" s="23"/>
+    </row>
+    <row r="11107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11107" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11107" s="16"/>
+      <c r="C11107" s="23"/>
+    </row>
+    <row r="11108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11108" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B11108" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11108" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11109" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11109" s="9"/>
+      <c r="C11109" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="11110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11110" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B11110" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11110" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11111" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11111" s="20"/>
+      <c r="C11111" s="21"/>
+    </row>
+    <row r="11152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11152" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B11152" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11152" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11153" s="4"/>
+      <c r="B11153" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11153" s="25"/>
+    </row>
+    <row r="11154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11154" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11154" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11154" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11155" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11155" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11155" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11156" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11156" s="9"/>
+      <c r="C11156" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11157" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11157" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11157" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11158" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11158" s="9"/>
+      <c r="C11158" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11159" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11159" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11159" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11160" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11160" s="9"/>
+      <c r="C11160" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11161" s="8"/>
+      <c r="B11161" s="9"/>
+      <c r="C11161" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11162" s="8"/>
+      <c r="B11162" s="9"/>
+      <c r="C11162" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11163" s="8"/>
+      <c r="B11163" s="9"/>
+      <c r="C11163" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11164" s="8"/>
+      <c r="B11164" s="9"/>
+      <c r="C11164" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11165" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B11165" s="16"/>
+      <c r="C11165" s="23"/>
+    </row>
+    <row r="11166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11166" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11166" s="16"/>
+      <c r="C11166" s="23"/>
+    </row>
+    <row r="11167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11167" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B11167" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11167" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11168" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11168" s="9"/>
+      <c r="C11168" s="10" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="11169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11169" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B11169" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11169" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11170" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11170" s="20"/>
+      <c r="C11170" s="21"/>
+    </row>
+    <row r="11211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11211" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11211" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11211" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11212" s="4"/>
+      <c r="B11212" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11212" s="25"/>
+    </row>
+    <row r="11213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11213" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11213" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11213" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11214" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11214" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11214" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11215" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11215" s="9"/>
+      <c r="C11215" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11216" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11216" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11216" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11217" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11217" s="9"/>
+      <c r="C11217" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11218" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11218" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11218" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11219" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11219" s="9"/>
+      <c r="C11219" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11220" s="8"/>
+      <c r="B11220" s="9"/>
+      <c r="C11220" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11221" s="8"/>
+      <c r="B11221" s="9"/>
+      <c r="C11221" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11222" s="8"/>
+      <c r="B11222" s="9"/>
+      <c r="C11222" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11223" s="8"/>
+      <c r="B11223" s="9"/>
+      <c r="C11223" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11224" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B11224" s="16"/>
+      <c r="C11224" s="23"/>
+    </row>
+    <row r="11225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11225" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11225" s="16"/>
+      <c r="C11225" s="23"/>
+    </row>
+    <row r="11226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11226" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B11226" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11226" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11227" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11227" s="9"/>
+      <c r="C11227" s="10" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11228" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B11228" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11228" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11229" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11229" s="20"/>
+      <c r="C11229" s="21"/>
+    </row>
+    <row r="11270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11270" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B11270" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11270" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11271" s="4"/>
+      <c r="B11271" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11271" s="25"/>
+    </row>
+    <row r="11272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11272" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11272" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11272" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11273" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11273" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11273" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11274" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11274" s="9"/>
+      <c r="C11274" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11275" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B11275" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11275" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11276" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B11276" s="9"/>
+      <c r="C11276" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11277" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11277" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11277" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11278" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B11278" s="9"/>
+      <c r="C11278" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11279" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B11279" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11279" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11280" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11280" s="9"/>
+      <c r="C11280" s="10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11281" s="8"/>
+      <c r="B11281" s="9"/>
+      <c r="C11281" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11282" s="8"/>
+      <c r="B11282" s="9"/>
+      <c r="C11282" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11283" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B11283" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11283" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11284" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11284" s="9"/>
+      <c r="C11284" s="10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11285" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B11285" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11285" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11286" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11286" s="20"/>
+      <c r="C11286" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="113">
+  <mergeCells count="122">
+    <mergeCell ref="B10809:B10811"/>
+    <mergeCell ref="B10813:B10815"/>
+    <mergeCell ref="B10799:C10799"/>
+    <mergeCell ref="B10563:C10563"/>
+    <mergeCell ref="C10629:C10630"/>
+    <mergeCell ref="C10688:C10689"/>
+    <mergeCell ref="C10747:C10748"/>
     <mergeCell ref="B9501:C9501"/>
+    <mergeCell ref="C10390:C10391"/>
+    <mergeCell ref="B10445:C10445"/>
     <mergeCell ref="B8925:B8927"/>
     <mergeCell ref="B8921:B8923"/>
     <mergeCell ref="C8741:C8742"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45562139-570B-46D4-937D-56FA35EB7848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ED1B08-133D-4FDE-BE5F-5227254ECB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$14981</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$14984</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5369" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5560" uniqueCount="553">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -12603,6 +12603,742 @@
   </si>
   <si>
     <t>CMP (DF)</t>
+  </si>
+  <si>
+    <t>CPX (E0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L == Operand.L), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L - Operand.L) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (Lo &lt; 0) Lo -= 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BorrowToHi = Lo &lt; 0 ? 1 : 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (HiSum &lt; 0) HiSum -= 6.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L) - ui16(Operand) - (1 - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result &lt;= $FF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  HiSum = int16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) - int16(Operand &gt;&gt; 4) - BorrowToHi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = HiSum &gt;= 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Lo = int16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; 0x0F) - int16(Operand &amp; 0x0F) - (1 - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>SEP (E2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= (Operand.L &amp; ~(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag)).</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E3)</t>
+  </si>
+  <si>
+    <t>CPX (E4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L == Operand.L), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L - Operand.L) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E5)</t>
+  </si>
+  <si>
+    <t>INC (E6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Operand.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -12858,6 +13594,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -12876,10 +13616,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13214,7 +13950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C13175"/>
+  <dimension ref="A1:C13587"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -13430,40 +14166,40 @@
       <c r="C22" s="21"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -13478,10 +14214,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
-      <c r="B61" s="34" t="s">
+      <c r="B61" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="35"/>
+      <c r="C61" s="37"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -13826,39 +14562,39 @@
       <c r="C137" s="22"/>
     </row>
     <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="37"/>
-      <c r="B139" s="37"/>
-      <c r="C139" s="37"/>
+      <c r="A139" s="39"/>
+      <c r="B139" s="39"/>
+      <c r="C139" s="39"/>
     </row>
     <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="37"/>
-      <c r="B140" s="37"/>
-      <c r="C140" s="37"/>
+      <c r="A140" s="39"/>
+      <c r="B140" s="39"/>
+      <c r="C140" s="39"/>
     </row>
     <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="37"/>
-      <c r="B141" s="37"/>
-      <c r="C141" s="37"/>
+      <c r="A141" s="39"/>
+      <c r="B141" s="39"/>
+      <c r="C141" s="39"/>
     </row>
     <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="37"/>
-      <c r="B142" s="37"/>
-      <c r="C142" s="37"/>
+      <c r="A142" s="39"/>
+      <c r="B142" s="39"/>
+      <c r="C142" s="39"/>
     </row>
     <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="37"/>
-      <c r="B143" s="37"/>
-      <c r="C143" s="37"/>
+      <c r="A143" s="39"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="39"/>
     </row>
     <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="37"/>
-      <c r="B144" s="37"/>
-      <c r="C144" s="37"/>
+      <c r="A144" s="39"/>
+      <c r="B144" s="39"/>
+      <c r="C144" s="39"/>
     </row>
     <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="37"/>
-      <c r="B145" s="37"/>
-      <c r="C145" s="37"/>
+      <c r="A145" s="39"/>
+      <c r="B145" s="39"/>
+      <c r="C145" s="39"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
@@ -13873,10 +14609,10 @@
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
-      <c r="B179" s="34" t="s">
+      <c r="B179" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C179" s="35"/>
+      <c r="C179" s="37"/>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
@@ -14382,14 +15118,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="33" t="s">
+      <c r="C367" s="35" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="33"/>
+      <c r="C368" s="35"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="18">
@@ -14440,10 +15176,10 @@
     </row>
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
-      <c r="B415" s="34" t="s">
+      <c r="B415" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C415" s="35"/>
+      <c r="C415" s="37"/>
     </row>
     <row r="416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="12" t="s">
@@ -15011,10 +15747,10 @@
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="4"/>
-      <c r="B710" s="34" t="s">
+      <c r="B710" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C710" s="35"/>
+      <c r="C710" s="37"/>
     </row>
     <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12" t="s">
@@ -15301,10 +16037,10 @@
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="4"/>
-      <c r="B828" s="34" t="s">
+      <c r="B828" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C828" s="35"/>
+      <c r="C828" s="37"/>
     </row>
     <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="12" t="s">
@@ -15411,14 +16147,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="33" t="s">
+      <c r="C839" s="35" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="33"/>
+      <c r="C840" s="35"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
@@ -15469,10 +16205,10 @@
     </row>
     <row r="887" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="4"/>
-      <c r="B887" s="34" t="s">
+      <c r="B887" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C887" s="35"/>
+      <c r="C887" s="37"/>
     </row>
     <row r="888" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="12" t="s">
@@ -15659,14 +16395,14 @@
       <c r="B950" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C950" s="33" t="s">
+      <c r="C950" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="8"/>
       <c r="B951" s="9"/>
-      <c r="C951" s="33"/>
+      <c r="C951" s="35"/>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="8">
@@ -15742,10 +16478,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="4"/>
-      <c r="B1005" s="34" t="s">
+      <c r="B1005" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C1005" s="35"/>
+      <c r="C1005" s="37"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="12" t="s">
@@ -15945,10 +16681,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="4"/>
-      <c r="B1064" s="34" t="s">
+      <c r="B1064" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="C1064" s="35"/>
+      <c r="C1064" s="37"/>
     </row>
     <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="12" t="s">
@@ -16104,10 +16840,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="4"/>
-      <c r="B1123" s="34" t="s">
+      <c r="B1123" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C1123" s="35"/>
+      <c r="C1123" s="37"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="12" t="s">
@@ -16291,10 +17027,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="4"/>
-      <c r="B1182" s="34" t="s">
+      <c r="B1182" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C1182" s="35"/>
+      <c r="C1182" s="37"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="12" t="s">
@@ -16518,14 +17254,14 @@
         <v>3.1</v>
       </c>
       <c r="B1248" s="9"/>
-      <c r="C1248" s="33" t="s">
+      <c r="C1248" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="8"/>
       <c r="B1249" s="9"/>
-      <c r="C1249" s="33"/>
+      <c r="C1249" s="35"/>
     </row>
     <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="15">
@@ -16592,10 +17328,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
-      <c r="B1300" s="34" t="s">
+      <c r="B1300" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="C1300" s="35"/>
+      <c r="C1300" s="37"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="12" t="s">
@@ -16660,14 +17396,14 @@
         <v>3.1</v>
       </c>
       <c r="B1307" s="9"/>
-      <c r="C1307" s="33" t="s">
+      <c r="C1307" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1308" s="8"/>
       <c r="B1308" s="9"/>
-      <c r="C1308" s="33"/>
+      <c r="C1308" s="35"/>
     </row>
     <row r="1309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="15">
@@ -16717,14 +17453,14 @@
         <v>6.1</v>
       </c>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="33" t="s">
+      <c r="C1314" s="35" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="33"/>
+      <c r="C1315" s="35"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="18">
@@ -16775,10 +17511,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="4"/>
-      <c r="B1359" s="34" t="s">
+      <c r="B1359" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C1359" s="35"/>
+      <c r="C1359" s="37"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="12" t="s">
@@ -16869,7 +17605,7 @@
       <c r="A1369" s="8">
         <v>4.2</v>
       </c>
-      <c r="B1369" s="36" t="s">
+      <c r="B1369" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C1369" s="14" t="s">
@@ -16878,12 +17614,12 @@
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="8"/>
-      <c r="B1370" s="36"/>
+      <c r="B1370" s="38"/>
       <c r="C1370" s="14"/>
     </row>
     <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="8"/>
-      <c r="B1371" s="36"/>
+      <c r="B1371" s="38"/>
       <c r="C1371" s="14"/>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16897,7 +17633,7 @@
       <c r="A1373" s="8">
         <v>5.2</v>
       </c>
-      <c r="B1373" s="36" t="s">
+      <c r="B1373" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C1373" s="10" t="s">
@@ -16906,12 +17642,12 @@
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1374" s="8"/>
-      <c r="B1374" s="36"/>
+      <c r="B1374" s="38"/>
       <c r="C1374" s="10"/>
     </row>
     <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="8"/>
-      <c r="B1375" s="36"/>
+      <c r="B1375" s="38"/>
       <c r="C1375" s="10"/>
     </row>
     <row r="1376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17075,10 +17811,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="4"/>
-      <c r="B1477" s="34" t="s">
+      <c r="B1477" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="C1477" s="35"/>
+      <c r="C1477" s="37"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="12" t="s">
@@ -17418,10 +18154,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="4"/>
-      <c r="B1654" s="34" t="s">
+      <c r="B1654" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="35"/>
+      <c r="C1654" s="37"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="12" t="s">
@@ -17581,10 +18317,10 @@
     </row>
     <row r="1713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1713" s="4"/>
-      <c r="B1713" s="34" t="s">
+      <c r="B1713" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C1713" s="35"/>
+      <c r="C1713" s="37"/>
     </row>
     <row r="1714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1714" s="12" t="s">
@@ -17750,10 +18486,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="4"/>
-      <c r="B1772" s="34" t="s">
+      <c r="B1772" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C1772" s="35"/>
+      <c r="C1772" s="37"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="12" t="s">
@@ -17888,14 +18624,14 @@
         <v>6.1</v>
       </c>
       <c r="B1787" s="9"/>
-      <c r="C1787" s="33" t="s">
+      <c r="C1787" s="35" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="8"/>
       <c r="B1788" s="9"/>
-      <c r="C1788" s="33"/>
+      <c r="C1788" s="35"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="18">
@@ -17946,10 +18682,10 @@
     </row>
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="4"/>
-      <c r="B1831" s="34" t="s">
+      <c r="B1831" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C1831" s="35"/>
+      <c r="C1831" s="37"/>
     </row>
     <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1832" s="12" t="s">
@@ -18107,10 +18843,10 @@
     </row>
     <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1890" s="4"/>
-      <c r="B1890" s="34" t="s">
+      <c r="B1890" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="C1890" s="35"/>
+      <c r="C1890" s="37"/>
     </row>
     <row r="1891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1891" s="12" t="s">
@@ -18272,10 +19008,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="4"/>
-      <c r="B1949" s="34" t="s">
+      <c r="B1949" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C1949" s="35"/>
+      <c r="C1949" s="37"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="12" t="s">
@@ -19013,10 +19749,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="4"/>
-      <c r="B2244" s="34" t="s">
+      <c r="B2244" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C2244" s="35"/>
+      <c r="C2244" s="37"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="12" t="s">
@@ -19119,14 +19855,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="33" t="s">
+      <c r="C2255" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="33"/>
+      <c r="C2256" s="35"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="18">
@@ -19905,10 +20641,10 @@
     </row>
     <row r="2657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2657" s="4"/>
-      <c r="B2657" s="34" t="s">
+      <c r="B2657" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C2657" s="35"/>
+      <c r="C2657" s="37"/>
     </row>
     <row r="2658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2658" s="12" t="s">
@@ -20032,10 +20768,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="4"/>
-      <c r="B2716" s="34" t="s">
+      <c r="B2716" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="35"/>
+      <c r="C2716" s="37"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="12" t="s">
@@ -20142,14 +20878,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="33" t="s">
+      <c r="C2727" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="33"/>
+      <c r="C2728" s="35"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="18">
@@ -20200,10 +20936,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="4"/>
-      <c r="B2775" s="34" t="s">
+      <c r="B2775" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C2775" s="35"/>
+      <c r="C2775" s="37"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="12" t="s">
@@ -20390,14 +21126,14 @@
       <c r="B2838" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C2838" s="33" t="s">
+      <c r="C2838" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2839" s="8"/>
       <c r="B2839" s="9"/>
-      <c r="C2839" s="33"/>
+      <c r="C2839" s="35"/>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2840" s="8">
@@ -20473,10 +21209,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="4"/>
-      <c r="B2893" s="34" t="s">
+      <c r="B2893" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C2893" s="35"/>
+      <c r="C2893" s="37"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="12" t="s">
@@ -20835,10 +21571,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="4"/>
-      <c r="B3011" s="34" t="s">
+      <c r="B3011" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C3011" s="35"/>
+      <c r="C3011" s="37"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="12" t="s">
@@ -21090,14 +21826,14 @@
         <v>3.1</v>
       </c>
       <c r="B3077" s="9"/>
-      <c r="C3077" s="33" t="s">
+      <c r="C3077" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3078" s="8"/>
       <c r="B3078" s="9"/>
-      <c r="C3078" s="33"/>
+      <c r="C3078" s="35"/>
     </row>
     <row r="3079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3079" s="15">
@@ -21242,14 +21978,14 @@
         <v>3.1</v>
       </c>
       <c r="B3136" s="9"/>
-      <c r="C3136" s="33" t="s">
+      <c r="C3136" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3137" s="8"/>
       <c r="B3137" s="9"/>
-      <c r="C3137" s="33"/>
+      <c r="C3137" s="35"/>
     </row>
     <row r="3138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3138" s="15">
@@ -21316,10 +22052,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="4"/>
-      <c r="B3188" s="34" t="s">
+      <c r="B3188" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C3188" s="35"/>
+      <c r="C3188" s="37"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="12" t="s">
@@ -21384,14 +22120,14 @@
         <v>3.1</v>
       </c>
       <c r="B3195" s="9"/>
-      <c r="C3195" s="33" t="s">
+      <c r="C3195" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3196" s="8"/>
       <c r="B3196" s="9"/>
-      <c r="C3196" s="33"/>
+      <c r="C3196" s="35"/>
     </row>
     <row r="3197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3197" s="15">
@@ -21441,14 +22177,14 @@
         <v>6.1</v>
       </c>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="33" t="s">
+      <c r="C3202" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="33"/>
+      <c r="C3203" s="35"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="18">
@@ -21509,10 +22245,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="4"/>
-      <c r="B3247" s="34" t="s">
+      <c r="B3247" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C3247" s="35"/>
+      <c r="C3247" s="37"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="12" t="s">
@@ -21603,7 +22339,7 @@
       <c r="A3257" s="8">
         <v>4.2</v>
       </c>
-      <c r="B3257" s="36" t="s">
+      <c r="B3257" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C3257" s="10" t="s">
@@ -21612,12 +22348,12 @@
     </row>
     <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3258" s="8"/>
-      <c r="B3258" s="36"/>
+      <c r="B3258" s="38"/>
       <c r="C3258" s="10"/>
     </row>
     <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3259" s="8"/>
-      <c r="B3259" s="36"/>
+      <c r="B3259" s="38"/>
       <c r="C3259" s="10"/>
     </row>
     <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21631,7 +22367,7 @@
       <c r="A3261" s="8">
         <v>5.2</v>
       </c>
-      <c r="B3261" s="36" t="s">
+      <c r="B3261" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C3261" s="10" t="s">
@@ -21640,12 +22376,12 @@
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3262" s="8"/>
-      <c r="B3262" s="36"/>
+      <c r="B3262" s="38"/>
       <c r="C3262" s="10"/>
     </row>
     <row r="3263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3263" s="8"/>
-      <c r="B3263" s="36"/>
+      <c r="B3263" s="38"/>
       <c r="C3263" s="10"/>
     </row>
     <row r="3264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21809,10 +22545,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="4"/>
-      <c r="B3365" s="34" t="s">
+      <c r="B3365" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="C3365" s="35"/>
+      <c r="C3365" s="37"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="12" t="s">
@@ -22490,10 +23226,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="4"/>
-      <c r="B3660" s="34" t="s">
+      <c r="B3660" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C3660" s="35"/>
+      <c r="C3660" s="37"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="12" t="s">
@@ -22628,14 +23364,14 @@
         <v>6.1</v>
       </c>
       <c r="B3675" s="9"/>
-      <c r="C3675" s="33" t="s">
+      <c r="C3675" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3676" s="8"/>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="33"/>
+      <c r="C3676" s="35"/>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="18">
@@ -23002,10 +23738,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="4"/>
-      <c r="B3837" s="34" t="s">
+      <c r="B3837" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C3837" s="35"/>
+      <c r="C3837" s="37"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="12" t="s">
@@ -23177,10 +23913,10 @@
     </row>
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="4"/>
-      <c r="B3896" s="34" t="s">
+      <c r="B3896" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C3896" s="35"/>
+      <c r="C3896" s="37"/>
     </row>
     <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3897" s="12" t="s">
@@ -23385,10 +24121,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
-      <c r="B4014" s="34" t="s">
+      <c r="B4014" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="C4014" s="35"/>
+      <c r="C4014" s="37"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="12" t="s">
@@ -23495,14 +24231,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="9"/>
-      <c r="C4025" s="33" t="s">
+      <c r="C4025" s="35" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="8"/>
       <c r="B4026" s="9"/>
-      <c r="C4026" s="33"/>
+      <c r="C4026" s="35"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="8">
@@ -23686,10 +24422,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="4"/>
-      <c r="B4132" s="34" t="s">
+      <c r="B4132" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C4132" s="35"/>
+      <c r="C4132" s="37"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="12" t="s">
@@ -23792,14 +24528,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="9"/>
-      <c r="C4143" s="33" t="s">
+      <c r="C4143" s="35" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="8"/>
       <c r="B4144" s="9"/>
-      <c r="C4144" s="33"/>
+      <c r="C4144" s="35"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="18">
@@ -23850,10 +24586,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="4"/>
-      <c r="B4191" s="34" t="s">
+      <c r="B4191" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C4191" s="35"/>
+      <c r="C4191" s="37"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="12" t="s">
@@ -24637,10 +25373,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="4"/>
-      <c r="B4604" s="34" t="s">
+      <c r="B4604" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="35"/>
+      <c r="C4604" s="37"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="12" t="s">
@@ -24747,14 +25483,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4615" s="9"/>
-      <c r="C4615" s="33" t="s">
+      <c r="C4615" s="35" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4616" s="8"/>
       <c r="B4616" s="9"/>
-      <c r="C4616" s="33"/>
+      <c r="C4616" s="35"/>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="18">
@@ -24805,10 +25541,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="4"/>
-      <c r="B4663" s="34" t="s">
+      <c r="B4663" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C4663" s="35"/>
+      <c r="C4663" s="37"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="12" t="s">
@@ -24995,14 +25731,14 @@
       <c r="B4726" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C4726" s="33" t="s">
+      <c r="C4726" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4727" s="8"/>
       <c r="B4727" s="9"/>
-      <c r="C4727" s="33"/>
+      <c r="C4727" s="35"/>
     </row>
     <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4728" s="8">
@@ -25078,10 +25814,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="4"/>
-      <c r="B4781" s="34" t="s">
+      <c r="B4781" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C4781" s="35"/>
+      <c r="C4781" s="37"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="12" t="s">
@@ -25433,10 +26169,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="4"/>
-      <c r="B4899" s="34" t="s">
+      <c r="B4899" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C4899" s="35"/>
+      <c r="C4899" s="37"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="12" t="s">
@@ -25730,14 +26466,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="9"/>
-      <c r="C4969" s="33" t="s">
+      <c r="C4969" s="35" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="8"/>
       <c r="B4970" s="9"/>
-      <c r="C4970" s="33"/>
+      <c r="C4970" s="35"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="8">
@@ -25866,14 +26602,14 @@
         <v>3.1</v>
       </c>
       <c r="B5024" s="9"/>
-      <c r="C5024" s="33" t="s">
+      <c r="C5024" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5025" s="8"/>
       <c r="B5025" s="9"/>
-      <c r="C5025" s="33"/>
+      <c r="C5025" s="35"/>
     </row>
     <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5026" s="15">
@@ -25940,10 +26676,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="4"/>
-      <c r="B5076" s="34" t="s">
+      <c r="B5076" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="C5076" s="35"/>
+      <c r="C5076" s="37"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="12" t="s">
@@ -26008,14 +26744,14 @@
         <v>3.1</v>
       </c>
       <c r="B5083" s="9"/>
-      <c r="C5083" s="33" t="s">
+      <c r="C5083" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5084" s="8"/>
       <c r="B5084" s="9"/>
-      <c r="C5084" s="33"/>
+      <c r="C5084" s="35"/>
     </row>
     <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5085" s="15">
@@ -26065,14 +26801,14 @@
         <v>6.1</v>
       </c>
       <c r="B5090" s="9"/>
-      <c r="C5090" s="33" t="s">
+      <c r="C5090" s="35" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="8"/>
       <c r="B5091" s="9"/>
-      <c r="C5091" s="33"/>
+      <c r="C5091" s="35"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="18">
@@ -26123,10 +26859,10 @@
     </row>
     <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5135" s="4"/>
-      <c r="B5135" s="34" t="s">
+      <c r="B5135" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C5135" s="35"/>
+      <c r="C5135" s="37"/>
     </row>
     <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5136" s="12" t="s">
@@ -26217,7 +26953,7 @@
       <c r="A5145" s="8">
         <v>4.2</v>
       </c>
-      <c r="B5145" s="36" t="s">
+      <c r="B5145" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C5145" s="10" t="s">
@@ -26226,12 +26962,12 @@
     </row>
     <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5146" s="8"/>
-      <c r="B5146" s="36"/>
+      <c r="B5146" s="38"/>
       <c r="C5146" s="10"/>
     </row>
     <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5147" s="8"/>
-      <c r="B5147" s="36"/>
+      <c r="B5147" s="38"/>
       <c r="C5147" s="10"/>
     </row>
     <row r="5148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26245,7 +26981,7 @@
       <c r="A5149" s="8">
         <v>5.2</v>
       </c>
-      <c r="B5149" s="36" t="s">
+      <c r="B5149" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C5149" s="10" t="s">
@@ -26254,12 +26990,12 @@
     </row>
     <row r="5150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5150" s="8"/>
-      <c r="B5150" s="36"/>
+      <c r="B5150" s="38"/>
       <c r="C5150" s="10"/>
     </row>
     <row r="5151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5151" s="8"/>
-      <c r="B5151" s="36"/>
+      <c r="B5151" s="38"/>
       <c r="C5151" s="10"/>
     </row>
     <row r="5152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26780,10 +27516,10 @@
     </row>
     <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5430" s="4"/>
-      <c r="B5430" s="34" t="s">
+      <c r="B5430" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="C5430" s="35"/>
+      <c r="C5430" s="37"/>
     </row>
     <row r="5431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5431" s="12" t="s">
@@ -26907,10 +27643,10 @@
     </row>
     <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5489" s="4"/>
-      <c r="B5489" s="34" t="s">
+      <c r="B5489" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C5489" s="35"/>
+      <c r="C5489" s="37"/>
     </row>
     <row r="5490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5490" s="12" t="s">
@@ -27069,10 +27805,10 @@
     </row>
     <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5548" s="4"/>
-      <c r="B5548" s="34" t="s">
+      <c r="B5548" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C5548" s="35"/>
+      <c r="C5548" s="37"/>
     </row>
     <row r="5549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5549" s="12" t="s">
@@ -27207,14 +27943,14 @@
         <v>6.1</v>
       </c>
       <c r="B5563" s="9"/>
-      <c r="C5563" s="33" t="s">
+      <c r="C5563" s="35" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="8"/>
       <c r="B5564" s="9"/>
-      <c r="C5564" s="33"/>
+      <c r="C5564" s="35"/>
     </row>
     <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5565" s="18">
@@ -27265,10 +28001,10 @@
     </row>
     <row r="5607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5607" s="4"/>
-      <c r="B5607" s="34" t="s">
+      <c r="B5607" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C5607" s="35"/>
+      <c r="C5607" s="37"/>
     </row>
     <row r="5608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5608" s="12" t="s">
@@ -27575,10 +28311,10 @@
     </row>
     <row r="5725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5725" s="4"/>
-      <c r="B5725" s="34" t="s">
+      <c r="B5725" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C5725" s="35"/>
+      <c r="C5725" s="37"/>
     </row>
     <row r="5726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5726" s="12" t="s">
@@ -27848,10 +28584,10 @@
     </row>
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="4"/>
-      <c r="B5784" s="34" t="s">
+      <c r="B5784" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="C5784" s="35"/>
+      <c r="C5784" s="37"/>
     </row>
     <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5785" s="12" t="s">
@@ -28568,10 +29304,10 @@
     </row>
     <row r="6020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6020" s="4"/>
-      <c r="B6020" s="34" t="s">
+      <c r="B6020" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C6020" s="35"/>
+      <c r="C6020" s="37"/>
     </row>
     <row r="6021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6021" s="12" t="s">
@@ -28674,14 +29410,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6031" s="9"/>
-      <c r="C6031" s="33" t="s">
+      <c r="C6031" s="35" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6032" s="8"/>
       <c r="B6032" s="9"/>
-      <c r="C6032" s="33"/>
+      <c r="C6032" s="35"/>
     </row>
     <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6033" s="18">
@@ -29917,10 +30653,10 @@
     </row>
     <row r="6492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6492" s="4"/>
-      <c r="B6492" s="34" t="s">
+      <c r="B6492" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C6492" s="35"/>
+      <c r="C6492" s="37"/>
     </row>
     <row r="6493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6493" s="12" t="s">
@@ -30027,14 +30763,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6503" s="9"/>
-      <c r="C6503" s="33" t="s">
+      <c r="C6503" s="35" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="8"/>
       <c r="B6504" s="9"/>
-      <c r="C6504" s="33"/>
+      <c r="C6504" s="35"/>
     </row>
     <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6505" s="18">
@@ -30373,14 +31109,14 @@
       <c r="B6614" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6614" s="33" t="s">
+      <c r="C6614" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6615" s="8"/>
       <c r="B6615" s="9"/>
-      <c r="C6615" s="33"/>
+      <c r="C6615" s="35"/>
     </row>
     <row r="6616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6616" s="8">
@@ -30456,10 +31192,10 @@
     </row>
     <row r="6669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6669" s="4"/>
-      <c r="B6669" s="34" t="s">
+      <c r="B6669" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C6669" s="35"/>
+      <c r="C6669" s="37"/>
     </row>
     <row r="6670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6670" s="12" t="s">
@@ -31014,10 +31750,10 @@
     </row>
     <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6787" s="4"/>
-      <c r="B6787" s="34" t="s">
+      <c r="B6787" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C6787" s="35"/>
+      <c r="C6787" s="37"/>
     </row>
     <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6788" s="12" t="s">
@@ -31367,14 +32103,14 @@
         <v>3.1</v>
       </c>
       <c r="B6853" s="9"/>
-      <c r="C6853" s="33" t="s">
+      <c r="C6853" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6854" s="8"/>
       <c r="B6854" s="9"/>
-      <c r="C6854" s="33"/>
+      <c r="C6854" s="35"/>
     </row>
     <row r="6855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6855" s="8">
@@ -31507,14 +32243,14 @@
         <v>3.1</v>
       </c>
       <c r="B6912" s="9"/>
-      <c r="C6912" s="33" t="s">
+      <c r="C6912" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6913" s="8"/>
       <c r="B6913" s="9"/>
-      <c r="C6913" s="33"/>
+      <c r="C6913" s="35"/>
     </row>
     <row r="6914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6914" s="8">
@@ -31679,10 +32415,10 @@
     </row>
     <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6964" s="4"/>
-      <c r="B6964" s="34" t="s">
+      <c r="B6964" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="C6964" s="35"/>
+      <c r="C6964" s="37"/>
     </row>
     <row r="6965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6965" s="12" t="s">
@@ -31747,14 +32483,14 @@
         <v>3.1</v>
       </c>
       <c r="B6971" s="9"/>
-      <c r="C6971" s="33" t="s">
+      <c r="C6971" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6972" s="8"/>
       <c r="B6972" s="9"/>
-      <c r="C6972" s="33"/>
+      <c r="C6972" s="35"/>
     </row>
     <row r="6973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6973" s="8">
@@ -31804,14 +32540,14 @@
         <v>6.1</v>
       </c>
       <c r="B6978" s="9"/>
-      <c r="C6978" s="33" t="s">
+      <c r="C6978" s="35" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="6979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6979" s="8"/>
       <c r="B6979" s="9"/>
-      <c r="C6979" s="33"/>
+      <c r="C6979" s="35"/>
     </row>
     <row r="6980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6980" s="18">
@@ -31862,10 +32598,10 @@
     </row>
     <row r="7023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7023" s="4"/>
-      <c r="B7023" s="34" t="s">
+      <c r="B7023" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C7023" s="35"/>
+      <c r="C7023" s="37"/>
     </row>
     <row r="7024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7024" s="12" t="s">
@@ -31956,7 +32692,7 @@
       <c r="A7033" s="8">
         <v>4.2</v>
       </c>
-      <c r="B7033" s="36" t="s">
+      <c r="B7033" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C7033" s="10" t="s">
@@ -31965,12 +32701,12 @@
     </row>
     <row r="7034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7034" s="8"/>
-      <c r="B7034" s="36"/>
+      <c r="B7034" s="38"/>
       <c r="C7034" s="10"/>
     </row>
     <row r="7035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7035" s="8"/>
-      <c r="B7035" s="36"/>
+      <c r="B7035" s="38"/>
       <c r="C7035" s="10"/>
     </row>
     <row r="7036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31984,7 +32720,7 @@
       <c r="A7037" s="8">
         <v>5.2</v>
       </c>
-      <c r="B7037" s="36" t="s">
+      <c r="B7037" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C7037" s="10" t="s">
@@ -31993,12 +32729,12 @@
     </row>
     <row r="7038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7038" s="8"/>
-      <c r="B7038" s="36"/>
+      <c r="B7038" s="38"/>
       <c r="C7038" s="10"/>
     </row>
     <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7039" s="8"/>
-      <c r="B7039" s="36"/>
+      <c r="B7039" s="38"/>
       <c r="C7039" s="10"/>
     </row>
     <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32608,19 +33344,19 @@
       <c r="A7209" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B7209" s="36" t="s">
+      <c r="B7209" s="38" t="s">
         <v>331</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
     <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7210" s="8"/>
-      <c r="B7210" s="36"/>
+      <c r="B7210" s="38"/>
       <c r="C7210" s="10"/>
     </row>
     <row r="7211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7211" s="8"/>
-      <c r="B7211" s="36"/>
+      <c r="B7211" s="38"/>
       <c r="C7211" s="10"/>
     </row>
     <row r="7212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32741,10 +33477,10 @@
     </row>
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
-      <c r="B7318" s="34" t="s">
+      <c r="B7318" s="36" t="s">
         <v>504</v>
       </c>
-      <c r="C7318" s="35"/>
+      <c r="C7318" s="37"/>
     </row>
     <row r="7319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7319" s="12" t="s">
@@ -33167,10 +33903,10 @@
     </row>
     <row r="7436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7436" s="4"/>
-      <c r="B7436" s="34" t="s">
+      <c r="B7436" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C7436" s="35"/>
+      <c r="C7436" s="37"/>
     </row>
     <row r="7437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7437" s="12" t="s">
@@ -33305,14 +34041,14 @@
         <v>6.1</v>
       </c>
       <c r="B7451" s="27"/>
-      <c r="C7451" s="33" t="s">
+      <c r="C7451" s="35" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="8"/>
       <c r="B7452" s="27"/>
-      <c r="C7452" s="33"/>
+      <c r="C7452" s="35"/>
     </row>
     <row r="7453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7453" s="18">
@@ -33665,14 +34401,14 @@
       <c r="B7558" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C7558" s="33" t="s">
+      <c r="C7558" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7559" s="18"/>
       <c r="B7559" s="9"/>
-      <c r="C7559" s="33"/>
+      <c r="C7559" s="35"/>
     </row>
     <row r="7560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7560" s="8">
@@ -33748,10 +34484,10 @@
     </row>
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
-      <c r="B7613" s="34" t="s">
+      <c r="B7613" s="36" t="s">
         <v>343</v>
       </c>
-      <c r="C7613" s="35"/>
+      <c r="C7613" s="37"/>
     </row>
     <row r="7614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7614" s="12" t="s">
@@ -33937,10 +34673,10 @@
     </row>
     <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7672" s="4"/>
-      <c r="B7672" s="34" t="s">
+      <c r="B7672" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="C7672" s="35"/>
+      <c r="C7672" s="37"/>
     </row>
     <row r="7673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7673" s="12" t="s">
@@ -35646,14 +36382,14 @@
       <c r="B8502" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C8502" s="33" t="s">
+      <c r="C8502" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="8503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8503" s="8"/>
       <c r="B8503" s="9"/>
-      <c r="C8503" s="33"/>
+      <c r="C8503" s="35"/>
     </row>
     <row r="8504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8504" s="8">
@@ -35729,10 +36465,10 @@
     </row>
     <row r="8557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8557" s="4"/>
-      <c r="B8557" s="34" t="s">
+      <c r="B8557" s="36" t="s">
         <v>381</v>
       </c>
-      <c r="C8557" s="35"/>
+      <c r="C8557" s="37"/>
     </row>
     <row r="8558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8558" s="12" t="s">
@@ -36077,10 +36813,10 @@
     </row>
     <row r="8675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8675" s="4"/>
-      <c r="B8675" s="34" t="s">
+      <c r="B8675" s="36" t="s">
         <v>385</v>
       </c>
-      <c r="C8675" s="35"/>
+      <c r="C8675" s="37"/>
     </row>
     <row r="8676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8676" s="12" t="s">
@@ -36332,14 +37068,14 @@
         <v>3.1</v>
       </c>
       <c r="B8741" s="9"/>
-      <c r="C8741" s="33" t="s">
+      <c r="C8741" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8742" s="8"/>
       <c r="B8742" s="9"/>
-      <c r="C8742" s="33"/>
+      <c r="C8742" s="35"/>
     </row>
     <row r="8743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8743" s="15">
@@ -36472,14 +37208,14 @@
         <v>3.1</v>
       </c>
       <c r="B8800" s="9"/>
-      <c r="C8800" s="33" t="s">
+      <c r="C8800" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8801" s="8"/>
       <c r="B8801" s="9"/>
-      <c r="C8801" s="33"/>
+      <c r="C8801" s="35"/>
     </row>
     <row r="8802" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8802" s="15">
@@ -36612,14 +37348,14 @@
         <v>3.1</v>
       </c>
       <c r="B8859" s="9"/>
-      <c r="C8859" s="33" t="s">
+      <c r="C8859" s="35" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="8860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8860" s="8"/>
       <c r="B8860" s="9"/>
-      <c r="C8860" s="33"/>
+      <c r="C8860" s="35"/>
     </row>
     <row r="8861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8861" s="15">
@@ -36684,10 +37420,10 @@
     </row>
     <row r="8911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8911" s="4"/>
-      <c r="B8911" s="34" t="s">
+      <c r="B8911" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="C8911" s="35"/>
+      <c r="C8911" s="37"/>
     </row>
     <row r="8912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8912" s="12" t="s">
@@ -36778,7 +37514,7 @@
       <c r="A8921" s="8">
         <v>4.2</v>
       </c>
-      <c r="B8921" s="36" t="s">
+      <c r="B8921" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C8921" s="14" t="s">
@@ -36787,12 +37523,12 @@
     </row>
     <row r="8922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8922" s="8"/>
-      <c r="B8922" s="36"/>
+      <c r="B8922" s="38"/>
       <c r="C8922" s="14"/>
     </row>
     <row r="8923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8923" s="8"/>
-      <c r="B8923" s="36"/>
+      <c r="B8923" s="38"/>
       <c r="C8923" s="14"/>
     </row>
     <row r="8924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36806,7 +37542,7 @@
       <c r="A8925" s="8">
         <v>5.2</v>
       </c>
-      <c r="B8925" s="36" t="s">
+      <c r="B8925" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C8925" s="14" t="s">
@@ -36815,12 +37551,12 @@
     </row>
     <row r="8926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8926" s="8"/>
-      <c r="B8926" s="36"/>
+      <c r="B8926" s="38"/>
       <c r="C8926" s="14"/>
     </row>
     <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8927" s="8"/>
-      <c r="B8927" s="36"/>
+      <c r="B8927" s="38"/>
       <c r="C8927" s="14"/>
     </row>
     <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37992,10 +38728,10 @@
     </row>
     <row r="9501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9501" s="4"/>
-      <c r="B9501" s="34" t="s">
+      <c r="B9501" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C9501" s="35"/>
+      <c r="C9501" s="37"/>
     </row>
     <row r="9502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9502" s="12" t="s">
@@ -39884,14 +40620,14 @@
       <c r="B10390" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C10390" s="33" t="s">
+      <c r="C10390" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="10391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10391" s="8"/>
       <c r="B10391" s="9"/>
-      <c r="C10391" s="33"/>
+      <c r="C10391" s="35"/>
     </row>
     <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10392" s="8">
@@ -39967,10 +40703,10 @@
     </row>
     <row r="10445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10445" s="4"/>
-      <c r="B10445" s="34" t="s">
+      <c r="B10445" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C10445" s="35"/>
+      <c r="C10445" s="37"/>
     </row>
     <row r="10446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10446" s="12" t="s">
@@ -40329,10 +41065,10 @@
     </row>
     <row r="10563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10563" s="4"/>
-      <c r="B10563" s="34" t="s">
+      <c r="B10563" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C10563" s="35"/>
+      <c r="C10563" s="37"/>
     </row>
     <row r="10564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10564" s="12" t="s">
@@ -40584,14 +41320,14 @@
         <v>3.1</v>
       </c>
       <c r="B10629" s="9"/>
-      <c r="C10629" s="33" t="s">
+      <c r="C10629" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10630" s="8"/>
       <c r="B10630" s="9"/>
-      <c r="C10630" s="33"/>
+      <c r="C10630" s="35"/>
     </row>
     <row r="10631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10631" s="15">
@@ -40726,14 +41462,14 @@
         <v>3.1</v>
       </c>
       <c r="B10688" s="9"/>
-      <c r="C10688" s="33" t="s">
+      <c r="C10688" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10689" s="8"/>
       <c r="B10689" s="9"/>
-      <c r="C10689" s="33"/>
+      <c r="C10689" s="35"/>
     </row>
     <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10690" s="15">
@@ -40868,14 +41604,14 @@
         <v>3.1</v>
       </c>
       <c r="B10747" s="9"/>
-      <c r="C10747" s="33" t="s">
+      <c r="C10747" s="35" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10748" s="8"/>
       <c r="B10748" s="9"/>
-      <c r="C10748" s="33"/>
+      <c r="C10748" s="35"/>
     </row>
     <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10749" s="15">
@@ -40942,10 +41678,10 @@
     </row>
     <row r="10799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10799" s="4"/>
-      <c r="B10799" s="34" t="s">
+      <c r="B10799" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C10799" s="35"/>
+      <c r="C10799" s="37"/>
     </row>
     <row r="10800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10800" s="12" t="s">
@@ -41036,7 +41772,7 @@
       <c r="A10809" s="8">
         <v>4.2</v>
       </c>
-      <c r="B10809" s="36" t="s">
+      <c r="B10809" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C10809" s="10" t="s">
@@ -41045,12 +41781,12 @@
     </row>
     <row r="10810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10810" s="8"/>
-      <c r="B10810" s="36"/>
+      <c r="B10810" s="38"/>
       <c r="C10810" s="10"/>
     </row>
     <row r="10811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10811" s="8"/>
-      <c r="B10811" s="36"/>
+      <c r="B10811" s="38"/>
       <c r="C10811" s="10"/>
     </row>
     <row r="10812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41064,7 +41800,7 @@
       <c r="A10813" s="8">
         <v>5.2</v>
       </c>
-      <c r="B10813" s="36" t="s">
+      <c r="B10813" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C10813" s="10" t="s">
@@ -41073,12 +41809,12 @@
     </row>
     <row r="10814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10814" s="8"/>
-      <c r="B10814" s="36"/>
+      <c r="B10814" s="38"/>
       <c r="C10814" s="10"/>
     </row>
     <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10815" s="8"/>
-      <c r="B10815" s="36"/>
+      <c r="B10815" s="38"/>
       <c r="C10815" s="10"/>
     </row>
     <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42305,14 +43041,14 @@
         <v>2.1</v>
       </c>
       <c r="B11335" s="9"/>
-      <c r="C11335" s="33" t="s">
+      <c r="C11335" s="35" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11336" s="8"/>
       <c r="B11336" s="9"/>
-      <c r="C11336" s="33"/>
+      <c r="C11336" s="35"/>
     </row>
     <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11337" s="8">
@@ -42345,10 +43081,10 @@
     </row>
     <row r="11389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11389" s="4"/>
-      <c r="B11389" s="34" t="s">
+      <c r="B11389" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C11389" s="35"/>
+      <c r="C11389" s="37"/>
     </row>
     <row r="11390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11390" s="12" t="s">
@@ -42499,14 +43235,14 @@
         <v>7.1</v>
       </c>
       <c r="B11406" s="9"/>
-      <c r="C11406" s="33" t="s">
+      <c r="C11406" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="11407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11407" s="8"/>
       <c r="B11407" s="9"/>
-      <c r="C11407" s="33"/>
+      <c r="C11407" s="35"/>
     </row>
     <row r="11408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11408" s="8">
@@ -42728,14 +43464,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11516" s="9"/>
-      <c r="C11516" s="33" t="s">
+      <c r="C11516" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11517" s="8"/>
       <c r="B11517" s="9"/>
-      <c r="C11517" s="33"/>
+      <c r="C11517" s="35"/>
     </row>
     <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11518" s="8">
@@ -42856,14 +43592,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11575" s="9"/>
-      <c r="C11575" s="33" t="s">
+      <c r="C11575" s="35" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="11576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11576" s="8"/>
       <c r="B11576" s="9"/>
-      <c r="C11576" s="33"/>
+      <c r="C11576" s="35"/>
     </row>
     <row r="11577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11577" s="8">
@@ -42984,14 +43720,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11634" s="9"/>
-      <c r="C11634" s="33" t="s">
+      <c r="C11634" s="35" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="11635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11635" s="8"/>
       <c r="B11635" s="9"/>
-      <c r="C11635" s="33"/>
+      <c r="C11635" s="35"/>
     </row>
     <row r="11636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11636" s="8">
@@ -43325,14 +44061,14 @@
         <v>7.1</v>
       </c>
       <c r="B11758" s="9"/>
-      <c r="C11758" s="33" t="s">
+      <c r="C11758" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="11759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11759" s="8"/>
       <c r="B11759" s="9"/>
-      <c r="C11759" s="33"/>
+      <c r="C11759" s="35"/>
     </row>
     <row r="11760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11760" s="8">
@@ -43504,14 +44240,14 @@
         <v>2.1</v>
       </c>
       <c r="B11866" s="9"/>
-      <c r="C11866" s="33" t="s">
+      <c r="C11866" s="35" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="11867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11867" s="8"/>
       <c r="B11867" s="9"/>
-      <c r="C11867" s="33"/>
+      <c r="C11867" s="35"/>
     </row>
     <row r="11868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11868" s="8">
@@ -43813,14 +44549,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12047" s="9"/>
-      <c r="C12047" s="33" t="s">
+      <c r="C12047" s="35" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="12048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12048" s="8"/>
       <c r="B12048" s="9"/>
-      <c r="C12048" s="33"/>
+      <c r="C12048" s="35"/>
     </row>
     <row r="12049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12049" s="8">
@@ -43945,14 +44681,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12106" s="9"/>
-      <c r="C12106" s="33" t="s">
+      <c r="C12106" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12107" s="8"/>
       <c r="B12107" s="9"/>
-      <c r="C12107" s="33"/>
+      <c r="C12107" s="35"/>
     </row>
     <row r="12108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12108" s="8">
@@ -43985,10 +44721,10 @@
     </row>
     <row r="12156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12156" s="4"/>
-      <c r="B12156" s="34" t="s">
+      <c r="B12156" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C12156" s="35"/>
+      <c r="C12156" s="37"/>
     </row>
     <row r="12157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12157" s="12" t="s">
@@ -44260,14 +44996,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12226" s="9"/>
-      <c r="C12226" s="33" t="s">
+      <c r="C12226" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12227" s="8"/>
       <c r="B12227" s="9"/>
-      <c r="C12227" s="33"/>
+      <c r="C12227" s="35"/>
     </row>
     <row r="12228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12228" s="8">
@@ -44343,14 +45079,14 @@
       <c r="B12278" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C12278" s="33" t="s">
+      <c r="C12278" s="35" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="12279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12279" s="8"/>
       <c r="B12279" s="9"/>
-      <c r="C12279" s="33"/>
+      <c r="C12279" s="35"/>
     </row>
     <row r="12280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12280" s="8">
@@ -44426,10 +45162,10 @@
     </row>
     <row r="12333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12333" s="4"/>
-      <c r="B12333" s="34" t="s">
+      <c r="B12333" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C12333" s="35"/>
+      <c r="C12333" s="37"/>
     </row>
     <row r="12334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12334" s="12" t="s">
@@ -44594,14 +45330,14 @@
         <v>7.1</v>
       </c>
       <c r="B12352" s="9"/>
-      <c r="C12352" s="33" t="s">
+      <c r="C12352" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12353" s="8"/>
       <c r="B12353" s="9"/>
-      <c r="C12353" s="33"/>
+      <c r="C12353" s="35"/>
     </row>
     <row r="12354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12354" s="8">
@@ -44758,14 +45494,14 @@
         <v>6.1</v>
       </c>
       <c r="B12405" s="9"/>
-      <c r="C12405" s="33" t="s">
+      <c r="C12405" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12406" s="8"/>
       <c r="B12406" s="9"/>
-      <c r="C12406" s="33"/>
+      <c r="C12406" s="35"/>
     </row>
     <row r="12407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12407" s="8">
@@ -44798,10 +45534,10 @@
     </row>
     <row r="12451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12451" s="4"/>
-      <c r="B12451" s="34" t="s">
+      <c r="B12451" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C12451" s="35"/>
+      <c r="C12451" s="37"/>
     </row>
     <row r="12452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12452" s="12" t="s">
@@ -44950,14 +45686,14 @@
         <v>7.1</v>
       </c>
       <c r="B12468" s="9"/>
-      <c r="C12468" s="33" t="s">
+      <c r="C12468" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12469" s="8"/>
       <c r="B12469" s="9"/>
-      <c r="C12469" s="33"/>
+      <c r="C12469" s="35"/>
     </row>
     <row r="12470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12470" s="8">
@@ -44990,10 +45726,10 @@
     </row>
     <row r="12510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12510" s="4"/>
-      <c r="B12510" s="34" t="s">
+      <c r="B12510" s="36" t="s">
         <v>511</v>
       </c>
-      <c r="C12510" s="35"/>
+      <c r="C12510" s="37"/>
     </row>
     <row r="12511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12511" s="12" t="s">
@@ -45084,7 +45820,7 @@
       <c r="A12520" s="8">
         <v>4.2</v>
       </c>
-      <c r="B12520" s="36" t="s">
+      <c r="B12520" s="38" t="s">
         <v>512</v>
       </c>
       <c r="C12520" s="10" t="s">
@@ -45093,12 +45829,12 @@
     </row>
     <row r="12521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12521" s="8"/>
-      <c r="B12521" s="36"/>
+      <c r="B12521" s="38"/>
       <c r="C12521" s="10"/>
     </row>
     <row r="12522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12522" s="8"/>
-      <c r="B12522" s="36"/>
+      <c r="B12522" s="38"/>
       <c r="C12522" s="10"/>
     </row>
     <row r="12523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45245,14 +45981,14 @@
         <v>3.1</v>
       </c>
       <c r="B12576" s="9"/>
-      <c r="C12576" s="33" t="s">
+      <c r="C12576" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12577" s="8"/>
       <c r="B12577" s="9"/>
-      <c r="C12577" s="33"/>
+      <c r="C12577" s="35"/>
     </row>
     <row r="12578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12578" s="8">
@@ -45284,14 +46020,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12581" s="27"/>
-      <c r="C12581" s="33" t="s">
+      <c r="C12581" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12582" s="8"/>
       <c r="B12582" s="27"/>
-      <c r="C12582" s="33"/>
+      <c r="C12582" s="35"/>
     </row>
     <row r="12583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12583" s="8">
@@ -45324,10 +46060,10 @@
     </row>
     <row r="12628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12628" s="4"/>
-      <c r="B12628" s="34" t="s">
+      <c r="B12628" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="C12628" s="35"/>
+      <c r="C12628" s="37"/>
     </row>
     <row r="12629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12629" s="12" t="s">
@@ -45392,14 +46128,14 @@
         <v>3.1</v>
       </c>
       <c r="B12635" s="9"/>
-      <c r="C12635" s="33" t="s">
+      <c r="C12635" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12636" s="8"/>
       <c r="B12636" s="9"/>
-      <c r="C12636" s="33"/>
+      <c r="C12636" s="35"/>
     </row>
     <row r="12637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12637" s="8">
@@ -45502,10 +46238,10 @@
     </row>
     <row r="12687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12687" s="4"/>
-      <c r="B12687" s="34" t="s">
+      <c r="B12687" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="C12687" s="35"/>
+      <c r="C12687" s="37"/>
     </row>
     <row r="12688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12688" s="12" t="s">
@@ -45596,7 +46332,7 @@
       <c r="A12697" s="8">
         <v>4.2</v>
       </c>
-      <c r="B12697" s="36" t="s">
+      <c r="B12697" s="38" t="s">
         <v>159</v>
       </c>
       <c r="C12697" s="10" t="s">
@@ -45605,12 +46341,12 @@
     </row>
     <row r="12698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12698" s="8"/>
-      <c r="B12698" s="36"/>
+      <c r="B12698" s="38"/>
       <c r="C12698" s="10"/>
     </row>
     <row r="12699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12699" s="8"/>
-      <c r="B12699" s="36"/>
+      <c r="B12699" s="38"/>
       <c r="C12699" s="10"/>
     </row>
     <row r="12700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45624,7 +46360,7 @@
       <c r="A12701" s="8">
         <v>5.2</v>
       </c>
-      <c r="B12701" s="36" t="s">
+      <c r="B12701" s="38" t="s">
         <v>160</v>
       </c>
       <c r="C12701" s="10" t="s">
@@ -45633,12 +46369,12 @@
     </row>
     <row r="12702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12702" s="8"/>
-      <c r="B12702" s="36"/>
+      <c r="B12702" s="38"/>
       <c r="C12702" s="10"/>
     </row>
     <row r="12703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12703" s="8"/>
-      <c r="B12703" s="36"/>
+      <c r="B12703" s="38"/>
       <c r="C12703" s="10"/>
     </row>
     <row r="12704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45680,14 +46416,14 @@
         <v>7.1</v>
       </c>
       <c r="B12708" s="9"/>
-      <c r="C12708" s="33" t="s">
+      <c r="C12708" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12709" s="8"/>
       <c r="B12709" s="9"/>
-      <c r="C12709" s="33"/>
+      <c r="C12709" s="35"/>
     </row>
     <row r="12710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12710" s="8">
@@ -45915,7 +46651,7 @@
       <c r="A12817" s="15">
         <v>3.2</v>
       </c>
-      <c r="B12817" s="39"/>
+      <c r="B12817" s="33"/>
       <c r="C12817" s="23"/>
     </row>
     <row r="12818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45941,14 +46677,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12820" s="27"/>
-      <c r="C12820" s="33" t="s">
+      <c r="C12820" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12821" s="8"/>
       <c r="B12821" s="27"/>
-      <c r="C12821" s="33"/>
+      <c r="C12821" s="35"/>
     </row>
     <row r="12822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12822" s="8">
@@ -46154,7 +46890,7 @@
       <c r="C12931" s="10"/>
     </row>
     <row r="12932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12932" s="40">
+      <c r="A12932" s="34">
         <v>4.0999999999999996</v>
       </c>
       <c r="B12932" s="30"/>
@@ -46175,10 +46911,10 @@
     </row>
     <row r="12982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12982" s="4"/>
-      <c r="B12982" s="34" t="s">
+      <c r="B12982" s="36" t="s">
         <v>526</v>
       </c>
-      <c r="C12982" s="35"/>
+      <c r="C12982" s="37"/>
     </row>
     <row r="12983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12983" s="12" t="s">
@@ -46291,7 +47027,7 @@
       <c r="A12994" s="18">
         <v>5.2</v>
       </c>
-      <c r="B12994" s="36" t="s">
+      <c r="B12994" s="38" t="s">
         <v>527</v>
       </c>
       <c r="C12994" s="10" t="s">
@@ -46300,12 +47036,12 @@
     </row>
     <row r="12995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12995" s="18"/>
-      <c r="B12995" s="36"/>
+      <c r="B12995" s="38"/>
       <c r="C12995" s="10"/>
     </row>
     <row r="12996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12996" s="18"/>
-      <c r="B12996" s="36"/>
+      <c r="B12996" s="38"/>
       <c r="C12996" s="10"/>
     </row>
     <row r="12997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46482,14 +47218,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13056" s="9"/>
-      <c r="C13056" s="33" t="s">
+      <c r="C13056" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="13057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13057" s="8"/>
       <c r="B13057" s="9"/>
-      <c r="C13057" s="33"/>
+      <c r="C13057" s="35"/>
     </row>
     <row r="13058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13058" s="8">
@@ -46522,10 +47258,10 @@
     </row>
     <row r="13100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13100" s="4"/>
-      <c r="B13100" s="34" t="s">
+      <c r="B13100" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C13100" s="35"/>
+      <c r="C13100" s="37"/>
     </row>
     <row r="13101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13101" s="12" t="s">
@@ -46839,14 +47575,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13172" s="9"/>
-      <c r="C13172" s="33" t="s">
+      <c r="C13172" s="35" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="13173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13173" s="8"/>
       <c r="B13173" s="9"/>
-      <c r="C13173" s="33"/>
+      <c r="C13173" s="35"/>
     </row>
     <row r="13174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13174" s="8">
@@ -46866,18 +47602,1216 @@
       <c r="B13175" s="20"/>
       <c r="C13175" s="21"/>
     </row>
+    <row r="13217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13217" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B13217" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13217" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13218" s="4"/>
+      <c r="B13218" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13218" s="25"/>
+    </row>
+    <row r="13219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13219" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13219" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13219" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13220" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13220" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13220" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13221" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13221" s="9"/>
+      <c r="C13221" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13222" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B13222" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13222" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13223" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13223" s="9"/>
+      <c r="C13223" s="35" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13224" s="8"/>
+      <c r="B13224" s="9"/>
+      <c r="C13224" s="35"/>
+    </row>
+    <row r="13225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13225" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13225" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13225" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13226" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13226" s="20"/>
+      <c r="C13226" s="21"/>
+    </row>
+    <row r="13276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13276" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B13276" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13276" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13277" s="4"/>
+      <c r="B13277" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13277" s="37"/>
+    </row>
+    <row r="13278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13278" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13278" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13278" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13279" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13279" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13279" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13280" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13280" s="9"/>
+      <c r="C13280" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13281" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13281" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13281" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13282" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13282" s="9"/>
+      <c r="C13282" s="10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13283" s="8"/>
+      <c r="B13283" s="9"/>
+      <c r="C13283" s="10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13284" s="8"/>
+      <c r="B13284" s="9"/>
+      <c r="C13284" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13285" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13285" s="9"/>
+      <c r="C13285" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13286" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13286" s="9"/>
+      <c r="C13286" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13287" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13287" s="9"/>
+      <c r="C13287" s="10"/>
+    </row>
+    <row r="13288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13288" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13288" s="9"/>
+      <c r="C13288" s="10"/>
+    </row>
+    <row r="13289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13289" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13289" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13289" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13290" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B13290" s="9"/>
+      <c r="C13290" s="10"/>
+    </row>
+    <row r="13291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13291" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B13291" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13291" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13292" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B13292" s="9"/>
+      <c r="C13292" s="10"/>
+    </row>
+    <row r="13293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13293" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B13293" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13293" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13294" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B13294" s="9"/>
+      <c r="C13294" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13295" s="8"/>
+      <c r="B13295" s="9"/>
+      <c r="C13295" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13296" s="8"/>
+      <c r="B13296" s="9"/>
+      <c r="C13296" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13297" s="8"/>
+      <c r="B13297" s="9"/>
+      <c r="C13297" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13298" s="8"/>
+      <c r="B13298" s="9"/>
+      <c r="C13298" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13299" s="8"/>
+      <c r="B13299" s="9"/>
+      <c r="C13299" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13300" s="8"/>
+      <c r="B13300" s="9"/>
+      <c r="C13300" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13301" s="8"/>
+      <c r="B13301" s="9"/>
+      <c r="C13301" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13302" s="8"/>
+      <c r="B13302" s="9"/>
+      <c r="C13302" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13303" s="8"/>
+      <c r="B13303" s="9"/>
+      <c r="C13303" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13304" s="8"/>
+      <c r="B13304" s="9"/>
+      <c r="C13304" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13305" s="8"/>
+      <c r="B13305" s="9"/>
+      <c r="C13305" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13306" s="8"/>
+      <c r="B13306" s="9"/>
+      <c r="C13306" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13307" s="8"/>
+      <c r="B13307" s="9"/>
+      <c r="C13307" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13308" s="8"/>
+      <c r="B13308" s="9"/>
+      <c r="C13308" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13309" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B13309" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13309" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13310" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13310" s="20"/>
+      <c r="C13310" s="21"/>
+    </row>
+    <row r="13335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13335" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B13335" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13335" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13336" s="4"/>
+      <c r="B13336" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13336" s="25"/>
+    </row>
+    <row r="13337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13337" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13337" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13337" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13338" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13338" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13338" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13339" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13339" s="9"/>
+      <c r="C13339" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13340" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13340" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13340" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13341" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13341" s="9"/>
+      <c r="C13341" s="10"/>
+    </row>
+    <row r="13342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13342" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13342" s="9"/>
+      <c r="C13342" s="10"/>
+    </row>
+    <row r="13343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13343" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13343" s="9"/>
+      <c r="C13343" s="10" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="13344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13344" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13344" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13344" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13345" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13345" s="20"/>
+      <c r="C13345" s="21"/>
+    </row>
+    <row r="13394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13394" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="B13394" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13394" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13395" s="4"/>
+      <c r="B13395" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13395" s="25"/>
+    </row>
+    <row r="13396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13396" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13396" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13396" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13397" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13397" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13397" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13398" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13398" s="9"/>
+      <c r="C13398" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13399" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13399" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13399" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13400" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13400" s="9"/>
+      <c r="C13400" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13401" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13401" s="9"/>
+      <c r="C13401" s="10"/>
+    </row>
+    <row r="13402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13402" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13402" s="9"/>
+      <c r="C13402" s="10"/>
+    </row>
+    <row r="13403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13403" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13403" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13403" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13404" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13404" s="9"/>
+      <c r="C13404" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13405" s="8"/>
+      <c r="B13405" s="9"/>
+      <c r="C13405" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13406" s="8"/>
+      <c r="B13406" s="9"/>
+      <c r="C13406" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13407" s="8"/>
+      <c r="B13407" s="9"/>
+      <c r="C13407" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13408" s="8"/>
+      <c r="B13408" s="9"/>
+      <c r="C13408" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13409" s="8"/>
+      <c r="B13409" s="9"/>
+      <c r="C13409" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13410" s="8"/>
+      <c r="B13410" s="9"/>
+      <c r="C13410" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13411" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13411" s="8"/>
+      <c r="B13411" s="9"/>
+      <c r="C13411" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13412" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13412" s="8"/>
+      <c r="B13412" s="9"/>
+      <c r="C13412" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13413" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13413" s="8"/>
+      <c r="B13413" s="9"/>
+      <c r="C13413" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13414" s="8"/>
+      <c r="B13414" s="9"/>
+      <c r="C13414" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13415" s="8"/>
+      <c r="B13415" s="9"/>
+      <c r="C13415" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13416" s="8"/>
+      <c r="B13416" s="9"/>
+      <c r="C13416" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13417" s="8"/>
+      <c r="B13417" s="9"/>
+      <c r="C13417" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13418" s="8"/>
+      <c r="B13418" s="9"/>
+      <c r="C13418" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13419" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13419" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13419" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13420" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13420" s="20"/>
+      <c r="C13420" s="21"/>
+    </row>
+    <row r="13453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13453" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13453" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13453" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13454" s="4"/>
+      <c r="B13454" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13454" s="25"/>
+    </row>
+    <row r="13455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13455" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13455" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13455" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13456" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13456" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13456" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13457" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13457" s="9"/>
+      <c r="C13457" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13458" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13458" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13458" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13459" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B13459" s="16"/>
+      <c r="C13459" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13460" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13460" s="16"/>
+      <c r="C13460" s="23"/>
+    </row>
+    <row r="13461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13461" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13461" s="9"/>
+      <c r="C13461" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13462" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B13462" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13462" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13463" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13463" s="9"/>
+      <c r="C13463" s="35" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="13464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13464" s="8"/>
+      <c r="B13464" s="9"/>
+      <c r="C13464" s="35"/>
+    </row>
+    <row r="13465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13465" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13465" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13465" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13466" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13466" s="20"/>
+      <c r="C13466" s="21"/>
+    </row>
+    <row r="13512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13512" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B13512" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13512" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13513" s="4"/>
+      <c r="B13513" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13513" s="25"/>
+    </row>
+    <row r="13514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13514" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13514" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13514" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13515" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13515" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13515" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13516" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13516" s="9"/>
+      <c r="C13516" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13517" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13517" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13517" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13518" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B13518" s="16"/>
+      <c r="C13518" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13519" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13519" s="16"/>
+      <c r="C13519" s="23"/>
+    </row>
+    <row r="13520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13520" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13520" s="9"/>
+      <c r="C13520" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13521" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B13521" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13521" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13522" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13522" s="9"/>
+      <c r="C13522" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13523" s="8"/>
+      <c r="B13523" s="9"/>
+      <c r="C13523" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13524" s="8"/>
+      <c r="B13524" s="9"/>
+      <c r="C13524" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13525" s="8"/>
+      <c r="B13525" s="9"/>
+      <c r="C13525" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13526" s="8"/>
+      <c r="B13526" s="9"/>
+      <c r="C13526" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13527" s="8"/>
+      <c r="B13527" s="9"/>
+      <c r="C13527" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13528" s="8"/>
+      <c r="B13528" s="9"/>
+      <c r="C13528" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13529" s="8"/>
+      <c r="B13529" s="9"/>
+      <c r="C13529" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13530" s="8"/>
+      <c r="B13530" s="9"/>
+      <c r="C13530" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13531" s="8"/>
+      <c r="B13531" s="9"/>
+      <c r="C13531" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13532" s="8"/>
+      <c r="B13532" s="9"/>
+      <c r="C13532" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13533" s="8"/>
+      <c r="B13533" s="9"/>
+      <c r="C13533" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13534" s="8"/>
+      <c r="B13534" s="9"/>
+      <c r="C13534" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13535" s="8"/>
+      <c r="B13535" s="9"/>
+      <c r="C13535" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13536" s="8"/>
+      <c r="B13536" s="9"/>
+      <c r="C13536" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13537" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13537" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13537" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13538" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13538" s="20"/>
+      <c r="C13538" s="21"/>
+    </row>
+    <row r="13571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13571" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B13571" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13571" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13572" s="4"/>
+      <c r="B13572" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13572" s="25"/>
+    </row>
+    <row r="13573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13573" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13573" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13573" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13574" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13574" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13574" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13575" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13575" s="9"/>
+      <c r="C13575" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13576" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13576" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13576" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13577" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B13577" s="16"/>
+      <c r="C13577" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13578" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13578" s="16"/>
+      <c r="C13578" s="23"/>
+    </row>
+    <row r="13579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13579" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13579" s="9"/>
+      <c r="C13579" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13580" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13580" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13580" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13581" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13581" s="9"/>
+      <c r="C13581" s="10"/>
+    </row>
+    <row r="13582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13582" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13582" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13582" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13583" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B13583" s="9"/>
+      <c r="C13583" s="10" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="13584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13584" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B13584" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13584" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13585" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13585" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B13585" s="9"/>
+      <c r="C13585" s="10"/>
+    </row>
+    <row r="13586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13586" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B13586" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13586" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13587" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13587" s="20"/>
+      <c r="C13587" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="156">
-    <mergeCell ref="C13056:C13057"/>
-    <mergeCell ref="B13100:C13100"/>
-    <mergeCell ref="C13172:C13173"/>
-    <mergeCell ref="C12820:C12821"/>
-    <mergeCell ref="B12982:C12982"/>
-    <mergeCell ref="B12994:B12996"/>
-    <mergeCell ref="B12687:C12687"/>
-    <mergeCell ref="B12701:B12703"/>
-    <mergeCell ref="B12697:B12699"/>
-    <mergeCell ref="C12708:C12709"/>
+  <mergeCells count="159">
+    <mergeCell ref="C13463:C13464"/>
     <mergeCell ref="B5725:C5725"/>
     <mergeCell ref="B6020:C6020"/>
     <mergeCell ref="B5607:C5607"/>
@@ -47015,6 +48949,8 @@
     <mergeCell ref="C11758:C11759"/>
     <mergeCell ref="C11866:C11867"/>
     <mergeCell ref="C12047:C12048"/>
+    <mergeCell ref="C13223:C13224"/>
+    <mergeCell ref="B13277:C13277"/>
     <mergeCell ref="C12581:C12582"/>
     <mergeCell ref="C12576:C12577"/>
     <mergeCell ref="B12628:C12628"/>
@@ -47024,6 +48960,16 @@
     <mergeCell ref="C12405:C12406"/>
     <mergeCell ref="B12451:C12451"/>
     <mergeCell ref="C12468:C12469"/>
+    <mergeCell ref="C13056:C13057"/>
+    <mergeCell ref="B13100:C13100"/>
+    <mergeCell ref="C13172:C13173"/>
+    <mergeCell ref="C12820:C12821"/>
+    <mergeCell ref="B12982:C12982"/>
+    <mergeCell ref="B12994:B12996"/>
+    <mergeCell ref="B12687:C12687"/>
+    <mergeCell ref="B12701:B12703"/>
+    <mergeCell ref="B12697:B12699"/>
+    <mergeCell ref="C12708:C12709"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ED1B08-133D-4FDE-BE5F-5227254ECB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AFC487-D52A-418F-8CB8-56237F9AEC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$14984</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$15104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5560" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6316" uniqueCount="590">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -13339,6 +13339,767 @@
       </rPr>
       <t xml:space="preserve"> based off Operand.L.</t>
     </r>
+  </si>
+  <si>
+    <t>SBC (E7)</t>
+  </si>
+  <si>
+    <t>INX (E8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E9)</t>
+  </si>
+  <si>
+    <t>NOP (EA)</t>
+  </si>
+  <si>
+    <t>XBA (EB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Swap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>CPX (EC)</t>
+  </si>
+  <si>
+    <t>SBC (ED)</t>
+  </si>
+  <si>
+    <t>INC (EE)</t>
+  </si>
+  <si>
+    <t>SBC (EF)</t>
+  </si>
+  <si>
+    <t>BEQ (F0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (F1)</t>
+  </si>
+  <si>
+    <t>SBC (F2)</t>
+  </si>
+  <si>
+    <t>SBC (F3)</t>
+  </si>
+  <si>
+    <t>PEA (F4)</t>
+  </si>
+  <si>
+    <t>Absolute (Push)</t>
+  </si>
+  <si>
+    <t>SBC (F5)</t>
+  </si>
+  <si>
+    <t>INC (F6)</t>
+  </si>
+  <si>
+    <t>SBC (F7)</t>
+  </si>
+  <si>
+    <t>SED (F8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (F9)</t>
+  </si>
+  <si>
+    <t>PLX (FA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 1 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>XCE (FB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exchanges the Carry and Emulation flags. If Emulation mode is entered, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags are set to 1, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H is set to 1, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H are cleared to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>JSR (FC)</t>
+  </si>
+  <si>
+    <t>Absolute Indexed Indirect (a,x) (Jump)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bank = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Pointer += </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 2 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. </t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (FD)</t>
+  </si>
+  <si>
+    <t>INC (FE)</t>
+  </si>
+  <si>
+    <t>SBC (FF)</t>
   </si>
 </sst>
 </file>
@@ -13950,7 +14711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C13587"/>
+  <dimension ref="A1:C15076"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -48809,146 +49570,4845 @@
       <c r="B13587" s="20"/>
       <c r="C13587" s="21"/>
     </row>
+    <row r="13630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13630" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B13630" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13630" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13631" s="4"/>
+      <c r="B13631" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13631" s="37"/>
+    </row>
+    <row r="13632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13632" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13632" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13632" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13633" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13633" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13633" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13634" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13634" s="9"/>
+      <c r="C13634" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13635" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13635" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13635" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13636" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B13636" s="16"/>
+      <c r="C13636" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13637" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13637" s="16"/>
+      <c r="C13637" s="23"/>
+    </row>
+    <row r="13638" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13638" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13638" s="9"/>
+      <c r="C13638" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13639" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13639" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13639" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13639" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13640" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13640" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13640" s="9"/>
+      <c r="C13640" s="10"/>
+    </row>
+    <row r="13641" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13641" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13641" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13641" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13642" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13642" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B13642" s="9"/>
+      <c r="C13642" s="10"/>
+    </row>
+    <row r="13643" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13643" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B13643" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13643" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13644" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13644" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B13644" s="9"/>
+      <c r="C13644" s="10"/>
+    </row>
+    <row r="13645" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13645" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B13645" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13645" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13646" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13646" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B13646" s="9"/>
+      <c r="C13646" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13647" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13647" s="8"/>
+      <c r="B13647" s="9"/>
+      <c r="C13647" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13648" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13648" s="8"/>
+      <c r="B13648" s="9"/>
+      <c r="C13648" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13649" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13649" s="8"/>
+      <c r="B13649" s="9"/>
+      <c r="C13649" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13650" s="8"/>
+      <c r="B13650" s="9"/>
+      <c r="C13650" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13651" s="8"/>
+      <c r="B13651" s="9"/>
+      <c r="C13651" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13652" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13652" s="8"/>
+      <c r="B13652" s="9"/>
+      <c r="C13652" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13653" s="8"/>
+      <c r="B13653" s="9"/>
+      <c r="C13653" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13654" s="8"/>
+      <c r="B13654" s="9"/>
+      <c r="C13654" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13655" s="8"/>
+      <c r="B13655" s="9"/>
+      <c r="C13655" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13656" s="8"/>
+      <c r="B13656" s="9"/>
+      <c r="C13656" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13657" s="8"/>
+      <c r="B13657" s="9"/>
+      <c r="C13657" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13658" s="8"/>
+      <c r="B13658" s="9"/>
+      <c r="C13658" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13659" s="8"/>
+      <c r="B13659" s="9"/>
+      <c r="C13659" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13660" s="8"/>
+      <c r="B13660" s="9"/>
+      <c r="C13660" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13661" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B13661" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13661" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13662" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13662" s="20"/>
+      <c r="C13662" s="21"/>
+    </row>
+    <row r="13689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13689" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B13689" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13689" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13690" s="4"/>
+      <c r="B13690" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13690" s="25"/>
+    </row>
+    <row r="13691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13691" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13691" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13691" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13692" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13692" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13692" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13693" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13693" s="9"/>
+      <c r="C13693" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13694" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B13694" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13694" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13695" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13695" s="9"/>
+      <c r="C13695" s="10" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="13696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13696" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13696" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13696" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13697" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13697" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13697" s="20"/>
+      <c r="C13697" s="21"/>
+    </row>
+    <row r="13748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13748" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B13748" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13748" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13749" s="4"/>
+      <c r="B13749" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13749" s="25"/>
+    </row>
+    <row r="13750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13750" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13750" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13750" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13751" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13751" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13751" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13752" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13752" s="9"/>
+      <c r="C13752" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13753" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B13753" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13753" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13754" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13754" s="9"/>
+      <c r="C13754" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13755" s="8"/>
+      <c r="B13755" s="9"/>
+      <c r="C13755" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13756" s="8"/>
+      <c r="B13756" s="9"/>
+      <c r="C13756" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13757" s="8"/>
+      <c r="B13757" s="9"/>
+      <c r="C13757" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13758" s="8"/>
+      <c r="B13758" s="9"/>
+      <c r="C13758" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13759" s="8"/>
+      <c r="B13759" s="9"/>
+      <c r="C13759" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="13760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13760" s="8"/>
+      <c r="B13760" s="9"/>
+      <c r="C13760" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="13761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13761" s="8"/>
+      <c r="B13761" s="9"/>
+      <c r="C13761" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13762" s="8"/>
+      <c r="B13762" s="9"/>
+      <c r="C13762" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13763" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13763" s="8"/>
+      <c r="B13763" s="9"/>
+      <c r="C13763" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="13764" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13764" s="8"/>
+      <c r="B13764" s="9"/>
+      <c r="C13764" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13765" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13765" s="8"/>
+      <c r="B13765" s="9"/>
+      <c r="C13765" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="13766" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13766" s="8"/>
+      <c r="B13766" s="9"/>
+      <c r="C13766" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13767" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13767" s="8"/>
+      <c r="B13767" s="9"/>
+      <c r="C13767" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13768" s="8"/>
+      <c r="B13768" s="9"/>
+      <c r="C13768" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="13769" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13769" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13769" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13769" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13770" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13770" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13770" s="20"/>
+      <c r="C13770" s="21"/>
+    </row>
+    <row r="13807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13807" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B13807" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13807" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13808" s="4"/>
+      <c r="B13808" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13808" s="25"/>
+    </row>
+    <row r="13809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13809" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13809" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13809" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13810" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13810" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13810" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13811" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13811" s="9"/>
+      <c r="C13811" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13812" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B13812" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13812" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13813" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13813" s="9"/>
+      <c r="C13813" s="10"/>
+    </row>
+    <row r="13814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13814" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13814" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13814" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13815" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13815" s="20"/>
+      <c r="C13815" s="21"/>
+    </row>
+    <row r="13866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13866" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B13866" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13866" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13867" s="4"/>
+      <c r="B13867" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13867" s="25"/>
+    </row>
+    <row r="13868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13868" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13868" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13868" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13869" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13869" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13869" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13870" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13870" s="9"/>
+      <c r="C13870" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13871" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13871" s="9"/>
+      <c r="C13871" s="10"/>
+    </row>
+    <row r="13872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13872" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13872" s="9"/>
+      <c r="C13872" s="10"/>
+    </row>
+    <row r="13873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13873" s="18">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13873" s="9"/>
+      <c r="C13873" s="10"/>
+    </row>
+    <row r="13874" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13874" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13874" s="9"/>
+      <c r="C13874" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13875" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B13875" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13875" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13876" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13876" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13876" s="20"/>
+      <c r="C13876" s="21"/>
+    </row>
+    <row r="13925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13925" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B13925" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13925" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13926" s="4"/>
+      <c r="B13926" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13926" s="25"/>
+    </row>
+    <row r="13927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13927" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13927" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13927" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13928" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13928" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13928" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13929" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13929" s="9"/>
+      <c r="C13929" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13930" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13930" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13930" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13931" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13931" s="9"/>
+      <c r="C13931" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13932" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13932" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13932" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13933" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13933" s="9"/>
+      <c r="C13933" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13934" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B13934" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13934" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13935" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13935" s="9"/>
+      <c r="C13935" s="35" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="13936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13936" s="8"/>
+      <c r="B13936" s="9"/>
+      <c r="C13936" s="35"/>
+    </row>
+    <row r="13937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13937" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B13937" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13937" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13938" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13938" s="20"/>
+      <c r="C13938" s="21"/>
+    </row>
+    <row r="13984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13984" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B13984" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13984" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13985" s="4"/>
+      <c r="B13985" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13985" s="25"/>
+    </row>
+    <row r="13986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13986" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13986" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13986" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13987" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13987" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13987" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13988" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B13988" s="9"/>
+      <c r="C13988" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13989" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B13989" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13989" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13990" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13990" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B13990" s="9"/>
+      <c r="C13990" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13991" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13991" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B13991" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13991" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13992" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B13992" s="9"/>
+      <c r="C13992" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13993" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B13993" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13993" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13994" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B13994" s="9"/>
+      <c r="C13994" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13995" s="8"/>
+      <c r="B13995" s="9"/>
+      <c r="C13995" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="13996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13996" s="8"/>
+      <c r="B13996" s="9"/>
+      <c r="C13996" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13997" s="8"/>
+      <c r="B13997" s="9"/>
+      <c r="C13997" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="13998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13998" s="8"/>
+      <c r="B13998" s="9"/>
+      <c r="C13998" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13999" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13999" s="8"/>
+      <c r="B13999" s="9"/>
+      <c r="C13999" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14000" s="8"/>
+      <c r="B14000" s="9"/>
+      <c r="C14000" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14001" s="8"/>
+      <c r="B14001" s="9"/>
+      <c r="C14001" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14002" s="8"/>
+      <c r="B14002" s="9"/>
+      <c r="C14002" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14003" s="8"/>
+      <c r="B14003" s="9"/>
+      <c r="C14003" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14004" s="8"/>
+      <c r="B14004" s="9"/>
+      <c r="C14004" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14005" s="8"/>
+      <c r="B14005" s="9"/>
+      <c r="C14005" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14006" s="8"/>
+      <c r="B14006" s="9"/>
+      <c r="C14006" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14007" s="8"/>
+      <c r="B14007" s="9"/>
+      <c r="C14007" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14008" s="8"/>
+      <c r="B14008" s="9"/>
+      <c r="C14008" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14009" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14009" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14009" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14010" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14010" s="20"/>
+      <c r="C14010" s="21"/>
+    </row>
+    <row r="14043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14043" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B14043" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14043" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14044" s="4"/>
+      <c r="B14044" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14044" s="37"/>
+    </row>
+    <row r="14045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14045" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14045" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14045" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14046" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14046" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14046" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14047" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14047" s="9"/>
+      <c r="C14047" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14048" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14048" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14048" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14049" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14049" s="9"/>
+      <c r="C14049" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14050" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14050" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14050" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14051" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14051" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14051" s="9"/>
+      <c r="C14051" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14052" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14052" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14052" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14053" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14053" s="9"/>
+      <c r="C14053" s="10"/>
+    </row>
+    <row r="14054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14054" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14054" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14054" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14055" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14055" s="9"/>
+      <c r="C14055" s="10" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="14056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14056" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B14056" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14056" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14057" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14057" s="9"/>
+      <c r="C14057" s="10"/>
+    </row>
+    <row r="14058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14058" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B14058" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14058" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14059" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14059" s="20"/>
+      <c r="C14059" s="21"/>
+    </row>
+    <row r="14102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14102" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B14102" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14102" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14103" s="4"/>
+      <c r="B14103" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14103" s="25"/>
+    </row>
+    <row r="14104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14104" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14104" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14105" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14105" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14105" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14106" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14106" s="9"/>
+      <c r="C14106" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14107" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14107" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14107" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14108" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14108" s="9"/>
+      <c r="C14108" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14109" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14109" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14109" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14110" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14110" s="9"/>
+      <c r="C14110" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14111" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14111" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14111" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14112" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14112" s="9"/>
+      <c r="C14112" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14113" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B14113" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14113" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14114" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14114" s="9"/>
+      <c r="C14114" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14115" s="8"/>
+      <c r="B14115" s="9"/>
+      <c r="C14115" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14116" s="8"/>
+      <c r="B14116" s="9"/>
+      <c r="C14116" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14117" s="8"/>
+      <c r="B14117" s="9"/>
+      <c r="C14117" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14118" s="8"/>
+      <c r="B14118" s="9"/>
+      <c r="C14118" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14119" s="8"/>
+      <c r="B14119" s="9"/>
+      <c r="C14119" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14120" s="8"/>
+      <c r="B14120" s="9"/>
+      <c r="C14120" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14121" s="8"/>
+      <c r="B14121" s="9"/>
+      <c r="C14121" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14122" s="8"/>
+      <c r="B14122" s="9"/>
+      <c r="C14122" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14123" s="8"/>
+      <c r="B14123" s="9"/>
+      <c r="C14123" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14124" s="8"/>
+      <c r="B14124" s="9"/>
+      <c r="C14124" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14125" s="8"/>
+      <c r="B14125" s="9"/>
+      <c r="C14125" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14126" s="8"/>
+      <c r="B14126" s="9"/>
+      <c r="C14126" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14127" s="8"/>
+      <c r="B14127" s="9"/>
+      <c r="C14127" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14128" s="8"/>
+      <c r="B14128" s="9"/>
+      <c r="C14128" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14129" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14129" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14129" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14130" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14130" s="20"/>
+      <c r="C14130" s="21"/>
+    </row>
+    <row r="14161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14161" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B14161" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14161" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14162" s="4"/>
+      <c r="B14162" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14162" s="6"/>
+    </row>
+    <row r="14163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14163" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14163" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14163" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14164" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14164" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14164" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14165" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14165" s="9"/>
+      <c r="C14165" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="14166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14166" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B14166" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14166" s="35" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14167" s="8"/>
+      <c r="B14167" s="9"/>
+      <c r="C14167" s="35"/>
+    </row>
+    <row r="14168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14168" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14168" s="9"/>
+      <c r="C14168" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14169" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14169" s="9"/>
+      <c r="C14169" s="10"/>
+    </row>
+    <row r="14170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14170" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14170" s="9"/>
+      <c r="C14170" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14171" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B14171" s="9"/>
+      <c r="C14171" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14172" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14172" s="9"/>
+      <c r="C14172" s="10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14173" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14173" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14173" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14174" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14174" s="20"/>
+      <c r="C14174" s="21"/>
+    </row>
+    <row r="14220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14220" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B14220" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14220" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14221" s="4"/>
+      <c r="B14221" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14221" s="37"/>
+    </row>
+    <row r="14222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14222" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14222" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14222" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14223" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14223" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14223" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14224" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14224" s="9"/>
+      <c r="C14224" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14225" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14225" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14225" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14226" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B14226" s="16"/>
+      <c r="C14226" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14227" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14227" s="16"/>
+      <c r="C14227" s="23"/>
+    </row>
+    <row r="14228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14228" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14228" s="9"/>
+      <c r="C14228" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14229" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14229" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14229" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14230" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14230" s="9"/>
+      <c r="C14230" s="10"/>
+    </row>
+    <row r="14231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14231" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14231" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14231" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14232" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14232" s="9"/>
+      <c r="C14232" s="10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14233" s="8"/>
+      <c r="B14233" s="9"/>
+      <c r="C14233" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14234" s="8"/>
+      <c r="B14234" s="9"/>
+      <c r="C14234" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14235" s="8"/>
+      <c r="B14235" s="9"/>
+      <c r="C14235" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14236" s="8"/>
+      <c r="B14236" s="9"/>
+      <c r="C14236" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14237" s="15">
+        <v>5.2</v>
+      </c>
+      <c r="B14237" s="16"/>
+      <c r="C14237" s="23"/>
+    </row>
+    <row r="14238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14238" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="B14238" s="16"/>
+      <c r="C14238" s="23"/>
+    </row>
+    <row r="14239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14239" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B14239" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14239" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14240" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B14240" s="9"/>
+      <c r="C14240" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14241" s="8"/>
+      <c r="B14241" s="9"/>
+      <c r="C14241" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14242" s="8"/>
+      <c r="B14242" s="9"/>
+      <c r="C14242" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14243" s="8"/>
+      <c r="B14243" s="9"/>
+      <c r="C14243" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14244" s="8"/>
+      <c r="B14244" s="9"/>
+      <c r="C14244" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14245" s="8"/>
+      <c r="B14245" s="9"/>
+      <c r="C14245" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14246" s="8"/>
+      <c r="B14246" s="9"/>
+      <c r="C14246" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14247" s="8"/>
+      <c r="B14247" s="9"/>
+      <c r="C14247" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14248" s="8"/>
+      <c r="B14248" s="9"/>
+      <c r="C14248" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14249" s="8"/>
+      <c r="B14249" s="9"/>
+      <c r="C14249" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14250" s="8"/>
+      <c r="B14250" s="9"/>
+      <c r="C14250" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14251" s="8"/>
+      <c r="B14251" s="9"/>
+      <c r="C14251" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14252" s="8"/>
+      <c r="B14252" s="9"/>
+      <c r="C14252" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14253" s="8"/>
+      <c r="B14253" s="9"/>
+      <c r="C14253" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14254" s="8"/>
+      <c r="B14254" s="9"/>
+      <c r="C14254" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14255" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B14255" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14255" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14256" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14256" s="20"/>
+      <c r="C14256" s="21"/>
+    </row>
+    <row r="14279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14279" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B14279" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14279" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14280" s="4"/>
+      <c r="B14280" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14280" s="25"/>
+    </row>
+    <row r="14281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14281" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14281" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14281" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14282" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14282" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14282" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14283" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14283" s="9"/>
+      <c r="C14283" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14284" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14284" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14284" s="10" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14285" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B14285" s="16"/>
+      <c r="C14285" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14286" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14286" s="16"/>
+      <c r="C14286" s="23"/>
+    </row>
+    <row r="14287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14287" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14287" s="9"/>
+      <c r="C14287" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14288" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14288" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14288" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14289" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14289" s="9"/>
+      <c r="C14289" s="10"/>
+    </row>
+    <row r="14290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14290" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14290" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14290" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14291" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14291" s="9"/>
+      <c r="C14291" s="10"/>
+    </row>
+    <row r="14292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14292" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="B14292" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14292" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14293" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14293" s="9"/>
+      <c r="C14293" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14294" s="8"/>
+      <c r="B14294" s="9"/>
+      <c r="C14294" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14295" s="8"/>
+      <c r="B14295" s="9"/>
+      <c r="C14295" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14296" s="8"/>
+      <c r="B14296" s="9"/>
+      <c r="C14296" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14297" s="8"/>
+      <c r="B14297" s="9"/>
+      <c r="C14297" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14298" s="8"/>
+      <c r="B14298" s="9"/>
+      <c r="C14298" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14299" s="8"/>
+      <c r="B14299" s="9"/>
+      <c r="C14299" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14300" s="8"/>
+      <c r="B14300" s="9"/>
+      <c r="C14300" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14301" s="8"/>
+      <c r="B14301" s="9"/>
+      <c r="C14301" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14302" s="8"/>
+      <c r="B14302" s="9"/>
+      <c r="C14302" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14303" s="8"/>
+      <c r="B14303" s="9"/>
+      <c r="C14303" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14304" s="8"/>
+      <c r="B14304" s="9"/>
+      <c r="C14304" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14305" s="8"/>
+      <c r="B14305" s="9"/>
+      <c r="C14305" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14306" s="8"/>
+      <c r="B14306" s="9"/>
+      <c r="C14306" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14307" s="8"/>
+      <c r="B14307" s="9"/>
+      <c r="C14307" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14308" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B14308" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14308" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14309" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14309" s="20"/>
+      <c r="C14309" s="21"/>
+    </row>
+    <row r="14338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14338" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B14338" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14338" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14339" s="4"/>
+      <c r="B14339" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14339" s="25"/>
+    </row>
+    <row r="14340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14340" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14340" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14340" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14341" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14341" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14341" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14342" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14342" s="9"/>
+      <c r="C14342" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14343" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14343" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14343" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14344" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14344" s="9"/>
+      <c r="C14344" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14345" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14345" s="9"/>
+      <c r="C14345" s="10"/>
+    </row>
+    <row r="14346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14346" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14346" s="9"/>
+      <c r="C14346" s="10"/>
+    </row>
+    <row r="14347" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14347" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14347" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14347" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14348" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14348" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14348" s="9"/>
+      <c r="C14348" s="10"/>
+    </row>
+    <row r="14349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14349" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14349" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14349" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14350" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14350" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14350" s="9"/>
+      <c r="C14350" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14351" s="8"/>
+      <c r="B14351" s="9"/>
+      <c r="C14351" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14352" s="8"/>
+      <c r="B14352" s="9"/>
+      <c r="C14352" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14353" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14353" s="9"/>
+      <c r="C14353" s="10"/>
+    </row>
+    <row r="14354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14354" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14354" s="9"/>
+      <c r="C14354" s="10"/>
+    </row>
+    <row r="14355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14355" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B14355" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14355" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14356" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B14356" s="9"/>
+      <c r="C14356" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14357" s="8"/>
+      <c r="B14357" s="9"/>
+      <c r="C14357" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14358" s="8"/>
+      <c r="B14358" s="9"/>
+      <c r="C14358" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14359" s="8"/>
+      <c r="B14359" s="9"/>
+      <c r="C14359" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14360" s="8"/>
+      <c r="B14360" s="9"/>
+      <c r="C14360" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14361" s="8"/>
+      <c r="B14361" s="9"/>
+      <c r="C14361" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14362" s="8"/>
+      <c r="B14362" s="9"/>
+      <c r="C14362" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14363" s="8"/>
+      <c r="B14363" s="9"/>
+      <c r="C14363" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14364" s="8"/>
+      <c r="B14364" s="9"/>
+      <c r="C14364" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14365" s="8"/>
+      <c r="B14365" s="9"/>
+      <c r="C14365" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14366" s="8"/>
+      <c r="B14366" s="9"/>
+      <c r="C14366" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14367" s="8"/>
+      <c r="B14367" s="9"/>
+      <c r="C14367" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14368" s="8"/>
+      <c r="B14368" s="9"/>
+      <c r="C14368" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14369" s="8"/>
+      <c r="B14369" s="9"/>
+      <c r="C14369" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14370" s="8"/>
+      <c r="B14370" s="9"/>
+      <c r="C14370" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14371" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B14371" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14371" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14372" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14372" s="20"/>
+      <c r="C14372" s="21"/>
+    </row>
+    <row r="14397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14397" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B14397" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14397" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14398" s="4"/>
+      <c r="B14398" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="C14398" s="25"/>
+    </row>
+    <row r="14399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14399" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14399" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14399" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14400" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14400" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14400" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14401" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14401" s="9"/>
+      <c r="C14401" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14402" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14402" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14402" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14403" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14403" s="9"/>
+      <c r="C14403" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14404" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14404" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14404" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14405" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14405" s="9"/>
+      <c r="C14405" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14406" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14406" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14406" s="10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="14407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14407" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14407" s="9"/>
+      <c r="C14407" s="10"/>
+    </row>
+    <row r="14408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14408" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B14408" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14408" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14409" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14409" s="9"/>
+      <c r="C14409" s="10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="14410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14410" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14410" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14410" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14411" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14411" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14411" s="20"/>
+      <c r="C14411" s="21"/>
+    </row>
+    <row r="14456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14456" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B14456" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14456" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14457" s="4"/>
+      <c r="B14457" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14457" s="37"/>
+    </row>
+    <row r="14458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14458" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14458" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14458" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14459" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14459" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14459" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14460" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14460" s="9"/>
+      <c r="C14460" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14461" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14461" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14461" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14462" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14462" s="9"/>
+      <c r="C14462" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14463" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14463" s="9"/>
+      <c r="C14463" s="10"/>
+    </row>
+    <row r="14464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14464" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14464" s="9"/>
+      <c r="C14464" s="35" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14465" s="8"/>
+      <c r="B14465" s="9"/>
+      <c r="C14465" s="35"/>
+    </row>
+    <row r="14466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14466" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B14466" s="16"/>
+      <c r="C14466" s="23"/>
+    </row>
+    <row r="14467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14467" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14467" s="16"/>
+      <c r="C14467" s="23"/>
+    </row>
+    <row r="14468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14468" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B14468" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14468" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14469" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14469" s="9"/>
+      <c r="C14469" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14470" s="8"/>
+      <c r="B14470" s="9"/>
+      <c r="C14470" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14471" s="8"/>
+      <c r="B14471" s="9"/>
+      <c r="C14471" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14472" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14472" s="8"/>
+      <c r="B14472" s="9"/>
+      <c r="C14472" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14473" s="8"/>
+      <c r="B14473" s="9"/>
+      <c r="C14473" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14474" s="8"/>
+      <c r="B14474" s="9"/>
+      <c r="C14474" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14475" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14475" s="8"/>
+      <c r="B14475" s="9"/>
+      <c r="C14475" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14476" s="8"/>
+      <c r="B14476" s="9"/>
+      <c r="C14476" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14477" s="8"/>
+      <c r="B14477" s="9"/>
+      <c r="C14477" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14478" s="8"/>
+      <c r="B14478" s="9"/>
+      <c r="C14478" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14479" s="8"/>
+      <c r="B14479" s="9"/>
+      <c r="C14479" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14480" s="8"/>
+      <c r="B14480" s="9"/>
+      <c r="C14480" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14481" s="8"/>
+      <c r="B14481" s="9"/>
+      <c r="C14481" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14482" s="8"/>
+      <c r="B14482" s="9"/>
+      <c r="C14482" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14483" s="8"/>
+      <c r="B14483" s="9"/>
+      <c r="C14483" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14484" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14484" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14484" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14485" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14485" s="20"/>
+      <c r="C14485" s="21"/>
+    </row>
+    <row r="14515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14515" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B14515" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14515" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14516" s="4"/>
+      <c r="B14516" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14516" s="37"/>
+    </row>
+    <row r="14517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14517" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14517" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14517" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14518" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14518" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14518" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14519" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14519" s="9"/>
+      <c r="C14519" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14520" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14520" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14520" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14521" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14521" s="9"/>
+      <c r="C14521" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14522" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14522" s="9"/>
+      <c r="C14522" s="10"/>
+    </row>
+    <row r="14523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14523" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14523" s="9"/>
+      <c r="C14523" s="35" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14524" s="8"/>
+      <c r="B14524" s="9"/>
+      <c r="C14524" s="35"/>
+    </row>
+    <row r="14525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14525" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14525" s="9"/>
+      <c r="C14525" s="10"/>
+    </row>
+    <row r="14526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14526" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14526" s="9"/>
+      <c r="C14526" s="10"/>
+    </row>
+    <row r="14527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14527" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14527" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14527" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14528" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14528" s="9"/>
+      <c r="C14528" s="10"/>
+    </row>
+    <row r="14529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14529" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14529" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14529" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14530" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14530" s="9"/>
+      <c r="C14530" s="10" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="14531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14531" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B14531" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14531" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14532" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B14532" s="9"/>
+      <c r="C14532" s="10"/>
+    </row>
+    <row r="14533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14533" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B14533" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14533" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14534" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14534" s="20"/>
+      <c r="C14534" s="21"/>
+    </row>
+    <row r="14574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14574" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B14574" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14574" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14575" s="4"/>
+      <c r="B14575" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14575" s="37"/>
+    </row>
+    <row r="14576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14576" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14576" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14576" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14577" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14577" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14577" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14578" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14578" s="9"/>
+      <c r="C14578" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14579" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14579" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14579" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14580" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="B14580" s="16"/>
+      <c r="C14580" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14581" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14581" s="16"/>
+      <c r="C14581" s="23"/>
+    </row>
+    <row r="14582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14582" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14582" s="9"/>
+      <c r="C14582" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14583" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14583" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14583" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14584" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14584" s="9"/>
+      <c r="C14584" s="10"/>
+    </row>
+    <row r="14585" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14585" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14585" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14585" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14586" s="8"/>
+      <c r="B14586" s="38"/>
+      <c r="C14586" s="10"/>
+    </row>
+    <row r="14587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14587" s="8"/>
+      <c r="B14587" s="38"/>
+      <c r="C14587" s="10"/>
+    </row>
+    <row r="14588" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14588" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14588" s="9"/>
+      <c r="C14588" s="10"/>
+    </row>
+    <row r="14589" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14589" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14589" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14589" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14590" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14590" s="8"/>
+      <c r="B14590" s="38"/>
+      <c r="C14590" s="10"/>
+    </row>
+    <row r="14591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14591" s="8"/>
+      <c r="B14591" s="38"/>
+      <c r="C14591" s="10"/>
+    </row>
+    <row r="14592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14592" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14592" s="9"/>
+      <c r="C14592" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14593" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14593" s="8"/>
+      <c r="B14593" s="9"/>
+      <c r="C14593" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14594" s="8"/>
+      <c r="B14594" s="9"/>
+      <c r="C14594" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14595" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B14595" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14595" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14596" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B14596" s="9"/>
+      <c r="C14596" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14597" s="8"/>
+      <c r="B14597" s="9"/>
+      <c r="C14597" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14598" s="8"/>
+      <c r="B14598" s="9"/>
+      <c r="C14598" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14599" s="8"/>
+      <c r="B14599" s="9"/>
+      <c r="C14599" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14600" s="8"/>
+      <c r="B14600" s="9"/>
+      <c r="C14600" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14601" s="8"/>
+      <c r="B14601" s="9"/>
+      <c r="C14601" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14602" s="8"/>
+      <c r="B14602" s="9"/>
+      <c r="C14602" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14603" s="8"/>
+      <c r="B14603" s="9"/>
+      <c r="C14603" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14604" s="8"/>
+      <c r="B14604" s="9"/>
+      <c r="C14604" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14605" s="8"/>
+      <c r="B14605" s="9"/>
+      <c r="C14605" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14606" s="8"/>
+      <c r="B14606" s="9"/>
+      <c r="C14606" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14607" s="8"/>
+      <c r="B14607" s="9"/>
+      <c r="C14607" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14608" s="8"/>
+      <c r="B14608" s="9"/>
+      <c r="C14608" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14609" s="8"/>
+      <c r="B14609" s="9"/>
+      <c r="C14609" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14610" s="8"/>
+      <c r="B14610" s="9"/>
+      <c r="C14610" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14611" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B14611" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14611" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14612" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14612" s="20"/>
+      <c r="C14612" s="21"/>
+    </row>
+    <row r="14633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14633" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B14633" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14633" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14634" s="4"/>
+      <c r="B14634" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14634" s="25"/>
+    </row>
+    <row r="14635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14635" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14635" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14635" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14636" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14636" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14636" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14637" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14637" s="9"/>
+      <c r="C14637" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14638" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14638" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B14638" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14638" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14639" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14639" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14639" s="9"/>
+      <c r="C14639" s="10" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="14640" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14640" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14640" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14640" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14641" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14641" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14641" s="20"/>
+      <c r="C14641" s="21"/>
+    </row>
+    <row r="14692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14692" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B14692" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14692" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14693" s="4"/>
+      <c r="B14693" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14693" s="25"/>
+    </row>
+    <row r="14694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14694" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14694" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14694" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14695" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14695" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14695" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14696" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14696" s="9"/>
+      <c r="C14696" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14697" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14697" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14697" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14697" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14698" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14698" s="9"/>
+      <c r="C14698" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14699" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14699" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14699" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14700" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14700" s="9"/>
+      <c r="C14700" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14701" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14701" s="8"/>
+      <c r="B14701" s="9"/>
+      <c r="C14701" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14702" s="8"/>
+      <c r="B14702" s="9"/>
+      <c r="C14702" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14703" s="8"/>
+      <c r="B14703" s="27"/>
+      <c r="C14703" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14704" s="8"/>
+      <c r="B14704" s="27"/>
+      <c r="C14704" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14705" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B14705" s="33"/>
+      <c r="C14705" s="23"/>
+    </row>
+    <row r="14706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14706" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14706" s="33"/>
+      <c r="C14706" s="23"/>
+    </row>
+    <row r="14707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14707" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B14707" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14707" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14708" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14708" s="9"/>
+      <c r="C14708" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14709" s="8"/>
+      <c r="B14709" s="27"/>
+      <c r="C14709" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14710" s="8"/>
+      <c r="B14710" s="27"/>
+      <c r="C14710" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14711" s="8"/>
+      <c r="B14711" s="27"/>
+      <c r="C14711" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14712" s="8"/>
+      <c r="B14712" s="9"/>
+      <c r="C14712" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14713" s="8"/>
+      <c r="B14713" s="9"/>
+      <c r="C14713" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14714" s="8"/>
+      <c r="B14714" s="9"/>
+      <c r="C14714" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14715" s="8"/>
+      <c r="B14715" s="9"/>
+      <c r="C14715" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14716" s="8"/>
+      <c r="B14716" s="9"/>
+      <c r="C14716" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14717" s="8"/>
+      <c r="B14717" s="9"/>
+      <c r="C14717" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14718" s="8"/>
+      <c r="B14718" s="9"/>
+      <c r="C14718" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14719" s="8"/>
+      <c r="B14719" s="9"/>
+      <c r="C14719" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14720" s="8"/>
+      <c r="B14720" s="9"/>
+      <c r="C14720" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14721" s="8"/>
+      <c r="B14721" s="9"/>
+      <c r="C14721" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14722" s="8"/>
+      <c r="B14722" s="9"/>
+      <c r="C14722" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14723" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14723" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14723" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14724" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14724" s="20"/>
+      <c r="C14724" s="21"/>
+    </row>
+    <row r="14751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14751" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B14751" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14751" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14752" s="4"/>
+      <c r="B14752" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14752" s="25"/>
+    </row>
+    <row r="14753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14753" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14753" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14753" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14754" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14754" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14754" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14755" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14755" s="9"/>
+      <c r="C14755" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14756" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14756" s="9"/>
+      <c r="C14756" s="10"/>
+    </row>
+    <row r="14757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14757" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14757" s="9"/>
+      <c r="C14757" s="10"/>
+    </row>
+    <row r="14758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14758" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14758" s="9"/>
+      <c r="C14758" s="10"/>
+    </row>
+    <row r="14759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14759" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14759" s="9"/>
+      <c r="C14759" s="14" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="14760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14760" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="B14760" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14760" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14761" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14761" s="27"/>
+      <c r="C14761" s="27" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="14762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14762" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14762" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14762" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14763" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14763" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14763" s="20"/>
+      <c r="C14763" s="21"/>
+    </row>
+    <row r="14810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14810" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B14810" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14810" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14811" s="4"/>
+      <c r="B14811" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14811" s="25"/>
+    </row>
+    <row r="14812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14812" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14812" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14812" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14813" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14813" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14813" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14814" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14814" s="9"/>
+      <c r="C14814" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14815" s="18">
+        <v>1.2</v>
+      </c>
+      <c r="B14815" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14815" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14816" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14816" s="27"/>
+      <c r="C14816" s="38" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="14817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14817" s="8"/>
+      <c r="B14817" s="27"/>
+      <c r="C14817" s="38"/>
+    </row>
+    <row r="14818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14818" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14818" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14818" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14819" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14819" s="20"/>
+      <c r="C14819" s="21"/>
+    </row>
+    <row r="14869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14869" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B14869" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14869" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14870" s="4"/>
+      <c r="B14870" s="36" t="s">
+        <v>583</v>
+      </c>
+      <c r="C14870" s="37"/>
+    </row>
+    <row r="14871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14871" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14871" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14871" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14872" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14872" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14872" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14873" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14873" s="9"/>
+      <c r="C14873" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14874" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14874" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14874" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14874" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14875" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14875" s="9"/>
+      <c r="C14875" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14876" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14876" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14876" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14876" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14877" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14877" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14877" s="9"/>
+      <c r="C14877" s="10"/>
+    </row>
+    <row r="14878" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14878" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14878" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14878" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14879" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14879" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14879" s="9"/>
+      <c r="C14879" s="10" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14880" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14880" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B14880" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14880" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14881" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14881" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14881" s="9"/>
+      <c r="C14881" s="10" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="14882" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14882" s="8"/>
+      <c r="B14882" s="9"/>
+      <c r="C14882" s="10" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="14883" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14883" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14883" s="9"/>
+      <c r="C14883" s="10"/>
+    </row>
+    <row r="14884" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14884" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B14884" s="9"/>
+      <c r="C14884" s="10"/>
+    </row>
+    <row r="14885" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14885" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="B14885" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14885" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14886" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B14886" s="9"/>
+      <c r="C14886" s="10"/>
+    </row>
+    <row r="14887" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14887" s="18">
+        <v>7.2</v>
+      </c>
+      <c r="B14887" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14887" s="10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14888" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14888" s="8">
+        <v>8.1</v>
+      </c>
+      <c r="B14888" s="9"/>
+      <c r="C14888" s="14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14889" s="8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B14889" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14889" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14890" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14890" s="20"/>
+      <c r="C14890" s="21"/>
+    </row>
+    <row r="14928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14928" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B14928" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14928" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14929" s="4"/>
+      <c r="B14929" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14929" s="25"/>
+    </row>
+    <row r="14930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14930" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14930" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14930" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14931" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14931" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14931" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14932" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14932" s="9"/>
+      <c r="C14932" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14933" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14933" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14933" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14934" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14934" s="9"/>
+      <c r="C14934" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14935" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14935" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14935" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14936" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14936" s="9"/>
+      <c r="C14936" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14937" s="8"/>
+      <c r="B14937" s="9"/>
+      <c r="C14937" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14938" s="8"/>
+      <c r="B14938" s="9"/>
+      <c r="C14938" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14939" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14939" s="8"/>
+      <c r="B14939" s="9"/>
+      <c r="C14939" s="10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14940" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14940" s="8"/>
+      <c r="B14940" s="9"/>
+      <c r="C14940" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14941" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14941" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="B14941" s="16"/>
+      <c r="C14941" s="23"/>
+    </row>
+    <row r="14942" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14942" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14942" s="16"/>
+      <c r="C14942" s="23"/>
+    </row>
+    <row r="14943" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14943" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B14943" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14943" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14944" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14944" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B14944" s="9"/>
+      <c r="C14944" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14945" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14945" s="8"/>
+      <c r="B14945" s="9"/>
+      <c r="C14945" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="14946" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14946" s="8"/>
+      <c r="B14946" s="9"/>
+      <c r="C14946" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="14947" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14947" s="8"/>
+      <c r="B14947" s="9"/>
+      <c r="C14947" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14948" s="8"/>
+      <c r="B14948" s="9"/>
+      <c r="C14948" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14949" s="8"/>
+      <c r="B14949" s="9"/>
+      <c r="C14949" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="14950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14950" s="8"/>
+      <c r="B14950" s="9"/>
+      <c r="C14950" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14951" s="8"/>
+      <c r="B14951" s="9"/>
+      <c r="C14951" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14952" s="8"/>
+      <c r="B14952" s="9"/>
+      <c r="C14952" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="14953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14953" s="8"/>
+      <c r="B14953" s="9"/>
+      <c r="C14953" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="14954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14954" s="8"/>
+      <c r="B14954" s="9"/>
+      <c r="C14954" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="14955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14955" s="8"/>
+      <c r="B14955" s="9"/>
+      <c r="C14955" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14956" s="8"/>
+      <c r="B14956" s="9"/>
+      <c r="C14956" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14957" s="8"/>
+      <c r="B14957" s="9"/>
+      <c r="C14957" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14958" s="8"/>
+      <c r="B14958" s="9"/>
+      <c r="C14958" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14959" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B14959" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14959" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14960" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14960" s="20"/>
+      <c r="C14960" s="21"/>
+    </row>
+    <row r="14987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14987" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B14987" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14987" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14988" s="4"/>
+      <c r="B14988" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14988" s="37"/>
+    </row>
+    <row r="14989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14989" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14989" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14989" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14990" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14990" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14990" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14990" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14991" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14991" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B14991" s="9"/>
+      <c r="C14991" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14992" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B14992" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14992" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14993" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B14993" s="9"/>
+      <c r="C14993" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14994" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B14994" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14994" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14995" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B14995" s="9"/>
+      <c r="C14995" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14996" s="8"/>
+      <c r="B14996" s="9"/>
+      <c r="C14996" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14997" s="8"/>
+      <c r="B14997" s="9"/>
+      <c r="C14997" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14998" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B14998" s="9"/>
+      <c r="C14998" s="10"/>
+    </row>
+    <row r="14999" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14999" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B14999" s="9"/>
+      <c r="C14999" s="10"/>
+    </row>
+    <row r="15000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15000" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="B15000" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15000" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15001" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B15001" s="9"/>
+      <c r="C15001" s="10"/>
+    </row>
+    <row r="15002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15002" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B15002" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15002" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15003" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B15003" s="9"/>
+      <c r="C15003" s="10" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="15004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15004" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B15004" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15004" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15005" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="B15005" s="9"/>
+      <c r="C15005" s="10"/>
+    </row>
+    <row r="15006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15006" s="8">
+        <v>7.2</v>
+      </c>
+      <c r="B15006" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15006" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15007" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15007" s="20"/>
+      <c r="C15007" s="21"/>
+    </row>
+    <row r="15046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15046" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B15046" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15046" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15047" s="4"/>
+      <c r="B15047" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15047" s="37"/>
+    </row>
+    <row r="15048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15048" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15048" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15048" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15049" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15049" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15049" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15050" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B15050" s="9"/>
+      <c r="C15050" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15051" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15051" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="B15051" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15051" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15052" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="B15052" s="9"/>
+      <c r="C15052" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15053" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B15053" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15053" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15054" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="B15054" s="9"/>
+      <c r="C15054" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15055" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="B15055" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15055" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15056" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B15056" s="9"/>
+      <c r="C15056" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15057" s="8"/>
+      <c r="B15057" s="9"/>
+      <c r="C15057" s="10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15058" s="8"/>
+      <c r="B15058" s="9"/>
+      <c r="C15058" s="10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15059" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="B15059" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15059" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15060" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15060" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B15060" s="9"/>
+      <c r="C15060" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15061" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15061" s="8"/>
+      <c r="B15061" s="9"/>
+      <c r="C15061" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="15062" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15062" s="8"/>
+      <c r="B15062" s="9"/>
+      <c r="C15062" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="15063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15063" s="8"/>
+      <c r="B15063" s="9"/>
+      <c r="C15063" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="15064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15064" s="8"/>
+      <c r="B15064" s="9"/>
+      <c r="C15064" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15065" s="8"/>
+      <c r="B15065" s="9"/>
+      <c r="C15065" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15066" s="8"/>
+      <c r="B15066" s="9"/>
+      <c r="C15066" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15067" s="8"/>
+      <c r="B15067" s="9"/>
+      <c r="C15067" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15068" s="8"/>
+      <c r="B15068" s="9"/>
+      <c r="C15068" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15069" s="8"/>
+      <c r="B15069" s="9"/>
+      <c r="C15069" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="15070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15070" s="8"/>
+      <c r="B15070" s="9"/>
+      <c r="C15070" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="15071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15071" s="8"/>
+      <c r="B15071" s="9"/>
+      <c r="C15071" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="15072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15072" s="8"/>
+      <c r="B15072" s="9"/>
+      <c r="C15072" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15073" s="8"/>
+      <c r="B15073" s="9"/>
+      <c r="C15073" s="10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15074" s="8"/>
+      <c r="B15074" s="9"/>
+      <c r="C15074" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="15075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15075" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="B15075" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15075" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15076" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15076" s="20"/>
+      <c r="C15076" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="159">
-    <mergeCell ref="C13463:C13464"/>
-    <mergeCell ref="B5725:C5725"/>
-    <mergeCell ref="B6020:C6020"/>
-    <mergeCell ref="B5607:C5607"/>
-    <mergeCell ref="B5430:C5430"/>
-    <mergeCell ref="B5489:C5489"/>
-    <mergeCell ref="B5548:C5548"/>
-    <mergeCell ref="C5563:C5564"/>
-    <mergeCell ref="B6669:C6669"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="C6031:C6032"/>
-    <mergeCell ref="B6492:C6492"/>
-    <mergeCell ref="C6503:C6504"/>
-    <mergeCell ref="C6614:C6615"/>
-    <mergeCell ref="C5024:C5025"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4615:C4616"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5147"/>
-    <mergeCell ref="B5149:B5151"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5083:C5084"/>
-    <mergeCell ref="C5090:C5091"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3675:C3676"/>
-    <mergeCell ref="B3257:B3259"/>
-    <mergeCell ref="B3261:B3263"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4726:C4727"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3896:C3896"/>
-    <mergeCell ref="C4143:C4144"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2838:C2839"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="B2657:C2657"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2727:C2728"/>
-    <mergeCell ref="C3202:C3203"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3077:C3078"/>
-    <mergeCell ref="C3136:C3137"/>
-    <mergeCell ref="C3195:C3196"/>
-    <mergeCell ref="C2255:C2256"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="B1890:C1890"/>
-    <mergeCell ref="B1831:C1831"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="B1713:C1713"/>
-    <mergeCell ref="C1787:C1788"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="B887:C887"/>
-    <mergeCell ref="C950:C951"/>
-    <mergeCell ref="B1064:C1064"/>
-    <mergeCell ref="C1248:C1249"/>
-    <mergeCell ref="C367:C368"/>
-    <mergeCell ref="B415:C415"/>
-    <mergeCell ref="B710:C710"/>
-    <mergeCell ref="B828:C828"/>
-    <mergeCell ref="C839:C840"/>
-    <mergeCell ref="C1307:C1308"/>
-    <mergeCell ref="C1314:C1315"/>
-    <mergeCell ref="B1369:B1371"/>
-    <mergeCell ref="B1373:B1375"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="A139:C144"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A24:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="C8741:C8742"/>
-    <mergeCell ref="C8800:C8801"/>
-    <mergeCell ref="C8859:C8860"/>
-    <mergeCell ref="B8911:C8911"/>
-    <mergeCell ref="C8502:C8503"/>
-    <mergeCell ref="B8557:C8557"/>
-    <mergeCell ref="B8675:C8675"/>
-    <mergeCell ref="B7613:C7613"/>
-    <mergeCell ref="B5784:C5784"/>
-    <mergeCell ref="B7672:C7672"/>
-    <mergeCell ref="C7451:C7452"/>
-    <mergeCell ref="B7436:C7436"/>
-    <mergeCell ref="C7558:C7559"/>
-    <mergeCell ref="B7209:B7211"/>
-    <mergeCell ref="B7318:C7318"/>
-    <mergeCell ref="C6978:C6979"/>
-    <mergeCell ref="B7023:C7023"/>
-    <mergeCell ref="B7033:B7035"/>
-    <mergeCell ref="B7037:B7039"/>
-    <mergeCell ref="C6853:C6854"/>
-    <mergeCell ref="C6912:C6913"/>
-    <mergeCell ref="C6971:C6972"/>
-    <mergeCell ref="B6964:C6964"/>
-    <mergeCell ref="B10563:C10563"/>
-    <mergeCell ref="C10629:C10630"/>
-    <mergeCell ref="C10688:C10689"/>
-    <mergeCell ref="C10747:C10748"/>
-    <mergeCell ref="B9501:C9501"/>
-    <mergeCell ref="C10390:C10391"/>
-    <mergeCell ref="B10445:C10445"/>
-    <mergeCell ref="B8925:B8927"/>
-    <mergeCell ref="B8921:B8923"/>
-    <mergeCell ref="C11516:C11517"/>
-    <mergeCell ref="C11575:C11576"/>
-    <mergeCell ref="C11634:C11635"/>
-    <mergeCell ref="C11335:C11336"/>
-    <mergeCell ref="B11389:C11389"/>
-    <mergeCell ref="C11406:C11407"/>
-    <mergeCell ref="B10809:B10811"/>
-    <mergeCell ref="B10813:B10815"/>
-    <mergeCell ref="B10799:C10799"/>
-    <mergeCell ref="C12278:C12279"/>
-    <mergeCell ref="B12333:C12333"/>
-    <mergeCell ref="C12352:C12353"/>
-    <mergeCell ref="C12106:C12107"/>
-    <mergeCell ref="B12156:C12156"/>
-    <mergeCell ref="C12226:C12227"/>
-    <mergeCell ref="C11758:C11759"/>
-    <mergeCell ref="C11866:C11867"/>
-    <mergeCell ref="C12047:C12048"/>
+  <mergeCells count="175">
+    <mergeCell ref="B14988:C14988"/>
+    <mergeCell ref="B15047:C15047"/>
+    <mergeCell ref="C14816:C14817"/>
+    <mergeCell ref="B14870:C14870"/>
+    <mergeCell ref="C14523:C14524"/>
+    <mergeCell ref="B14516:C14516"/>
+    <mergeCell ref="B14457:C14457"/>
+    <mergeCell ref="B14575:C14575"/>
+    <mergeCell ref="B14585:B14587"/>
+    <mergeCell ref="B14589:B14591"/>
+    <mergeCell ref="B13631:C13631"/>
+    <mergeCell ref="C13935:C13936"/>
+    <mergeCell ref="B14044:C14044"/>
+    <mergeCell ref="C14166:C14167"/>
+    <mergeCell ref="B14221:C14221"/>
+    <mergeCell ref="C14464:C14465"/>
     <mergeCell ref="C13223:C13224"/>
     <mergeCell ref="B13277:C13277"/>
     <mergeCell ref="C12581:C12582"/>
@@ -48970,6 +54430,144 @@
     <mergeCell ref="B12701:B12703"/>
     <mergeCell ref="B12697:B12699"/>
     <mergeCell ref="C12708:C12709"/>
+    <mergeCell ref="C12278:C12279"/>
+    <mergeCell ref="B12333:C12333"/>
+    <mergeCell ref="C12352:C12353"/>
+    <mergeCell ref="C12106:C12107"/>
+    <mergeCell ref="B12156:C12156"/>
+    <mergeCell ref="C12226:C12227"/>
+    <mergeCell ref="C11758:C11759"/>
+    <mergeCell ref="C11866:C11867"/>
+    <mergeCell ref="C12047:C12048"/>
+    <mergeCell ref="C11516:C11517"/>
+    <mergeCell ref="C11575:C11576"/>
+    <mergeCell ref="C11634:C11635"/>
+    <mergeCell ref="C11335:C11336"/>
+    <mergeCell ref="B11389:C11389"/>
+    <mergeCell ref="C11406:C11407"/>
+    <mergeCell ref="B10809:B10811"/>
+    <mergeCell ref="B10813:B10815"/>
+    <mergeCell ref="B10799:C10799"/>
+    <mergeCell ref="C6853:C6854"/>
+    <mergeCell ref="C6912:C6913"/>
+    <mergeCell ref="C6971:C6972"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="B10563:C10563"/>
+    <mergeCell ref="C10629:C10630"/>
+    <mergeCell ref="C10688:C10689"/>
+    <mergeCell ref="C10747:C10748"/>
+    <mergeCell ref="B9501:C9501"/>
+    <mergeCell ref="C10390:C10391"/>
+    <mergeCell ref="B10445:C10445"/>
+    <mergeCell ref="B8925:B8927"/>
+    <mergeCell ref="B8921:B8923"/>
+    <mergeCell ref="C7451:C7452"/>
+    <mergeCell ref="B7436:C7436"/>
+    <mergeCell ref="C7558:C7559"/>
+    <mergeCell ref="B7209:B7211"/>
+    <mergeCell ref="B7318:C7318"/>
+    <mergeCell ref="C6978:C6979"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7035"/>
+    <mergeCell ref="B7037:B7039"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="A139:C144"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A24:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="B887:C887"/>
+    <mergeCell ref="C950:C951"/>
+    <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="C1248:C1249"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="B415:C415"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B828:C828"/>
+    <mergeCell ref="C839:C840"/>
+    <mergeCell ref="C1307:C1308"/>
+    <mergeCell ref="C1314:C1315"/>
+    <mergeCell ref="B1369:B1371"/>
+    <mergeCell ref="B1373:B1375"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="C2255:C2256"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="B1890:C1890"/>
+    <mergeCell ref="B1831:C1831"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="B1713:C1713"/>
+    <mergeCell ref="C1787:C1788"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2838:C2839"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B2657:C2657"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2727:C2728"/>
+    <mergeCell ref="C3202:C3203"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3077:C3078"/>
+    <mergeCell ref="C3136:C3137"/>
+    <mergeCell ref="C3195:C3196"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3675:C3676"/>
+    <mergeCell ref="B3257:B3259"/>
+    <mergeCell ref="B3261:B3263"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4726:C4727"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="C4143:C4144"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C5024:C5025"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4615:C4616"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5147"/>
+    <mergeCell ref="B5149:B5151"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5083:C5084"/>
+    <mergeCell ref="C5090:C5091"/>
+    <mergeCell ref="C13463:C13464"/>
+    <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="B6020:C6020"/>
+    <mergeCell ref="B5607:C5607"/>
+    <mergeCell ref="B5430:C5430"/>
+    <mergeCell ref="B5489:C5489"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
+    <mergeCell ref="B6669:C6669"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="C6031:C6032"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6503:C6504"/>
+    <mergeCell ref="C6614:C6615"/>
+    <mergeCell ref="C8741:C8742"/>
+    <mergeCell ref="C8800:C8801"/>
+    <mergeCell ref="C8859:C8860"/>
+    <mergeCell ref="B8911:C8911"/>
+    <mergeCell ref="C8502:C8503"/>
+    <mergeCell ref="B8557:C8557"/>
+    <mergeCell ref="B8675:C8675"/>
+    <mergeCell ref="B7613:C7613"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B7672:C7672"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
